--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -3681,10 +3681,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129113791</v>
+        <v>129112885</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3692,42 +3692,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455304</v>
+        <v>455288</v>
       </c>
       <c r="R30" t="n">
-        <v>6773316</v>
+        <v>6773318</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3793,7 +3788,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129112885</v>
+        <v>129110462</v>
       </c>
       <c r="B31" t="n">
         <v>79034</v>
@@ -3828,10 +3823,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455288</v>
+        <v>455333</v>
       </c>
       <c r="R31" t="n">
-        <v>6773318</v>
+        <v>6773289</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3900,10 +3895,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129110462</v>
+        <v>129113791</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3911,37 +3906,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455333</v>
+        <v>455304</v>
       </c>
       <c r="R32" t="n">
-        <v>6773289</v>
+        <v>6773316</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -7246,45 +7246,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129112093</v>
+        <v>129110475</v>
       </c>
       <c r="B63" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455241</v>
+        <v>455333</v>
       </c>
       <c r="R63" t="n">
-        <v>6773279</v>
+        <v>6773289</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7353,32 +7358,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129110960</v>
+        <v>129114704</v>
       </c>
       <c r="B64" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7388,10 +7393,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455260</v>
+        <v>455438</v>
       </c>
       <c r="R64" t="n">
-        <v>6773245</v>
+        <v>6773400</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7460,10 +7465,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129107474</v>
+        <v>129112093</v>
       </c>
       <c r="B65" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7471,39 +7476,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455385</v>
+        <v>455241</v>
       </c>
       <c r="R65" t="n">
-        <v>6773193</v>
+        <v>6773279</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7572,50 +7572,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129110475</v>
+        <v>129110960</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455333</v>
+        <v>455260</v>
       </c>
       <c r="R66" t="n">
-        <v>6773289</v>
+        <v>6773245</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7684,45 +7679,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129114704</v>
+        <v>129107474</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455438</v>
+        <v>455385</v>
       </c>
       <c r="R67" t="n">
-        <v>6773400</v>
+        <v>6773193</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129113900</v>
+        <v>129112739</v>
       </c>
       <c r="B89" t="n">
         <v>79034</v>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>455329</v>
+        <v>455290</v>
       </c>
       <c r="R89" t="n">
-        <v>6773342</v>
+        <v>6773279</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10182,7 +10182,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129114734</v>
+        <v>129113900</v>
       </c>
       <c r="B90" t="n">
         <v>79034</v>
@@ -10217,10 +10217,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>455438</v>
+        <v>455329</v>
       </c>
       <c r="R90" t="n">
-        <v>6773400</v>
+        <v>6773342</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10289,7 +10289,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129112739</v>
+        <v>129114734</v>
       </c>
       <c r="B91" t="n">
         <v>79034</v>
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>455290</v>
+        <v>455438</v>
       </c>
       <c r="R91" t="n">
-        <v>6773279</v>
+        <v>6773400</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112610</v>
+        <v>129112804</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455308</v>
+        <v>455289</v>
       </c>
       <c r="R2" t="n">
-        <v>6773282</v>
+        <v>6773299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129112438</v>
+        <v>129108187</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455258</v>
+        <v>455412</v>
       </c>
       <c r="R3" t="n">
-        <v>6773321</v>
+        <v>6773172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129108044</v>
+        <v>129112610</v>
       </c>
       <c r="B4" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455412</v>
+        <v>455308</v>
       </c>
       <c r="R4" t="n">
-        <v>6773172</v>
+        <v>6773282</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112479</v>
+        <v>129112438</v>
       </c>
       <c r="B5" t="n">
         <v>79034</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455272</v>
+        <v>455258</v>
       </c>
       <c r="R5" t="n">
-        <v>6773302</v>
+        <v>6773321</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129112804</v>
+        <v>129108044</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>79653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455289</v>
+        <v>455412</v>
       </c>
       <c r="R6" t="n">
-        <v>6773299</v>
+        <v>6773172</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129108187</v>
+        <v>129112479</v>
       </c>
       <c r="B7" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455412</v>
+        <v>455272</v>
       </c>
       <c r="R7" t="n">
-        <v>6773172</v>
+        <v>6773302</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129110825</v>
+        <v>129109404</v>
       </c>
       <c r="B8" t="n">
         <v>79034</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455259</v>
+        <v>455484</v>
       </c>
       <c r="R8" t="n">
-        <v>6773246</v>
+        <v>6773211</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129107453</v>
+        <v>129113163</v>
       </c>
       <c r="B9" t="n">
         <v>79034</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455385</v>
+        <v>455283</v>
       </c>
       <c r="R9" t="n">
-        <v>6773193</v>
+        <v>6773359</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129109404</v>
+        <v>129110825</v>
       </c>
       <c r="B10" t="n">
         <v>79034</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455484</v>
+        <v>455259</v>
       </c>
       <c r="R10" t="n">
-        <v>6773211</v>
+        <v>6773246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129113163</v>
+        <v>129107453</v>
       </c>
       <c r="B11" t="n">
         <v>79034</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455283</v>
+        <v>455385</v>
       </c>
       <c r="R11" t="n">
-        <v>6773359</v>
+        <v>6773193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129113882</v>
+        <v>129110737</v>
       </c>
       <c r="B12" t="n">
-        <v>97522</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455329</v>
+        <v>455259</v>
       </c>
       <c r="R12" t="n">
-        <v>6773342</v>
+        <v>6773216</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129110737</v>
+        <v>129113882</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>97527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455259</v>
+        <v>455329</v>
       </c>
       <c r="R13" t="n">
-        <v>6773216</v>
+        <v>6773342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129112774</v>
+        <v>129107736</v>
       </c>
       <c r="B24" t="n">
         <v>79034</v>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455289</v>
+        <v>455372</v>
       </c>
       <c r="R24" t="n">
-        <v>6773299</v>
+        <v>6773181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129107736</v>
+        <v>129109613</v>
       </c>
       <c r="B25" t="n">
         <v>79034</v>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455372</v>
+        <v>455494</v>
       </c>
       <c r="R25" t="n">
-        <v>6773181</v>
+        <v>6773197</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129109613</v>
+        <v>129111088</v>
       </c>
       <c r="B26" t="n">
         <v>79034</v>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455494</v>
+        <v>455248</v>
       </c>
       <c r="R26" t="n">
-        <v>6773197</v>
+        <v>6773274</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129111088</v>
+        <v>129114098</v>
       </c>
       <c r="B27" t="n">
         <v>79034</v>
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455248</v>
+        <v>455394</v>
       </c>
       <c r="R27" t="n">
-        <v>6773274</v>
+        <v>6773349</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129114098</v>
+        <v>129113094</v>
       </c>
       <c r="B28" t="n">
         <v>79034</v>
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455394</v>
+        <v>455301</v>
       </c>
       <c r="R28" t="n">
-        <v>6773349</v>
+        <v>6773331</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129113094</v>
+        <v>129112885</v>
       </c>
       <c r="B29" t="n">
         <v>79034</v>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455301</v>
+        <v>455288</v>
       </c>
       <c r="R29" t="n">
-        <v>6773331</v>
+        <v>6773318</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129112885</v>
+        <v>129110462</v>
       </c>
       <c r="B30" t="n">
         <v>79034</v>
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455288</v>
+        <v>455333</v>
       </c>
       <c r="R30" t="n">
-        <v>6773318</v>
+        <v>6773289</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129110462</v>
+        <v>129113791</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3799,37 +3799,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455333</v>
+        <v>455304</v>
       </c>
       <c r="R31" t="n">
-        <v>6773289</v>
+        <v>6773316</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3895,10 +3900,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129113791</v>
+        <v>129110782</v>
       </c>
       <c r="B32" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,42 +3911,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455304</v>
+        <v>455237</v>
       </c>
       <c r="R32" t="n">
-        <v>6773316</v>
+        <v>6773232</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129110782</v>
+        <v>129107986</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455237</v>
+        <v>455389</v>
       </c>
       <c r="R33" t="n">
-        <v>6773232</v>
+        <v>6773170</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,10 +4114,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129107986</v>
+        <v>129110662</v>
       </c>
       <c r="B34" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4125,21 +4125,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455389</v>
+        <v>455273</v>
       </c>
       <c r="R34" t="n">
-        <v>6773170</v>
+        <v>6773208</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129110662</v>
+        <v>129106783</v>
       </c>
       <c r="B35" t="n">
         <v>79034</v>
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455273</v>
+        <v>455407</v>
       </c>
       <c r="R35" t="n">
-        <v>6773208</v>
+        <v>6773196</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4328,7 +4328,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129106783</v>
+        <v>129110692</v>
       </c>
       <c r="B36" t="n">
         <v>79034</v>
@@ -4363,13 +4363,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455407</v>
+        <v>455270</v>
       </c>
       <c r="R36" t="n">
-        <v>6773196</v>
+        <v>6773216</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4435,10 +4435,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129110692</v>
+        <v>129109514</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4446,37 +4446,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455270</v>
+        <v>455494</v>
       </c>
       <c r="R37" t="n">
-        <v>6773216</v>
+        <v>6773187</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4542,10 +4547,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129109514</v>
+        <v>129110861</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4553,39 +4558,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455494</v>
+        <v>455267</v>
       </c>
       <c r="R38" t="n">
-        <v>6773187</v>
+        <v>6773233</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4654,50 +4654,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129110522</v>
+        <v>129108956</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455304</v>
+        <v>455473</v>
       </c>
       <c r="R39" t="n">
-        <v>6773265</v>
+        <v>6773221</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4766,45 +4761,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129110861</v>
+        <v>129110522</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455267</v>
+        <v>455304</v>
       </c>
       <c r="R40" t="n">
-        <v>6773233</v>
+        <v>6773265</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4873,7 +4873,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129108956</v>
+        <v>129114507</v>
       </c>
       <c r="B41" t="n">
         <v>79034</v>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455473</v>
+        <v>455391</v>
       </c>
       <c r="R41" t="n">
-        <v>6773221</v>
+        <v>6773367</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,10 +4980,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129107072</v>
+        <v>129107679</v>
       </c>
       <c r="B42" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4991,21 +4991,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455389</v>
+        <v>455353</v>
       </c>
       <c r="R42" t="n">
-        <v>6773203</v>
+        <v>6773191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129114507</v>
+        <v>129110029</v>
       </c>
       <c r="B43" t="n">
         <v>79034</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455391</v>
+        <v>455333</v>
       </c>
       <c r="R43" t="n">
-        <v>6773367</v>
+        <v>6773241</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129107679</v>
+        <v>129107072</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455353</v>
+        <v>455389</v>
       </c>
       <c r="R44" t="n">
-        <v>6773191</v>
+        <v>6773203</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129110029</v>
+        <v>129109327</v>
       </c>
       <c r="B45" t="n">
         <v>79034</v>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455333</v>
+        <v>455477</v>
       </c>
       <c r="R45" t="n">
-        <v>6773241</v>
+        <v>6773206</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129109327</v>
+        <v>129109369</v>
       </c>
       <c r="B46" t="n">
         <v>79034</v>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455477</v>
+        <v>455473</v>
       </c>
       <c r="R46" t="n">
-        <v>6773206</v>
+        <v>6773219</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129109369</v>
+        <v>129112595</v>
       </c>
       <c r="B47" t="n">
         <v>79034</v>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455473</v>
+        <v>455279</v>
       </c>
       <c r="R47" t="n">
-        <v>6773219</v>
+        <v>6773275</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5622,7 +5622,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129112595</v>
+        <v>129112827</v>
       </c>
       <c r="B48" t="n">
         <v>79034</v>
@@ -5657,10 +5657,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455279</v>
+        <v>455277</v>
       </c>
       <c r="R48" t="n">
-        <v>6773275</v>
+        <v>6773300</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5729,7 +5729,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129112827</v>
+        <v>129110148</v>
       </c>
       <c r="B49" t="n">
         <v>79034</v>
@@ -5764,10 +5764,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455277</v>
+        <v>455349</v>
       </c>
       <c r="R49" t="n">
-        <v>6773300</v>
+        <v>6773250</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,7 +5836,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129110148</v>
+        <v>129114165</v>
       </c>
       <c r="B50" t="n">
         <v>79034</v>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455349</v>
+        <v>455390</v>
       </c>
       <c r="R50" t="n">
-        <v>6773250</v>
+        <v>6773344</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5943,7 +5943,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129114165</v>
+        <v>129109151</v>
       </c>
       <c r="B51" t="n">
         <v>79034</v>
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455390</v>
+        <v>455459</v>
       </c>
       <c r="R51" t="n">
-        <v>6773344</v>
+        <v>6773195</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6050,45 +6050,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129109151</v>
+        <v>129109267</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455459</v>
+        <v>455477</v>
       </c>
       <c r="R52" t="n">
-        <v>6773195</v>
+        <v>6773206</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6157,38 +6162,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129109267</v>
+        <v>129112645</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>58153</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>103001</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6197,10 +6206,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455477</v>
+        <v>455308</v>
       </c>
       <c r="R53" t="n">
-        <v>6773206</v>
+        <v>6773282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6269,54 +6278,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129112645</v>
+        <v>129112375</v>
       </c>
       <c r="B54" t="n">
-        <v>58153</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103001</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455308</v>
+        <v>455269</v>
       </c>
       <c r="R54" t="n">
-        <v>6773282</v>
+        <v>6773288</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6385,32 +6385,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129112375</v>
+        <v>129114697</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455269</v>
+        <v>455428</v>
       </c>
       <c r="R55" t="n">
-        <v>6773288</v>
+        <v>6773376</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6599,7 +6599,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129114697</v>
+        <v>129110757</v>
       </c>
       <c r="B57" t="n">
         <v>79034</v>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455428</v>
+        <v>455252</v>
       </c>
       <c r="R57" t="n">
-        <v>6773376</v>
+        <v>6773222</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129110757</v>
+        <v>129113107</v>
       </c>
       <c r="B58" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455252</v>
+        <v>455308</v>
       </c>
       <c r="R58" t="n">
-        <v>6773222</v>
+        <v>6773336</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6813,32 +6813,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129113107</v>
+        <v>129112005</v>
       </c>
       <c r="B59" t="n">
-        <v>79066</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455308</v>
+        <v>455235</v>
       </c>
       <c r="R59" t="n">
-        <v>6773336</v>
+        <v>6773290</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129112005</v>
+        <v>129110915</v>
       </c>
       <c r="B60" t="n">
         <v>8450</v>
@@ -6955,10 +6955,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455235</v>
+        <v>455267</v>
       </c>
       <c r="R60" t="n">
-        <v>6773290</v>
+        <v>6773233</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7027,7 +7027,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129110915</v>
+        <v>129108995</v>
       </c>
       <c r="B61" t="n">
         <v>8450</v>
@@ -7056,16 +7056,21 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455267</v>
+        <v>455473</v>
       </c>
       <c r="R61" t="n">
-        <v>6773233</v>
+        <v>6773221</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7134,38 +7139,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129108995</v>
+        <v>129107474</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7174,10 +7179,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455473</v>
+        <v>455385</v>
       </c>
       <c r="R62" t="n">
-        <v>6773221</v>
+        <v>6773193</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7679,50 +7684,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129107474</v>
+        <v>129110844</v>
       </c>
       <c r="B67" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455385</v>
+        <v>455259</v>
       </c>
       <c r="R67" t="n">
-        <v>6773193</v>
+        <v>6773246</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,32 +7791,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129110844</v>
+        <v>129110941</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7826,10 +7826,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455259</v>
+        <v>455281</v>
       </c>
       <c r="R68" t="n">
-        <v>6773246</v>
+        <v>6773251</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7898,7 +7898,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129110941</v>
+        <v>129112114</v>
       </c>
       <c r="B69" t="n">
         <v>79034</v>
@@ -7933,10 +7933,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455281</v>
+        <v>455233</v>
       </c>
       <c r="R69" t="n">
-        <v>6773251</v>
+        <v>6773294</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8005,10 +8005,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129112114</v>
+        <v>129113193</v>
       </c>
       <c r="B70" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8016,34 +8016,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455233</v>
+        <v>455283</v>
       </c>
       <c r="R70" t="n">
-        <v>6773294</v>
+        <v>6773359</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8112,10 +8117,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129113193</v>
+        <v>129113854</v>
       </c>
       <c r="B71" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8123,39 +8128,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455283</v>
+        <v>455337</v>
       </c>
       <c r="R71" t="n">
-        <v>6773359</v>
+        <v>6773325</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8227,7 +8227,7 @@
         <v>129124330</v>
       </c>
       <c r="B72" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8329,10 +8329,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129113854</v>
+        <v>129107854</v>
       </c>
       <c r="B73" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8340,21 +8340,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>455337</v>
+        <v>455397</v>
       </c>
       <c r="R73" t="n">
-        <v>6773325</v>
+        <v>6773180</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8436,10 +8436,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129107854</v>
+        <v>129112107</v>
       </c>
       <c r="B74" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8447,21 +8447,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8471,10 +8471,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455397</v>
+        <v>455235</v>
       </c>
       <c r="R74" t="n">
-        <v>6773180</v>
+        <v>6773290</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8543,53 +8543,51 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129110810</v>
+        <v>129114483</v>
       </c>
       <c r="B75" t="n">
-        <v>57720</v>
+        <v>90905</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455237</v>
+        <v>455394</v>
       </c>
       <c r="R75" t="n">
-        <v>6773232</v>
+        <v>6773349</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8631,12 +8629,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8655,10 +8659,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129112107</v>
+        <v>129110810</v>
       </c>
       <c r="B76" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8666,34 +8670,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455235</v>
+        <v>455237</v>
       </c>
       <c r="R76" t="n">
-        <v>6773290</v>
+        <v>6773232</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8762,51 +8771,53 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129114483</v>
+        <v>129109071</v>
       </c>
       <c r="B77" t="n">
-        <v>90902</v>
+        <v>57720</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>455394</v>
+        <v>455467</v>
       </c>
       <c r="R77" t="n">
-        <v>6773349</v>
+        <v>6773201</v>
       </c>
       <c r="S77" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8848,18 +8859,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8878,10 +8883,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129109071</v>
+        <v>129107895</v>
       </c>
       <c r="B78" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8889,39 +8894,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>455467</v>
+        <v>455397</v>
       </c>
       <c r="R78" t="n">
-        <v>6773201</v>
+        <v>6773180</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8990,7 +8990,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129107895</v>
+        <v>129109466</v>
       </c>
       <c r="B79" t="n">
         <v>79034</v>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>455397</v>
+        <v>455479</v>
       </c>
       <c r="R79" t="n">
-        <v>6773180</v>
+        <v>6773185</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9097,7 +9097,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129109466</v>
+        <v>129109225</v>
       </c>
       <c r="B80" t="n">
         <v>79034</v>
@@ -9132,10 +9132,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455479</v>
+        <v>455468</v>
       </c>
       <c r="R80" t="n">
-        <v>6773185</v>
+        <v>6773198</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9204,10 +9204,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B81" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9215,34 +9215,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R81" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9311,10 +9316,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129114154</v>
+        <v>129107617</v>
       </c>
       <c r="B82" t="n">
-        <v>57723</v>
+        <v>79624</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9322,39 +9327,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>455390</v>
+        <v>455352</v>
       </c>
       <c r="R82" t="n">
-        <v>6773344</v>
+        <v>6773200</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9423,10 +9423,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129107617</v>
+        <v>129113130</v>
       </c>
       <c r="B83" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9434,21 +9434,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9458,10 +9458,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>455352</v>
+        <v>455297</v>
       </c>
       <c r="R83" t="n">
-        <v>6773200</v>
+        <v>6773355</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9530,10 +9530,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129113130</v>
+        <v>129111012</v>
       </c>
       <c r="B84" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9541,34 +9541,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>455297</v>
+        <v>455258</v>
       </c>
       <c r="R84" t="n">
-        <v>6773355</v>
+        <v>6773256</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9637,10 +9642,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129111012</v>
+        <v>129112346</v>
       </c>
       <c r="B85" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9648,16 +9653,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9668,7 +9673,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9677,10 +9682,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>455258</v>
+        <v>455248</v>
       </c>
       <c r="R85" t="n">
-        <v>6773256</v>
+        <v>6773310</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9749,50 +9754,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129112346</v>
+        <v>129111017</v>
       </c>
       <c r="B86" t="n">
-        <v>57723</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>455248</v>
+        <v>455258</v>
       </c>
       <c r="R86" t="n">
-        <v>6773310</v>
+        <v>6773256</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9861,32 +9861,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129111017</v>
+        <v>129110007</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9896,10 +9896,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>455258</v>
+        <v>455316</v>
       </c>
       <c r="R87" t="n">
-        <v>6773256</v>
+        <v>6773247</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129110007</v>
+        <v>129112739</v>
       </c>
       <c r="B88" t="n">
         <v>79034</v>
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>455316</v>
+        <v>455290</v>
       </c>
       <c r="R88" t="n">
-        <v>6773247</v>
+        <v>6773279</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129112739</v>
+        <v>129113900</v>
       </c>
       <c r="B89" t="n">
         <v>79034</v>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>455290</v>
+        <v>455329</v>
       </c>
       <c r="R89" t="n">
-        <v>6773279</v>
+        <v>6773342</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10182,7 +10182,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129113900</v>
+        <v>129114734</v>
       </c>
       <c r="B90" t="n">
         <v>79034</v>
@@ -10217,10 +10217,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>455329</v>
+        <v>455438</v>
       </c>
       <c r="R90" t="n">
-        <v>6773342</v>
+        <v>6773400</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10289,10 +10289,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129114734</v>
+        <v>129114442</v>
       </c>
       <c r="B91" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10300,37 +10300,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>455438</v>
+        <v>455394</v>
       </c>
       <c r="R91" t="n">
-        <v>6773400</v>
+        <v>6773349</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10396,10 +10401,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129114442</v>
+        <v>129112774</v>
       </c>
       <c r="B92" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10407,42 +10412,40 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>455394</v>
+        <v>455289</v>
       </c>
       <c r="R92" t="n">
-        <v>6773349</v>
+        <v>6773299</v>
       </c>
       <c r="S92" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10484,12 +10487,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112804</v>
+        <v>129108044</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455289</v>
+        <v>455412</v>
       </c>
       <c r="R2" t="n">
-        <v>6773299</v>
+        <v>6773172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +785,7 @@
         <v>129108187</v>
       </c>
       <c r="B3" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +892,7 @@
         <v>129112610</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +999,7 @@
         <v>129112438</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129108044</v>
+        <v>129112479</v>
       </c>
       <c r="B6" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455412</v>
+        <v>455272</v>
       </c>
       <c r="R6" t="n">
-        <v>6773172</v>
+        <v>6773302</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129112479</v>
+        <v>129112804</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455272</v>
+        <v>455289</v>
       </c>
       <c r="R7" t="n">
-        <v>6773302</v>
+        <v>6773299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129109404</v>
+        <v>129110825</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455484</v>
+        <v>455259</v>
       </c>
       <c r="R8" t="n">
-        <v>6773211</v>
+        <v>6773246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129113163</v>
+        <v>129107453</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455283</v>
+        <v>455385</v>
       </c>
       <c r="R9" t="n">
-        <v>6773359</v>
+        <v>6773193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129110825</v>
+        <v>129109404</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455259</v>
+        <v>455484</v>
       </c>
       <c r="R10" t="n">
-        <v>6773246</v>
+        <v>6773211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129107453</v>
+        <v>129113163</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455385</v>
+        <v>455283</v>
       </c>
       <c r="R11" t="n">
-        <v>6773193</v>
+        <v>6773359</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1860,7 +1860,7 @@
         <v>129113882</v>
       </c>
       <c r="B13" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>129107035</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>129109078</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>129110979</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>129107916</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129109713</v>
+        <v>129110813</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455494</v>
+        <v>455237</v>
       </c>
       <c r="R20" t="n">
-        <v>6773187</v>
+        <v>6773232</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129110813</v>
+        <v>129109713</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455237</v>
+        <v>455494</v>
       </c>
       <c r="R21" t="n">
-        <v>6773232</v>
+        <v>6773187</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,7 +2828,7 @@
         <v>129107601</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>129112407</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>129107736</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>129109613</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>129111088</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>129114098</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>129113094</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>129112885</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>129110462</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>129110782</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129107986</v>
+        <v>129110662</v>
       </c>
       <c r="B33" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455389</v>
+        <v>455273</v>
       </c>
       <c r="R33" t="n">
-        <v>6773170</v>
+        <v>6773208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,10 +4114,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129110662</v>
+        <v>129106783</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455273</v>
+        <v>455407</v>
       </c>
       <c r="R34" t="n">
-        <v>6773208</v>
+        <v>6773196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4221,10 +4221,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129106783</v>
+        <v>129110692</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,13 +4256,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455407</v>
+        <v>455270</v>
       </c>
       <c r="R35" t="n">
-        <v>6773196</v>
+        <v>6773216</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129110692</v>
+        <v>129109514</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4339,37 +4339,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455270</v>
+        <v>455494</v>
       </c>
       <c r="R36" t="n">
-        <v>6773216</v>
+        <v>6773187</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4435,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129109514</v>
+        <v>129107986</v>
       </c>
       <c r="B37" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4446,39 +4451,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455494</v>
+        <v>455389</v>
       </c>
       <c r="R37" t="n">
-        <v>6773187</v>
+        <v>6773170</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4547,45 +4547,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129110861</v>
+        <v>129110522</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455267</v>
+        <v>455304</v>
       </c>
       <c r="R38" t="n">
-        <v>6773233</v>
+        <v>6773265</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4654,10 +4659,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129108956</v>
+        <v>129110861</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4689,10 +4694,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455473</v>
+        <v>455267</v>
       </c>
       <c r="R39" t="n">
-        <v>6773221</v>
+        <v>6773233</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4761,50 +4766,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129110522</v>
+        <v>129108956</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455304</v>
+        <v>455473</v>
       </c>
       <c r="R40" t="n">
-        <v>6773265</v>
+        <v>6773221</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129114507</v>
+        <v>129107072</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>79625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455391</v>
+        <v>455389</v>
       </c>
       <c r="R41" t="n">
-        <v>6773367</v>
+        <v>6773203</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,10 +4980,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129107679</v>
+        <v>129114507</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455353</v>
+        <v>455391</v>
       </c>
       <c r="R42" t="n">
-        <v>6773191</v>
+        <v>6773367</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129110029</v>
+        <v>129107679</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455333</v>
+        <v>455353</v>
       </c>
       <c r="R43" t="n">
-        <v>6773241</v>
+        <v>6773191</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129107072</v>
+        <v>129110029</v>
       </c>
       <c r="B44" t="n">
-        <v>79624</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455389</v>
+        <v>455333</v>
       </c>
       <c r="R44" t="n">
-        <v>6773203</v>
+        <v>6773241</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5304,7 +5304,7 @@
         <v>129109327</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>129109369</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>129112595</v>
       </c>
       <c r="B47" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>129112827</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>129110148</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>129114165</v>
       </c>
       <c r="B50" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>129109151</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>129114697</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6492,32 +6492,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129114115</v>
+        <v>129112005</v>
       </c>
       <c r="B56" t="n">
-        <v>83010</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455394</v>
+        <v>455235</v>
       </c>
       <c r="R56" t="n">
-        <v>6773349</v>
+        <v>6773290</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6599,32 +6599,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129110757</v>
+        <v>129110915</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455252</v>
+        <v>455267</v>
       </c>
       <c r="R57" t="n">
-        <v>6773222</v>
+        <v>6773233</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,45 +6706,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129113107</v>
+        <v>129108995</v>
       </c>
       <c r="B58" t="n">
-        <v>79066</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455308</v>
+        <v>455473</v>
       </c>
       <c r="R58" t="n">
-        <v>6773336</v>
+        <v>6773221</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6813,32 +6818,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129112005</v>
+        <v>129110757</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6848,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455235</v>
+        <v>455252</v>
       </c>
       <c r="R59" t="n">
-        <v>6773290</v>
+        <v>6773222</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6920,32 +6925,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129110915</v>
+        <v>129113107</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79067</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6955,10 +6960,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455267</v>
+        <v>455308</v>
       </c>
       <c r="R60" t="n">
-        <v>6773233</v>
+        <v>6773336</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7027,53 +7032,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129108995</v>
+        <v>129114115</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>83011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455473</v>
+        <v>455394</v>
       </c>
       <c r="R61" t="n">
-        <v>6773221</v>
+        <v>6773349</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129107474</v>
+        <v>129112093</v>
       </c>
       <c r="B62" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,39 +7150,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455385</v>
+        <v>455241</v>
       </c>
       <c r="R62" t="n">
-        <v>6773193</v>
+        <v>6773279</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7251,50 +7246,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129110475</v>
+        <v>129110960</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455333</v>
+        <v>455260</v>
       </c>
       <c r="R63" t="n">
-        <v>6773289</v>
+        <v>6773245</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7363,45 +7353,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129114704</v>
+        <v>129107474</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455438</v>
+        <v>455385</v>
       </c>
       <c r="R64" t="n">
-        <v>6773400</v>
+        <v>6773193</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7470,45 +7465,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129112093</v>
+        <v>129110475</v>
       </c>
       <c r="B65" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455241</v>
+        <v>455333</v>
       </c>
       <c r="R65" t="n">
-        <v>6773279</v>
+        <v>6773289</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7577,32 +7577,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129110960</v>
+        <v>129114704</v>
       </c>
       <c r="B66" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455260</v>
+        <v>455438</v>
       </c>
       <c r="R66" t="n">
-        <v>6773245</v>
+        <v>6773400</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7684,45 +7684,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129110844</v>
+        <v>129113193</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455259</v>
+        <v>455283</v>
       </c>
       <c r="R67" t="n">
-        <v>6773246</v>
+        <v>6773359</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7794,7 +7799,7 @@
         <v>129110941</v>
       </c>
       <c r="B68" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7901,7 +7906,7 @@
         <v>129112114</v>
       </c>
       <c r="B69" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8005,50 +8010,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129113193</v>
+        <v>129110844</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455283</v>
+        <v>455259</v>
       </c>
       <c r="R70" t="n">
-        <v>6773359</v>
+        <v>6773246</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8120,7 +8120,7 @@
         <v>129113854</v>
       </c>
       <c r="B71" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>129124330</v>
       </c>
       <c r="B72" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>129107854</v>
       </c>
       <c r="B73" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>129112107</v>
       </c>
       <c r="B74" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>129114483</v>
       </c>
       <c r="B75" t="n">
-        <v>90905</v>
+        <v>90908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>129107895</v>
       </c>
       <c r="B78" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>129109466</v>
       </c>
       <c r="B79" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B80" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,34 +9108,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R80" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9204,10 +9209,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B81" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9215,39 +9220,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R81" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9319,7 +9319,7 @@
         <v>129107617</v>
       </c>
       <c r="B82" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>129113130</v>
       </c>
       <c r="B83" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>129110007</v>
       </c>
       <c r="B87" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>129112739</v>
       </c>
       <c r="B88" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>129113900</v>
       </c>
       <c r="B89" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>129114734</v>
       </c>
       <c r="B90" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>129112774</v>
       </c>
       <c r="B92" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129108044</v>
+        <v>129112610</v>
       </c>
       <c r="B2" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455412</v>
+        <v>455308</v>
       </c>
       <c r="R2" t="n">
-        <v>6773172</v>
+        <v>6773282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129108187</v>
+        <v>129112438</v>
       </c>
       <c r="B3" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455412</v>
+        <v>455258</v>
       </c>
       <c r="R3" t="n">
-        <v>6773172</v>
+        <v>6773321</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129112610</v>
+        <v>129108044</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455308</v>
+        <v>455412</v>
       </c>
       <c r="R4" t="n">
-        <v>6773282</v>
+        <v>6773172</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112438</v>
+        <v>129112479</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455258</v>
+        <v>455272</v>
       </c>
       <c r="R5" t="n">
-        <v>6773321</v>
+        <v>6773302</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129112479</v>
+        <v>129112804</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455272</v>
+        <v>455289</v>
       </c>
       <c r="R6" t="n">
-        <v>6773302</v>
+        <v>6773299</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129112804</v>
+        <v>129108187</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>79625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,39 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455289</v>
+        <v>455412</v>
       </c>
       <c r="R7" t="n">
-        <v>6773299</v>
+        <v>6773172</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129110825</v>
+        <v>129110737</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
         <v>455259</v>
       </c>
       <c r="R8" t="n">
-        <v>6773246</v>
+        <v>6773216</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129107453</v>
+        <v>129113882</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>97530</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455385</v>
+        <v>455329</v>
       </c>
       <c r="R9" t="n">
-        <v>6773193</v>
+        <v>6773342</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129109404</v>
+        <v>129110825</v>
       </c>
       <c r="B10" t="n">
         <v>79035</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455484</v>
+        <v>455259</v>
       </c>
       <c r="R10" t="n">
-        <v>6773211</v>
+        <v>6773246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129113163</v>
+        <v>129107453</v>
       </c>
       <c r="B11" t="n">
         <v>79035</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455283</v>
+        <v>455385</v>
       </c>
       <c r="R11" t="n">
-        <v>6773359</v>
+        <v>6773193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129110737</v>
+        <v>129109404</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455259</v>
+        <v>455484</v>
       </c>
       <c r="R12" t="n">
-        <v>6773216</v>
+        <v>6773211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129113882</v>
+        <v>129113163</v>
       </c>
       <c r="B13" t="n">
-        <v>97530</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455329</v>
+        <v>455283</v>
       </c>
       <c r="R13" t="n">
-        <v>6773342</v>
+        <v>6773359</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2397,32 +2397,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129107916</v>
+        <v>129108219</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455389</v>
+        <v>455412</v>
       </c>
       <c r="R18" t="n">
-        <v>6773170</v>
+        <v>6773172</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,32 +2504,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129108219</v>
+        <v>129107916</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455412</v>
+        <v>455389</v>
       </c>
       <c r="R19" t="n">
-        <v>6773172</v>
+        <v>6773170</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129110662</v>
+        <v>129107986</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455273</v>
+        <v>455389</v>
       </c>
       <c r="R33" t="n">
-        <v>6773208</v>
+        <v>6773170</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129106783</v>
+        <v>129110662</v>
       </c>
       <c r="B34" t="n">
         <v>79035</v>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455407</v>
+        <v>455273</v>
       </c>
       <c r="R34" t="n">
-        <v>6773196</v>
+        <v>6773208</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129110692</v>
+        <v>129106783</v>
       </c>
       <c r="B35" t="n">
         <v>79035</v>
@@ -4256,13 +4256,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455270</v>
+        <v>455407</v>
       </c>
       <c r="R35" t="n">
-        <v>6773216</v>
+        <v>6773196</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129109514</v>
+        <v>129110692</v>
       </c>
       <c r="B36" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4339,42 +4339,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455494</v>
+        <v>455270</v>
       </c>
       <c r="R36" t="n">
-        <v>6773187</v>
+        <v>6773216</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4440,10 +4435,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129107986</v>
+        <v>129109514</v>
       </c>
       <c r="B37" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4451,34 +4446,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455389</v>
+        <v>455494</v>
       </c>
       <c r="R37" t="n">
-        <v>6773170</v>
+        <v>6773187</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129107072</v>
+        <v>129114507</v>
       </c>
       <c r="B41" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455389</v>
+        <v>455391</v>
       </c>
       <c r="R41" t="n">
-        <v>6773203</v>
+        <v>6773367</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129114507</v>
+        <v>129107679</v>
       </c>
       <c r="B42" t="n">
         <v>79035</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455391</v>
+        <v>455353</v>
       </c>
       <c r="R42" t="n">
-        <v>6773367</v>
+        <v>6773191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129107679</v>
+        <v>129110029</v>
       </c>
       <c r="B43" t="n">
         <v>79035</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455353</v>
+        <v>455333</v>
       </c>
       <c r="R43" t="n">
-        <v>6773191</v>
+        <v>6773241</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129110029</v>
+        <v>129107072</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455333</v>
+        <v>455389</v>
       </c>
       <c r="R44" t="n">
-        <v>6773241</v>
+        <v>6773203</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6385,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129114697</v>
+        <v>129114115</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>83011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,21 +6396,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455428</v>
+        <v>455394</v>
       </c>
       <c r="R55" t="n">
-        <v>6773376</v>
+        <v>6773349</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6492,32 +6492,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129112005</v>
+        <v>129114697</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455235</v>
+        <v>455428</v>
       </c>
       <c r="R56" t="n">
-        <v>6773290</v>
+        <v>6773376</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6599,32 +6599,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129110915</v>
+        <v>129110757</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455267</v>
+        <v>455252</v>
       </c>
       <c r="R57" t="n">
-        <v>6773233</v>
+        <v>6773222</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,50 +6706,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129108995</v>
+        <v>129113107</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>79067</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455473</v>
+        <v>455308</v>
       </c>
       <c r="R58" t="n">
-        <v>6773221</v>
+        <v>6773336</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6818,32 +6813,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129110757</v>
+        <v>129112005</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6853,10 +6848,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455252</v>
+        <v>455235</v>
       </c>
       <c r="R59" t="n">
-        <v>6773222</v>
+        <v>6773290</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6925,32 +6920,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129113107</v>
+        <v>129110915</v>
       </c>
       <c r="B60" t="n">
-        <v>79067</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6960,10 +6955,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455308</v>
+        <v>455267</v>
       </c>
       <c r="R60" t="n">
-        <v>6773336</v>
+        <v>6773233</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7032,48 +7027,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129114115</v>
+        <v>129108995</v>
       </c>
       <c r="B61" t="n">
-        <v>83011</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455394</v>
+        <v>455473</v>
       </c>
       <c r="R61" t="n">
-        <v>6773349</v>
+        <v>6773221</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7684,10 +7684,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129113193</v>
+        <v>129110941</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7695,39 +7695,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455283</v>
+        <v>455281</v>
       </c>
       <c r="R67" t="n">
-        <v>6773359</v>
+        <v>6773251</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7796,7 +7791,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129110941</v>
+        <v>129112114</v>
       </c>
       <c r="B68" t="n">
         <v>79035</v>
@@ -7831,10 +7826,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455281</v>
+        <v>455233</v>
       </c>
       <c r="R68" t="n">
-        <v>6773251</v>
+        <v>6773294</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7903,10 +7898,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129112114</v>
+        <v>129113193</v>
       </c>
       <c r="B69" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7914,34 +7909,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455233</v>
+        <v>455283</v>
       </c>
       <c r="R69" t="n">
-        <v>6773294</v>
+        <v>6773359</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8436,48 +8436,51 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129112107</v>
+        <v>129114483</v>
       </c>
       <c r="B74" t="n">
-        <v>79035</v>
+        <v>90908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455235</v>
+        <v>455394</v>
       </c>
       <c r="R74" t="n">
-        <v>6773290</v>
+        <v>6773349</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8519,12 +8522,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8543,51 +8552,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129114483</v>
+        <v>129112107</v>
       </c>
       <c r="B75" t="n">
-        <v>90908</v>
+        <v>79035</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455394</v>
+        <v>455235</v>
       </c>
       <c r="R75" t="n">
-        <v>6773349</v>
+        <v>6773290</v>
       </c>
       <c r="S75" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8629,18 +8635,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B80" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,39 +9108,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R80" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9209,10 +9204,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9220,34 +9215,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R81" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112610</v>
+        <v>129108044</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455308</v>
+        <v>455412</v>
       </c>
       <c r="R2" t="n">
-        <v>6773282</v>
+        <v>6773172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129112438</v>
+        <v>129112479</v>
       </c>
       <c r="B3" t="n">
         <v>79035</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455258</v>
+        <v>455272</v>
       </c>
       <c r="R3" t="n">
-        <v>6773321</v>
+        <v>6773302</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129108044</v>
+        <v>129112804</v>
       </c>
       <c r="B4" t="n">
-        <v>79654</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455412</v>
+        <v>455289</v>
       </c>
       <c r="R4" t="n">
-        <v>6773172</v>
+        <v>6773299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112479</v>
+        <v>129112610</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455272</v>
+        <v>455308</v>
       </c>
       <c r="R5" t="n">
-        <v>6773302</v>
+        <v>6773282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129112804</v>
+        <v>129112438</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455289</v>
+        <v>455258</v>
       </c>
       <c r="R6" t="n">
-        <v>6773299</v>
+        <v>6773321</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129110737</v>
+        <v>129110825</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
         <v>455259</v>
       </c>
       <c r="R8" t="n">
-        <v>6773216</v>
+        <v>6773246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129113882</v>
+        <v>129107453</v>
       </c>
       <c r="B9" t="n">
-        <v>97530</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455329</v>
+        <v>455385</v>
       </c>
       <c r="R9" t="n">
-        <v>6773342</v>
+        <v>6773193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129110825</v>
+        <v>129109404</v>
       </c>
       <c r="B10" t="n">
         <v>79035</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455259</v>
+        <v>455484</v>
       </c>
       <c r="R10" t="n">
-        <v>6773246</v>
+        <v>6773211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129107453</v>
+        <v>129110737</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455385</v>
+        <v>455259</v>
       </c>
       <c r="R11" t="n">
-        <v>6773193</v>
+        <v>6773216</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129109404</v>
+        <v>129113882</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>97530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455484</v>
+        <v>455329</v>
       </c>
       <c r="R12" t="n">
-        <v>6773211</v>
+        <v>6773342</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129110813</v>
+        <v>129109713</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455237</v>
+        <v>455494</v>
       </c>
       <c r="R20" t="n">
-        <v>6773232</v>
+        <v>6773187</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129109713</v>
+        <v>129110813</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455494</v>
+        <v>455237</v>
       </c>
       <c r="R21" t="n">
-        <v>6773187</v>
+        <v>6773232</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -6385,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129114115</v>
+        <v>129113107</v>
       </c>
       <c r="B55" t="n">
-        <v>83011</v>
+        <v>79067</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,21 +6396,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455394</v>
+        <v>455308</v>
       </c>
       <c r="R55" t="n">
-        <v>6773349</v>
+        <v>6773336</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6492,10 +6492,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129114697</v>
+        <v>129114115</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>83011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,21 +6503,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455428</v>
+        <v>455394</v>
       </c>
       <c r="R56" t="n">
-        <v>6773376</v>
+        <v>6773349</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129110757</v>
+        <v>129114697</v>
       </c>
       <c r="B57" t="n">
         <v>79035</v>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455252</v>
+        <v>455428</v>
       </c>
       <c r="R57" t="n">
-        <v>6773222</v>
+        <v>6773376</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129113107</v>
+        <v>129110757</v>
       </c>
       <c r="B58" t="n">
-        <v>79067</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455308</v>
+        <v>455252</v>
       </c>
       <c r="R58" t="n">
-        <v>6773336</v>
+        <v>6773222</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8117,10 +8117,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129113854</v>
+        <v>129124330</v>
       </c>
       <c r="B71" t="n">
-        <v>79035</v>
+        <v>92857</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8128,34 +8128,41 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455337</v>
+        <v>455412</v>
       </c>
       <c r="R71" t="n">
-        <v>6773325</v>
+        <v>6773178</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8185,27 +8192,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8224,10 +8222,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124330</v>
+        <v>129113854</v>
       </c>
       <c r="B72" t="n">
-        <v>92857</v>
+        <v>79035</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8235,41 +8233,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455412</v>
+        <v>455337</v>
       </c>
       <c r="R72" t="n">
-        <v>6773178</v>
+        <v>6773325</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8299,18 +8290,27 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129108044</v>
+        <v>129112804</v>
       </c>
       <c r="B2" t="n">
-        <v>79654</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455412</v>
+        <v>455289</v>
       </c>
       <c r="R2" t="n">
-        <v>6773172</v>
+        <v>6773299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129112479</v>
+        <v>129112610</v>
       </c>
       <c r="B3" t="n">
         <v>79035</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455272</v>
+        <v>455308</v>
       </c>
       <c r="R3" t="n">
-        <v>6773302</v>
+        <v>6773282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129112804</v>
+        <v>129112438</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455289</v>
+        <v>455258</v>
       </c>
       <c r="R4" t="n">
-        <v>6773299</v>
+        <v>6773321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112610</v>
+        <v>129112479</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455308</v>
+        <v>455272</v>
       </c>
       <c r="R5" t="n">
-        <v>6773282</v>
+        <v>6773302</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129112438</v>
+        <v>129108044</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455258</v>
+        <v>455412</v>
       </c>
       <c r="R6" t="n">
-        <v>6773321</v>
+        <v>6773172</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129109404</v>
+        <v>129113163</v>
       </c>
       <c r="B10" t="n">
         <v>79035</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455484</v>
+        <v>455283</v>
       </c>
       <c r="R10" t="n">
-        <v>6773211</v>
+        <v>6773359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129110737</v>
+        <v>129109404</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455259</v>
+        <v>455484</v>
       </c>
       <c r="R11" t="n">
-        <v>6773216</v>
+        <v>6773211</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129113882</v>
+        <v>129110737</v>
       </c>
       <c r="B12" t="n">
-        <v>97530</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455329</v>
+        <v>455259</v>
       </c>
       <c r="R12" t="n">
-        <v>6773342</v>
+        <v>6773216</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129113163</v>
+        <v>129113882</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>97530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455283</v>
+        <v>455329</v>
       </c>
       <c r="R13" t="n">
-        <v>6773359</v>
+        <v>6773342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129109078</v>
+        <v>129110979</v>
       </c>
       <c r="B16" t="n">
         <v>79035</v>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455467</v>
+        <v>455258</v>
       </c>
       <c r="R16" t="n">
-        <v>6773201</v>
+        <v>6773256</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129110979</v>
+        <v>129107916</v>
       </c>
       <c r="B17" t="n">
         <v>79035</v>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455258</v>
+        <v>455389</v>
       </c>
       <c r="R17" t="n">
-        <v>6773256</v>
+        <v>6773170</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,32 +2397,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129108219</v>
+        <v>129109078</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455412</v>
+        <v>455467</v>
       </c>
       <c r="R18" t="n">
-        <v>6773172</v>
+        <v>6773201</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,32 +2504,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129107916</v>
+        <v>129108219</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455389</v>
+        <v>455412</v>
       </c>
       <c r="R19" t="n">
-        <v>6773170</v>
+        <v>6773172</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129109713</v>
+        <v>129110813</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455494</v>
+        <v>455237</v>
       </c>
       <c r="R20" t="n">
-        <v>6773187</v>
+        <v>6773232</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129110813</v>
+        <v>129109713</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455237</v>
+        <v>455494</v>
       </c>
       <c r="R21" t="n">
-        <v>6773232</v>
+        <v>6773187</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129107601</v>
+        <v>129113094</v>
       </c>
       <c r="B22" t="n">
         <v>79035</v>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455352</v>
+        <v>455301</v>
       </c>
       <c r="R22" t="n">
-        <v>6773200</v>
+        <v>6773331</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129112407</v>
+        <v>129107601</v>
       </c>
       <c r="B23" t="n">
         <v>79035</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455248</v>
+        <v>455352</v>
       </c>
       <c r="R23" t="n">
-        <v>6773310</v>
+        <v>6773200</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129107736</v>
+        <v>129112407</v>
       </c>
       <c r="B24" t="n">
         <v>79035</v>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455372</v>
+        <v>455248</v>
       </c>
       <c r="R24" t="n">
-        <v>6773181</v>
+        <v>6773310</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129109613</v>
+        <v>129107736</v>
       </c>
       <c r="B25" t="n">
         <v>79035</v>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455494</v>
+        <v>455372</v>
       </c>
       <c r="R25" t="n">
-        <v>6773197</v>
+        <v>6773181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129111088</v>
+        <v>129109613</v>
       </c>
       <c r="B26" t="n">
         <v>79035</v>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455248</v>
+        <v>455494</v>
       </c>
       <c r="R26" t="n">
-        <v>6773274</v>
+        <v>6773197</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129114098</v>
+        <v>129111088</v>
       </c>
       <c r="B27" t="n">
         <v>79035</v>
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455394</v>
+        <v>455248</v>
       </c>
       <c r="R27" t="n">
-        <v>6773349</v>
+        <v>6773274</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129113094</v>
+        <v>129114098</v>
       </c>
       <c r="B28" t="n">
         <v>79035</v>
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455301</v>
+        <v>455394</v>
       </c>
       <c r="R28" t="n">
-        <v>6773331</v>
+        <v>6773349</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129107986</v>
+        <v>129110662</v>
       </c>
       <c r="B33" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455389</v>
+        <v>455273</v>
       </c>
       <c r="R33" t="n">
-        <v>6773170</v>
+        <v>6773208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129110662</v>
+        <v>129106783</v>
       </c>
       <c r="B34" t="n">
         <v>79035</v>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455273</v>
+        <v>455407</v>
       </c>
       <c r="R34" t="n">
-        <v>6773208</v>
+        <v>6773196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4221,10 +4221,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129106783</v>
+        <v>129107986</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,21 +4232,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455407</v>
+        <v>455389</v>
       </c>
       <c r="R35" t="n">
-        <v>6773196</v>
+        <v>6773170</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129114507</v>
+        <v>129107072</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455391</v>
+        <v>455389</v>
       </c>
       <c r="R41" t="n">
-        <v>6773367</v>
+        <v>6773203</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129107679</v>
+        <v>129114507</v>
       </c>
       <c r="B42" t="n">
         <v>79035</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455353</v>
+        <v>455391</v>
       </c>
       <c r="R42" t="n">
-        <v>6773191</v>
+        <v>6773367</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129110029</v>
+        <v>129107679</v>
       </c>
       <c r="B43" t="n">
         <v>79035</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455333</v>
+        <v>455353</v>
       </c>
       <c r="R43" t="n">
-        <v>6773241</v>
+        <v>6773191</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129107072</v>
+        <v>129110029</v>
       </c>
       <c r="B44" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455389</v>
+        <v>455333</v>
       </c>
       <c r="R44" t="n">
-        <v>6773203</v>
+        <v>6773241</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6385,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129113107</v>
+        <v>129114115</v>
       </c>
       <c r="B55" t="n">
-        <v>79067</v>
+        <v>83011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,21 +6396,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455308</v>
+        <v>455394</v>
       </c>
       <c r="R55" t="n">
-        <v>6773336</v>
+        <v>6773349</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6492,10 +6492,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129114115</v>
+        <v>129113107</v>
       </c>
       <c r="B56" t="n">
-        <v>83011</v>
+        <v>79067</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,21 +6503,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455394</v>
+        <v>455308</v>
       </c>
       <c r="R56" t="n">
-        <v>6773349</v>
+        <v>6773336</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129107895</v>
+        <v>129109466</v>
       </c>
       <c r="B78" t="n">
         <v>79035</v>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>455397</v>
+        <v>455479</v>
       </c>
       <c r="R78" t="n">
-        <v>6773180</v>
+        <v>6773185</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8990,7 +8990,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129109466</v>
+        <v>129107895</v>
       </c>
       <c r="B79" t="n">
         <v>79035</v>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>455479</v>
+        <v>455397</v>
       </c>
       <c r="R79" t="n">
-        <v>6773185</v>
+        <v>6773180</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112804</v>
+        <v>129108044</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>79658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455289</v>
+        <v>455412</v>
       </c>
       <c r="R2" t="n">
-        <v>6773299</v>
+        <v>6773172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +785,7 @@
         <v>129112610</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +892,7 @@
         <v>129112438</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +999,7 @@
         <v>129112479</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129108044</v>
+        <v>129112804</v>
       </c>
       <c r="B6" t="n">
-        <v>79654</v>
+        <v>57722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455412</v>
+        <v>455289</v>
       </c>
       <c r="R6" t="n">
-        <v>6773172</v>
+        <v>6773299</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
         <v>129108187</v>
       </c>
       <c r="B7" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>129110825</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>129107453</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129113163</v>
+        <v>129109404</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455283</v>
+        <v>455484</v>
       </c>
       <c r="R10" t="n">
-        <v>6773359</v>
+        <v>6773211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129109404</v>
+        <v>129113882</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>97540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455484</v>
+        <v>455329</v>
       </c>
       <c r="R11" t="n">
-        <v>6773211</v>
+        <v>6773342</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129110737</v>
+        <v>129113163</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455259</v>
+        <v>455283</v>
       </c>
       <c r="R12" t="n">
-        <v>6773216</v>
+        <v>6773359</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129113882</v>
+        <v>129110737</v>
       </c>
       <c r="B13" t="n">
-        <v>97530</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455329</v>
+        <v>455259</v>
       </c>
       <c r="R13" t="n">
-        <v>6773342</v>
+        <v>6773216</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
         <v>129114066</v>
       </c>
       <c r="B14" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>129107035</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129110979</v>
+        <v>129107916</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455258</v>
+        <v>455389</v>
       </c>
       <c r="R16" t="n">
-        <v>6773256</v>
+        <v>6773170</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129107916</v>
+        <v>129110979</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455389</v>
+        <v>455258</v>
       </c>
       <c r="R17" t="n">
-        <v>6773170</v>
+        <v>6773256</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
         <v>129109078</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>129109713</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129113094</v>
+        <v>129109613</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455301</v>
+        <v>455494</v>
       </c>
       <c r="R22" t="n">
-        <v>6773331</v>
+        <v>6773197</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,10 +2932,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129107601</v>
+        <v>129112407</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455352</v>
+        <v>455248</v>
       </c>
       <c r="R23" t="n">
-        <v>6773200</v>
+        <v>6773310</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129112407</v>
+        <v>129111088</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>455248</v>
       </c>
       <c r="R24" t="n">
-        <v>6773310</v>
+        <v>6773274</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129107736</v>
+        <v>129114098</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3181,13 +3181,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455372</v>
+        <v>455394</v>
       </c>
       <c r="R25" t="n">
-        <v>6773181</v>
+        <v>6773349</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3253,10 +3253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129109613</v>
+        <v>129113094</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455494</v>
+        <v>455301</v>
       </c>
       <c r="R26" t="n">
-        <v>6773197</v>
+        <v>6773331</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,10 +3360,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129111088</v>
+        <v>129107601</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455248</v>
+        <v>455352</v>
       </c>
       <c r="R27" t="n">
-        <v>6773274</v>
+        <v>6773200</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129114098</v>
+        <v>129107736</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455394</v>
+        <v>455372</v>
       </c>
       <c r="R28" t="n">
-        <v>6773349</v>
+        <v>6773181</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129112885</v>
+        <v>129113791</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,37 +3585,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455288</v>
+        <v>455304</v>
       </c>
       <c r="R29" t="n">
-        <v>6773318</v>
+        <v>6773316</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3681,10 +3686,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129110462</v>
+        <v>129112885</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3716,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455333</v>
+        <v>455288</v>
       </c>
       <c r="R30" t="n">
-        <v>6773289</v>
+        <v>6773318</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3788,10 +3793,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129113791</v>
+        <v>129110462</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3799,42 +3804,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455304</v>
+        <v>455333</v>
       </c>
       <c r="R31" t="n">
-        <v>6773316</v>
+        <v>6773289</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>129110782</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129110662</v>
+        <v>129110692</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4042,13 +4042,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455273</v>
+        <v>455270</v>
       </c>
       <c r="R33" t="n">
-        <v>6773208</v>
+        <v>6773216</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>129106783</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>129107986</v>
       </c>
       <c r="B35" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129110692</v>
+        <v>129110662</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4363,13 +4363,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455270</v>
+        <v>455273</v>
       </c>
       <c r="R36" t="n">
-        <v>6773216</v>
+        <v>6773208</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>129109514</v>
       </c>
       <c r="B37" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4547,50 +4547,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129110522</v>
+        <v>129108956</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455304</v>
+        <v>455473</v>
       </c>
       <c r="R38" t="n">
-        <v>6773265</v>
+        <v>6773221</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4662,7 +4657,7 @@
         <v>129110861</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4766,45 +4761,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129108956</v>
+        <v>129110522</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455473</v>
+        <v>455304</v>
       </c>
       <c r="R40" t="n">
-        <v>6773221</v>
+        <v>6773265</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129107072</v>
+        <v>129107679</v>
       </c>
       <c r="B41" t="n">
-        <v>79625</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455389</v>
+        <v>455353</v>
       </c>
       <c r="R41" t="n">
-        <v>6773203</v>
+        <v>6773191</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4983,7 +4983,7 @@
         <v>129114507</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129107679</v>
+        <v>129110029</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455353</v>
+        <v>455333</v>
       </c>
       <c r="R43" t="n">
-        <v>6773191</v>
+        <v>6773241</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129110029</v>
+        <v>129107072</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>79629</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455333</v>
+        <v>455389</v>
       </c>
       <c r="R44" t="n">
-        <v>6773241</v>
+        <v>6773203</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5304,7 +5304,7 @@
         <v>129109327</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129109369</v>
+        <v>129112595</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455473</v>
+        <v>455279</v>
       </c>
       <c r="R46" t="n">
-        <v>6773219</v>
+        <v>6773275</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5515,10 +5515,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129112595</v>
+        <v>129109369</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455279</v>
+        <v>455473</v>
       </c>
       <c r="R47" t="n">
-        <v>6773275</v>
+        <v>6773219</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
         <v>129112827</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5729,10 +5729,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129110148</v>
+        <v>129114165</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5764,10 +5764,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455349</v>
+        <v>455390</v>
       </c>
       <c r="R49" t="n">
-        <v>6773250</v>
+        <v>6773344</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129114165</v>
+        <v>129110148</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455390</v>
+        <v>455349</v>
       </c>
       <c r="R50" t="n">
-        <v>6773344</v>
+        <v>6773250</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5946,7 +5946,7 @@
         <v>129109151</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6162,54 +6162,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129112645</v>
+        <v>129112375</v>
       </c>
       <c r="B53" t="n">
-        <v>58153</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103001</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455308</v>
+        <v>455269</v>
       </c>
       <c r="R53" t="n">
-        <v>6773282</v>
+        <v>6773288</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6278,45 +6269,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129112375</v>
+        <v>129112645</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>58155</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>103001</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455269</v>
+        <v>455308</v>
       </c>
       <c r="R54" t="n">
-        <v>6773288</v>
+        <v>6773282</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6388,7 +6388,7 @@
         <v>129114115</v>
       </c>
       <c r="B55" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6492,10 +6492,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129113107</v>
+        <v>129114697</v>
       </c>
       <c r="B56" t="n">
-        <v>79067</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,21 +6503,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455308</v>
+        <v>455428</v>
       </c>
       <c r="R56" t="n">
-        <v>6773336</v>
+        <v>6773376</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6599,10 +6599,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129114697</v>
+        <v>129113107</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>79071</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6610,21 +6610,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455428</v>
+        <v>455308</v>
       </c>
       <c r="R57" t="n">
-        <v>6773376</v>
+        <v>6773336</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6709,7 +6709,7 @@
         <v>129110757</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129112093</v>
+        <v>129110960</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455241</v>
+        <v>455260</v>
       </c>
       <c r="R62" t="n">
-        <v>6773279</v>
+        <v>6773245</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7246,10 +7246,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129110960</v>
+        <v>129112093</v>
       </c>
       <c r="B63" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455260</v>
+        <v>455241</v>
       </c>
       <c r="R63" t="n">
-        <v>6773245</v>
+        <v>6773279</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7356,7 +7356,7 @@
         <v>129107474</v>
       </c>
       <c r="B64" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>129110941</v>
       </c>
       <c r="B67" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>129112114</v>
       </c>
       <c r="B68" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>129113193</v>
       </c>
       <c r="B69" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8117,10 +8117,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124330</v>
+        <v>129113854</v>
       </c>
       <c r="B71" t="n">
-        <v>92857</v>
+        <v>79039</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8128,41 +8128,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455412</v>
+        <v>455337</v>
       </c>
       <c r="R71" t="n">
-        <v>6773178</v>
+        <v>6773325</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8192,18 +8185,27 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8222,10 +8224,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129113854</v>
+        <v>129124330</v>
       </c>
       <c r="B72" t="n">
-        <v>79035</v>
+        <v>92864</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8233,34 +8235,41 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455337</v>
+        <v>455412</v>
       </c>
       <c r="R72" t="n">
-        <v>6773325</v>
+        <v>6773178</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8290,27 +8299,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8332,7 +8332,7 @@
         <v>129107854</v>
       </c>
       <c r="B73" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8436,51 +8436,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129114483</v>
+        <v>129112107</v>
       </c>
       <c r="B74" t="n">
-        <v>90908</v>
+        <v>79039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455394</v>
+        <v>455235</v>
       </c>
       <c r="R74" t="n">
-        <v>6773349</v>
+        <v>6773290</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8522,18 +8519,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8552,10 +8543,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129112107</v>
+        <v>129110810</v>
       </c>
       <c r="B75" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8563,34 +8554,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455235</v>
+        <v>455237</v>
       </c>
       <c r="R75" t="n">
-        <v>6773290</v>
+        <v>6773232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8659,53 +8655,51 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129110810</v>
+        <v>129114483</v>
       </c>
       <c r="B76" t="n">
-        <v>57720</v>
+        <v>90912</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455237</v>
+        <v>455394</v>
       </c>
       <c r="R76" t="n">
-        <v>6773232</v>
+        <v>6773349</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8747,12 +8741,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>129109071</v>
       </c>
       <c r="B77" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>129109466</v>
       </c>
       <c r="B78" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>129107895</v>
       </c>
       <c r="B79" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B80" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,34 +9108,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R80" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9204,10 +9209,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B81" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9215,39 +9220,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R81" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9319,7 +9319,7 @@
         <v>129107617</v>
       </c>
       <c r="B82" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>129113130</v>
       </c>
       <c r="B83" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>129111012</v>
       </c>
       <c r="B84" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>129112346</v>
       </c>
       <c r="B85" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>129110007</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>129112739</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>129113900</v>
       </c>
       <c r="B89" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>129114734</v>
       </c>
       <c r="B90" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>129114442</v>
       </c>
       <c r="B91" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>129112774</v>
       </c>
       <c r="B92" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -1643,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129113882</v>
+        <v>129113163</v>
       </c>
       <c r="B11" t="n">
-        <v>97540</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455329</v>
+        <v>455283</v>
       </c>
       <c r="R11" t="n">
-        <v>6773342</v>
+        <v>6773359</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129113163</v>
+        <v>129110737</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455283</v>
+        <v>455259</v>
       </c>
       <c r="R12" t="n">
-        <v>6773359</v>
+        <v>6773216</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129110737</v>
+        <v>129113882</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>97540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455259</v>
+        <v>455329</v>
       </c>
       <c r="R13" t="n">
-        <v>6773216</v>
+        <v>6773342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129110692</v>
+        <v>129109514</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,37 +4018,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455270</v>
+        <v>455494</v>
       </c>
       <c r="R33" t="n">
-        <v>6773216</v>
+        <v>6773187</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4114,10 +4119,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129106783</v>
+        <v>129107986</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4125,21 +4130,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4149,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455407</v>
+        <v>455389</v>
       </c>
       <c r="R34" t="n">
-        <v>6773196</v>
+        <v>6773170</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4221,10 +4226,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129107986</v>
+        <v>129110662</v>
       </c>
       <c r="B35" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,21 +4237,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4256,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455389</v>
+        <v>455273</v>
       </c>
       <c r="R35" t="n">
-        <v>6773170</v>
+        <v>6773208</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4328,7 +4333,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129110662</v>
+        <v>129110692</v>
       </c>
       <c r="B36" t="n">
         <v>79039</v>
@@ -4363,13 +4368,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455273</v>
+        <v>455270</v>
       </c>
       <c r="R36" t="n">
-        <v>6773208</v>
+        <v>6773216</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4435,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129109514</v>
+        <v>129106783</v>
       </c>
       <c r="B37" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4446,39 +4451,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455494</v>
+        <v>455407</v>
       </c>
       <c r="R37" t="n">
-        <v>6773187</v>
+        <v>6773196</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129110960</v>
+        <v>129107474</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,34 +7150,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455260</v>
+        <v>455385</v>
       </c>
       <c r="R62" t="n">
-        <v>6773245</v>
+        <v>6773193</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7246,45 +7251,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129112093</v>
+        <v>129110475</v>
       </c>
       <c r="B63" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455241</v>
+        <v>455333</v>
       </c>
       <c r="R63" t="n">
-        <v>6773279</v>
+        <v>6773289</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7353,10 +7363,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129107474</v>
+        <v>129110960</v>
       </c>
       <c r="B64" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7364,39 +7374,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455385</v>
+        <v>455260</v>
       </c>
       <c r="R64" t="n">
-        <v>6773193</v>
+        <v>6773245</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7465,50 +7470,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129110475</v>
+        <v>129112093</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455333</v>
+        <v>455241</v>
       </c>
       <c r="R65" t="n">
-        <v>6773289</v>
+        <v>6773279</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B80" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,39 +9108,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R80" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9209,10 +9204,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B81" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9220,34 +9215,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R81" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -1860,7 +1860,7 @@
         <v>129113882</v>
       </c>
       <c r="B13" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129107916</v>
+        <v>129109078</v>
       </c>
       <c r="B16" t="n">
         <v>79039</v>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455389</v>
+        <v>455467</v>
       </c>
       <c r="R16" t="n">
-        <v>6773170</v>
+        <v>6773201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129109078</v>
+        <v>129107916</v>
       </c>
       <c r="B18" t="n">
         <v>79039</v>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455467</v>
+        <v>455389</v>
       </c>
       <c r="R18" t="n">
-        <v>6773201</v>
+        <v>6773170</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129110813</v>
+        <v>129109713</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455237</v>
+        <v>455494</v>
       </c>
       <c r="R20" t="n">
-        <v>6773232</v>
+        <v>6773187</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129109713</v>
+        <v>129110813</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455494</v>
+        <v>455237</v>
       </c>
       <c r="R21" t="n">
-        <v>6773187</v>
+        <v>6773232</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129109613</v>
+        <v>129107601</v>
       </c>
       <c r="B22" t="n">
         <v>79039</v>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455494</v>
+        <v>455352</v>
       </c>
       <c r="R22" t="n">
-        <v>6773197</v>
+        <v>6773200</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129111088</v>
+        <v>129107736</v>
       </c>
       <c r="B24" t="n">
         <v>79039</v>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455248</v>
+        <v>455372</v>
       </c>
       <c r="R24" t="n">
-        <v>6773274</v>
+        <v>6773181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129114098</v>
+        <v>129109613</v>
       </c>
       <c r="B25" t="n">
         <v>79039</v>
@@ -3181,13 +3181,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455394</v>
+        <v>455494</v>
       </c>
       <c r="R25" t="n">
-        <v>6773349</v>
+        <v>6773197</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129113094</v>
+        <v>129111088</v>
       </c>
       <c r="B26" t="n">
         <v>79039</v>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455301</v>
+        <v>455248</v>
       </c>
       <c r="R26" t="n">
-        <v>6773331</v>
+        <v>6773274</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129107601</v>
+        <v>129114098</v>
       </c>
       <c r="B27" t="n">
         <v>79039</v>
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455352</v>
+        <v>455394</v>
       </c>
       <c r="R27" t="n">
-        <v>6773200</v>
+        <v>6773349</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129107736</v>
+        <v>129113094</v>
       </c>
       <c r="B28" t="n">
         <v>79039</v>
@@ -3502,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455372</v>
+        <v>455301</v>
       </c>
       <c r="R28" t="n">
-        <v>6773181</v>
+        <v>6773331</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129109514</v>
+        <v>129110662</v>
       </c>
       <c r="B33" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,39 +4018,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455494</v>
+        <v>455273</v>
       </c>
       <c r="R33" t="n">
-        <v>6773187</v>
+        <v>6773208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4119,10 +4114,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129107986</v>
+        <v>129106783</v>
       </c>
       <c r="B34" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4130,21 +4125,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4154,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455389</v>
+        <v>455407</v>
       </c>
       <c r="R34" t="n">
-        <v>6773170</v>
+        <v>6773196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4226,7 +4221,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129110662</v>
+        <v>129110692</v>
       </c>
       <c r="B35" t="n">
         <v>79039</v>
@@ -4261,13 +4256,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455273</v>
+        <v>455270</v>
       </c>
       <c r="R35" t="n">
-        <v>6773208</v>
+        <v>6773216</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4333,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129110692</v>
+        <v>129109514</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,37 +4339,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455270</v>
+        <v>455494</v>
       </c>
       <c r="R36" t="n">
-        <v>6773216</v>
+        <v>6773187</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129106783</v>
+        <v>129107986</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455407</v>
+        <v>455389</v>
       </c>
       <c r="R37" t="n">
-        <v>6773196</v>
+        <v>6773170</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129108956</v>
+        <v>129110861</v>
       </c>
       <c r="B38" t="n">
         <v>79039</v>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455473</v>
+        <v>455267</v>
       </c>
       <c r="R38" t="n">
-        <v>6773221</v>
+        <v>6773233</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129110861</v>
+        <v>129108956</v>
       </c>
       <c r="B39" t="n">
         <v>79039</v>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455267</v>
+        <v>455473</v>
       </c>
       <c r="R39" t="n">
-        <v>6773233</v>
+        <v>6773221</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4873,7 +4873,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129107679</v>
+        <v>129114507</v>
       </c>
       <c r="B41" t="n">
         <v>79039</v>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455353</v>
+        <v>455391</v>
       </c>
       <c r="R41" t="n">
-        <v>6773191</v>
+        <v>6773367</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129114507</v>
+        <v>129107679</v>
       </c>
       <c r="B42" t="n">
         <v>79039</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455391</v>
+        <v>455353</v>
       </c>
       <c r="R42" t="n">
-        <v>6773367</v>
+        <v>6773191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129112595</v>
+        <v>129109369</v>
       </c>
       <c r="B46" t="n">
         <v>79039</v>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455279</v>
+        <v>455473</v>
       </c>
       <c r="R46" t="n">
-        <v>6773275</v>
+        <v>6773219</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129109369</v>
+        <v>129112595</v>
       </c>
       <c r="B47" t="n">
         <v>79039</v>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455473</v>
+        <v>455279</v>
       </c>
       <c r="R47" t="n">
-        <v>6773219</v>
+        <v>6773275</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5729,45 +5729,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129114165</v>
+        <v>129109267</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455390</v>
+        <v>455477</v>
       </c>
       <c r="R49" t="n">
-        <v>6773344</v>
+        <v>6773206</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5943,7 +5948,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129109151</v>
+        <v>129114165</v>
       </c>
       <c r="B51" t="n">
         <v>79039</v>
@@ -5978,10 +5983,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455459</v>
+        <v>455390</v>
       </c>
       <c r="R51" t="n">
-        <v>6773195</v>
+        <v>6773344</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6050,50 +6055,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129109267</v>
+        <v>129109151</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455477</v>
+        <v>455459</v>
       </c>
       <c r="R52" t="n">
-        <v>6773206</v>
+        <v>6773195</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6385,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129114115</v>
+        <v>129113107</v>
       </c>
       <c r="B55" t="n">
-        <v>83015</v>
+        <v>79071</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,21 +6396,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455394</v>
+        <v>455308</v>
       </c>
       <c r="R55" t="n">
-        <v>6773349</v>
+        <v>6773336</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6492,32 +6492,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129114697</v>
+        <v>129112005</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455428</v>
+        <v>455235</v>
       </c>
       <c r="R56" t="n">
-        <v>6773376</v>
+        <v>6773290</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6599,32 +6599,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129113107</v>
+        <v>129110915</v>
       </c>
       <c r="B57" t="n">
-        <v>79071</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455308</v>
+        <v>455267</v>
       </c>
       <c r="R57" t="n">
-        <v>6773336</v>
+        <v>6773233</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,45 +6706,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129110757</v>
+        <v>129108995</v>
       </c>
       <c r="B58" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455252</v>
+        <v>455473</v>
       </c>
       <c r="R58" t="n">
-        <v>6773222</v>
+        <v>6773221</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6813,32 +6818,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129112005</v>
+        <v>129114697</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6848,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455235</v>
+        <v>455428</v>
       </c>
       <c r="R59" t="n">
-        <v>6773290</v>
+        <v>6773376</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6920,32 +6925,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129110915</v>
+        <v>129110757</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6955,10 +6960,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455267</v>
+        <v>455252</v>
       </c>
       <c r="R60" t="n">
-        <v>6773233</v>
+        <v>6773222</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7027,53 +7032,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129108995</v>
+        <v>129114115</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>83005</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455473</v>
+        <v>455394</v>
       </c>
       <c r="R61" t="n">
-        <v>6773221</v>
+        <v>6773349</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129107474</v>
+        <v>129112093</v>
       </c>
       <c r="B62" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,39 +7150,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455385</v>
+        <v>455241</v>
       </c>
       <c r="R62" t="n">
-        <v>6773193</v>
+        <v>6773279</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7251,50 +7246,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129110475</v>
+        <v>129110960</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455333</v>
+        <v>455260</v>
       </c>
       <c r="R63" t="n">
-        <v>6773289</v>
+        <v>6773245</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7363,10 +7353,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129110960</v>
+        <v>129107474</v>
       </c>
       <c r="B64" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7374,34 +7364,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455260</v>
+        <v>455385</v>
       </c>
       <c r="R64" t="n">
-        <v>6773245</v>
+        <v>6773193</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7470,45 +7465,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129112093</v>
+        <v>129110475</v>
       </c>
       <c r="B65" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455241</v>
+        <v>455333</v>
       </c>
       <c r="R65" t="n">
-        <v>6773279</v>
+        <v>6773289</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7898,50 +7898,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129113193</v>
+        <v>129110844</v>
       </c>
       <c r="B69" t="n">
-        <v>57725</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455283</v>
+        <v>455259</v>
       </c>
       <c r="R69" t="n">
-        <v>6773359</v>
+        <v>6773246</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8010,45 +8005,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129110844</v>
+        <v>129113193</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>57725</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455259</v>
+        <v>455283</v>
       </c>
       <c r="R70" t="n">
-        <v>6773246</v>
+        <v>6773359</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8227,7 +8227,7 @@
         <v>129124330</v>
       </c>
       <c r="B72" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8436,48 +8436,51 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129112107</v>
+        <v>129114483</v>
       </c>
       <c r="B74" t="n">
-        <v>79039</v>
+        <v>90919</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455235</v>
+        <v>455394</v>
       </c>
       <c r="R74" t="n">
-        <v>6773290</v>
+        <v>6773349</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8519,12 +8522,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8543,10 +8552,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129110810</v>
+        <v>129112107</v>
       </c>
       <c r="B75" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8554,39 +8563,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455237</v>
+        <v>455235</v>
       </c>
       <c r="R75" t="n">
-        <v>6773232</v>
+        <v>6773290</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8655,51 +8659,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129114483</v>
+        <v>129110810</v>
       </c>
       <c r="B76" t="n">
-        <v>90912</v>
+        <v>57722</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455394</v>
+        <v>455237</v>
       </c>
       <c r="R76" t="n">
-        <v>6773349</v>
+        <v>6773232</v>
       </c>
       <c r="S76" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8741,18 +8747,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8883,7 +8883,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129109466</v>
+        <v>129107895</v>
       </c>
       <c r="B78" t="n">
         <v>79039</v>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>455479</v>
+        <v>455397</v>
       </c>
       <c r="R78" t="n">
-        <v>6773185</v>
+        <v>6773180</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8990,7 +8990,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129107895</v>
+        <v>129109466</v>
       </c>
       <c r="B79" t="n">
         <v>79039</v>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>455397</v>
+        <v>455479</v>
       </c>
       <c r="R79" t="n">
-        <v>6773180</v>
+        <v>6773185</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129108044</v>
+        <v>129112438</v>
       </c>
       <c r="B2" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455412</v>
+        <v>455258</v>
       </c>
       <c r="R2" t="n">
-        <v>6773172</v>
+        <v>6773321</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129112610</v>
+        <v>129108044</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455308</v>
+        <v>455412</v>
       </c>
       <c r="R3" t="n">
-        <v>6773282</v>
+        <v>6773172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129112438</v>
+        <v>129112479</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455258</v>
+        <v>455272</v>
       </c>
       <c r="R4" t="n">
-        <v>6773321</v>
+        <v>6773302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112479</v>
+        <v>129112610</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455272</v>
+        <v>455308</v>
       </c>
       <c r="R5" t="n">
-        <v>6773302</v>
+        <v>6773282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129112804</v>
+        <v>129108187</v>
       </c>
       <c r="B6" t="n">
-        <v>57722</v>
+        <v>79631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455289</v>
+        <v>455412</v>
       </c>
       <c r="R6" t="n">
-        <v>6773299</v>
+        <v>6773172</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129108187</v>
+        <v>129112804</v>
       </c>
       <c r="B7" t="n">
-        <v>79629</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455412</v>
+        <v>455289</v>
       </c>
       <c r="R7" t="n">
-        <v>6773172</v>
+        <v>6773299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129110825</v>
+        <v>129110737</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
         <v>455259</v>
       </c>
       <c r="R8" t="n">
-        <v>6773246</v>
+        <v>6773216</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129107453</v>
+        <v>129113882</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>97549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455385</v>
+        <v>455329</v>
       </c>
       <c r="R9" t="n">
-        <v>6773193</v>
+        <v>6773342</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129109404</v>
+        <v>129110825</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455484</v>
+        <v>455259</v>
       </c>
       <c r="R10" t="n">
-        <v>6773211</v>
+        <v>6773246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129113163</v>
+        <v>129107453</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455283</v>
+        <v>455385</v>
       </c>
       <c r="R11" t="n">
-        <v>6773359</v>
+        <v>6773193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129110737</v>
+        <v>129109404</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455259</v>
+        <v>455484</v>
       </c>
       <c r="R12" t="n">
-        <v>6773216</v>
+        <v>6773211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129113882</v>
+        <v>129113163</v>
       </c>
       <c r="B13" t="n">
-        <v>97547</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455329</v>
+        <v>455283</v>
       </c>
       <c r="R13" t="n">
-        <v>6773342</v>
+        <v>6773359</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1967,7 @@
         <v>129114066</v>
       </c>
       <c r="B14" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>129107035</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>129109078</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>129110979</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>129107916</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>129109713</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129107601</v>
+        <v>129112407</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455352</v>
+        <v>455248</v>
       </c>
       <c r="R22" t="n">
-        <v>6773200</v>
+        <v>6773310</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,10 +2932,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129112407</v>
+        <v>129107736</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455248</v>
+        <v>455372</v>
       </c>
       <c r="R23" t="n">
-        <v>6773310</v>
+        <v>6773181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129107736</v>
+        <v>129109613</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455372</v>
+        <v>455494</v>
       </c>
       <c r="R24" t="n">
-        <v>6773181</v>
+        <v>6773197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129109613</v>
+        <v>129113094</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455494</v>
+        <v>455301</v>
       </c>
       <c r="R25" t="n">
-        <v>6773197</v>
+        <v>6773331</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3256,7 +3256,7 @@
         <v>129111088</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>129114098</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129113094</v>
+        <v>129107601</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455301</v>
+        <v>455352</v>
       </c>
       <c r="R28" t="n">
-        <v>6773331</v>
+        <v>6773200</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129113791</v>
+        <v>129112885</v>
       </c>
       <c r="B29" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,42 +3585,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455304</v>
+        <v>455288</v>
       </c>
       <c r="R29" t="n">
-        <v>6773316</v>
+        <v>6773318</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3686,10 +3681,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129112885</v>
+        <v>129110462</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3721,10 +3716,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455288</v>
+        <v>455333</v>
       </c>
       <c r="R30" t="n">
-        <v>6773318</v>
+        <v>6773289</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3793,10 +3788,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129110462</v>
+        <v>129113791</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3804,37 +3799,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455333</v>
+        <v>455304</v>
       </c>
       <c r="R31" t="n">
-        <v>6773289</v>
+        <v>6773316</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>129110782</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129110662</v>
+        <v>129109514</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,34 +4018,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455273</v>
+        <v>455494</v>
       </c>
       <c r="R33" t="n">
-        <v>6773208</v>
+        <v>6773187</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,10 +4119,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129106783</v>
+        <v>129107986</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4125,21 +4130,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4149,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455407</v>
+        <v>455389</v>
       </c>
       <c r="R34" t="n">
-        <v>6773196</v>
+        <v>6773170</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4221,10 +4226,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129110692</v>
+        <v>129110662</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,13 +4261,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455270</v>
+        <v>455273</v>
       </c>
       <c r="R35" t="n">
-        <v>6773216</v>
+        <v>6773208</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4328,10 +4333,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129109514</v>
+        <v>129106783</v>
       </c>
       <c r="B36" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4339,39 +4344,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455494</v>
+        <v>455407</v>
       </c>
       <c r="R36" t="n">
-        <v>6773187</v>
+        <v>6773196</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129107986</v>
+        <v>129110692</v>
       </c>
       <c r="B37" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455389</v>
+        <v>455270</v>
       </c>
       <c r="R37" t="n">
-        <v>6773170</v>
+        <v>6773216</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4547,45 +4547,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129110861</v>
+        <v>129110522</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455267</v>
+        <v>455304</v>
       </c>
       <c r="R38" t="n">
-        <v>6773233</v>
+        <v>6773265</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4654,10 +4659,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129108956</v>
+        <v>129110861</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4689,10 +4694,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455473</v>
+        <v>455267</v>
       </c>
       <c r="R39" t="n">
-        <v>6773221</v>
+        <v>6773233</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4761,50 +4766,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129110522</v>
+        <v>129108956</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455304</v>
+        <v>455473</v>
       </c>
       <c r="R40" t="n">
-        <v>6773265</v>
+        <v>6773221</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4876,7 +4876,7 @@
         <v>129114507</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>129107679</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>129110029</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>129107072</v>
       </c>
       <c r="B44" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>129109327</v>
       </c>
       <c r="B45" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>129109369</v>
       </c>
       <c r="B46" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>129112595</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>129112827</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>129110148</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>129114165</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>129109151</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>129112645</v>
       </c>
       <c r="B54" t="n">
-        <v>58155</v>
+        <v>58157</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6385,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129113107</v>
+        <v>129114115</v>
       </c>
       <c r="B55" t="n">
-        <v>79071</v>
+        <v>83007</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,21 +6396,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455308</v>
+        <v>455394</v>
       </c>
       <c r="R55" t="n">
-        <v>6773336</v>
+        <v>6773349</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6492,32 +6492,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129112005</v>
+        <v>129114697</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455235</v>
+        <v>455428</v>
       </c>
       <c r="R56" t="n">
-        <v>6773290</v>
+        <v>6773376</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6599,32 +6599,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129110915</v>
+        <v>129110757</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455267</v>
+        <v>455252</v>
       </c>
       <c r="R57" t="n">
-        <v>6773233</v>
+        <v>6773222</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,50 +6706,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129108995</v>
+        <v>129113107</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>79073</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455473</v>
+        <v>455308</v>
       </c>
       <c r="R58" t="n">
-        <v>6773221</v>
+        <v>6773336</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6818,32 +6813,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129114697</v>
+        <v>129112005</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6853,10 +6848,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455428</v>
+        <v>455235</v>
       </c>
       <c r="R59" t="n">
-        <v>6773376</v>
+        <v>6773290</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6925,32 +6920,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129110757</v>
+        <v>129110915</v>
       </c>
       <c r="B60" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6960,10 +6955,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455252</v>
+        <v>455267</v>
       </c>
       <c r="R60" t="n">
-        <v>6773222</v>
+        <v>6773233</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7032,48 +7027,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129114115</v>
+        <v>129108995</v>
       </c>
       <c r="B61" t="n">
-        <v>83005</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455394</v>
+        <v>455473</v>
       </c>
       <c r="R61" t="n">
-        <v>6773349</v>
+        <v>6773221</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>129112093</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>129110960</v>
       </c>
       <c r="B63" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>129107474</v>
       </c>
       <c r="B64" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>129110941</v>
       </c>
       <c r="B67" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>129112114</v>
       </c>
       <c r="B68" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7898,45 +7898,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129110844</v>
+        <v>129113193</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455259</v>
+        <v>455283</v>
       </c>
       <c r="R69" t="n">
-        <v>6773246</v>
+        <v>6773359</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8005,50 +8010,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129113193</v>
+        <v>129110844</v>
       </c>
       <c r="B70" t="n">
-        <v>57725</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455283</v>
+        <v>455259</v>
       </c>
       <c r="R70" t="n">
-        <v>6773359</v>
+        <v>6773246</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8120,7 +8120,7 @@
         <v>129113854</v>
       </c>
       <c r="B71" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>129124330</v>
       </c>
       <c r="B72" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>129107854</v>
       </c>
       <c r="B73" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8436,51 +8436,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129114483</v>
+        <v>129112107</v>
       </c>
       <c r="B74" t="n">
-        <v>90919</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455394</v>
+        <v>455235</v>
       </c>
       <c r="R74" t="n">
-        <v>6773349</v>
+        <v>6773290</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8522,18 +8519,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8552,10 +8543,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129112107</v>
+        <v>129110810</v>
       </c>
       <c r="B75" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8563,34 +8554,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455235</v>
+        <v>455237</v>
       </c>
       <c r="R75" t="n">
-        <v>6773290</v>
+        <v>6773232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8659,53 +8655,51 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129110810</v>
+        <v>129114483</v>
       </c>
       <c r="B76" t="n">
-        <v>57722</v>
+        <v>90921</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455237</v>
+        <v>455394</v>
       </c>
       <c r="R76" t="n">
-        <v>6773232</v>
+        <v>6773349</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8747,12 +8741,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>129109071</v>
       </c>
       <c r="B77" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>129107895</v>
       </c>
       <c r="B78" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>129109466</v>
       </c>
       <c r="B79" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>129109225</v>
       </c>
       <c r="B80" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>129114154</v>
       </c>
       <c r="B81" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>129107617</v>
       </c>
       <c r="B82" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>129113130</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>129111012</v>
       </c>
       <c r="B84" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>129112346</v>
       </c>
       <c r="B85" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>129110007</v>
       </c>
       <c r="B87" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>129112739</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>129113900</v>
       </c>
       <c r="B89" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>129114734</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>129114442</v>
       </c>
       <c r="B91" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>129112774</v>
       </c>
       <c r="B92" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112438</v>
+        <v>129112610</v>
       </c>
       <c r="B2" t="n">
         <v>79041</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455258</v>
+        <v>455308</v>
       </c>
       <c r="R2" t="n">
-        <v>6773321</v>
+        <v>6773282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129108044</v>
+        <v>129112438</v>
       </c>
       <c r="B3" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455412</v>
+        <v>455258</v>
       </c>
       <c r="R3" t="n">
-        <v>6773172</v>
+        <v>6773321</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112610</v>
+        <v>129112804</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455308</v>
+        <v>455289</v>
       </c>
       <c r="R5" t="n">
-        <v>6773282</v>
+        <v>6773299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129112804</v>
+        <v>129108044</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,39 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455289</v>
+        <v>455412</v>
       </c>
       <c r="R7" t="n">
-        <v>6773299</v>
+        <v>6773172</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129110737</v>
+        <v>129113882</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>97549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455259</v>
+        <v>455329</v>
       </c>
       <c r="R8" t="n">
-        <v>6773216</v>
+        <v>6773342</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129113882</v>
+        <v>129110825</v>
       </c>
       <c r="B9" t="n">
-        <v>97549</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455329</v>
+        <v>455259</v>
       </c>
       <c r="R9" t="n">
-        <v>6773342</v>
+        <v>6773246</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129110825</v>
+        <v>129107453</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455259</v>
+        <v>455385</v>
       </c>
       <c r="R10" t="n">
-        <v>6773246</v>
+        <v>6773193</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129107453</v>
+        <v>129109404</v>
       </c>
       <c r="B11" t="n">
         <v>79041</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455385</v>
+        <v>455484</v>
       </c>
       <c r="R11" t="n">
-        <v>6773193</v>
+        <v>6773211</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129109404</v>
+        <v>129113163</v>
       </c>
       <c r="B12" t="n">
         <v>79041</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455484</v>
+        <v>455283</v>
       </c>
       <c r="R12" t="n">
-        <v>6773211</v>
+        <v>6773359</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129113163</v>
+        <v>129110737</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455283</v>
+        <v>455259</v>
       </c>
       <c r="R13" t="n">
-        <v>6773359</v>
+        <v>6773216</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2183,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129109078</v>
+        <v>129108219</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455467</v>
+        <v>455412</v>
       </c>
       <c r="R16" t="n">
-        <v>6773201</v>
+        <v>6773172</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2504,32 +2504,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129108219</v>
+        <v>129109078</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455412</v>
+        <v>455467</v>
       </c>
       <c r="R19" t="n">
-        <v>6773172</v>
+        <v>6773201</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129112407</v>
+        <v>129107601</v>
       </c>
       <c r="B22" t="n">
         <v>79041</v>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455248</v>
+        <v>455352</v>
       </c>
       <c r="R22" t="n">
-        <v>6773310</v>
+        <v>6773200</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129107736</v>
+        <v>129112407</v>
       </c>
       <c r="B23" t="n">
         <v>79041</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455372</v>
+        <v>455248</v>
       </c>
       <c r="R23" t="n">
-        <v>6773181</v>
+        <v>6773310</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129109613</v>
+        <v>129107736</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455494</v>
+        <v>455372</v>
       </c>
       <c r="R24" t="n">
-        <v>6773197</v>
+        <v>6773181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129113094</v>
+        <v>129109613</v>
       </c>
       <c r="B25" t="n">
         <v>79041</v>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455301</v>
+        <v>455494</v>
       </c>
       <c r="R25" t="n">
-        <v>6773331</v>
+        <v>6773197</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129107601</v>
+        <v>129113094</v>
       </c>
       <c r="B28" t="n">
         <v>79041</v>
@@ -3502,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455352</v>
+        <v>455301</v>
       </c>
       <c r="R28" t="n">
-        <v>6773200</v>
+        <v>6773331</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129109514</v>
+        <v>129107986</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>78798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,39 +4018,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455494</v>
+        <v>455389</v>
       </c>
       <c r="R33" t="n">
-        <v>6773187</v>
+        <v>6773170</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4119,10 +4114,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129107986</v>
+        <v>129109514</v>
       </c>
       <c r="B34" t="n">
-        <v>78798</v>
+        <v>57724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4130,34 +4125,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455389</v>
+        <v>455494</v>
       </c>
       <c r="R34" t="n">
-        <v>6773170</v>
+        <v>6773187</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4547,50 +4547,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129110522</v>
+        <v>129108956</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455304</v>
+        <v>455473</v>
       </c>
       <c r="R38" t="n">
-        <v>6773265</v>
+        <v>6773221</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4766,45 +4761,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129108956</v>
+        <v>129110522</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455473</v>
+        <v>455304</v>
       </c>
       <c r="R40" t="n">
-        <v>6773221</v>
+        <v>6773265</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4980,10 +4980,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129107679</v>
+        <v>129107072</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4991,21 +4991,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455353</v>
+        <v>455389</v>
       </c>
       <c r="R42" t="n">
-        <v>6773191</v>
+        <v>6773203</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129110029</v>
+        <v>129107679</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455333</v>
+        <v>455353</v>
       </c>
       <c r="R43" t="n">
-        <v>6773241</v>
+        <v>6773191</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129107072</v>
+        <v>129110029</v>
       </c>
       <c r="B44" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455389</v>
+        <v>455333</v>
       </c>
       <c r="R44" t="n">
-        <v>6773203</v>
+        <v>6773241</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129109327</v>
+        <v>129112595</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455477</v>
+        <v>455279</v>
       </c>
       <c r="R45" t="n">
-        <v>6773206</v>
+        <v>6773275</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129109369</v>
+        <v>129109327</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455473</v>
+        <v>455477</v>
       </c>
       <c r="R46" t="n">
-        <v>6773219</v>
+        <v>6773206</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129112595</v>
+        <v>129109369</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455279</v>
+        <v>455473</v>
       </c>
       <c r="R47" t="n">
-        <v>6773275</v>
+        <v>6773219</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6162,45 +6162,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129112375</v>
+        <v>129112645</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>58157</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>103001</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455269</v>
+        <v>455308</v>
       </c>
       <c r="R53" t="n">
-        <v>6773288</v>
+        <v>6773282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6269,54 +6278,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129112645</v>
+        <v>129112375</v>
       </c>
       <c r="B54" t="n">
-        <v>58157</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103001</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455308</v>
+        <v>455269</v>
       </c>
       <c r="R54" t="n">
-        <v>6773282</v>
+        <v>6773288</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6385,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129114115</v>
+        <v>129113107</v>
       </c>
       <c r="B55" t="n">
-        <v>83007</v>
+        <v>79073</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,21 +6396,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455394</v>
+        <v>455308</v>
       </c>
       <c r="R55" t="n">
-        <v>6773349</v>
+        <v>6773336</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6492,10 +6492,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129114697</v>
+        <v>129114115</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>83007</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,21 +6503,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455428</v>
+        <v>455394</v>
       </c>
       <c r="R56" t="n">
-        <v>6773376</v>
+        <v>6773349</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129110757</v>
+        <v>129114697</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455252</v>
+        <v>455428</v>
       </c>
       <c r="R57" t="n">
-        <v>6773222</v>
+        <v>6773376</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129113107</v>
+        <v>129110757</v>
       </c>
       <c r="B58" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455308</v>
+        <v>455252</v>
       </c>
       <c r="R58" t="n">
-        <v>6773336</v>
+        <v>6773222</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129112093</v>
+        <v>129107474</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,34 +7150,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455241</v>
+        <v>455385</v>
       </c>
       <c r="R62" t="n">
-        <v>6773279</v>
+        <v>6773193</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7246,45 +7251,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129110960</v>
+        <v>129110475</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455260</v>
+        <v>455333</v>
       </c>
       <c r="R63" t="n">
-        <v>6773245</v>
+        <v>6773289</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7353,50 +7363,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129107474</v>
+        <v>129114704</v>
       </c>
       <c r="B64" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455385</v>
+        <v>455438</v>
       </c>
       <c r="R64" t="n">
-        <v>6773193</v>
+        <v>6773400</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7465,50 +7470,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129110475</v>
+        <v>129112093</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455333</v>
+        <v>455241</v>
       </c>
       <c r="R65" t="n">
-        <v>6773289</v>
+        <v>6773279</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7577,32 +7577,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129114704</v>
+        <v>129110960</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455438</v>
+        <v>455260</v>
       </c>
       <c r="R66" t="n">
-        <v>6773400</v>
+        <v>6773245</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7684,10 +7684,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129110941</v>
+        <v>129113193</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7695,34 +7695,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455281</v>
+        <v>455283</v>
       </c>
       <c r="R67" t="n">
-        <v>6773251</v>
+        <v>6773359</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7898,10 +7903,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129113193</v>
+        <v>129110941</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7909,39 +7914,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455283</v>
+        <v>455281</v>
       </c>
       <c r="R69" t="n">
-        <v>6773359</v>
+        <v>6773251</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8543,53 +8543,51 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129110810</v>
+        <v>129114483</v>
       </c>
       <c r="B75" t="n">
-        <v>57724</v>
+        <v>90921</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455237</v>
+        <v>455394</v>
       </c>
       <c r="R75" t="n">
-        <v>6773232</v>
+        <v>6773349</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8631,12 +8629,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8655,51 +8659,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129114483</v>
+        <v>129110810</v>
       </c>
       <c r="B76" t="n">
-        <v>90921</v>
+        <v>57724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455394</v>
+        <v>455237</v>
       </c>
       <c r="R76" t="n">
-        <v>6773349</v>
+        <v>6773232</v>
       </c>
       <c r="S76" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8741,18 +8747,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112804</v>
+        <v>129108044</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455289</v>
+        <v>455412</v>
       </c>
       <c r="R5" t="n">
-        <v>6773299</v>
+        <v>6773172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129108187</v>
+        <v>129112804</v>
       </c>
       <c r="B6" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455412</v>
+        <v>455289</v>
       </c>
       <c r="R6" t="n">
-        <v>6773172</v>
+        <v>6773299</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129108044</v>
+        <v>129108187</v>
       </c>
       <c r="B7" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129107986</v>
+        <v>129110662</v>
       </c>
       <c r="B33" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455389</v>
+        <v>455273</v>
       </c>
       <c r="R33" t="n">
-        <v>6773170</v>
+        <v>6773208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,10 +4114,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129109514</v>
+        <v>129106783</v>
       </c>
       <c r="B34" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4125,39 +4125,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455494</v>
+        <v>455407</v>
       </c>
       <c r="R34" t="n">
-        <v>6773187</v>
+        <v>6773196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4226,7 +4221,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129110662</v>
+        <v>129110692</v>
       </c>
       <c r="B35" t="n">
         <v>79041</v>
@@ -4261,13 +4256,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455273</v>
+        <v>455270</v>
       </c>
       <c r="R35" t="n">
-        <v>6773208</v>
+        <v>6773216</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4333,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129106783</v>
+        <v>129109514</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,34 +4339,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455407</v>
+        <v>455494</v>
       </c>
       <c r="R36" t="n">
-        <v>6773196</v>
+        <v>6773187</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129110692</v>
+        <v>129107986</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455270</v>
+        <v>455389</v>
       </c>
       <c r="R37" t="n">
-        <v>6773216</v>
+        <v>6773170</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5729,50 +5729,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129109267</v>
+        <v>129110148</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455477</v>
+        <v>455349</v>
       </c>
       <c r="R49" t="n">
-        <v>6773206</v>
+        <v>6773250</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5836,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129110148</v>
+        <v>129114165</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5876,10 +5871,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455349</v>
+        <v>455390</v>
       </c>
       <c r="R50" t="n">
-        <v>6773250</v>
+        <v>6773344</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,7 +5943,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129114165</v>
+        <v>129109151</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5983,10 +5978,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455390</v>
+        <v>455459</v>
       </c>
       <c r="R51" t="n">
-        <v>6773344</v>
+        <v>6773195</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6055,45 +6050,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129109151</v>
+        <v>129109267</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455459</v>
+        <v>455477</v>
       </c>
       <c r="R52" t="n">
-        <v>6773195</v>
+        <v>6773206</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7684,10 +7684,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129113193</v>
+        <v>129112114</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7695,39 +7695,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455283</v>
+        <v>455233</v>
       </c>
       <c r="R67" t="n">
-        <v>6773359</v>
+        <v>6773294</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7796,7 +7791,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129112114</v>
+        <v>129110941</v>
       </c>
       <c r="B68" t="n">
         <v>79041</v>
@@ -7831,10 +7826,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455233</v>
+        <v>455281</v>
       </c>
       <c r="R68" t="n">
-        <v>6773294</v>
+        <v>6773251</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7903,10 +7898,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129110941</v>
+        <v>129113193</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7914,34 +7909,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455281</v>
+        <v>455283</v>
       </c>
       <c r="R69" t="n">
-        <v>6773251</v>
+        <v>6773359</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8117,10 +8117,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129113854</v>
+        <v>129124330</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>92873</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8128,34 +8128,41 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455337</v>
+        <v>455412</v>
       </c>
       <c r="R71" t="n">
-        <v>6773325</v>
+        <v>6773178</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8185,27 +8192,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8224,10 +8222,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124330</v>
+        <v>129113854</v>
       </c>
       <c r="B72" t="n">
-        <v>92873</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8235,41 +8233,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455412</v>
+        <v>455337</v>
       </c>
       <c r="R72" t="n">
-        <v>6773178</v>
+        <v>6773325</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8299,18 +8290,27 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112610</v>
+        <v>129112804</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455308</v>
+        <v>455289</v>
       </c>
       <c r="R2" t="n">
-        <v>6773282</v>
+        <v>6773299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129112438</v>
+        <v>129108044</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455258</v>
+        <v>455412</v>
       </c>
       <c r="R3" t="n">
-        <v>6773321</v>
+        <v>6773172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129112479</v>
+        <v>129108187</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455272</v>
+        <v>455412</v>
       </c>
       <c r="R4" t="n">
-        <v>6773302</v>
+        <v>6773172</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129108044</v>
+        <v>129112610</v>
       </c>
       <c r="B5" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455412</v>
+        <v>455308</v>
       </c>
       <c r="R5" t="n">
-        <v>6773172</v>
+        <v>6773282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129112804</v>
+        <v>129112438</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455289</v>
+        <v>455258</v>
       </c>
       <c r="R6" t="n">
-        <v>6773299</v>
+        <v>6773321</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129108187</v>
+        <v>129112479</v>
       </c>
       <c r="B7" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455412</v>
+        <v>455272</v>
       </c>
       <c r="R7" t="n">
-        <v>6773172</v>
+        <v>6773302</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129113882</v>
+        <v>129110737</v>
       </c>
       <c r="B8" t="n">
-        <v>97549</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455329</v>
+        <v>455259</v>
       </c>
       <c r="R8" t="n">
-        <v>6773342</v>
+        <v>6773216</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129110825</v>
+        <v>129113882</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>97575</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455259</v>
+        <v>455329</v>
       </c>
       <c r="R9" t="n">
-        <v>6773246</v>
+        <v>6773342</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129107453</v>
+        <v>129110825</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455385</v>
+        <v>455259</v>
       </c>
       <c r="R10" t="n">
-        <v>6773193</v>
+        <v>6773246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129109404</v>
+        <v>129107453</v>
       </c>
       <c r="B11" t="n">
         <v>79041</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455484</v>
+        <v>455385</v>
       </c>
       <c r="R11" t="n">
-        <v>6773211</v>
+        <v>6773193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129113163</v>
+        <v>129109404</v>
       </c>
       <c r="B12" t="n">
         <v>79041</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455283</v>
+        <v>455484</v>
       </c>
       <c r="R12" t="n">
-        <v>6773359</v>
+        <v>6773211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129110737</v>
+        <v>129113163</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455259</v>
+        <v>455283</v>
       </c>
       <c r="R13" t="n">
-        <v>6773216</v>
+        <v>6773359</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2183,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129108219</v>
+        <v>129109078</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455412</v>
+        <v>455467</v>
       </c>
       <c r="R16" t="n">
-        <v>6773172</v>
+        <v>6773201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2504,32 +2504,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129109078</v>
+        <v>129108219</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455467</v>
+        <v>455412</v>
       </c>
       <c r="R19" t="n">
-        <v>6773201</v>
+        <v>6773172</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129110662</v>
+        <v>129107986</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455273</v>
+        <v>455389</v>
       </c>
       <c r="R33" t="n">
-        <v>6773208</v>
+        <v>6773170</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129106783</v>
+        <v>129110662</v>
       </c>
       <c r="B34" t="n">
         <v>79041</v>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455407</v>
+        <v>455273</v>
       </c>
       <c r="R34" t="n">
-        <v>6773196</v>
+        <v>6773208</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129110692</v>
+        <v>129106783</v>
       </c>
       <c r="B35" t="n">
         <v>79041</v>
@@ -4256,13 +4256,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455270</v>
+        <v>455407</v>
       </c>
       <c r="R35" t="n">
-        <v>6773216</v>
+        <v>6773196</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129109514</v>
+        <v>129110692</v>
       </c>
       <c r="B36" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4339,42 +4339,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455494</v>
+        <v>455270</v>
       </c>
       <c r="R36" t="n">
-        <v>6773187</v>
+        <v>6773216</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4440,10 +4435,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129107986</v>
+        <v>129109514</v>
       </c>
       <c r="B37" t="n">
-        <v>78798</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4451,34 +4446,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455389</v>
+        <v>455494</v>
       </c>
       <c r="R37" t="n">
-        <v>6773170</v>
+        <v>6773187</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129108956</v>
+        <v>129110861</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455473</v>
+        <v>455267</v>
       </c>
       <c r="R38" t="n">
-        <v>6773221</v>
+        <v>6773233</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129110861</v>
+        <v>129108956</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455267</v>
+        <v>455473</v>
       </c>
       <c r="R39" t="n">
-        <v>6773233</v>
+        <v>6773221</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129114507</v>
+        <v>129107072</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455391</v>
+        <v>455389</v>
       </c>
       <c r="R41" t="n">
-        <v>6773367</v>
+        <v>6773203</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,10 +4980,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129107072</v>
+        <v>129114507</v>
       </c>
       <c r="B42" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4991,21 +4991,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455389</v>
+        <v>455391</v>
       </c>
       <c r="R42" t="n">
-        <v>6773203</v>
+        <v>6773367</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129112595</v>
+        <v>129109327</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455279</v>
+        <v>455477</v>
       </c>
       <c r="R45" t="n">
-        <v>6773275</v>
+        <v>6773206</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129109327</v>
+        <v>129109369</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455477</v>
+        <v>455473</v>
       </c>
       <c r="R46" t="n">
-        <v>6773206</v>
+        <v>6773219</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129109369</v>
+        <v>129112595</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455473</v>
+        <v>455279</v>
       </c>
       <c r="R47" t="n">
-        <v>6773219</v>
+        <v>6773275</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6385,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129113107</v>
+        <v>129114115</v>
       </c>
       <c r="B55" t="n">
-        <v>79073</v>
+        <v>83007</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,21 +6396,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455308</v>
+        <v>455394</v>
       </c>
       <c r="R55" t="n">
-        <v>6773336</v>
+        <v>6773349</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6492,10 +6492,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129114115</v>
+        <v>129114697</v>
       </c>
       <c r="B56" t="n">
-        <v>83007</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,21 +6503,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455394</v>
+        <v>455428</v>
       </c>
       <c r="R56" t="n">
-        <v>6773349</v>
+        <v>6773376</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129114697</v>
+        <v>129110757</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455428</v>
+        <v>455252</v>
       </c>
       <c r="R57" t="n">
-        <v>6773376</v>
+        <v>6773222</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129110757</v>
+        <v>129113107</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455252</v>
+        <v>455308</v>
       </c>
       <c r="R58" t="n">
-        <v>6773222</v>
+        <v>6773336</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7139,38 +7139,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129107474</v>
+        <v>129110475</v>
       </c>
       <c r="B62" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455385</v>
+        <v>455333</v>
       </c>
       <c r="R62" t="n">
-        <v>6773193</v>
+        <v>6773289</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7251,7 +7251,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129110475</v>
+        <v>129114704</v>
       </c>
       <c r="B63" t="n">
         <v>8450</v>
@@ -7280,21 +7280,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455333</v>
+        <v>455438</v>
       </c>
       <c r="R63" t="n">
-        <v>6773289</v>
+        <v>6773400</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7363,32 +7358,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129114704</v>
+        <v>129112093</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7398,10 +7393,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455438</v>
+        <v>455241</v>
       </c>
       <c r="R64" t="n">
-        <v>6773400</v>
+        <v>6773279</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7470,7 +7465,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129112093</v>
+        <v>129110960</v>
       </c>
       <c r="B65" t="n">
         <v>79041</v>
@@ -7505,10 +7500,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455241</v>
+        <v>455260</v>
       </c>
       <c r="R65" t="n">
-        <v>6773279</v>
+        <v>6773245</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7577,10 +7572,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129110960</v>
+        <v>129107474</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7588,34 +7583,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455260</v>
+        <v>455385</v>
       </c>
       <c r="R66" t="n">
-        <v>6773245</v>
+        <v>6773193</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7684,32 +7684,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129112114</v>
+        <v>129110844</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455233</v>
+        <v>455259</v>
       </c>
       <c r="R67" t="n">
-        <v>6773294</v>
+        <v>6773246</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7898,10 +7898,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129113193</v>
+        <v>129112114</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7909,39 +7909,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455283</v>
+        <v>455233</v>
       </c>
       <c r="R69" t="n">
-        <v>6773359</v>
+        <v>6773294</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8010,45 +8005,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129110844</v>
+        <v>129113193</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455259</v>
+        <v>455283</v>
       </c>
       <c r="R70" t="n">
-        <v>6773246</v>
+        <v>6773359</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8120,7 +8120,7 @@
         <v>129124330</v>
       </c>
       <c r="B71" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8436,10 +8436,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129112107</v>
+        <v>129110810</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8447,34 +8447,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455235</v>
+        <v>455237</v>
       </c>
       <c r="R74" t="n">
-        <v>6773290</v>
+        <v>6773232</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8546,7 +8551,7 @@
         <v>129114483</v>
       </c>
       <c r="B75" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8659,10 +8664,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129110810</v>
+        <v>129112107</v>
       </c>
       <c r="B76" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8670,39 +8675,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455237</v>
+        <v>455235</v>
       </c>
       <c r="R76" t="n">
-        <v>6773232</v>
+        <v>6773290</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,34 +9108,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R80" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9204,10 +9209,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9215,39 +9220,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R81" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112804</v>
+        <v>129112610</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455289</v>
+        <v>455308</v>
       </c>
       <c r="R2" t="n">
-        <v>6773299</v>
+        <v>6773282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129108044</v>
+        <v>129112438</v>
       </c>
       <c r="B3" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455412</v>
+        <v>455258</v>
       </c>
       <c r="R3" t="n">
-        <v>6773172</v>
+        <v>6773321</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129108187</v>
+        <v>129112479</v>
       </c>
       <c r="B4" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455412</v>
+        <v>455272</v>
       </c>
       <c r="R4" t="n">
-        <v>6773172</v>
+        <v>6773302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112610</v>
+        <v>129108187</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455308</v>
+        <v>455412</v>
       </c>
       <c r="R5" t="n">
-        <v>6773282</v>
+        <v>6773172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129112438</v>
+        <v>129108044</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455258</v>
+        <v>455412</v>
       </c>
       <c r="R6" t="n">
-        <v>6773321</v>
+        <v>6773172</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129112479</v>
+        <v>129112804</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455272</v>
+        <v>455289</v>
       </c>
       <c r="R7" t="n">
-        <v>6773302</v>
+        <v>6773299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129110737</v>
+        <v>129110825</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
         <v>455259</v>
       </c>
       <c r="R8" t="n">
-        <v>6773216</v>
+        <v>6773246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129113882</v>
+        <v>129107453</v>
       </c>
       <c r="B9" t="n">
-        <v>97575</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455329</v>
+        <v>455385</v>
       </c>
       <c r="R9" t="n">
-        <v>6773342</v>
+        <v>6773193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129110825</v>
+        <v>129109404</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455259</v>
+        <v>455484</v>
       </c>
       <c r="R10" t="n">
-        <v>6773246</v>
+        <v>6773211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129107453</v>
+        <v>129113163</v>
       </c>
       <c r="B11" t="n">
         <v>79041</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455385</v>
+        <v>455283</v>
       </c>
       <c r="R11" t="n">
-        <v>6773193</v>
+        <v>6773359</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129109404</v>
+        <v>129110737</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455484</v>
+        <v>455259</v>
       </c>
       <c r="R12" t="n">
-        <v>6773211</v>
+        <v>6773216</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129113163</v>
+        <v>129113882</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>97576</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455283</v>
+        <v>455329</v>
       </c>
       <c r="R13" t="n">
-        <v>6773359</v>
+        <v>6773342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2183,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129109078</v>
+        <v>129108219</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455467</v>
+        <v>455412</v>
       </c>
       <c r="R16" t="n">
-        <v>6773201</v>
+        <v>6773172</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129110979</v>
+        <v>129109078</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455258</v>
+        <v>455467</v>
       </c>
       <c r="R17" t="n">
-        <v>6773256</v>
+        <v>6773201</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129107916</v>
+        <v>129110979</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455389</v>
+        <v>455258</v>
       </c>
       <c r="R18" t="n">
-        <v>6773170</v>
+        <v>6773256</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,32 +2504,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129108219</v>
+        <v>129107916</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455412</v>
+        <v>455389</v>
       </c>
       <c r="R19" t="n">
-        <v>6773172</v>
+        <v>6773170</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129112885</v>
+        <v>129113791</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,37 +3585,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455288</v>
+        <v>455304</v>
       </c>
       <c r="R29" t="n">
-        <v>6773318</v>
+        <v>6773316</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3788,10 +3793,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129113791</v>
+        <v>129112885</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3799,42 +3804,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455304</v>
+        <v>455288</v>
       </c>
       <c r="R31" t="n">
-        <v>6773316</v>
+        <v>6773318</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4114,10 +4114,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129110662</v>
+        <v>129109514</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4125,34 +4125,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455273</v>
+        <v>455494</v>
       </c>
       <c r="R34" t="n">
-        <v>6773208</v>
+        <v>6773187</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4221,7 +4226,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129106783</v>
+        <v>129110662</v>
       </c>
       <c r="B35" t="n">
         <v>79041</v>
@@ -4256,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455407</v>
+        <v>455273</v>
       </c>
       <c r="R35" t="n">
-        <v>6773196</v>
+        <v>6773208</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4328,7 +4333,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129110692</v>
+        <v>129106783</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4363,13 +4368,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455270</v>
+        <v>455407</v>
       </c>
       <c r="R36" t="n">
-        <v>6773216</v>
+        <v>6773196</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4435,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129109514</v>
+        <v>129110692</v>
       </c>
       <c r="B37" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4446,42 +4451,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455494</v>
+        <v>455270</v>
       </c>
       <c r="R37" t="n">
-        <v>6773187</v>
+        <v>6773216</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129107072</v>
+        <v>129114507</v>
       </c>
       <c r="B41" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455389</v>
+        <v>455391</v>
       </c>
       <c r="R41" t="n">
-        <v>6773203</v>
+        <v>6773367</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129114507</v>
+        <v>129107679</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455391</v>
+        <v>455353</v>
       </c>
       <c r="R42" t="n">
-        <v>6773367</v>
+        <v>6773191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129107679</v>
+        <v>129110029</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455353</v>
+        <v>455333</v>
       </c>
       <c r="R43" t="n">
-        <v>6773191</v>
+        <v>6773241</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129110029</v>
+        <v>129107072</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455333</v>
+        <v>455389</v>
       </c>
       <c r="R44" t="n">
-        <v>6773241</v>
+        <v>6773203</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6385,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129114115</v>
+        <v>129113107</v>
       </c>
       <c r="B55" t="n">
-        <v>83007</v>
+        <v>79073</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,21 +6396,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455394</v>
+        <v>455308</v>
       </c>
       <c r="R55" t="n">
-        <v>6773349</v>
+        <v>6773336</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6492,10 +6492,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129114697</v>
+        <v>129114115</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>83007</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,21 +6503,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455428</v>
+        <v>455394</v>
       </c>
       <c r="R56" t="n">
-        <v>6773376</v>
+        <v>6773349</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129110757</v>
+        <v>129114697</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455252</v>
+        <v>455428</v>
       </c>
       <c r="R57" t="n">
-        <v>6773222</v>
+        <v>6773376</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129113107</v>
+        <v>129110757</v>
       </c>
       <c r="B58" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455308</v>
+        <v>455252</v>
       </c>
       <c r="R58" t="n">
-        <v>6773336</v>
+        <v>6773222</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6813,7 +6813,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129112005</v>
+        <v>129108995</v>
       </c>
       <c r="B59" t="n">
         <v>8450</v>
@@ -6842,16 +6842,21 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455235</v>
+        <v>455473</v>
       </c>
       <c r="R59" t="n">
-        <v>6773290</v>
+        <v>6773221</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6920,7 +6925,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129110915</v>
+        <v>129112005</v>
       </c>
       <c r="B60" t="n">
         <v>8450</v>
@@ -6955,10 +6960,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455267</v>
+        <v>455235</v>
       </c>
       <c r="R60" t="n">
-        <v>6773233</v>
+        <v>6773290</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7027,7 +7032,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129108995</v>
+        <v>129110915</v>
       </c>
       <c r="B61" t="n">
         <v>8450</v>
@@ -7056,21 +7061,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455473</v>
+        <v>455267</v>
       </c>
       <c r="R61" t="n">
-        <v>6773221</v>
+        <v>6773233</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7684,45 +7684,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129110844</v>
+        <v>129113193</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455259</v>
+        <v>455283</v>
       </c>
       <c r="R67" t="n">
-        <v>6773246</v>
+        <v>6773359</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,32 +7796,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129110941</v>
+        <v>129110844</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7826,10 +7831,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455281</v>
+        <v>455259</v>
       </c>
       <c r="R68" t="n">
-        <v>6773251</v>
+        <v>6773246</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7898,7 +7903,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129112114</v>
+        <v>129110941</v>
       </c>
       <c r="B69" t="n">
         <v>79041</v>
@@ -7933,10 +7938,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455233</v>
+        <v>455281</v>
       </c>
       <c r="R69" t="n">
-        <v>6773294</v>
+        <v>6773251</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8005,10 +8010,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129113193</v>
+        <v>129112114</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8016,39 +8021,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455283</v>
+        <v>455233</v>
       </c>
       <c r="R70" t="n">
-        <v>6773359</v>
+        <v>6773294</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8117,10 +8117,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124330</v>
+        <v>129113854</v>
       </c>
       <c r="B71" t="n">
-        <v>92859</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8128,41 +8128,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455412</v>
+        <v>455337</v>
       </c>
       <c r="R71" t="n">
-        <v>6773178</v>
+        <v>6773325</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8192,18 +8185,27 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8222,10 +8224,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129113854</v>
+        <v>129124330</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>92860</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8233,34 +8235,41 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455337</v>
+        <v>455412</v>
       </c>
       <c r="R72" t="n">
-        <v>6773325</v>
+        <v>6773178</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8290,27 +8299,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8436,10 +8436,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129110810</v>
+        <v>129112107</v>
       </c>
       <c r="B74" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8447,39 +8447,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455237</v>
+        <v>455235</v>
       </c>
       <c r="R74" t="n">
-        <v>6773232</v>
+        <v>6773290</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8664,10 +8659,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129112107</v>
+        <v>129110810</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8675,34 +8670,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455235</v>
+        <v>455237</v>
       </c>
       <c r="R76" t="n">
-        <v>6773290</v>
+        <v>6773232</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,39 +9108,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R80" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9209,10 +9204,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9220,34 +9215,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R81" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129112739</v>
+        <v>129113900</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>455290</v>
+        <v>455329</v>
       </c>
       <c r="R88" t="n">
-        <v>6773279</v>
+        <v>6773342</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129113900</v>
+        <v>129112739</v>
       </c>
       <c r="B89" t="n">
         <v>79041</v>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>455329</v>
+        <v>455290</v>
       </c>
       <c r="R89" t="n">
-        <v>6773342</v>
+        <v>6773279</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112610</v>
+        <v>129112804</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455308</v>
+        <v>455289</v>
       </c>
       <c r="R2" t="n">
-        <v>6773282</v>
+        <v>6773299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129112438</v>
+        <v>129112610</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455258</v>
+        <v>455308</v>
       </c>
       <c r="R3" t="n">
-        <v>6773321</v>
+        <v>6773282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129112479</v>
+        <v>129112438</v>
       </c>
       <c r="B4" t="n">
         <v>79041</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455272</v>
+        <v>455258</v>
       </c>
       <c r="R4" t="n">
-        <v>6773302</v>
+        <v>6773321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129108187</v>
+        <v>129108044</v>
       </c>
       <c r="B5" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129108044</v>
+        <v>129112479</v>
       </c>
       <c r="B6" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455412</v>
+        <v>455272</v>
       </c>
       <c r="R6" t="n">
-        <v>6773172</v>
+        <v>6773302</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129112804</v>
+        <v>129108187</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>79631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,39 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455289</v>
+        <v>455412</v>
       </c>
       <c r="R7" t="n">
-        <v>6773299</v>
+        <v>6773172</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1860,7 +1860,7 @@
         <v>129113882</v>
       </c>
       <c r="B13" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129110462</v>
+        <v>129112885</v>
       </c>
       <c r="B30" t="n">
         <v>79041</v>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455333</v>
+        <v>455288</v>
       </c>
       <c r="R30" t="n">
-        <v>6773289</v>
+        <v>6773318</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129112885</v>
+        <v>129110462</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455288</v>
+        <v>455333</v>
       </c>
       <c r="R31" t="n">
-        <v>6773318</v>
+        <v>6773289</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129107986</v>
+        <v>129109514</v>
       </c>
       <c r="B33" t="n">
-        <v>78798</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,34 +4018,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455389</v>
+        <v>455494</v>
       </c>
       <c r="R33" t="n">
-        <v>6773170</v>
+        <v>6773187</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,10 +4119,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129109514</v>
+        <v>129107986</v>
       </c>
       <c r="B34" t="n">
-        <v>57724</v>
+        <v>78798</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4125,39 +4130,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455494</v>
+        <v>455389</v>
       </c>
       <c r="R34" t="n">
-        <v>6773187</v>
+        <v>6773170</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5729,45 +5729,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129110148</v>
+        <v>129109267</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455349</v>
+        <v>455477</v>
       </c>
       <c r="R49" t="n">
-        <v>6773250</v>
+        <v>6773206</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,7 +5841,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129114165</v>
+        <v>129110148</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5871,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455390</v>
+        <v>455349</v>
       </c>
       <c r="R50" t="n">
-        <v>6773344</v>
+        <v>6773250</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5943,7 +5948,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129109151</v>
+        <v>129114165</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5978,10 +5983,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455459</v>
+        <v>455390</v>
       </c>
       <c r="R51" t="n">
-        <v>6773195</v>
+        <v>6773344</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6050,50 +6055,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129109267</v>
+        <v>129109151</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455477</v>
+        <v>455459</v>
       </c>
       <c r="R52" t="n">
-        <v>6773206</v>
+        <v>6773195</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6813,7 +6813,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129108995</v>
+        <v>129112005</v>
       </c>
       <c r="B59" t="n">
         <v>8450</v>
@@ -6842,21 +6842,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455473</v>
+        <v>455235</v>
       </c>
       <c r="R59" t="n">
-        <v>6773221</v>
+        <v>6773290</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6925,7 +6920,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129112005</v>
+        <v>129110915</v>
       </c>
       <c r="B60" t="n">
         <v>8450</v>
@@ -6960,10 +6955,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455235</v>
+        <v>455267</v>
       </c>
       <c r="R60" t="n">
-        <v>6773290</v>
+        <v>6773233</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7032,7 +7027,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129110915</v>
+        <v>129108995</v>
       </c>
       <c r="B61" t="n">
         <v>8450</v>
@@ -7061,16 +7056,21 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455267</v>
+        <v>455473</v>
       </c>
       <c r="R61" t="n">
-        <v>6773233</v>
+        <v>6773221</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7139,38 +7139,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129110475</v>
+        <v>129107474</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455333</v>
+        <v>455385</v>
       </c>
       <c r="R62" t="n">
-        <v>6773289</v>
+        <v>6773193</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7251,32 +7251,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129114704</v>
+        <v>129112093</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455438</v>
+        <v>455241</v>
       </c>
       <c r="R63" t="n">
-        <v>6773400</v>
+        <v>6773279</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7358,7 +7358,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129112093</v>
+        <v>129110960</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455241</v>
+        <v>455260</v>
       </c>
       <c r="R64" t="n">
-        <v>6773279</v>
+        <v>6773245</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7465,45 +7465,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129110960</v>
+        <v>129110475</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455260</v>
+        <v>455333</v>
       </c>
       <c r="R65" t="n">
-        <v>6773245</v>
+        <v>6773289</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7572,50 +7577,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129107474</v>
+        <v>129114704</v>
       </c>
       <c r="B66" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455385</v>
+        <v>455438</v>
       </c>
       <c r="R66" t="n">
-        <v>6773193</v>
+        <v>6773400</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7796,32 +7796,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129110844</v>
+        <v>129110941</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455259</v>
+        <v>455281</v>
       </c>
       <c r="R68" t="n">
-        <v>6773246</v>
+        <v>6773251</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7903,7 +7903,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129110941</v>
+        <v>129112114</v>
       </c>
       <c r="B69" t="n">
         <v>79041</v>
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455281</v>
+        <v>455233</v>
       </c>
       <c r="R69" t="n">
-        <v>6773251</v>
+        <v>6773294</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8010,32 +8010,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129112114</v>
+        <v>129110844</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455233</v>
+        <v>455259</v>
       </c>
       <c r="R70" t="n">
-        <v>6773294</v>
+        <v>6773246</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8436,48 +8436,51 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129112107</v>
+        <v>129114483</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>90922</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455235</v>
+        <v>455394</v>
       </c>
       <c r="R74" t="n">
-        <v>6773290</v>
+        <v>6773349</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8519,12 +8522,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8543,51 +8552,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129114483</v>
+        <v>129110810</v>
       </c>
       <c r="B75" t="n">
-        <v>90922</v>
+        <v>57724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455394</v>
+        <v>455237</v>
       </c>
       <c r="R75" t="n">
-        <v>6773349</v>
+        <v>6773232</v>
       </c>
       <c r="S75" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8629,18 +8640,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8659,10 +8664,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129110810</v>
+        <v>129112107</v>
       </c>
       <c r="B76" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8670,39 +8675,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455237</v>
+        <v>455235</v>
       </c>
       <c r="R76" t="n">
-        <v>6773232</v>
+        <v>6773290</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129113900</v>
+        <v>129112739</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>455329</v>
+        <v>455290</v>
       </c>
       <c r="R88" t="n">
-        <v>6773342</v>
+        <v>6773279</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129112739</v>
+        <v>129113900</v>
       </c>
       <c r="B89" t="n">
         <v>79041</v>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>455290</v>
+        <v>455329</v>
       </c>
       <c r="R89" t="n">
-        <v>6773279</v>
+        <v>6773342</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112804</v>
+        <v>129112610</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455289</v>
+        <v>455308</v>
       </c>
       <c r="R2" t="n">
-        <v>6773299</v>
+        <v>6773282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129112610</v>
+        <v>129112438</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455308</v>
+        <v>455258</v>
       </c>
       <c r="R3" t="n">
-        <v>6773282</v>
+        <v>6773321</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129112438</v>
+        <v>129112479</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455258</v>
+        <v>455272</v>
       </c>
       <c r="R4" t="n">
-        <v>6773321</v>
+        <v>6773302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129108044</v>
+        <v>129112804</v>
       </c>
       <c r="B5" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455412</v>
+        <v>455289</v>
       </c>
       <c r="R5" t="n">
-        <v>6773172</v>
+        <v>6773299</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129112479</v>
+        <v>129108044</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455272</v>
+        <v>455412</v>
       </c>
       <c r="R6" t="n">
-        <v>6773302</v>
+        <v>6773172</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
         <v>129108187</v>
       </c>
       <c r="B7" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129110825</v>
+        <v>129113882</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>97581</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455259</v>
+        <v>455329</v>
       </c>
       <c r="R8" t="n">
-        <v>6773246</v>
+        <v>6773342</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129107453</v>
+        <v>129110825</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455385</v>
+        <v>455259</v>
       </c>
       <c r="R9" t="n">
-        <v>6773193</v>
+        <v>6773246</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129109404</v>
+        <v>129107453</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455484</v>
+        <v>455385</v>
       </c>
       <c r="R10" t="n">
-        <v>6773211</v>
+        <v>6773193</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129113163</v>
+        <v>129109404</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455283</v>
+        <v>455484</v>
       </c>
       <c r="R11" t="n">
-        <v>6773359</v>
+        <v>6773211</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129110737</v>
+        <v>129113163</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455259</v>
+        <v>455283</v>
       </c>
       <c r="R12" t="n">
-        <v>6773216</v>
+        <v>6773359</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129113882</v>
+        <v>129110737</v>
       </c>
       <c r="B13" t="n">
-        <v>97577</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455329</v>
+        <v>455259</v>
       </c>
       <c r="R13" t="n">
-        <v>6773342</v>
+        <v>6773216</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
         <v>129107035</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129108219</v>
+        <v>129109078</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455412</v>
+        <v>455467</v>
       </c>
       <c r="R16" t="n">
-        <v>6773172</v>
+        <v>6773201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129109078</v>
+        <v>129110979</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455467</v>
+        <v>455258</v>
       </c>
       <c r="R17" t="n">
-        <v>6773201</v>
+        <v>6773256</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129110979</v>
+        <v>129107916</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455258</v>
+        <v>455389</v>
       </c>
       <c r="R18" t="n">
-        <v>6773256</v>
+        <v>6773170</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,32 +2504,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129107916</v>
+        <v>129108219</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455389</v>
+        <v>455412</v>
       </c>
       <c r="R19" t="n">
-        <v>6773170</v>
+        <v>6773172</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,7 +2614,7 @@
         <v>129109713</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>129107601</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>129112407</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>129107736</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>129109613</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>129111088</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>129114098</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>129113094</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129113791</v>
+        <v>129112885</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,42 +3585,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455304</v>
+        <v>455288</v>
       </c>
       <c r="R29" t="n">
-        <v>6773316</v>
+        <v>6773318</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3686,10 +3681,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129112885</v>
+        <v>129110462</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3721,10 +3716,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455288</v>
+        <v>455333</v>
       </c>
       <c r="R30" t="n">
-        <v>6773318</v>
+        <v>6773289</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3793,10 +3788,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129110462</v>
+        <v>129113791</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3804,37 +3799,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455333</v>
+        <v>455304</v>
       </c>
       <c r="R31" t="n">
-        <v>6773289</v>
+        <v>6773316</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>129110782</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129109514</v>
+        <v>129110662</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,39 +4018,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455494</v>
+        <v>455273</v>
       </c>
       <c r="R33" t="n">
-        <v>6773187</v>
+        <v>6773208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4119,10 +4114,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129107986</v>
+        <v>129106783</v>
       </c>
       <c r="B34" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4130,21 +4125,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4154,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455389</v>
+        <v>455407</v>
       </c>
       <c r="R34" t="n">
-        <v>6773170</v>
+        <v>6773196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4226,10 +4221,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129110662</v>
+        <v>129110692</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,13 +4256,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455273</v>
+        <v>455270</v>
       </c>
       <c r="R35" t="n">
-        <v>6773208</v>
+        <v>6773216</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4333,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129106783</v>
+        <v>129107986</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,21 +4339,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4368,10 +4363,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455407</v>
+        <v>455389</v>
       </c>
       <c r="R36" t="n">
-        <v>6773196</v>
+        <v>6773170</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4440,10 +4435,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129110692</v>
+        <v>129109514</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4451,37 +4446,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455270</v>
+        <v>455494</v>
       </c>
       <c r="R37" t="n">
-        <v>6773216</v>
+        <v>6773187</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4547,45 +4547,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129110861</v>
+        <v>129110522</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455267</v>
+        <v>455304</v>
       </c>
       <c r="R38" t="n">
-        <v>6773233</v>
+        <v>6773265</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4654,10 +4659,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129108956</v>
+        <v>129110861</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4689,10 +4694,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455473</v>
+        <v>455267</v>
       </c>
       <c r="R39" t="n">
-        <v>6773221</v>
+        <v>6773233</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4761,50 +4766,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129110522</v>
+        <v>129108956</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455304</v>
+        <v>455473</v>
       </c>
       <c r="R40" t="n">
-        <v>6773265</v>
+        <v>6773221</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4876,7 +4876,7 @@
         <v>129114507</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>129107679</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>129110029</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>129107072</v>
       </c>
       <c r="B44" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>129109327</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>129109369</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>129112595</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>129112827</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5729,50 +5729,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129109267</v>
+        <v>129110148</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455477</v>
+        <v>455349</v>
       </c>
       <c r="R49" t="n">
-        <v>6773206</v>
+        <v>6773250</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,10 +5836,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129110148</v>
+        <v>129114165</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5876,10 +5871,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455349</v>
+        <v>455390</v>
       </c>
       <c r="R50" t="n">
-        <v>6773250</v>
+        <v>6773344</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,10 +5943,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129114165</v>
+        <v>129109151</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5983,10 +5978,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455390</v>
+        <v>455459</v>
       </c>
       <c r="R51" t="n">
-        <v>6773344</v>
+        <v>6773195</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6055,45 +6050,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129109151</v>
+        <v>129109267</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455459</v>
+        <v>455477</v>
       </c>
       <c r="R52" t="n">
-        <v>6773195</v>
+        <v>6773206</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6162,54 +6162,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129112645</v>
+        <v>129112375</v>
       </c>
       <c r="B53" t="n">
-        <v>58157</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103001</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455308</v>
+        <v>455269</v>
       </c>
       <c r="R53" t="n">
-        <v>6773282</v>
+        <v>6773288</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6278,45 +6269,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129112375</v>
+        <v>129112645</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>58157</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>103001</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455269</v>
+        <v>455308</v>
       </c>
       <c r="R54" t="n">
-        <v>6773288</v>
+        <v>6773282</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6388,7 +6388,7 @@
         <v>129113107</v>
       </c>
       <c r="B55" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>129114115</v>
       </c>
       <c r="B56" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>129114697</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>129110757</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129107474</v>
+        <v>129112093</v>
       </c>
       <c r="B62" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,39 +7150,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455385</v>
+        <v>455241</v>
       </c>
       <c r="R62" t="n">
-        <v>6773193</v>
+        <v>6773279</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7251,10 +7246,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129112093</v>
+        <v>129110960</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7286,10 +7281,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455241</v>
+        <v>455260</v>
       </c>
       <c r="R63" t="n">
-        <v>6773279</v>
+        <v>6773245</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7358,45 +7353,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129110960</v>
+        <v>129110475</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455260</v>
+        <v>455333</v>
       </c>
       <c r="R64" t="n">
-        <v>6773245</v>
+        <v>6773289</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7465,7 +7465,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129110475</v>
+        <v>129114704</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7494,21 +7494,16 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455333</v>
+        <v>455438</v>
       </c>
       <c r="R65" t="n">
-        <v>6773289</v>
+        <v>6773400</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7577,45 +7572,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129114704</v>
+        <v>129107474</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455438</v>
+        <v>455385</v>
       </c>
       <c r="R66" t="n">
-        <v>6773400</v>
+        <v>6773193</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7796,32 +7796,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129110941</v>
+        <v>129110844</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455281</v>
+        <v>455259</v>
       </c>
       <c r="R68" t="n">
-        <v>6773251</v>
+        <v>6773246</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7903,10 +7903,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129112114</v>
+        <v>129110941</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455233</v>
+        <v>455281</v>
       </c>
       <c r="R69" t="n">
-        <v>6773294</v>
+        <v>6773251</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8010,32 +8010,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129110844</v>
+        <v>129112114</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455259</v>
+        <v>455233</v>
       </c>
       <c r="R70" t="n">
-        <v>6773246</v>
+        <v>6773294</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8120,7 +8120,7 @@
         <v>129113854</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>129124330</v>
       </c>
       <c r="B72" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>129107854</v>
       </c>
       <c r="B73" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>129114483</v>
       </c>
       <c r="B74" t="n">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8552,10 +8552,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129110810</v>
+        <v>129112107</v>
       </c>
       <c r="B75" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8563,39 +8563,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455237</v>
+        <v>455235</v>
       </c>
       <c r="R75" t="n">
-        <v>6773232</v>
+        <v>6773290</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8664,10 +8659,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129112107</v>
+        <v>129110810</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8675,34 +8670,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455235</v>
+        <v>455237</v>
       </c>
       <c r="R76" t="n">
-        <v>6773290</v>
+        <v>6773232</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8886,7 +8886,7 @@
         <v>129107895</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>129109466</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,34 +9108,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R80" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9204,10 +9209,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9215,39 +9220,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R81" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9319,7 +9319,7 @@
         <v>129107617</v>
       </c>
       <c r="B82" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>129113130</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>129110007</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>129112739</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>129113900</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>129114734</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>129112774</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112804</v>
+        <v>129108187</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>79633</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455289</v>
+        <v>455412</v>
       </c>
       <c r="R5" t="n">
-        <v>6773299</v>
+        <v>6773172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129108187</v>
+        <v>129112804</v>
       </c>
       <c r="B7" t="n">
-        <v>79633</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455412</v>
+        <v>455289</v>
       </c>
       <c r="R7" t="n">
-        <v>6773172</v>
+        <v>6773299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129113882</v>
+        <v>129110825</v>
       </c>
       <c r="B8" t="n">
-        <v>97581</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455329</v>
+        <v>455259</v>
       </c>
       <c r="R8" t="n">
-        <v>6773342</v>
+        <v>6773246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129110825</v>
+        <v>129107453</v>
       </c>
       <c r="B9" t="n">
         <v>79043</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455259</v>
+        <v>455385</v>
       </c>
       <c r="R9" t="n">
-        <v>6773246</v>
+        <v>6773193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129107453</v>
+        <v>129109404</v>
       </c>
       <c r="B10" t="n">
         <v>79043</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455385</v>
+        <v>455484</v>
       </c>
       <c r="R10" t="n">
-        <v>6773193</v>
+        <v>6773211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129109404</v>
+        <v>129113163</v>
       </c>
       <c r="B11" t="n">
         <v>79043</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455484</v>
+        <v>455283</v>
       </c>
       <c r="R11" t="n">
-        <v>6773211</v>
+        <v>6773359</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129113163</v>
+        <v>129110737</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455283</v>
+        <v>455259</v>
       </c>
       <c r="R12" t="n">
-        <v>6773359</v>
+        <v>6773216</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129110737</v>
+        <v>129113882</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>97581</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455259</v>
+        <v>455329</v>
       </c>
       <c r="R13" t="n">
-        <v>6773216</v>
+        <v>6773342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129109713</v>
+        <v>129110813</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455494</v>
+        <v>455237</v>
       </c>
       <c r="R20" t="n">
-        <v>6773187</v>
+        <v>6773232</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129110813</v>
+        <v>129109713</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455237</v>
+        <v>455494</v>
       </c>
       <c r="R21" t="n">
-        <v>6773232</v>
+        <v>6773187</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4547,50 +4547,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129110522</v>
+        <v>129110861</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455304</v>
+        <v>455267</v>
       </c>
       <c r="R38" t="n">
-        <v>6773265</v>
+        <v>6773233</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4659,7 +4654,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129110861</v>
+        <v>129108956</v>
       </c>
       <c r="B39" t="n">
         <v>79043</v>
@@ -4694,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455267</v>
+        <v>455473</v>
       </c>
       <c r="R39" t="n">
-        <v>6773233</v>
+        <v>6773221</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4766,45 +4761,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129108956</v>
+        <v>129110522</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455473</v>
+        <v>455304</v>
       </c>
       <c r="R40" t="n">
-        <v>6773221</v>
+        <v>6773265</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129112093</v>
+        <v>129107474</v>
       </c>
       <c r="B62" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,34 +7150,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455241</v>
+        <v>455385</v>
       </c>
       <c r="R62" t="n">
-        <v>6773279</v>
+        <v>6773193</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7246,45 +7251,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129110960</v>
+        <v>129110475</v>
       </c>
       <c r="B63" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455260</v>
+        <v>455333</v>
       </c>
       <c r="R63" t="n">
-        <v>6773245</v>
+        <v>6773289</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7353,7 +7363,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129110475</v>
+        <v>129114704</v>
       </c>
       <c r="B64" t="n">
         <v>8450</v>
@@ -7382,21 +7392,16 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455333</v>
+        <v>455438</v>
       </c>
       <c r="R64" t="n">
-        <v>6773289</v>
+        <v>6773400</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7465,32 +7470,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129114704</v>
+        <v>129112093</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7500,10 +7505,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455438</v>
+        <v>455241</v>
       </c>
       <c r="R65" t="n">
-        <v>6773400</v>
+        <v>6773279</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7572,10 +7577,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129107474</v>
+        <v>129110960</v>
       </c>
       <c r="B66" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7583,39 +7588,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455385</v>
+        <v>455260</v>
       </c>
       <c r="R66" t="n">
-        <v>6773193</v>
+        <v>6773245</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7684,50 +7684,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129113193</v>
+        <v>129110844</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455283</v>
+        <v>455259</v>
       </c>
       <c r="R67" t="n">
-        <v>6773359</v>
+        <v>6773246</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7796,32 +7791,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129110844</v>
+        <v>129110941</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7831,10 +7826,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455259</v>
+        <v>455281</v>
       </c>
       <c r="R68" t="n">
-        <v>6773246</v>
+        <v>6773251</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7903,7 +7898,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129110941</v>
+        <v>129112114</v>
       </c>
       <c r="B69" t="n">
         <v>79043</v>
@@ -7938,10 +7933,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455281</v>
+        <v>455233</v>
       </c>
       <c r="R69" t="n">
-        <v>6773251</v>
+        <v>6773294</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8010,10 +8005,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129112114</v>
+        <v>129113193</v>
       </c>
       <c r="B70" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8021,34 +8016,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455233</v>
+        <v>455283</v>
       </c>
       <c r="R70" t="n">
-        <v>6773294</v>
+        <v>6773359</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129112610</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129112438</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129112479</v>
+        <v>129108044</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455272</v>
+        <v>455412</v>
       </c>
       <c r="R4" t="n">
-        <v>6773302</v>
+        <v>6773172</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129108187</v>
+        <v>129112479</v>
       </c>
       <c r="B5" t="n">
-        <v>79633</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455412</v>
+        <v>455272</v>
       </c>
       <c r="R5" t="n">
-        <v>6773172</v>
+        <v>6773302</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129108044</v>
+        <v>129108187</v>
       </c>
       <c r="B6" t="n">
-        <v>79662</v>
+        <v>79634</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129110825</v>
+        <v>129110737</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
         <v>455259</v>
       </c>
       <c r="R8" t="n">
-        <v>6773246</v>
+        <v>6773216</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129107453</v>
+        <v>129113882</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>97583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455385</v>
+        <v>455329</v>
       </c>
       <c r="R9" t="n">
-        <v>6773193</v>
+        <v>6773342</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129109404</v>
+        <v>129110825</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455484</v>
+        <v>455259</v>
       </c>
       <c r="R10" t="n">
-        <v>6773211</v>
+        <v>6773246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129113163</v>
+        <v>129107453</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455283</v>
+        <v>455385</v>
       </c>
       <c r="R11" t="n">
-        <v>6773359</v>
+        <v>6773193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129110737</v>
+        <v>129109404</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455259</v>
+        <v>455484</v>
       </c>
       <c r="R12" t="n">
-        <v>6773216</v>
+        <v>6773211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129113882</v>
+        <v>129113163</v>
       </c>
       <c r="B13" t="n">
-        <v>97581</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455329</v>
+        <v>455283</v>
       </c>
       <c r="R13" t="n">
-        <v>6773342</v>
+        <v>6773359</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
         <v>129107035</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129109078</v>
+        <v>129108219</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455467</v>
+        <v>455412</v>
       </c>
       <c r="R16" t="n">
-        <v>6773201</v>
+        <v>6773172</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129110979</v>
+        <v>129109078</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455258</v>
+        <v>455467</v>
       </c>
       <c r="R17" t="n">
-        <v>6773256</v>
+        <v>6773201</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129107916</v>
+        <v>129110979</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455389</v>
+        <v>455258</v>
       </c>
       <c r="R18" t="n">
-        <v>6773170</v>
+        <v>6773256</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,32 +2504,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129108219</v>
+        <v>129107916</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455412</v>
+        <v>455389</v>
       </c>
       <c r="R19" t="n">
-        <v>6773172</v>
+        <v>6773170</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2721,7 +2721,7 @@
         <v>129109713</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>129107601</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>129112407</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>129107736</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>129109613</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>129111088</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>129114098</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>129113094</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>129112885</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>129110462</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>129110782</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129110662</v>
+        <v>129109514</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,34 +4018,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455273</v>
+        <v>455494</v>
       </c>
       <c r="R33" t="n">
-        <v>6773208</v>
+        <v>6773187</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,10 +4119,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129106783</v>
+        <v>129107986</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>78801</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4125,21 +4130,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4149,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455407</v>
+        <v>455389</v>
       </c>
       <c r="R34" t="n">
-        <v>6773196</v>
+        <v>6773170</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4221,10 +4226,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129110692</v>
+        <v>129110662</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,13 +4261,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455270</v>
+        <v>455273</v>
       </c>
       <c r="R35" t="n">
-        <v>6773216</v>
+        <v>6773208</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4328,10 +4333,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129107986</v>
+        <v>129106783</v>
       </c>
       <c r="B36" t="n">
-        <v>78800</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4339,21 +4344,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4363,10 +4368,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455389</v>
+        <v>455407</v>
       </c>
       <c r="R36" t="n">
-        <v>6773170</v>
+        <v>6773196</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4435,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129109514</v>
+        <v>129110692</v>
       </c>
       <c r="B37" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4446,42 +4451,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455494</v>
+        <v>455270</v>
       </c>
       <c r="R37" t="n">
-        <v>6773187</v>
+        <v>6773216</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>129110861</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>129108956</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129114507</v>
+        <v>129107072</v>
       </c>
       <c r="B41" t="n">
-        <v>79043</v>
+        <v>79634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455391</v>
+        <v>455389</v>
       </c>
       <c r="R41" t="n">
-        <v>6773367</v>
+        <v>6773203</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,10 +4980,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129107679</v>
+        <v>129114507</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455353</v>
+        <v>455391</v>
       </c>
       <c r="R42" t="n">
-        <v>6773191</v>
+        <v>6773367</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129110029</v>
+        <v>129107679</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455333</v>
+        <v>455353</v>
       </c>
       <c r="R43" t="n">
-        <v>6773241</v>
+        <v>6773191</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129107072</v>
+        <v>129110029</v>
       </c>
       <c r="B44" t="n">
-        <v>79633</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455389</v>
+        <v>455333</v>
       </c>
       <c r="R44" t="n">
-        <v>6773203</v>
+        <v>6773241</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5304,7 +5304,7 @@
         <v>129109327</v>
       </c>
       <c r="B45" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>129109369</v>
       </c>
       <c r="B46" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>129112595</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>129112827</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>129110148</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>129114165</v>
       </c>
       <c r="B50" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>129109151</v>
       </c>
       <c r="B51" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6162,45 +6162,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129112375</v>
+        <v>129112645</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>58157</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>103001</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455269</v>
+        <v>455308</v>
       </c>
       <c r="R53" t="n">
-        <v>6773288</v>
+        <v>6773282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6269,54 +6278,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129112645</v>
+        <v>129112375</v>
       </c>
       <c r="B54" t="n">
-        <v>58157</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103001</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455308</v>
+        <v>455269</v>
       </c>
       <c r="R54" t="n">
-        <v>6773282</v>
+        <v>6773288</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6385,32 +6385,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129113107</v>
+        <v>129112005</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455308</v>
+        <v>455235</v>
       </c>
       <c r="R55" t="n">
-        <v>6773336</v>
+        <v>6773290</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6492,32 +6492,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129114115</v>
+        <v>129110915</v>
       </c>
       <c r="B56" t="n">
-        <v>83011</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455394</v>
+        <v>455267</v>
       </c>
       <c r="R56" t="n">
-        <v>6773349</v>
+        <v>6773233</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6599,45 +6599,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129114697</v>
+        <v>129108995</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455428</v>
+        <v>455473</v>
       </c>
       <c r="R57" t="n">
-        <v>6773376</v>
+        <v>6773221</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,10 +6711,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129110757</v>
+        <v>129113107</v>
       </c>
       <c r="B58" t="n">
-        <v>79043</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6717,21 +6722,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6741,10 +6746,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455252</v>
+        <v>455308</v>
       </c>
       <c r="R58" t="n">
-        <v>6773222</v>
+        <v>6773336</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6813,32 +6818,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129112005</v>
+        <v>129114115</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>83012</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6848,13 +6853,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455235</v>
+        <v>455394</v>
       </c>
       <c r="R59" t="n">
-        <v>6773290</v>
+        <v>6773349</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6920,32 +6925,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129110915</v>
+        <v>129114697</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6955,10 +6960,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455267</v>
+        <v>455428</v>
       </c>
       <c r="R60" t="n">
-        <v>6773233</v>
+        <v>6773376</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7027,50 +7032,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129108995</v>
+        <v>129110757</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455473</v>
+        <v>455252</v>
       </c>
       <c r="R61" t="n">
-        <v>6773221</v>
+        <v>6773222</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7473,7 +7473,7 @@
         <v>129112093</v>
       </c>
       <c r="B65" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>129110960</v>
       </c>
       <c r="B66" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7684,32 +7684,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129110844</v>
+        <v>129110941</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455259</v>
+        <v>455281</v>
       </c>
       <c r="R67" t="n">
-        <v>6773246</v>
+        <v>6773251</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,10 +7791,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129110941</v>
+        <v>129112114</v>
       </c>
       <c r="B68" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7826,10 +7826,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455281</v>
+        <v>455233</v>
       </c>
       <c r="R68" t="n">
-        <v>6773251</v>
+        <v>6773294</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7898,10 +7898,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129112114</v>
+        <v>129113193</v>
       </c>
       <c r="B69" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7909,34 +7909,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455233</v>
+        <v>455283</v>
       </c>
       <c r="R69" t="n">
-        <v>6773294</v>
+        <v>6773359</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8005,50 +8010,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129113193</v>
+        <v>129110844</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455283</v>
+        <v>455259</v>
       </c>
       <c r="R70" t="n">
-        <v>6773359</v>
+        <v>6773246</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8120,7 +8120,7 @@
         <v>129113854</v>
       </c>
       <c r="B71" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>129124330</v>
       </c>
       <c r="B72" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>129107854</v>
       </c>
       <c r="B73" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>129114483</v>
       </c>
       <c r="B74" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>129112107</v>
       </c>
       <c r="B75" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>129107895</v>
       </c>
       <c r="B78" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>129109466</v>
       </c>
       <c r="B79" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>129109225</v>
       </c>
       <c r="B81" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>129107617</v>
       </c>
       <c r="B82" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>129113130</v>
       </c>
       <c r="B83" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>129110007</v>
       </c>
       <c r="B87" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>129112739</v>
       </c>
       <c r="B88" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>129113900</v>
       </c>
       <c r="B89" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>129114734</v>
       </c>
       <c r="B90" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>129112774</v>
       </c>
       <c r="B92" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AY125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129108044</v>
+        <v>129112479</v>
       </c>
       <c r="B4" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455412</v>
+        <v>455272</v>
       </c>
       <c r="R4" t="n">
-        <v>6773172</v>
+        <v>6773302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112479</v>
+        <v>129108044</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455272</v>
+        <v>455412</v>
       </c>
       <c r="R5" t="n">
-        <v>6773302</v>
+        <v>6773172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129108187</v>
+        <v>129112804</v>
       </c>
       <c r="B6" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455412</v>
+        <v>455289</v>
       </c>
       <c r="R6" t="n">
-        <v>6773172</v>
+        <v>6773299</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129112804</v>
+        <v>129108187</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>79634</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,39 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455289</v>
+        <v>455412</v>
       </c>
       <c r="R7" t="n">
-        <v>6773299</v>
+        <v>6773172</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129110737</v>
+        <v>129110825</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
         <v>455259</v>
       </c>
       <c r="R8" t="n">
-        <v>6773216</v>
+        <v>6773246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129113882</v>
+        <v>129107453</v>
       </c>
       <c r="B9" t="n">
-        <v>97583</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455329</v>
+        <v>455385</v>
       </c>
       <c r="R9" t="n">
-        <v>6773342</v>
+        <v>6773193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129110825</v>
+        <v>129109404</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455259</v>
+        <v>455484</v>
       </c>
       <c r="R10" t="n">
-        <v>6773246</v>
+        <v>6773211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129107453</v>
+        <v>129113163</v>
       </c>
       <c r="B11" t="n">
         <v>79044</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455385</v>
+        <v>455283</v>
       </c>
       <c r="R11" t="n">
-        <v>6773193</v>
+        <v>6773359</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129109404</v>
+        <v>129110737</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455484</v>
+        <v>455259</v>
       </c>
       <c r="R12" t="n">
-        <v>6773211</v>
+        <v>6773216</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129113163</v>
+        <v>129113882</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>97587</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455283</v>
+        <v>455329</v>
       </c>
       <c r="R13" t="n">
-        <v>6773359</v>
+        <v>6773342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2183,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129108219</v>
+        <v>129109078</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455412</v>
+        <v>455467</v>
       </c>
       <c r="R16" t="n">
-        <v>6773172</v>
+        <v>6773201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129109078</v>
+        <v>129110979</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455467</v>
+        <v>455258</v>
       </c>
       <c r="R17" t="n">
-        <v>6773201</v>
+        <v>6773256</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129110979</v>
+        <v>129107916</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455258</v>
+        <v>455389</v>
       </c>
       <c r="R18" t="n">
-        <v>6773256</v>
+        <v>6773170</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,32 +2504,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129107916</v>
+        <v>129108219</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455389</v>
+        <v>455412</v>
       </c>
       <c r="R19" t="n">
-        <v>6773170</v>
+        <v>6773172</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129110813</v>
+        <v>129109713</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455237</v>
+        <v>455494</v>
       </c>
       <c r="R20" t="n">
-        <v>6773232</v>
+        <v>6773187</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129109713</v>
+        <v>129110813</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455494</v>
+        <v>455237</v>
       </c>
       <c r="R21" t="n">
-        <v>6773187</v>
+        <v>6773232</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129109514</v>
+        <v>129110662</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,39 +4018,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455494</v>
+        <v>455273</v>
       </c>
       <c r="R33" t="n">
-        <v>6773187</v>
+        <v>6773208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4119,10 +4114,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129107986</v>
+        <v>129106783</v>
       </c>
       <c r="B34" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4130,21 +4125,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4154,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455389</v>
+        <v>455407</v>
       </c>
       <c r="R34" t="n">
-        <v>6773170</v>
+        <v>6773196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4226,7 +4221,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129110662</v>
+        <v>129110692</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4261,13 +4256,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455273</v>
+        <v>455270</v>
       </c>
       <c r="R35" t="n">
-        <v>6773208</v>
+        <v>6773216</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4333,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129106783</v>
+        <v>129109514</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,34 +4339,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455407</v>
+        <v>455494</v>
       </c>
       <c r="R36" t="n">
-        <v>6773196</v>
+        <v>6773187</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129110692</v>
+        <v>129107986</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455270</v>
+        <v>455389</v>
       </c>
       <c r="R37" t="n">
-        <v>6773216</v>
+        <v>6773170</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129107474</v>
+        <v>129112093</v>
       </c>
       <c r="B62" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,39 +7150,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455385</v>
+        <v>455241</v>
       </c>
       <c r="R62" t="n">
-        <v>6773193</v>
+        <v>6773279</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7251,50 +7246,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129110475</v>
+        <v>129110960</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455333</v>
+        <v>455260</v>
       </c>
       <c r="R63" t="n">
-        <v>6773289</v>
+        <v>6773245</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7363,45 +7353,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129114704</v>
+        <v>129107474</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455438</v>
+        <v>455385</v>
       </c>
       <c r="R64" t="n">
-        <v>6773400</v>
+        <v>6773193</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7470,45 +7465,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129112093</v>
+        <v>129110475</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455241</v>
+        <v>455333</v>
       </c>
       <c r="R65" t="n">
-        <v>6773279</v>
+        <v>6773289</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7577,32 +7577,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129110960</v>
+        <v>129114704</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455260</v>
+        <v>455438</v>
       </c>
       <c r="R66" t="n">
-        <v>6773245</v>
+        <v>6773400</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7684,32 +7684,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129110941</v>
+        <v>129110844</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455281</v>
+        <v>455259</v>
       </c>
       <c r="R67" t="n">
-        <v>6773251</v>
+        <v>6773246</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129112114</v>
+        <v>129110941</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7826,10 +7826,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455233</v>
+        <v>455281</v>
       </c>
       <c r="R68" t="n">
-        <v>6773294</v>
+        <v>6773251</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7898,10 +7898,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129113193</v>
+        <v>129112114</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7909,39 +7909,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455283</v>
+        <v>455233</v>
       </c>
       <c r="R69" t="n">
-        <v>6773359</v>
+        <v>6773294</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8010,45 +8005,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129110844</v>
+        <v>129113193</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455259</v>
+        <v>455283</v>
       </c>
       <c r="R70" t="n">
-        <v>6773246</v>
+        <v>6773359</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8117,10 +8117,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129113854</v>
+        <v>129124330</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>92869</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8128,34 +8128,41 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455337</v>
+        <v>455412</v>
       </c>
       <c r="R71" t="n">
-        <v>6773325</v>
+        <v>6773178</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8185,27 +8192,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8224,10 +8222,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124330</v>
+        <v>129113854</v>
       </c>
       <c r="B72" t="n">
-        <v>92865</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8235,41 +8233,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455412</v>
+        <v>455337</v>
       </c>
       <c r="R72" t="n">
-        <v>6773178</v>
+        <v>6773325</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8299,18 +8290,27 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8436,51 +8436,53 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129114483</v>
+        <v>129110810</v>
       </c>
       <c r="B74" t="n">
-        <v>90927</v>
+        <v>57724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455394</v>
+        <v>455237</v>
       </c>
       <c r="R74" t="n">
-        <v>6773349</v>
+        <v>6773232</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8522,18 +8524,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8659,53 +8655,51 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129110810</v>
+        <v>129114483</v>
       </c>
       <c r="B76" t="n">
-        <v>57724</v>
+        <v>90931</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455237</v>
+        <v>455394</v>
       </c>
       <c r="R76" t="n">
-        <v>6773232</v>
+        <v>6773349</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8747,12 +8741,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,39 +9108,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R80" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9209,10 +9204,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9220,34 +9215,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R81" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10515,6 +10515,3422 @@
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129516242</v>
+      </c>
+      <c r="B93" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>455380</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6773669</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129516232</v>
+      </c>
+      <c r="B94" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>455380</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6773633</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129516224</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>455383</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6773634</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129516251</v>
+      </c>
+      <c r="B96" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>455481</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6773645</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>129516243</v>
+      </c>
+      <c r="B97" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>455377</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6773671</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129516248</v>
+      </c>
+      <c r="B98" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>455414</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6773624</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129516249</v>
+      </c>
+      <c r="B99" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>455432</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6773615</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>129516237</v>
+      </c>
+      <c r="B100" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>455395</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6773693</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129516236</v>
+      </c>
+      <c r="B101" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>455443</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6773653</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>129516220</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79663</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>455424</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6773664</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>129516245</v>
+      </c>
+      <c r="B103" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>455365</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6773649</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>129516229</v>
+      </c>
+      <c r="B104" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>455351</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6773588</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Död höna nyligen slagen</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129516253</v>
+      </c>
+      <c r="B105" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>455476</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6773655</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>129516247</v>
+      </c>
+      <c r="B106" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>455382</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6773633</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>129516271</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>455378</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6773718</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129516241</v>
+      </c>
+      <c r="B108" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>455391</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6773687</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>129516240</v>
+      </c>
+      <c r="B109" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>455369</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6773717</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>129516235</v>
+      </c>
+      <c r="B110" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>455444</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6773639</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>129516272</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>455357</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6773686</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>129516226</v>
+      </c>
+      <c r="B112" t="n">
+        <v>91500</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>112</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>455448</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6773621</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>129516227</v>
+      </c>
+      <c r="B113" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>455382</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6773594</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>129516252</v>
+      </c>
+      <c r="B114" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>455472</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6773649</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>129516231</v>
+      </c>
+      <c r="B115" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>455353</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6773643</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>129516275</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>455381</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6773638</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>129516228</v>
+      </c>
+      <c r="B117" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>455480</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6773643</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129516238</v>
+      </c>
+      <c r="B118" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>455392</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6773703</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>129516239</v>
+      </c>
+      <c r="B119" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>455382</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6773720</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>129516234</v>
+      </c>
+      <c r="B120" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>455459</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6773658</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>129516270</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>455383</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6773719</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>129516222</v>
+      </c>
+      <c r="B122" t="n">
+        <v>79634</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>455510</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6773641</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>129516223</v>
+      </c>
+      <c r="B123" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>455394</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6773684</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>129516277</v>
+      </c>
+      <c r="B124" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>455410</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6773604</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>129516274</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Kurutjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>455353</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6773642</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY125"/>
+  <dimension ref="A1:AY177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112610</v>
+        <v>129112804</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455308</v>
+        <v>455289</v>
       </c>
       <c r="R2" t="n">
-        <v>6773282</v>
+        <v>6773299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129112438</v>
+        <v>129108044</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455258</v>
+        <v>455412</v>
       </c>
       <c r="R3" t="n">
-        <v>6773321</v>
+        <v>6773172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129112479</v>
+        <v>129108187</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455272</v>
+        <v>455412</v>
       </c>
       <c r="R4" t="n">
-        <v>6773302</v>
+        <v>6773172</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129108044</v>
+        <v>129112610</v>
       </c>
       <c r="B5" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455412</v>
+        <v>455308</v>
       </c>
       <c r="R5" t="n">
-        <v>6773172</v>
+        <v>6773282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129112804</v>
+        <v>129112438</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455289</v>
+        <v>455258</v>
       </c>
       <c r="R6" t="n">
-        <v>6773299</v>
+        <v>6773321</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129108187</v>
+        <v>129112479</v>
       </c>
       <c r="B7" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455412</v>
+        <v>455272</v>
       </c>
       <c r="R7" t="n">
-        <v>6773172</v>
+        <v>6773302</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129110737</v>
+        <v>129113882</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>97595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455259</v>
+        <v>455329</v>
       </c>
       <c r="R12" t="n">
-        <v>6773216</v>
+        <v>6773342</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129113882</v>
+        <v>129110737</v>
       </c>
       <c r="B13" t="n">
-        <v>97587</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455329</v>
+        <v>455259</v>
       </c>
       <c r="R13" t="n">
-        <v>6773342</v>
+        <v>6773216</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129109713</v>
+        <v>129110813</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455494</v>
+        <v>455237</v>
       </c>
       <c r="R20" t="n">
-        <v>6773187</v>
+        <v>6773232</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129110813</v>
+        <v>129109713</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455237</v>
+        <v>455494</v>
       </c>
       <c r="R21" t="n">
-        <v>6773232</v>
+        <v>6773187</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -6385,32 +6385,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129112005</v>
+        <v>129113107</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455235</v>
+        <v>455308</v>
       </c>
       <c r="R55" t="n">
-        <v>6773290</v>
+        <v>6773336</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6492,32 +6492,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129110915</v>
+        <v>129114115</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>83012</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455267</v>
+        <v>455394</v>
       </c>
       <c r="R56" t="n">
-        <v>6773233</v>
+        <v>6773349</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6599,50 +6599,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129108995</v>
+        <v>129114697</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455473</v>
+        <v>455428</v>
       </c>
       <c r="R57" t="n">
-        <v>6773221</v>
+        <v>6773376</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6711,10 +6706,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129113107</v>
+        <v>129110757</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6722,21 +6717,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6746,10 +6741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455308</v>
+        <v>455252</v>
       </c>
       <c r="R58" t="n">
-        <v>6773336</v>
+        <v>6773222</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6818,32 +6813,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129114115</v>
+        <v>129112005</v>
       </c>
       <c r="B59" t="n">
-        <v>83012</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6853,13 +6848,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455394</v>
+        <v>455235</v>
       </c>
       <c r="R59" t="n">
-        <v>6773349</v>
+        <v>6773290</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6925,32 +6920,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129114697</v>
+        <v>129110915</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6960,10 +6955,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455428</v>
+        <v>455267</v>
       </c>
       <c r="R60" t="n">
-        <v>6773376</v>
+        <v>6773233</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7032,45 +7027,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129110757</v>
+        <v>129108995</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455252</v>
+        <v>455473</v>
       </c>
       <c r="R61" t="n">
-        <v>6773222</v>
+        <v>6773221</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7353,38 +7353,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129107474</v>
+        <v>129110475</v>
       </c>
       <c r="B64" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455385</v>
+        <v>455333</v>
       </c>
       <c r="R64" t="n">
-        <v>6773193</v>
+        <v>6773289</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7465,7 +7465,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129110475</v>
+        <v>129114704</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7494,21 +7494,16 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455333</v>
+        <v>455438</v>
       </c>
       <c r="R65" t="n">
-        <v>6773289</v>
+        <v>6773400</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7577,45 +7572,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129114704</v>
+        <v>129107474</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455438</v>
+        <v>455385</v>
       </c>
       <c r="R66" t="n">
-        <v>6773400</v>
+        <v>6773193</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7684,32 +7684,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129110844</v>
+        <v>129110941</v>
       </c>
       <c r="B67" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455259</v>
+        <v>455281</v>
       </c>
       <c r="R67" t="n">
-        <v>6773246</v>
+        <v>6773251</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129110941</v>
+        <v>129112114</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7826,10 +7826,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455281</v>
+        <v>455233</v>
       </c>
       <c r="R68" t="n">
-        <v>6773251</v>
+        <v>6773294</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7898,10 +7898,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129112114</v>
+        <v>129113193</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7909,34 +7909,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455233</v>
+        <v>455283</v>
       </c>
       <c r="R69" t="n">
-        <v>6773294</v>
+        <v>6773359</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8005,50 +8010,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129113193</v>
+        <v>129110844</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455283</v>
+        <v>455259</v>
       </c>
       <c r="R70" t="n">
-        <v>6773359</v>
+        <v>6773246</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8120,7 +8120,7 @@
         <v>129124330</v>
       </c>
       <c r="B71" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8436,10 +8436,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129110810</v>
+        <v>129112107</v>
       </c>
       <c r="B74" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8447,39 +8447,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455237</v>
+        <v>455235</v>
       </c>
       <c r="R74" t="n">
-        <v>6773232</v>
+        <v>6773290</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8548,10 +8543,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129112107</v>
+        <v>129110810</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8559,34 +8554,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455235</v>
+        <v>455237</v>
       </c>
       <c r="R75" t="n">
-        <v>6773290</v>
+        <v>6773232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8658,7 +8658,7 @@
         <v>129114483</v>
       </c>
       <c r="B76" t="n">
-        <v>90931</v>
+        <v>90932</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,34 +9108,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R80" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9204,10 +9209,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9215,39 +9220,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R81" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10517,44 +10517,35 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129516242</v>
+        <v>129516232</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>92870</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
@@ -10564,7 +10555,7 @@
         <v>455380</v>
       </c>
       <c r="R93" t="n">
-        <v>6773669</v>
+        <v>6773633</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10605,7 +10596,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10624,35 +10614,44 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129516232</v>
+        <v>129516242</v>
       </c>
       <c r="B94" t="n">
-        <v>92869</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
@@ -10662,7 +10661,7 @@
         <v>455380</v>
       </c>
       <c r="R94" t="n">
-        <v>6773633</v>
+        <v>6773669</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10703,6 +10702,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10721,40 +10721,41 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129516224</v>
+        <v>129516251</v>
       </c>
       <c r="B95" t="n">
-        <v>57887</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10764,10 +10765,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>455383</v>
+        <v>455481</v>
       </c>
       <c r="R95" t="n">
-        <v>6773634</v>
+        <v>6773645</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10808,6 +10809,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10826,41 +10828,40 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129516251</v>
+        <v>129516224</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>57887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10870,10 +10871,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>455481</v>
+        <v>455383</v>
       </c>
       <c r="R96" t="n">
-        <v>6773645</v>
+        <v>6773634</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10914,7 +10915,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11885,54 +11885,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129516247</v>
+        <v>129516271</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>455382</v>
+        <v>455378</v>
       </c>
       <c r="R106" t="n">
-        <v>6773633</v>
+        <v>6773718</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11973,7 +11964,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11992,45 +11982,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129516271</v>
+        <v>129516247</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>455378</v>
+        <v>455382</v>
       </c>
       <c r="R107" t="n">
-        <v>6773718</v>
+        <v>6773633</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12071,6 +12070,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>129516226</v>
       </c>
       <c r="B112" t="n">
-        <v>91500</v>
+        <v>91501</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12604,40 +12604,41 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129516227</v>
+        <v>129516252</v>
       </c>
       <c r="B113" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12647,10 +12648,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>455382</v>
+        <v>455472</v>
       </c>
       <c r="R113" t="n">
-        <v>6773594</v>
+        <v>6773649</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12691,6 +12692,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12709,41 +12711,40 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129516252</v>
+        <v>129516227</v>
       </c>
       <c r="B114" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12753,10 +12754,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455472</v>
+        <v>455382</v>
       </c>
       <c r="R114" t="n">
-        <v>6773649</v>
+        <v>6773594</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12797,7 +12798,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12819,7 +12819,7 @@
         <v>129516231</v>
       </c>
       <c r="B115" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13436,10 +13436,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129516270</v>
+        <v>129516222</v>
       </c>
       <c r="B121" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13447,21 +13447,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>455383</v>
+        <v>455510</v>
       </c>
       <c r="R121" t="n">
-        <v>6773719</v>
+        <v>6773641</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13533,10 +13533,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129516222</v>
+        <v>129516270</v>
       </c>
       <c r="B122" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13544,21 +13544,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13568,10 +13568,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>455510</v>
+        <v>455383</v>
       </c>
       <c r="R122" t="n">
-        <v>6773641</v>
+        <v>6773719</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13931,6 +13931,5709 @@
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>129525056</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>455743</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6773438</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>129520976</v>
+      </c>
+      <c r="B127" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>455562</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6773304</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>129524323</v>
+      </c>
+      <c r="B128" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>455677</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6773324</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>129520384</v>
+      </c>
+      <c r="B129" t="n">
+        <v>79663</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>455530</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6773282</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129520392</v>
+      </c>
+      <c r="B130" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>455530</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6773282</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129520126</v>
+      </c>
+      <c r="B131" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>455494</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6773317</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>129524264</v>
+      </c>
+      <c r="B132" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>455687</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6773304</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>129522291</v>
+      </c>
+      <c r="B133" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>455660</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6773320</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>129521661</v>
+      </c>
+      <c r="B134" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>455547</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6773313</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i äldre tallar samt gran</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>129524757</v>
+      </c>
+      <c r="B135" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>455745</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6773387</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>129524992</v>
+      </c>
+      <c r="B136" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>455715</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6773435</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>129524157</v>
+      </c>
+      <c r="B137" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>455658</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6773278</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>129524794</v>
+      </c>
+      <c r="B138" t="n">
+        <v>79663</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>455725</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6773375</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>129521094</v>
+      </c>
+      <c r="B139" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>455547</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6773313</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>129522884</v>
+      </c>
+      <c r="B140" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>455654</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6773335</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>129524463</v>
+      </c>
+      <c r="B141" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>455664</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6773257</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>129522915</v>
+      </c>
+      <c r="B142" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>455660</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6773320</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>129522761</v>
+      </c>
+      <c r="B143" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>455639</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6773364</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>129525475</v>
+      </c>
+      <c r="B144" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>455623</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6773393</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>129522134</v>
+      </c>
+      <c r="B145" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>455646</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6773308</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>129520408</v>
+      </c>
+      <c r="B146" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>455524</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6773304</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>129520906</v>
+      </c>
+      <c r="B147" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>455570</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6773300</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>129525079</v>
+      </c>
+      <c r="B148" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>455743</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6773438</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>129520622</v>
+      </c>
+      <c r="B149" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>455540</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6773296</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>129524776</v>
+      </c>
+      <c r="B150" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>455745</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6773387</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>129525476</v>
+      </c>
+      <c r="B151" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>455623</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6773393</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>129524645</v>
+      </c>
+      <c r="B152" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>455677</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6773324</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>129521282</v>
+      </c>
+      <c r="B153" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>455537</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6773309</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>129524704</v>
+      </c>
+      <c r="B154" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>455681</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6773324</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>129522797</v>
+      </c>
+      <c r="B155" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>455650</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6773365</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>129525097</v>
+      </c>
+      <c r="B156" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>455756</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6773423</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>129520463</v>
+      </c>
+      <c r="B157" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>455514</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6773311</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>129520135</v>
+      </c>
+      <c r="B158" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>455497</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6773300</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>129521090</v>
+      </c>
+      <c r="B159" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>455547</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6773313</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>129522366</v>
+      </c>
+      <c r="B160" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>455660</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6773320</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Rikligt i synfältet, radie på ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>129522130</v>
+      </c>
+      <c r="B161" t="n">
+        <v>79663</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>455646</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6773308</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>129520605</v>
+      </c>
+      <c r="B162" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>455537</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6773309</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>129524253</v>
+      </c>
+      <c r="B163" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>455687</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6773304</v>
+      </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>129520400</v>
+      </c>
+      <c r="B164" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>455528</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6773294</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>129520768</v>
+      </c>
+      <c r="B165" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>455562</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6773304</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>129524860</v>
+      </c>
+      <c r="B166" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>455743</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6773384</v>
+      </c>
+      <c r="S166" t="n">
+        <v>10</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>129522648</v>
+      </c>
+      <c r="B167" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>455650</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6773365</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>129521993</v>
+      </c>
+      <c r="B168" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>455615</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6773317</v>
+      </c>
+      <c r="S168" t="n">
+        <v>50</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>129525452</v>
+      </c>
+      <c r="B169" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>455677</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6773354</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>129524742</v>
+      </c>
+      <c r="B170" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>455747</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6773363</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>129524269</v>
+      </c>
+      <c r="B171" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>455687</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6773304</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>129520910</v>
+      </c>
+      <c r="B172" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>455570</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6773300</v>
+      </c>
+      <c r="S172" t="n">
+        <v>10</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>129520755</v>
+      </c>
+      <c r="B173" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>455550</v>
+      </c>
+      <c r="R173" t="n">
+        <v>6773288</v>
+      </c>
+      <c r="S173" t="n">
+        <v>10</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Vedsvamp på låga bredvid</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>129520654</v>
+      </c>
+      <c r="B174" t="n">
+        <v>79663</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>455559</v>
+      </c>
+      <c r="R174" t="n">
+        <v>6773284</v>
+      </c>
+      <c r="S174" t="n">
+        <v>10</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>129524675</v>
+      </c>
+      <c r="B175" t="n">
+        <v>91571</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>455677</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6773324</v>
+      </c>
+      <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>129524033</v>
+      </c>
+      <c r="B176" t="n">
+        <v>92832</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>455658</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6773278</v>
+      </c>
+      <c r="S176" t="n">
+        <v>10</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>129520115</v>
+      </c>
+      <c r="B177" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>455499</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6773331</v>
+      </c>
+      <c r="S177" t="n">
+        <v>50</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>1 bild</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112804</v>
+        <v>129108187</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>79634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455289</v>
+        <v>455412</v>
       </c>
       <c r="R2" t="n">
-        <v>6773299</v>
+        <v>6773172</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129108187</v>
+        <v>129112804</v>
       </c>
       <c r="B4" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455412</v>
+        <v>455289</v>
       </c>
       <c r="R4" t="n">
-        <v>6773172</v>
+        <v>6773299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129110825</v>
+        <v>129110737</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
         <v>455259</v>
       </c>
       <c r="R8" t="n">
-        <v>6773246</v>
+        <v>6773216</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129107453</v>
+        <v>129113163</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455385</v>
+        <v>455283</v>
       </c>
       <c r="R9" t="n">
-        <v>6773193</v>
+        <v>6773359</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129109404</v>
+        <v>129110825</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455484</v>
+        <v>455259</v>
       </c>
       <c r="R10" t="n">
-        <v>6773211</v>
+        <v>6773246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129113163</v>
+        <v>129107453</v>
       </c>
       <c r="B11" t="n">
         <v>79044</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455283</v>
+        <v>455385</v>
       </c>
       <c r="R11" t="n">
-        <v>6773359</v>
+        <v>6773193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129113882</v>
+        <v>129109404</v>
       </c>
       <c r="B12" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455329</v>
+        <v>455484</v>
       </c>
       <c r="R12" t="n">
-        <v>6773342</v>
+        <v>6773211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129110737</v>
+        <v>129113882</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>97595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455259</v>
+        <v>455329</v>
       </c>
       <c r="R13" t="n">
-        <v>6773216</v>
+        <v>6773342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129110813</v>
+        <v>129109713</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455237</v>
+        <v>455494</v>
       </c>
       <c r="R20" t="n">
-        <v>6773232</v>
+        <v>6773187</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129109713</v>
+        <v>129110813</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455494</v>
+        <v>455237</v>
       </c>
       <c r="R21" t="n">
-        <v>6773187</v>
+        <v>6773232</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129107601</v>
+        <v>129112407</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455352</v>
+        <v>455248</v>
       </c>
       <c r="R22" t="n">
-        <v>6773200</v>
+        <v>6773310</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129112407</v>
+        <v>129109613</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455248</v>
+        <v>455494</v>
       </c>
       <c r="R23" t="n">
-        <v>6773310</v>
+        <v>6773197</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129107736</v>
+        <v>129114098</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455372</v>
+        <v>455394</v>
       </c>
       <c r="R24" t="n">
-        <v>6773181</v>
+        <v>6773349</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129109613</v>
+        <v>129113094</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455494</v>
+        <v>455301</v>
       </c>
       <c r="R25" t="n">
-        <v>6773197</v>
+        <v>6773331</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129111088</v>
+        <v>129107601</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455248</v>
+        <v>455352</v>
       </c>
       <c r="R26" t="n">
-        <v>6773274</v>
+        <v>6773200</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129114098</v>
+        <v>129111088</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455394</v>
+        <v>455248</v>
       </c>
       <c r="R27" t="n">
-        <v>6773349</v>
+        <v>6773274</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129113094</v>
+        <v>129107736</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3502,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455301</v>
+        <v>455372</v>
       </c>
       <c r="R28" t="n">
-        <v>6773331</v>
+        <v>6773181</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4221,10 +4221,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129110692</v>
+        <v>129109514</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,37 +4232,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455270</v>
+        <v>455494</v>
       </c>
       <c r="R35" t="n">
-        <v>6773216</v>
+        <v>6773187</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4328,10 +4333,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129109514</v>
+        <v>129107986</v>
       </c>
       <c r="B36" t="n">
-        <v>57724</v>
+        <v>78801</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4339,39 +4344,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455494</v>
+        <v>455389</v>
       </c>
       <c r="R36" t="n">
-        <v>6773187</v>
+        <v>6773170</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129107986</v>
+        <v>129110692</v>
       </c>
       <c r="B37" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455389</v>
+        <v>455270</v>
       </c>
       <c r="R37" t="n">
-        <v>6773170</v>
+        <v>6773216</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129107072</v>
+        <v>129114507</v>
       </c>
       <c r="B41" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455389</v>
+        <v>455391</v>
       </c>
       <c r="R41" t="n">
-        <v>6773203</v>
+        <v>6773367</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129114507</v>
+        <v>129107679</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455391</v>
+        <v>455353</v>
       </c>
       <c r="R42" t="n">
-        <v>6773367</v>
+        <v>6773191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129107679</v>
+        <v>129110029</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455353</v>
+        <v>455333</v>
       </c>
       <c r="R43" t="n">
-        <v>6773191</v>
+        <v>6773241</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129110029</v>
+        <v>129107072</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455333</v>
+        <v>455389</v>
       </c>
       <c r="R44" t="n">
-        <v>6773241</v>
+        <v>6773203</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129109327</v>
+        <v>129112595</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455477</v>
+        <v>455279</v>
       </c>
       <c r="R45" t="n">
-        <v>6773206</v>
+        <v>6773275</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129109369</v>
+        <v>129109327</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455473</v>
+        <v>455477</v>
       </c>
       <c r="R46" t="n">
-        <v>6773219</v>
+        <v>6773206</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129112595</v>
+        <v>129109369</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455279</v>
+        <v>455473</v>
       </c>
       <c r="R47" t="n">
-        <v>6773275</v>
+        <v>6773219</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6162,54 +6162,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129112645</v>
+        <v>129112375</v>
       </c>
       <c r="B53" t="n">
-        <v>58157</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103001</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455308</v>
+        <v>455269</v>
       </c>
       <c r="R53" t="n">
-        <v>6773282</v>
+        <v>6773288</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6278,45 +6269,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129112375</v>
+        <v>129112645</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>58157</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>103001</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455269</v>
+        <v>455308</v>
       </c>
       <c r="R54" t="n">
-        <v>6773288</v>
+        <v>6773282</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6385,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129113107</v>
+        <v>129114697</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,21 +6396,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455308</v>
+        <v>455428</v>
       </c>
       <c r="R55" t="n">
-        <v>6773336</v>
+        <v>6773376</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6492,10 +6492,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129114115</v>
+        <v>129113107</v>
       </c>
       <c r="B56" t="n">
-        <v>83012</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,21 +6503,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455394</v>
+        <v>455308</v>
       </c>
       <c r="R56" t="n">
-        <v>6773349</v>
+        <v>6773336</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6599,10 +6599,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129114697</v>
+        <v>129114115</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6610,21 +6610,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6634,13 +6634,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455428</v>
+        <v>455394</v>
       </c>
       <c r="R57" t="n">
-        <v>6773376</v>
+        <v>6773349</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129112093</v>
+        <v>129110960</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455241</v>
+        <v>455260</v>
       </c>
       <c r="R62" t="n">
-        <v>6773279</v>
+        <v>6773245</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129110960</v>
+        <v>129112093</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455260</v>
+        <v>455241</v>
       </c>
       <c r="R63" t="n">
-        <v>6773245</v>
+        <v>6773279</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8436,10 +8436,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129112107</v>
+        <v>129110810</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8447,34 +8447,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455235</v>
+        <v>455237</v>
       </c>
       <c r="R74" t="n">
-        <v>6773290</v>
+        <v>6773232</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8543,53 +8548,51 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129110810</v>
+        <v>129114483</v>
       </c>
       <c r="B75" t="n">
-        <v>57724</v>
+        <v>90932</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455237</v>
+        <v>455394</v>
       </c>
       <c r="R75" t="n">
-        <v>6773232</v>
+        <v>6773349</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8631,12 +8634,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8655,51 +8664,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129114483</v>
+        <v>129112107</v>
       </c>
       <c r="B76" t="n">
-        <v>90932</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455394</v>
+        <v>455235</v>
       </c>
       <c r="R76" t="n">
-        <v>6773349</v>
+        <v>6773290</v>
       </c>
       <c r="S76" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8741,18 +8747,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8883,7 +8883,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129107895</v>
+        <v>129109466</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>455397</v>
+        <v>455479</v>
       </c>
       <c r="R78" t="n">
-        <v>6773180</v>
+        <v>6773185</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8990,7 +8990,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129109466</v>
+        <v>129107895</v>
       </c>
       <c r="B79" t="n">
         <v>79044</v>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>455479</v>
+        <v>455397</v>
       </c>
       <c r="R79" t="n">
-        <v>6773185</v>
+        <v>6773180</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,39 +9108,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R80" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9209,10 +9204,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9220,34 +9215,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R81" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129112739</v>
+        <v>129113900</v>
       </c>
       <c r="B88" t="n">
         <v>79044</v>
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>455290</v>
+        <v>455329</v>
       </c>
       <c r="R88" t="n">
-        <v>6773279</v>
+        <v>6773342</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129113900</v>
+        <v>129112739</v>
       </c>
       <c r="B89" t="n">
         <v>79044</v>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>455329</v>
+        <v>455290</v>
       </c>
       <c r="R89" t="n">
-        <v>6773342</v>
+        <v>6773279</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10721,41 +10721,40 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129516251</v>
+        <v>129516224</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>57887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10765,10 +10764,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>455481</v>
+        <v>455383</v>
       </c>
       <c r="R95" t="n">
-        <v>6773645</v>
+        <v>6773634</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10809,7 +10808,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10828,40 +10826,41 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129516224</v>
+        <v>129516251</v>
       </c>
       <c r="B96" t="n">
-        <v>57887</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10871,10 +10870,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>455383</v>
+        <v>455481</v>
       </c>
       <c r="R96" t="n">
-        <v>6773634</v>
+        <v>6773645</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10915,6 +10914,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10933,7 +10933,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129516243</v>
+        <v>129516248</v>
       </c>
       <c r="B97" t="n">
         <v>8450</v>
@@ -10977,10 +10977,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>455377</v>
+        <v>455414</v>
       </c>
       <c r="R97" t="n">
-        <v>6773671</v>
+        <v>6773624</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11040,7 +11040,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129516248</v>
+        <v>129516243</v>
       </c>
       <c r="B98" t="n">
         <v>8450</v>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>455414</v>
+        <v>455377</v>
       </c>
       <c r="R98" t="n">
-        <v>6773624</v>
+        <v>6773671</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11147,7 +11147,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129516249</v>
+        <v>129516237</v>
       </c>
       <c r="B99" t="n">
         <v>8450</v>
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>455432</v>
+        <v>455395</v>
       </c>
       <c r="R99" t="n">
-        <v>6773615</v>
+        <v>6773693</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11254,7 +11254,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129516237</v>
+        <v>129516249</v>
       </c>
       <c r="B100" t="n">
         <v>8450</v>
@@ -11298,10 +11298,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>455395</v>
+        <v>455432</v>
       </c>
       <c r="R100" t="n">
-        <v>6773693</v>
+        <v>6773615</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12604,41 +12604,40 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129516252</v>
+        <v>129516227</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12648,10 +12647,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>455472</v>
+        <v>455382</v>
       </c>
       <c r="R113" t="n">
-        <v>6773649</v>
+        <v>6773594</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12692,7 +12691,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12711,40 +12709,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129516227</v>
+        <v>129516252</v>
       </c>
       <c r="B114" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12754,10 +12753,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455382</v>
+        <v>455472</v>
       </c>
       <c r="R114" t="n">
-        <v>6773594</v>
+        <v>6773649</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12798,6 +12797,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12913,10 +12913,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129516275</v>
+        <v>129516228</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12924,34 +12924,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>455381</v>
+        <v>455480</v>
       </c>
       <c r="R116" t="n">
-        <v>6773638</v>
+        <v>6773643</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13010,10 +13018,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129516228</v>
+        <v>129516275</v>
       </c>
       <c r="B117" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13021,42 +13029,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>455480</v>
+        <v>455381</v>
       </c>
       <c r="R117" t="n">
-        <v>6773643</v>
+        <v>6773638</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13436,10 +13436,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129516222</v>
+        <v>129516270</v>
       </c>
       <c r="B121" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13447,21 +13447,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>455510</v>
+        <v>455383</v>
       </c>
       <c r="R121" t="n">
-        <v>6773641</v>
+        <v>6773719</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13533,10 +13533,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129516270</v>
+        <v>129516222</v>
       </c>
       <c r="B122" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13544,21 +13544,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13568,10 +13568,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>455383</v>
+        <v>455510</v>
       </c>
       <c r="R122" t="n">
-        <v>6773719</v>
+        <v>6773641</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13933,45 +13933,49 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129525056</v>
+        <v>129524323</v>
       </c>
       <c r="B126" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>455743</v>
+        <v>455677</v>
       </c>
       <c r="R126" t="n">
-        <v>6773438</v>
+        <v>6773324</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14151,49 +14155,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129524323</v>
+        <v>129525056</v>
       </c>
       <c r="B128" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>455677</v>
+        <v>455743</v>
       </c>
       <c r="R128" t="n">
-        <v>6773324</v>
+        <v>6773438</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14262,10 +14262,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129520384</v>
+        <v>129520392</v>
       </c>
       <c r="B129" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14273,21 +14273,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14369,10 +14369,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129520392</v>
+        <v>129520384</v>
       </c>
       <c r="B130" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14380,21 +14380,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14805,7 +14805,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129521661</v>
+        <v>129524757</v>
       </c>
       <c r="B134" t="n">
         <v>79044</v>
@@ -14840,10 +14840,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>455547</v>
+        <v>455745</v>
       </c>
       <c r="R134" t="n">
-        <v>6773313</v>
+        <v>6773387</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14875,7 +14875,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14885,12 +14885,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i äldre tallar samt gran</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14917,7 +14912,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129524757</v>
+        <v>129521661</v>
       </c>
       <c r="B135" t="n">
         <v>79044</v>
@@ -14952,10 +14947,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>455745</v>
+        <v>455547</v>
       </c>
       <c r="R135" t="n">
-        <v>6773387</v>
+        <v>6773313</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14987,7 +14982,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14997,7 +14992,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i äldre tallar samt gran</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15024,7 +15024,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129524992</v>
+        <v>129524157</v>
       </c>
       <c r="B136" t="n">
         <v>79044</v>
@@ -15059,10 +15059,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>455715</v>
+        <v>455658</v>
       </c>
       <c r="R136" t="n">
-        <v>6773435</v>
+        <v>6773278</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15105,6 +15105,11 @@
       <c r="AB136" t="inlineStr">
         <is>
           <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15131,7 +15136,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129524157</v>
+        <v>129524992</v>
       </c>
       <c r="B137" t="n">
         <v>79044</v>
@@ -15166,10 +15171,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>455658</v>
+        <v>455715</v>
       </c>
       <c r="R137" t="n">
-        <v>6773278</v>
+        <v>6773435</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15212,11 +15217,6 @@
       <c r="AB137" t="inlineStr">
         <is>
           <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15243,45 +15243,49 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129524794</v>
+        <v>129522884</v>
       </c>
       <c r="B138" t="n">
-        <v>79663</v>
+        <v>92832</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>455725</v>
+        <v>455654</v>
       </c>
       <c r="R138" t="n">
-        <v>6773375</v>
+        <v>6773335</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15313,7 +15317,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15323,7 +15327,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15457,49 +15461,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129522884</v>
+        <v>129524794</v>
       </c>
       <c r="B140" t="n">
-        <v>92832</v>
+        <v>79663</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>455654</v>
+        <v>455725</v>
       </c>
       <c r="R140" t="n">
-        <v>6773335</v>
+        <v>6773375</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15568,10 +15568,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129524463</v>
+        <v>129522761</v>
       </c>
       <c r="B141" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15579,39 +15579,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>455664</v>
+        <v>455639</v>
       </c>
       <c r="R141" t="n">
-        <v>6773257</v>
+        <v>6773364</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15643,7 +15638,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15653,7 +15648,12 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15680,50 +15680,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129522915</v>
+        <v>129520550</v>
       </c>
       <c r="B142" t="n">
-        <v>56917</v>
+        <v>79044</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>455660</v>
+        <v>455524</v>
       </c>
       <c r="R142" t="n">
-        <v>6773320</v>
+        <v>6773304</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15792,7 +15787,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129522761</v>
+        <v>129522134</v>
       </c>
       <c r="B143" t="n">
         <v>79044</v>
@@ -15827,10 +15822,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>455639</v>
+        <v>455646</v>
       </c>
       <c r="R143" t="n">
-        <v>6773364</v>
+        <v>6773308</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15873,11 +15868,6 @@
       <c r="AB143" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16016,10 +16006,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129522134</v>
+        <v>129524463</v>
       </c>
       <c r="B145" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16027,34 +16017,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>455646</v>
+        <v>455664</v>
       </c>
       <c r="R145" t="n">
-        <v>6773308</v>
+        <v>6773257</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16086,7 +16081,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16096,7 +16091,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16123,45 +16118,50 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129520408</v>
+        <v>129522915</v>
       </c>
       <c r="B146" t="n">
-        <v>79044</v>
+        <v>56917</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>455524</v>
+        <v>455660</v>
       </c>
       <c r="R146" t="n">
-        <v>6773304</v>
+        <v>6773320</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16230,10 +16230,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129520906</v>
+        <v>129520622</v>
       </c>
       <c r="B147" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16241,39 +16241,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>455570</v>
+        <v>455540</v>
       </c>
       <c r="R147" t="n">
-        <v>6773300</v>
+        <v>6773296</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16342,45 +16337,50 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129525079</v>
+        <v>129520906</v>
       </c>
       <c r="B148" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>455743</v>
+        <v>455570</v>
       </c>
       <c r="R148" t="n">
-        <v>6773438</v>
+        <v>6773300</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16412,7 +16412,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16449,32 +16449,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129520622</v>
+        <v>129525079</v>
       </c>
       <c r="B149" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16484,10 +16484,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>455540</v>
+        <v>455743</v>
       </c>
       <c r="R149" t="n">
-        <v>6773296</v>
+        <v>6773438</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17103,49 +17103,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129522797</v>
+        <v>129520463</v>
       </c>
       <c r="B155" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>455650</v>
+        <v>455514</v>
       </c>
       <c r="R155" t="n">
-        <v>6773365</v>
+        <v>6773311</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17321,45 +17317,49 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129520463</v>
+        <v>129522797</v>
       </c>
       <c r="B157" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>455514</v>
+        <v>455650</v>
       </c>
       <c r="R157" t="n">
-        <v>6773311</v>
+        <v>6773365</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17978,10 +17978,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129524253</v>
+        <v>129520400</v>
       </c>
       <c r="B163" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17989,39 +17989,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>455687</v>
+        <v>455528</v>
       </c>
       <c r="R163" t="n">
-        <v>6773304</v>
+        <v>6773294</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18053,7 +18048,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18063,7 +18058,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18090,10 +18085,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129520400</v>
+        <v>129524253</v>
       </c>
       <c r="B164" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18101,34 +18096,39 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>455528</v>
+        <v>455687</v>
       </c>
       <c r="R164" t="n">
-        <v>6773294</v>
+        <v>6773304</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18160,7 +18160,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18170,7 +18170,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18197,7 +18197,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129520768</v>
+        <v>129521008</v>
       </c>
       <c r="B165" t="n">
         <v>79044</v>
@@ -18278,6 +18278,11 @@
       <c r="AB165" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18416,10 +18421,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129522648</v>
+        <v>129521993</v>
       </c>
       <c r="B167" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18427,42 +18432,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>455650</v>
+        <v>455615</v>
       </c>
       <c r="R167" t="n">
-        <v>6773365</v>
+        <v>6773317</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18502,6 +18502,11 @@
       <c r="AB167" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18528,10 +18533,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129521993</v>
+        <v>129522648</v>
       </c>
       <c r="B168" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18539,37 +18544,42 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>455615</v>
+        <v>455650</v>
       </c>
       <c r="R168" t="n">
-        <v>6773317</v>
+        <v>6773365</v>
       </c>
       <c r="S168" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18609,11 +18619,6 @@
       <c r="AB168" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18752,7 +18757,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129524742</v>
+        <v>129520910</v>
       </c>
       <c r="B170" t="n">
         <v>79044</v>
@@ -18787,10 +18792,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>455747</v>
+        <v>455570</v>
       </c>
       <c r="R170" t="n">
-        <v>6773363</v>
+        <v>6773300</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18822,7 +18827,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18832,7 +18837,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18966,7 +18971,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129520910</v>
+        <v>129524742</v>
       </c>
       <c r="B172" t="n">
         <v>79044</v>
@@ -19001,10 +19006,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>455570</v>
+        <v>455747</v>
       </c>
       <c r="R172" t="n">
-        <v>6773300</v>
+        <v>6773363</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19036,7 +19041,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19046,7 +19051,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19185,10 +19190,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129520654</v>
+        <v>129524675</v>
       </c>
       <c r="B174" t="n">
-        <v>79663</v>
+        <v>91571</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19196,21 +19201,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19220,10 +19225,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>455559</v>
+        <v>455677</v>
       </c>
       <c r="R174" t="n">
-        <v>6773284</v>
+        <v>6773324</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19255,7 +19260,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19265,7 +19270,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19292,45 +19297,49 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129524675</v>
+        <v>129524033</v>
       </c>
       <c r="B175" t="n">
-        <v>91571</v>
+        <v>92832</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>455677</v>
+        <v>455658</v>
       </c>
       <c r="R175" t="n">
-        <v>6773324</v>
+        <v>6773278</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19362,7 +19371,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19372,7 +19381,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19399,49 +19408,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129524033</v>
+        <v>129520654</v>
       </c>
       <c r="B176" t="n">
-        <v>92832</v>
+        <v>79663</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>455658</v>
+        <v>455559</v>
       </c>
       <c r="R176" t="n">
-        <v>6773278</v>
+        <v>6773284</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY177"/>
+  <dimension ref="A1:AY205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3574,10 +3574,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129112885</v>
+        <v>129113791</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,37 +3585,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455288</v>
+        <v>455304</v>
       </c>
       <c r="R29" t="n">
-        <v>6773318</v>
+        <v>6773316</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3681,7 +3686,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129110462</v>
+        <v>129112885</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3716,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455333</v>
+        <v>455288</v>
       </c>
       <c r="R30" t="n">
-        <v>6773289</v>
+        <v>6773318</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3788,10 +3793,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129113791</v>
+        <v>129110462</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3799,42 +3804,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455304</v>
+        <v>455333</v>
       </c>
       <c r="R31" t="n">
-        <v>6773316</v>
+        <v>6773289</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129110662</v>
+        <v>129109514</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,34 +4018,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455273</v>
+        <v>455494</v>
       </c>
       <c r="R33" t="n">
-        <v>6773208</v>
+        <v>6773187</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,7 +4119,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129106783</v>
+        <v>129110662</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -4149,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455407</v>
+        <v>455273</v>
       </c>
       <c r="R34" t="n">
-        <v>6773196</v>
+        <v>6773208</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4221,10 +4226,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129109514</v>
+        <v>129106783</v>
       </c>
       <c r="B35" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,39 +4237,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455494</v>
+        <v>455407</v>
       </c>
       <c r="R35" t="n">
-        <v>6773187</v>
+        <v>6773196</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -6162,45 +6162,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129112375</v>
+        <v>129112645</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>58157</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>103001</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455269</v>
+        <v>455308</v>
       </c>
       <c r="R53" t="n">
-        <v>6773288</v>
+        <v>6773282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6269,54 +6278,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129112645</v>
+        <v>129112375</v>
       </c>
       <c r="B54" t="n">
-        <v>58157</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103001</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455308</v>
+        <v>455269</v>
       </c>
       <c r="R54" t="n">
-        <v>6773282</v>
+        <v>6773288</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129110960</v>
+        <v>129107474</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,34 +7150,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455260</v>
+        <v>455385</v>
       </c>
       <c r="R62" t="n">
-        <v>6773245</v>
+        <v>6773193</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7246,7 +7251,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129112093</v>
+        <v>129110960</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7281,10 +7286,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455241</v>
+        <v>455260</v>
       </c>
       <c r="R63" t="n">
-        <v>6773279</v>
+        <v>6773245</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7353,50 +7358,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129110475</v>
+        <v>129112093</v>
       </c>
       <c r="B64" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455333</v>
+        <v>455241</v>
       </c>
       <c r="R64" t="n">
-        <v>6773289</v>
+        <v>6773279</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7465,7 +7465,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129114704</v>
+        <v>129110475</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7494,16 +7494,21 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455438</v>
+        <v>455333</v>
       </c>
       <c r="R65" t="n">
-        <v>6773400</v>
+        <v>6773289</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7572,50 +7577,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129107474</v>
+        <v>129114704</v>
       </c>
       <c r="B66" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455385</v>
+        <v>455438</v>
       </c>
       <c r="R66" t="n">
-        <v>6773193</v>
+        <v>6773400</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8436,53 +8436,51 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129110810</v>
+        <v>129114483</v>
       </c>
       <c r="B74" t="n">
-        <v>57724</v>
+        <v>90932</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455237</v>
+        <v>455394</v>
       </c>
       <c r="R74" t="n">
-        <v>6773232</v>
+        <v>6773349</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8524,12 +8522,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8548,51 +8552,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129114483</v>
+        <v>129112107</v>
       </c>
       <c r="B75" t="n">
-        <v>90932</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455394</v>
+        <v>455235</v>
       </c>
       <c r="R75" t="n">
-        <v>6773349</v>
+        <v>6773290</v>
       </c>
       <c r="S75" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8634,18 +8635,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8664,10 +8659,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129112107</v>
+        <v>129110810</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8675,34 +8670,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455235</v>
+        <v>455237</v>
       </c>
       <c r="R76" t="n">
-        <v>6773290</v>
+        <v>6773232</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8883,7 +8883,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129109466</v>
+        <v>129107895</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>455479</v>
+        <v>455397</v>
       </c>
       <c r="R78" t="n">
-        <v>6773185</v>
+        <v>6773180</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8990,7 +8990,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129107895</v>
+        <v>129109466</v>
       </c>
       <c r="B79" t="n">
         <v>79044</v>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>455397</v>
+        <v>455479</v>
       </c>
       <c r="R79" t="n">
-        <v>6773180</v>
+        <v>6773185</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,34 +9108,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R80" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9204,10 +9209,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9215,39 +9220,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R81" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10517,35 +10517,44 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129516232</v>
+        <v>129516242</v>
       </c>
       <c r="B93" t="n">
-        <v>92870</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
@@ -10555,7 +10564,7 @@
         <v>455380</v>
       </c>
       <c r="R93" t="n">
-        <v>6773633</v>
+        <v>6773669</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10596,6 +10605,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10614,44 +10624,35 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129516242</v>
+        <v>129516232</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>92870</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
@@ -10661,7 +10662,7 @@
         <v>455380</v>
       </c>
       <c r="R94" t="n">
-        <v>6773669</v>
+        <v>6773633</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10702,7 +10703,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -12913,10 +12913,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129516228</v>
+        <v>129516275</v>
       </c>
       <c r="B116" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12924,42 +12924,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>455480</v>
+        <v>455381</v>
       </c>
       <c r="R116" t="n">
-        <v>6773643</v>
+        <v>6773638</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13018,10 +13010,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129516275</v>
+        <v>129516228</v>
       </c>
       <c r="B117" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13029,34 +13021,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>455381</v>
+        <v>455480</v>
       </c>
       <c r="R117" t="n">
-        <v>6773638</v>
+        <v>6773643</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13933,49 +13933,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129524323</v>
+        <v>129525056</v>
       </c>
       <c r="B126" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>455677</v>
+        <v>455743</v>
       </c>
       <c r="R126" t="n">
-        <v>6773324</v>
+        <v>6773438</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14044,7 +14040,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129520976</v>
+        <v>129524323</v>
       </c>
       <c r="B127" t="n">
         <v>92832</v>
@@ -14074,7 +14070,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14083,10 +14079,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>455562</v>
+        <v>455677</v>
       </c>
       <c r="R127" t="n">
-        <v>6773304</v>
+        <v>6773324</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14118,7 +14114,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14128,7 +14124,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14155,45 +14151,49 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129525056</v>
+        <v>129520976</v>
       </c>
       <c r="B128" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>455743</v>
+        <v>455562</v>
       </c>
       <c r="R128" t="n">
-        <v>6773438</v>
+        <v>6773304</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14476,45 +14476,49 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129520126</v>
+        <v>129524264</v>
       </c>
       <c r="B131" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>455494</v>
+        <v>455687</v>
       </c>
       <c r="R131" t="n">
-        <v>6773317</v>
+        <v>6773304</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14546,7 +14550,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14556,7 +14560,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14583,49 +14587,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129524264</v>
+        <v>129520126</v>
       </c>
       <c r="B132" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>455687</v>
+        <v>455494</v>
       </c>
       <c r="R132" t="n">
-        <v>6773304</v>
+        <v>6773317</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -17103,45 +17103,49 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129520463</v>
+        <v>129522797</v>
       </c>
       <c r="B155" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>455514</v>
+        <v>455650</v>
       </c>
       <c r="R155" t="n">
-        <v>6773311</v>
+        <v>6773365</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17210,7 +17214,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129525097</v>
+        <v>129520463</v>
       </c>
       <c r="B156" t="n">
         <v>79044</v>
@@ -17245,10 +17249,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>455756</v>
+        <v>455514</v>
       </c>
       <c r="R156" t="n">
-        <v>6773423</v>
+        <v>6773311</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17280,7 +17284,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17290,7 +17294,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17317,49 +17321,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129522797</v>
+        <v>129525097</v>
       </c>
       <c r="B157" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>455650</v>
+        <v>455756</v>
       </c>
       <c r="R157" t="n">
-        <v>6773365</v>
+        <v>6773423</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17401,7 +17401,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18645,7 +18645,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129525452</v>
+        <v>129524742</v>
       </c>
       <c r="B169" t="n">
         <v>79044</v>
@@ -18680,10 +18680,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>455677</v>
+        <v>455747</v>
       </c>
       <c r="R169" t="n">
-        <v>6773354</v>
+        <v>6773363</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18726,11 +18726,6 @@
       <c r="AB169" t="inlineStr">
         <is>
           <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18757,7 +18752,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129520910</v>
+        <v>129525452</v>
       </c>
       <c r="B170" t="n">
         <v>79044</v>
@@ -18792,10 +18787,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>455570</v>
+        <v>455677</v>
       </c>
       <c r="R170" t="n">
-        <v>6773300</v>
+        <v>6773354</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18827,7 +18822,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18837,7 +18832,12 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18864,7 +18864,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129524269</v>
+        <v>129520910</v>
       </c>
       <c r="B171" t="n">
         <v>79044</v>
@@ -18899,10 +18899,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>455687</v>
+        <v>455570</v>
       </c>
       <c r="R171" t="n">
-        <v>6773304</v>
+        <v>6773300</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18971,7 +18971,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129524742</v>
+        <v>129524269</v>
       </c>
       <c r="B172" t="n">
         <v>79044</v>
@@ -19006,10 +19006,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>455747</v>
+        <v>455687</v>
       </c>
       <c r="R172" t="n">
-        <v>6773363</v>
+        <v>6773304</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19639,6 +19639,3080 @@
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>129561893</v>
+      </c>
+      <c r="B178" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>455839</v>
+      </c>
+      <c r="R178" t="n">
+        <v>6773507</v>
+      </c>
+      <c r="S178" t="n">
+        <v>10</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>129561832</v>
+      </c>
+      <c r="B179" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>455852</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6773480</v>
+      </c>
+      <c r="S179" t="n">
+        <v>50</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>129561829</v>
+      </c>
+      <c r="B180" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>455852</v>
+      </c>
+      <c r="R180" t="n">
+        <v>6773480</v>
+      </c>
+      <c r="S180" t="n">
+        <v>50</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>129561895</v>
+      </c>
+      <c r="B181" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>455839</v>
+      </c>
+      <c r="R181" t="n">
+        <v>6773507</v>
+      </c>
+      <c r="S181" t="n">
+        <v>10</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>129563002</v>
+      </c>
+      <c r="B182" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>455729</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6773474</v>
+      </c>
+      <c r="S182" t="n">
+        <v>10</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Massor minst 100 st</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>129561879</v>
+      </c>
+      <c r="B183" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>455839</v>
+      </c>
+      <c r="R183" t="n">
+        <v>6773507</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>129555147</v>
+      </c>
+      <c r="B184" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>455622</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6773376</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>129555566</v>
+      </c>
+      <c r="B185" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>455671</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6773369</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>129555318</v>
+      </c>
+      <c r="B186" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>455588</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6773371</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>129562560</v>
+      </c>
+      <c r="B187" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>455727</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6773501</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>129555967</v>
+      </c>
+      <c r="B188" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>455737</v>
+      </c>
+      <c r="R188" t="n">
+        <v>6773382</v>
+      </c>
+      <c r="S188" t="n">
+        <v>10</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>129562306</v>
+      </c>
+      <c r="B189" t="n">
+        <v>58097</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>455754</v>
+      </c>
+      <c r="R189" t="n">
+        <v>6773518</v>
+      </c>
+      <c r="S189" t="n">
+        <v>50</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>129559838</v>
+      </c>
+      <c r="B190" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>455782</v>
+      </c>
+      <c r="R190" t="n">
+        <v>6773516</v>
+      </c>
+      <c r="S190" t="n">
+        <v>10</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>129560778</v>
+      </c>
+      <c r="B191" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>455843</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6773492</v>
+      </c>
+      <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>129562442</v>
+      </c>
+      <c r="B192" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>455705</v>
+      </c>
+      <c r="R192" t="n">
+        <v>6773527</v>
+      </c>
+      <c r="S192" t="n">
+        <v>10</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>129559217</v>
+      </c>
+      <c r="B193" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>455762</v>
+      </c>
+      <c r="R193" t="n">
+        <v>6773481</v>
+      </c>
+      <c r="S193" t="n">
+        <v>10</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Garnlav samt miljöbilder för området. Gammal skog, tall och gran</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>129555275</v>
+      </c>
+      <c r="B194" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>455583</v>
+      </c>
+      <c r="R194" t="n">
+        <v>6773359</v>
+      </c>
+      <c r="S194" t="n">
+        <v>10</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>129560763</v>
+      </c>
+      <c r="B195" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>455843</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6773492</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>129561831</v>
+      </c>
+      <c r="B196" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>455852</v>
+      </c>
+      <c r="R196" t="n">
+        <v>6773480</v>
+      </c>
+      <c r="S196" t="n">
+        <v>50</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>129562358</v>
+      </c>
+      <c r="B197" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>455754</v>
+      </c>
+      <c r="R197" t="n">
+        <v>6773518</v>
+      </c>
+      <c r="S197" t="n">
+        <v>50</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>129555030</v>
+      </c>
+      <c r="B198" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>455599</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6773404</v>
+      </c>
+      <c r="S198" t="n">
+        <v>10</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>129555631</v>
+      </c>
+      <c r="B199" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>455677</v>
+      </c>
+      <c r="R199" t="n">
+        <v>6773354</v>
+      </c>
+      <c r="S199" t="n">
+        <v>10</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>129555824</v>
+      </c>
+      <c r="B200" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>455731</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6773361</v>
+      </c>
+      <c r="S200" t="n">
+        <v>10</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>129555339</v>
+      </c>
+      <c r="B201" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>455612</v>
+      </c>
+      <c r="R201" t="n">
+        <v>6773368</v>
+      </c>
+      <c r="S201" t="n">
+        <v>50</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>129555039</v>
+      </c>
+      <c r="B202" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>455617</v>
+      </c>
+      <c r="R202" t="n">
+        <v>6773406</v>
+      </c>
+      <c r="S202" t="n">
+        <v>10</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>129555463</v>
+      </c>
+      <c r="B203" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>455663</v>
+      </c>
+      <c r="R203" t="n">
+        <v>6773398</v>
+      </c>
+      <c r="S203" t="n">
+        <v>50</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>129559639</v>
+      </c>
+      <c r="B204" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Skärberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>455773</v>
+      </c>
+      <c r="R204" t="n">
+        <v>6773504</v>
+      </c>
+      <c r="S204" t="n">
+        <v>10</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>129562904</v>
+      </c>
+      <c r="B205" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>455727</v>
+      </c>
+      <c r="R205" t="n">
+        <v>6773501</v>
+      </c>
+      <c r="S205" t="n">
+        <v>10</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Minst hundra!</t>
+        </is>
+      </c>
+      <c r="AD205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY205"/>
+  <dimension ref="A1:AY207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129108187</v>
+        <v>129108044</v>
       </c>
       <c r="B2" t="n">
-        <v>79634</v>
+        <v>79663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129108044</v>
+        <v>129112610</v>
       </c>
       <c r="B3" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455412</v>
+        <v>455308</v>
       </c>
       <c r="R3" t="n">
-        <v>6773172</v>
+        <v>6773282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129112804</v>
+        <v>129112438</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455289</v>
+        <v>455258</v>
       </c>
       <c r="R4" t="n">
-        <v>6773299</v>
+        <v>6773321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112610</v>
+        <v>129112479</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455308</v>
+        <v>455272</v>
       </c>
       <c r="R5" t="n">
-        <v>6773282</v>
+        <v>6773302</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129112438</v>
+        <v>129112804</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455258</v>
+        <v>455289</v>
       </c>
       <c r="R6" t="n">
-        <v>6773321</v>
+        <v>6773299</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129112479</v>
+        <v>129108187</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455272</v>
+        <v>455412</v>
       </c>
       <c r="R7" t="n">
-        <v>6773302</v>
+        <v>6773172</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129113163</v>
+        <v>129109404</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455283</v>
+        <v>455484</v>
       </c>
       <c r="R9" t="n">
-        <v>6773359</v>
+        <v>6773211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129107453</v>
+        <v>129113163</v>
       </c>
       <c r="B11" t="n">
         <v>79044</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455385</v>
+        <v>455283</v>
       </c>
       <c r="R11" t="n">
-        <v>6773193</v>
+        <v>6773359</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129109404</v>
+        <v>129107453</v>
       </c>
       <c r="B12" t="n">
         <v>79044</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455484</v>
+        <v>455385</v>
       </c>
       <c r="R12" t="n">
-        <v>6773211</v>
+        <v>6773193</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1860,7 @@
         <v>129113882</v>
       </c>
       <c r="B13" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129110979</v>
+        <v>129107916</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455258</v>
+        <v>455389</v>
       </c>
       <c r="R17" t="n">
-        <v>6773256</v>
+        <v>6773170</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129107916</v>
+        <v>129110979</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455389</v>
+        <v>455258</v>
       </c>
       <c r="R18" t="n">
-        <v>6773170</v>
+        <v>6773256</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129112407</v>
+        <v>129109613</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455248</v>
+        <v>455494</v>
       </c>
       <c r="R22" t="n">
-        <v>6773310</v>
+        <v>6773197</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129109613</v>
+        <v>129112407</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455494</v>
+        <v>455248</v>
       </c>
       <c r="R23" t="n">
-        <v>6773197</v>
+        <v>6773310</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129114098</v>
+        <v>129111088</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455394</v>
+        <v>455248</v>
       </c>
       <c r="R24" t="n">
-        <v>6773349</v>
+        <v>6773274</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129113094</v>
+        <v>129114098</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3181,13 +3181,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455301</v>
+        <v>455394</v>
       </c>
       <c r="R25" t="n">
-        <v>6773331</v>
+        <v>6773349</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129107601</v>
+        <v>129113094</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455352</v>
+        <v>455301</v>
       </c>
       <c r="R26" t="n">
-        <v>6773200</v>
+        <v>6773331</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129111088</v>
+        <v>129107601</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455248</v>
+        <v>455352</v>
       </c>
       <c r="R27" t="n">
-        <v>6773274</v>
+        <v>6773200</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129113791</v>
+        <v>129112885</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,42 +3585,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455304</v>
+        <v>455288</v>
       </c>
       <c r="R29" t="n">
-        <v>6773316</v>
+        <v>6773318</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3686,7 +3681,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129112885</v>
+        <v>129110462</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3721,10 +3716,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455288</v>
+        <v>455333</v>
       </c>
       <c r="R30" t="n">
-        <v>6773318</v>
+        <v>6773289</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3793,10 +3788,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129110462</v>
+        <v>129113791</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3804,37 +3799,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455333</v>
+        <v>455304</v>
       </c>
       <c r="R31" t="n">
-        <v>6773289</v>
+        <v>6773316</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129109514</v>
+        <v>129110662</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,39 +4018,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455494</v>
+        <v>455273</v>
       </c>
       <c r="R33" t="n">
-        <v>6773187</v>
+        <v>6773208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4119,7 +4114,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129110662</v>
+        <v>129110692</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -4154,13 +4149,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455273</v>
+        <v>455270</v>
       </c>
       <c r="R34" t="n">
-        <v>6773208</v>
+        <v>6773216</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4440,10 +4435,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129110692</v>
+        <v>129109514</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4451,37 +4446,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455270</v>
+        <v>455494</v>
       </c>
       <c r="R37" t="n">
-        <v>6773216</v>
+        <v>6773187</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129110861</v>
+        <v>129108956</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455267</v>
+        <v>455473</v>
       </c>
       <c r="R38" t="n">
-        <v>6773233</v>
+        <v>6773221</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129108956</v>
+        <v>129110861</v>
       </c>
       <c r="B39" t="n">
         <v>79044</v>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455473</v>
+        <v>455267</v>
       </c>
       <c r="R39" t="n">
-        <v>6773221</v>
+        <v>6773233</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129114507</v>
+        <v>129107072</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455391</v>
+        <v>455389</v>
       </c>
       <c r="R41" t="n">
-        <v>6773367</v>
+        <v>6773203</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129107679</v>
+        <v>129110029</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455353</v>
+        <v>455333</v>
       </c>
       <c r="R42" t="n">
-        <v>6773191</v>
+        <v>6773241</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129110029</v>
+        <v>129107679</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455333</v>
+        <v>455353</v>
       </c>
       <c r="R43" t="n">
-        <v>6773241</v>
+        <v>6773191</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129107072</v>
+        <v>129114507</v>
       </c>
       <c r="B44" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455389</v>
+        <v>455391</v>
       </c>
       <c r="R44" t="n">
-        <v>6773203</v>
+        <v>6773367</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129112595</v>
+        <v>129109327</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455279</v>
+        <v>455477</v>
       </c>
       <c r="R45" t="n">
-        <v>6773275</v>
+        <v>6773206</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129109327</v>
+        <v>129112595</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455477</v>
+        <v>455279</v>
       </c>
       <c r="R46" t="n">
-        <v>6773206</v>
+        <v>6773275</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5729,45 +5729,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129110148</v>
+        <v>129109267</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455349</v>
+        <v>455477</v>
       </c>
       <c r="R49" t="n">
-        <v>6773250</v>
+        <v>6773206</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5943,7 +5948,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129109151</v>
+        <v>129110148</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5978,10 +5983,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455459</v>
+        <v>455349</v>
       </c>
       <c r="R51" t="n">
-        <v>6773195</v>
+        <v>6773250</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6050,50 +6055,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129109267</v>
+        <v>129109151</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455477</v>
+        <v>455459</v>
       </c>
       <c r="R52" t="n">
-        <v>6773206</v>
+        <v>6773195</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6385,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129114697</v>
+        <v>129114115</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,21 +6396,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455428</v>
+        <v>455394</v>
       </c>
       <c r="R55" t="n">
-        <v>6773376</v>
+        <v>6773349</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6492,45 +6492,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129113107</v>
+        <v>129108995</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455308</v>
+        <v>455473</v>
       </c>
       <c r="R56" t="n">
-        <v>6773336</v>
+        <v>6773221</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6599,32 +6604,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129114115</v>
+        <v>129112005</v>
       </c>
       <c r="B57" t="n">
-        <v>83012</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6634,13 +6639,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455394</v>
+        <v>455235</v>
       </c>
       <c r="R57" t="n">
-        <v>6773349</v>
+        <v>6773290</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6706,32 +6711,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129110757</v>
+        <v>129110915</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6741,10 +6746,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455252</v>
+        <v>455267</v>
       </c>
       <c r="R58" t="n">
-        <v>6773222</v>
+        <v>6773233</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6813,32 +6818,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129112005</v>
+        <v>129113107</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6848,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455235</v>
+        <v>455308</v>
       </c>
       <c r="R59" t="n">
-        <v>6773290</v>
+        <v>6773336</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6920,32 +6925,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129110915</v>
+        <v>129110757</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6955,10 +6960,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455267</v>
+        <v>455252</v>
       </c>
       <c r="R60" t="n">
-        <v>6773233</v>
+        <v>6773222</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7027,50 +7032,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129108995</v>
+        <v>129114697</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455473</v>
+        <v>455428</v>
       </c>
       <c r="R61" t="n">
-        <v>6773221</v>
+        <v>6773376</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7139,38 +7139,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129107474</v>
+        <v>129110475</v>
       </c>
       <c r="B62" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455385</v>
+        <v>455333</v>
       </c>
       <c r="R62" t="n">
-        <v>6773193</v>
+        <v>6773289</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7251,32 +7251,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129110960</v>
+        <v>129114704</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455260</v>
+        <v>455438</v>
       </c>
       <c r="R63" t="n">
-        <v>6773245</v>
+        <v>6773400</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7358,7 +7358,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129112093</v>
+        <v>129110960</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455241</v>
+        <v>455260</v>
       </c>
       <c r="R64" t="n">
-        <v>6773279</v>
+        <v>6773245</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7465,50 +7465,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129110475</v>
+        <v>129112093</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455333</v>
+        <v>455241</v>
       </c>
       <c r="R65" t="n">
-        <v>6773289</v>
+        <v>6773279</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7577,45 +7572,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129114704</v>
+        <v>129107474</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455438</v>
+        <v>455385</v>
       </c>
       <c r="R66" t="n">
-        <v>6773400</v>
+        <v>6773193</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7684,10 +7684,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129110941</v>
+        <v>129113193</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7695,34 +7695,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455281</v>
+        <v>455283</v>
       </c>
       <c r="R67" t="n">
-        <v>6773251</v>
+        <v>6773359</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,7 +7796,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129112114</v>
+        <v>129110941</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7826,10 +7831,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455233</v>
+        <v>455281</v>
       </c>
       <c r="R68" t="n">
-        <v>6773294</v>
+        <v>6773251</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7898,10 +7903,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129113193</v>
+        <v>129112114</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7909,39 +7914,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455283</v>
+        <v>455233</v>
       </c>
       <c r="R69" t="n">
-        <v>6773359</v>
+        <v>6773294</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8120,7 +8120,7 @@
         <v>129124330</v>
       </c>
       <c r="B71" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8436,51 +8436,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129114483</v>
+        <v>129112107</v>
       </c>
       <c r="B74" t="n">
-        <v>90932</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455394</v>
+        <v>455235</v>
       </c>
       <c r="R74" t="n">
-        <v>6773349</v>
+        <v>6773290</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8522,18 +8519,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8552,10 +8543,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129112107</v>
+        <v>129110810</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8563,34 +8554,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455235</v>
+        <v>455237</v>
       </c>
       <c r="R75" t="n">
-        <v>6773290</v>
+        <v>6773232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8659,53 +8655,51 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129110810</v>
+        <v>129114483</v>
       </c>
       <c r="B76" t="n">
-        <v>57724</v>
+        <v>90935</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455237</v>
+        <v>455394</v>
       </c>
       <c r="R76" t="n">
-        <v>6773232</v>
+        <v>6773349</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8747,12 +8741,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,39 +9108,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R80" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9209,10 +9204,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9220,34 +9215,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R81" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129113900</v>
+        <v>129114734</v>
       </c>
       <c r="B88" t="n">
         <v>79044</v>
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>455329</v>
+        <v>455438</v>
       </c>
       <c r="R88" t="n">
-        <v>6773342</v>
+        <v>6773400</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129112739</v>
+        <v>129113900</v>
       </c>
       <c r="B89" t="n">
         <v>79044</v>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>455290</v>
+        <v>455329</v>
       </c>
       <c r="R89" t="n">
-        <v>6773279</v>
+        <v>6773342</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10182,7 +10182,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129114734</v>
+        <v>129112739</v>
       </c>
       <c r="B90" t="n">
         <v>79044</v>
@@ -10217,10 +10217,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>455438</v>
+        <v>455290</v>
       </c>
       <c r="R90" t="n">
-        <v>6773400</v>
+        <v>6773279</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10517,44 +10517,35 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129516242</v>
+        <v>129516232</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>92873</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
@@ -10564,7 +10555,7 @@
         <v>455380</v>
       </c>
       <c r="R93" t="n">
-        <v>6773669</v>
+        <v>6773633</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10605,7 +10596,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10624,35 +10614,44 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129516232</v>
+        <v>129516242</v>
       </c>
       <c r="B94" t="n">
-        <v>92870</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
@@ -10662,7 +10661,7 @@
         <v>455380</v>
       </c>
       <c r="R94" t="n">
-        <v>6773633</v>
+        <v>6773669</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10703,6 +10702,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10721,40 +10721,41 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129516224</v>
+        <v>129516251</v>
       </c>
       <c r="B95" t="n">
-        <v>57887</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10764,10 +10765,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>455383</v>
+        <v>455481</v>
       </c>
       <c r="R95" t="n">
-        <v>6773634</v>
+        <v>6773645</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10808,6 +10809,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10826,41 +10828,40 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129516251</v>
+        <v>129516224</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>57887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10870,10 +10871,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>455481</v>
+        <v>455383</v>
       </c>
       <c r="R96" t="n">
-        <v>6773645</v>
+        <v>6773634</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10914,7 +10915,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10933,7 +10933,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129516248</v>
+        <v>129516243</v>
       </c>
       <c r="B97" t="n">
         <v>8450</v>
@@ -10977,10 +10977,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>455414</v>
+        <v>455377</v>
       </c>
       <c r="R97" t="n">
-        <v>6773624</v>
+        <v>6773671</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11040,7 +11040,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129516243</v>
+        <v>129516248</v>
       </c>
       <c r="B98" t="n">
         <v>8450</v>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>455377</v>
+        <v>455414</v>
       </c>
       <c r="R98" t="n">
-        <v>6773671</v>
+        <v>6773624</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11147,7 +11147,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129516237</v>
+        <v>129516249</v>
       </c>
       <c r="B99" t="n">
         <v>8450</v>
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>455395</v>
+        <v>455432</v>
       </c>
       <c r="R99" t="n">
-        <v>6773693</v>
+        <v>6773615</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11254,7 +11254,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129516249</v>
+        <v>129516237</v>
       </c>
       <c r="B100" t="n">
         <v>8450</v>
@@ -11298,10 +11298,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>455432</v>
+        <v>455395</v>
       </c>
       <c r="R100" t="n">
-        <v>6773615</v>
+        <v>6773693</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12507,45 +12507,54 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129516226</v>
+        <v>129516252</v>
       </c>
       <c r="B112" t="n">
-        <v>91501</v>
+        <v>8450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>112</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>455448</v>
+        <v>455472</v>
       </c>
       <c r="R112" t="n">
-        <v>6773621</v>
+        <v>6773649</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12586,6 +12595,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12604,10 +12614,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129516227</v>
+        <v>129516226</v>
       </c>
       <c r="B113" t="n">
-        <v>57724</v>
+        <v>91504</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12615,42 +12625,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>455382</v>
+        <v>455448</v>
       </c>
       <c r="R113" t="n">
-        <v>6773594</v>
+        <v>6773621</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12709,41 +12711,40 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129516252</v>
+        <v>129516227</v>
       </c>
       <c r="B114" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12753,10 +12754,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455472</v>
+        <v>455382</v>
       </c>
       <c r="R114" t="n">
-        <v>6773649</v>
+        <v>6773594</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12797,7 +12798,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12819,7 +12819,7 @@
         <v>129516231</v>
       </c>
       <c r="B115" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>129524323</v>
       </c>
       <c r="B127" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>129520976</v>
       </c>
       <c r="B128" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14262,10 +14262,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129520392</v>
+        <v>129520384</v>
       </c>
       <c r="B129" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14273,21 +14273,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14369,10 +14369,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129520384</v>
+        <v>129520392</v>
       </c>
       <c r="B130" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14380,21 +14380,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14476,49 +14476,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129524264</v>
+        <v>129520126</v>
       </c>
       <c r="B131" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>455687</v>
+        <v>455494</v>
       </c>
       <c r="R131" t="n">
-        <v>6773304</v>
+        <v>6773317</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14550,7 +14546,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14560,7 +14556,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14587,45 +14583,49 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129520126</v>
+        <v>129524264</v>
       </c>
       <c r="B132" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>455494</v>
+        <v>455687</v>
       </c>
       <c r="R132" t="n">
-        <v>6773317</v>
+        <v>6773304</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14694,49 +14694,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129522291</v>
+        <v>129524757</v>
       </c>
       <c r="B133" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>455660</v>
+        <v>455745</v>
       </c>
       <c r="R133" t="n">
-        <v>6773320</v>
+        <v>6773387</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14768,7 +14764,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14778,7 +14774,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14805,7 +14801,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129524757</v>
+        <v>129521661</v>
       </c>
       <c r="B134" t="n">
         <v>79044</v>
@@ -14840,10 +14836,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>455745</v>
+        <v>455547</v>
       </c>
       <c r="R134" t="n">
-        <v>6773387</v>
+        <v>6773313</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14875,7 +14871,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14885,7 +14881,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i äldre tallar samt gran</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14912,45 +14913,49 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129521661</v>
+        <v>129522291</v>
       </c>
       <c r="B135" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>455547</v>
+        <v>455660</v>
       </c>
       <c r="R135" t="n">
-        <v>6773313</v>
+        <v>6773320</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14993,11 +14998,6 @@
       <c r="AB135" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i äldre tallar samt gran</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15024,7 +15024,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129524157</v>
+        <v>129524992</v>
       </c>
       <c r="B136" t="n">
         <v>79044</v>
@@ -15059,10 +15059,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>455658</v>
+        <v>455715</v>
       </c>
       <c r="R136" t="n">
-        <v>6773278</v>
+        <v>6773435</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15105,11 +15105,6 @@
       <c r="AB136" t="inlineStr">
         <is>
           <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15136,7 +15131,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129524992</v>
+        <v>129524157</v>
       </c>
       <c r="B137" t="n">
         <v>79044</v>
@@ -15171,10 +15166,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>455715</v>
+        <v>455658</v>
       </c>
       <c r="R137" t="n">
-        <v>6773435</v>
+        <v>6773278</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15217,6 +15212,11 @@
       <c r="AB137" t="inlineStr">
         <is>
           <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15243,10 +15243,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129522884</v>
+        <v>129521094</v>
       </c>
       <c r="B138" t="n">
-        <v>92832</v>
+        <v>8450</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15254,38 +15254,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>455654</v>
+        <v>455547</v>
       </c>
       <c r="R138" t="n">
-        <v>6773335</v>
+        <v>6773313</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15354,32 +15350,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129521094</v>
+        <v>129524794</v>
       </c>
       <c r="B139" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15389,10 +15385,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>455547</v>
+        <v>455725</v>
       </c>
       <c r="R139" t="n">
-        <v>6773313</v>
+        <v>6773375</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15424,7 +15420,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15434,7 +15430,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15461,45 +15457,49 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129524794</v>
+        <v>129522884</v>
       </c>
       <c r="B140" t="n">
-        <v>79663</v>
+        <v>92835</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>455725</v>
+        <v>455654</v>
       </c>
       <c r="R140" t="n">
-        <v>6773375</v>
+        <v>6773335</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15568,7 +15568,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129522761</v>
+        <v>129520408</v>
       </c>
       <c r="B141" t="n">
         <v>79044</v>
@@ -15603,10 +15603,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>455639</v>
+        <v>455524</v>
       </c>
       <c r="R141" t="n">
-        <v>6773364</v>
+        <v>6773304</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15649,11 +15649,6 @@
       <c r="AB141" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15680,7 +15675,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129520550</v>
+        <v>129522134</v>
       </c>
       <c r="B142" t="n">
         <v>79044</v>
@@ -15715,10 +15710,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>455524</v>
+        <v>455646</v>
       </c>
       <c r="R142" t="n">
-        <v>6773304</v>
+        <v>6773308</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15787,7 +15782,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129522134</v>
+        <v>129522761</v>
       </c>
       <c r="B143" t="n">
         <v>79044</v>
@@ -15822,10 +15817,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>455646</v>
+        <v>455639</v>
       </c>
       <c r="R143" t="n">
-        <v>6773308</v>
+        <v>6773364</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15868,6 +15863,11 @@
       <c r="AB143" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16452,7 +16452,7 @@
         <v>129525079</v>
       </c>
       <c r="B149" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>129524776</v>
       </c>
       <c r="B150" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129525476</v>
+        <v>129524645</v>
       </c>
       <c r="B151" t="n">
         <v>79044</v>
@@ -16702,10 +16702,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>455623</v>
+        <v>455677</v>
       </c>
       <c r="R151" t="n">
-        <v>6773393</v>
+        <v>6773324</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16774,7 +16774,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129524645</v>
+        <v>129525476</v>
       </c>
       <c r="B152" t="n">
         <v>79044</v>
@@ -16809,10 +16809,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>455677</v>
+        <v>455623</v>
       </c>
       <c r="R152" t="n">
-        <v>6773324</v>
+        <v>6773393</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16884,7 +16884,7 @@
         <v>129521282</v>
       </c>
       <c r="B153" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>129524704</v>
       </c>
       <c r="B154" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>129522797</v>
       </c>
       <c r="B155" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129520463</v>
+        <v>129525097</v>
       </c>
       <c r="B156" t="n">
         <v>79044</v>
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>455514</v>
+        <v>455756</v>
       </c>
       <c r="R156" t="n">
-        <v>6773311</v>
+        <v>6773423</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17321,7 +17321,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129525097</v>
+        <v>129520463</v>
       </c>
       <c r="B157" t="n">
         <v>79044</v>
@@ -17356,10 +17356,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>455756</v>
+        <v>455514</v>
       </c>
       <c r="R157" t="n">
-        <v>6773423</v>
+        <v>6773311</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17401,7 +17401,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17978,10 +17978,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129520400</v>
+        <v>129524253</v>
       </c>
       <c r="B163" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17989,34 +17989,39 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>455528</v>
+        <v>455687</v>
       </c>
       <c r="R163" t="n">
-        <v>6773294</v>
+        <v>6773304</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18048,7 +18053,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18058,7 +18063,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18085,10 +18090,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129524253</v>
+        <v>129520400</v>
       </c>
       <c r="B164" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18096,39 +18101,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>455687</v>
+        <v>455528</v>
       </c>
       <c r="R164" t="n">
-        <v>6773304</v>
+        <v>6773294</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18160,7 +18160,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18170,7 +18170,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18197,7 +18197,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129521008</v>
+        <v>129520768</v>
       </c>
       <c r="B165" t="n">
         <v>79044</v>
@@ -18278,11 +18278,6 @@
       <c r="AB165" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18645,7 +18640,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129524742</v>
+        <v>129525452</v>
       </c>
       <c r="B169" t="n">
         <v>79044</v>
@@ -18680,10 +18675,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>455747</v>
+        <v>455677</v>
       </c>
       <c r="R169" t="n">
-        <v>6773363</v>
+        <v>6773354</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18726,6 +18721,11 @@
       <c r="AB169" t="inlineStr">
         <is>
           <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18752,7 +18752,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129525452</v>
+        <v>129524742</v>
       </c>
       <c r="B170" t="n">
         <v>79044</v>
@@ -18787,10 +18787,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>455677</v>
+        <v>455747</v>
       </c>
       <c r="R170" t="n">
-        <v>6773354</v>
+        <v>6773363</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18833,11 +18833,6 @@
       <c r="AB170" t="inlineStr">
         <is>
           <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18864,7 +18859,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129520910</v>
+        <v>129524269</v>
       </c>
       <c r="B171" t="n">
         <v>79044</v>
@@ -18899,10 +18894,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>455570</v>
+        <v>455687</v>
       </c>
       <c r="R171" t="n">
-        <v>6773300</v>
+        <v>6773304</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18934,7 +18929,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18944,7 +18939,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18971,7 +18966,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129524269</v>
+        <v>129520910</v>
       </c>
       <c r="B172" t="n">
         <v>79044</v>
@@ -19006,10 +19001,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>455687</v>
+        <v>455570</v>
       </c>
       <c r="R172" t="n">
-        <v>6773304</v>
+        <v>6773300</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19041,7 +19036,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19051,7 +19046,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19190,48 +19185,62 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129524675</v>
+        <v>129520115</v>
       </c>
       <c r="B174" t="n">
-        <v>91571</v>
+        <v>56917</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>455677</v>
+        <v>455499</v>
       </c>
       <c r="R174" t="n">
-        <v>6773324</v>
+        <v>6773331</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19260,7 +19269,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19270,7 +19279,12 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19297,49 +19311,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129524033</v>
+        <v>129524675</v>
       </c>
       <c r="B175" t="n">
-        <v>92832</v>
+        <v>91574</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>455658</v>
+        <v>455677</v>
       </c>
       <c r="R175" t="n">
-        <v>6773278</v>
+        <v>6773324</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19371,7 +19381,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19381,7 +19391,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19515,10 +19525,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129520115</v>
+        <v>129524033</v>
       </c>
       <c r="B177" t="n">
-        <v>56917</v>
+        <v>92835</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19526,36 +19536,26 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -19564,13 +19564,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>455499</v>
+        <v>455658</v>
       </c>
       <c r="R177" t="n">
-        <v>6773331</v>
+        <v>6773278</v>
       </c>
       <c r="S177" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19610,11 +19610,6 @@
       <c r="AB177" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19641,10 +19636,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129561893</v>
+        <v>129561832</v>
       </c>
       <c r="B178" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19652,42 +19647,37 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>455839</v>
+        <v>455852</v>
       </c>
       <c r="R178" t="n">
-        <v>6773507</v>
+        <v>6773480</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19753,10 +19743,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129561832</v>
+        <v>129561893</v>
       </c>
       <c r="B179" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19764,37 +19754,42 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>455852</v>
+        <v>455839</v>
       </c>
       <c r="R179" t="n">
-        <v>6773480</v>
+        <v>6773507</v>
       </c>
       <c r="S179" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19860,38 +19855,37 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129561829</v>
+        <v>129563002</v>
       </c>
       <c r="B180" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -19900,13 +19894,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>455852</v>
+        <v>455729</v>
       </c>
       <c r="R180" t="n">
-        <v>6773480</v>
+        <v>6773474</v>
       </c>
       <c r="S180" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19935,7 +19929,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19945,7 +19939,12 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Massor minst 100 st</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19972,40 +19971,35 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129561895</v>
+        <v>129561879</v>
       </c>
       <c r="B181" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
@@ -20084,37 +20078,38 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129563002</v>
+        <v>129561829</v>
       </c>
       <c r="B182" t="n">
-        <v>98724</v>
+        <v>57724</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -20123,13 +20118,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>455729</v>
+        <v>455852</v>
       </c>
       <c r="R182" t="n">
-        <v>6773474</v>
+        <v>6773480</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20158,7 +20153,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20168,12 +20163,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Massor minst 100 st</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20200,35 +20190,40 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129561879</v>
+        <v>129561895</v>
       </c>
       <c r="B183" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
@@ -21285,7 +21280,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129559217</v>
+        <v>129555275</v>
       </c>
       <c r="B193" t="n">
         <v>79044</v>
@@ -21320,10 +21315,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>455762</v>
+        <v>455583</v>
       </c>
       <c r="R193" t="n">
-        <v>6773481</v>
+        <v>6773359</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21366,11 +21361,6 @@
       <c r="AB193" t="inlineStr">
         <is>
           <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Garnlav samt miljöbilder för området. Gammal skog, tall och gran</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21397,7 +21387,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129555275</v>
+        <v>129559217</v>
       </c>
       <c r="B194" t="n">
         <v>79044</v>
@@ -21432,10 +21422,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>455583</v>
+        <v>455762</v>
       </c>
       <c r="R194" t="n">
-        <v>6773359</v>
+        <v>6773481</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21478,6 +21468,11 @@
       <c r="AB194" t="inlineStr">
         <is>
           <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Garnlav samt miljöbilder för området. Gammal skog, tall och gran</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21616,50 +21611,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129561831</v>
+        <v>129562358</v>
       </c>
       <c r="B196" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>455852</v>
+        <v>455754</v>
       </c>
       <c r="R196" t="n">
-        <v>6773480</v>
+        <v>6773518</v>
       </c>
       <c r="S196" t="n">
         <v>50</v>
@@ -21691,7 +21681,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21701,7 +21691,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21728,45 +21718,50 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129562358</v>
+        <v>129561831</v>
       </c>
       <c r="B197" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>455754</v>
+        <v>455852</v>
       </c>
       <c r="R197" t="n">
-        <v>6773518</v>
+        <v>6773480</v>
       </c>
       <c r="S197" t="n">
         <v>50</v>
@@ -21798,7 +21793,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21808,7 +21803,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21942,10 +21937,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129555631</v>
+        <v>129555824</v>
       </c>
       <c r="B199" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21953,39 +21948,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>455677</v>
+        <v>455731</v>
       </c>
       <c r="R199" t="n">
-        <v>6773354</v>
+        <v>6773361</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22054,10 +22044,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129555824</v>
+        <v>129555631</v>
       </c>
       <c r="B200" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22065,34 +22055,39 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>455731</v>
+        <v>455677</v>
       </c>
       <c r="R200" t="n">
-        <v>6773361</v>
+        <v>6773354</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22380,7 +22375,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129555463</v>
+        <v>129559639</v>
       </c>
       <c r="B203" t="n">
         <v>79044</v>
@@ -22415,13 +22410,13 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>455663</v>
+        <v>455773</v>
       </c>
       <c r="R203" t="n">
-        <v>6773398</v>
+        <v>6773504</v>
       </c>
       <c r="S203" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22461,11 +22456,6 @@
       <c r="AB203" t="inlineStr">
         <is>
           <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22492,7 +22482,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129559639</v>
+        <v>129555463</v>
       </c>
       <c r="B204" t="n">
         <v>79044</v>
@@ -22527,13 +22517,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>455773</v>
+        <v>455663</v>
       </c>
       <c r="R204" t="n">
-        <v>6773504</v>
+        <v>6773398</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -22573,6 +22563,11 @@
       <c r="AB204" t="inlineStr">
         <is>
           <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22602,7 +22597,7 @@
         <v>129562904</v>
       </c>
       <c r="B205" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22712,6 +22707,229 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>129580035</v>
+      </c>
+      <c r="B206" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>455742</v>
+      </c>
+      <c r="R206" t="n">
+        <v>6773450</v>
+      </c>
+      <c r="S206" t="n">
+        <v>10</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>129578682</v>
+      </c>
+      <c r="B207" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Kurutjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>455767</v>
+      </c>
+      <c r="R207" t="n">
+        <v>6773448</v>
+      </c>
+      <c r="S207" t="n">
+        <v>10</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129108044</v>
+        <v>129112438</v>
       </c>
       <c r="B2" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455412</v>
+        <v>455258</v>
       </c>
       <c r="R2" t="n">
-        <v>6773172</v>
+        <v>6773321</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129112610</v>
+        <v>129112479</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455308</v>
+        <v>455272</v>
       </c>
       <c r="R3" t="n">
-        <v>6773282</v>
+        <v>6773302</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129112438</v>
+        <v>129112610</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455258</v>
+        <v>455308</v>
       </c>
       <c r="R4" t="n">
-        <v>6773321</v>
+        <v>6773282</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112479</v>
+        <v>129108044</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455272</v>
+        <v>455412</v>
       </c>
       <c r="R5" t="n">
-        <v>6773302</v>
+        <v>6773172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129110737</v>
+        <v>129113882</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>97598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455259</v>
+        <v>455329</v>
       </c>
       <c r="R8" t="n">
-        <v>6773216</v>
+        <v>6773342</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129109404</v>
+        <v>129107453</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455484</v>
+        <v>455385</v>
       </c>
       <c r="R9" t="n">
-        <v>6773211</v>
+        <v>6773193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129110825</v>
+        <v>129113163</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455259</v>
+        <v>455283</v>
       </c>
       <c r="R10" t="n">
-        <v>6773246</v>
+        <v>6773359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129113163</v>
+        <v>129110737</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455283</v>
+        <v>455259</v>
       </c>
       <c r="R11" t="n">
-        <v>6773359</v>
+        <v>6773216</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129107453</v>
+        <v>129110825</v>
       </c>
       <c r="B12" t="n">
         <v>79044</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455385</v>
+        <v>455259</v>
       </c>
       <c r="R12" t="n">
-        <v>6773193</v>
+        <v>6773246</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129113882</v>
+        <v>129109404</v>
       </c>
       <c r="B13" t="n">
-        <v>97598</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455329</v>
+        <v>455484</v>
       </c>
       <c r="R13" t="n">
-        <v>6773342</v>
+        <v>6773211</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129107916</v>
+        <v>129110979</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455389</v>
+        <v>455258</v>
       </c>
       <c r="R17" t="n">
-        <v>6773170</v>
+        <v>6773256</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129110979</v>
+        <v>129107916</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455258</v>
+        <v>455389</v>
       </c>
       <c r="R18" t="n">
-        <v>6773256</v>
+        <v>6773170</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129112407</v>
+        <v>129107601</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455248</v>
+        <v>455352</v>
       </c>
       <c r="R23" t="n">
-        <v>6773310</v>
+        <v>6773200</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129114098</v>
+        <v>129112407</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3181,13 +3181,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455394</v>
+        <v>455248</v>
       </c>
       <c r="R25" t="n">
-        <v>6773349</v>
+        <v>6773310</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129113094</v>
+        <v>129107736</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455301</v>
+        <v>455372</v>
       </c>
       <c r="R26" t="n">
-        <v>6773331</v>
+        <v>6773181</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129107601</v>
+        <v>129114098</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455352</v>
+        <v>455394</v>
       </c>
       <c r="R27" t="n">
-        <v>6773200</v>
+        <v>6773349</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129107736</v>
+        <v>129113094</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3502,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455372</v>
+        <v>455301</v>
       </c>
       <c r="R28" t="n">
-        <v>6773181</v>
+        <v>6773331</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129112885</v>
+        <v>129110462</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455288</v>
+        <v>455333</v>
       </c>
       <c r="R29" t="n">
-        <v>6773318</v>
+        <v>6773289</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129110462</v>
+        <v>129112885</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455333</v>
+        <v>455288</v>
       </c>
       <c r="R30" t="n">
-        <v>6773289</v>
+        <v>6773318</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129110662</v>
+        <v>129109514</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,34 +4018,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455273</v>
+        <v>455494</v>
       </c>
       <c r="R33" t="n">
-        <v>6773208</v>
+        <v>6773187</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,7 +4119,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129110692</v>
+        <v>129110662</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -4149,13 +4154,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455270</v>
+        <v>455273</v>
       </c>
       <c r="R34" t="n">
-        <v>6773216</v>
+        <v>6773208</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4328,10 +4333,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129107986</v>
+        <v>129110692</v>
       </c>
       <c r="B36" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4339,21 +4344,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4363,13 +4368,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455389</v>
+        <v>455270</v>
       </c>
       <c r="R36" t="n">
-        <v>6773170</v>
+        <v>6773216</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4435,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129109514</v>
+        <v>129107986</v>
       </c>
       <c r="B37" t="n">
-        <v>57724</v>
+        <v>78801</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4446,39 +4451,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455494</v>
+        <v>455389</v>
       </c>
       <c r="R37" t="n">
-        <v>6773187</v>
+        <v>6773170</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129108956</v>
+        <v>129110861</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455473</v>
+        <v>455267</v>
       </c>
       <c r="R38" t="n">
-        <v>6773221</v>
+        <v>6773233</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129110861</v>
+        <v>129108956</v>
       </c>
       <c r="B39" t="n">
         <v>79044</v>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455267</v>
+        <v>455473</v>
       </c>
       <c r="R39" t="n">
-        <v>6773233</v>
+        <v>6773221</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129107072</v>
+        <v>129110029</v>
       </c>
       <c r="B41" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455389</v>
+        <v>455333</v>
       </c>
       <c r="R41" t="n">
-        <v>6773203</v>
+        <v>6773241</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129110029</v>
+        <v>129114507</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455333</v>
+        <v>455391</v>
       </c>
       <c r="R42" t="n">
-        <v>6773241</v>
+        <v>6773367</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129114507</v>
+        <v>129107072</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455391</v>
+        <v>455389</v>
       </c>
       <c r="R44" t="n">
-        <v>6773367</v>
+        <v>6773203</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129112595</v>
+        <v>129109369</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455279</v>
+        <v>455473</v>
       </c>
       <c r="R46" t="n">
-        <v>6773275</v>
+        <v>6773219</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129109369</v>
+        <v>129112595</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455473</v>
+        <v>455279</v>
       </c>
       <c r="R47" t="n">
-        <v>6773219</v>
+        <v>6773275</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129114165</v>
+        <v>129110148</v>
       </c>
       <c r="B50" t="n">
         <v>79044</v>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455390</v>
+        <v>455349</v>
       </c>
       <c r="R50" t="n">
-        <v>6773344</v>
+        <v>6773250</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129110148</v>
+        <v>129114165</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455349</v>
+        <v>455390</v>
       </c>
       <c r="R51" t="n">
-        <v>6773250</v>
+        <v>6773344</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6162,54 +6162,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129112645</v>
+        <v>129112375</v>
       </c>
       <c r="B53" t="n">
-        <v>58157</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103001</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455308</v>
+        <v>455269</v>
       </c>
       <c r="R53" t="n">
-        <v>6773282</v>
+        <v>6773288</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6278,45 +6269,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129112375</v>
+        <v>129112645</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>58157</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>103001</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455269</v>
+        <v>455308</v>
       </c>
       <c r="R54" t="n">
-        <v>6773288</v>
+        <v>6773282</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6385,32 +6385,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129114115</v>
+        <v>129110915</v>
       </c>
       <c r="B55" t="n">
-        <v>83012</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455394</v>
+        <v>455267</v>
       </c>
       <c r="R55" t="n">
-        <v>6773349</v>
+        <v>6773233</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6711,32 +6711,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129110915</v>
+        <v>129113107</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455267</v>
+        <v>455308</v>
       </c>
       <c r="R58" t="n">
-        <v>6773233</v>
+        <v>6773336</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6818,10 +6818,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129113107</v>
+        <v>129114697</v>
       </c>
       <c r="B59" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6829,21 +6829,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455308</v>
+        <v>455428</v>
       </c>
       <c r="R59" t="n">
-        <v>6773336</v>
+        <v>6773376</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7032,10 +7032,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129114697</v>
+        <v>129114115</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7043,21 +7043,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7067,13 +7067,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455428</v>
+        <v>455394</v>
       </c>
       <c r="R61" t="n">
-        <v>6773376</v>
+        <v>6773349</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129110475</v>
+        <v>129114704</v>
       </c>
       <c r="B62" t="n">
         <v>8450</v>
@@ -7168,21 +7168,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455333</v>
+        <v>455438</v>
       </c>
       <c r="R62" t="n">
-        <v>6773289</v>
+        <v>6773400</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7251,32 +7246,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129114704</v>
+        <v>129112093</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7286,10 +7281,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455438</v>
+        <v>455241</v>
       </c>
       <c r="R63" t="n">
-        <v>6773400</v>
+        <v>6773279</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7465,10 +7460,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129112093</v>
+        <v>129107474</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7476,34 +7471,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455241</v>
+        <v>455385</v>
       </c>
       <c r="R65" t="n">
-        <v>6773279</v>
+        <v>6773193</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7572,38 +7572,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129107474</v>
+        <v>129110475</v>
       </c>
       <c r="B66" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455385</v>
+        <v>455333</v>
       </c>
       <c r="R66" t="n">
-        <v>6773193</v>
+        <v>6773289</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7684,10 +7684,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129113193</v>
+        <v>129110941</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7695,39 +7695,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455283</v>
+        <v>455281</v>
       </c>
       <c r="R67" t="n">
-        <v>6773359</v>
+        <v>6773251</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7796,10 +7791,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129110941</v>
+        <v>129113193</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7807,34 +7802,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455281</v>
+        <v>455283</v>
       </c>
       <c r="R68" t="n">
-        <v>6773251</v>
+        <v>6773359</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8117,10 +8117,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124330</v>
+        <v>129113854</v>
       </c>
       <c r="B71" t="n">
-        <v>92873</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8128,41 +8128,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455412</v>
+        <v>455337</v>
       </c>
       <c r="R71" t="n">
-        <v>6773178</v>
+        <v>6773325</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8192,18 +8185,27 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8222,10 +8224,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129113854</v>
+        <v>129124330</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>92873</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8233,34 +8235,41 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455337</v>
+        <v>455412</v>
       </c>
       <c r="R72" t="n">
-        <v>6773325</v>
+        <v>6773178</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8290,27 +8299,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8436,48 +8436,51 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129112107</v>
+        <v>129114483</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>90935</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455235</v>
+        <v>455394</v>
       </c>
       <c r="R74" t="n">
-        <v>6773290</v>
+        <v>6773349</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8519,12 +8522,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8543,10 +8552,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129110810</v>
+        <v>129112107</v>
       </c>
       <c r="B75" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8554,39 +8563,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455237</v>
+        <v>455235</v>
       </c>
       <c r="R75" t="n">
-        <v>6773232</v>
+        <v>6773290</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8655,51 +8659,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129114483</v>
+        <v>129110810</v>
       </c>
       <c r="B76" t="n">
-        <v>90935</v>
+        <v>57724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455394</v>
+        <v>455237</v>
       </c>
       <c r="R76" t="n">
-        <v>6773349</v>
+        <v>6773232</v>
       </c>
       <c r="S76" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8741,18 +8747,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -10721,41 +10721,40 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129516251</v>
+        <v>129516224</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>57887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10765,10 +10764,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>455481</v>
+        <v>455383</v>
       </c>
       <c r="R95" t="n">
-        <v>6773645</v>
+        <v>6773634</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10809,7 +10808,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10828,40 +10826,41 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129516224</v>
+        <v>129516251</v>
       </c>
       <c r="B96" t="n">
-        <v>57887</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10871,10 +10870,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>455383</v>
+        <v>455481</v>
       </c>
       <c r="R96" t="n">
-        <v>6773634</v>
+        <v>6773645</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10915,6 +10914,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11468,45 +11468,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129516220</v>
+        <v>129516245</v>
       </c>
       <c r="B102" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>455424</v>
+        <v>455365</v>
       </c>
       <c r="R102" t="n">
-        <v>6773664</v>
+        <v>6773649</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11547,6 +11556,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11565,54 +11575,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129516245</v>
+        <v>129516220</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>455365</v>
+        <v>455424</v>
       </c>
       <c r="R103" t="n">
-        <v>6773649</v>
+        <v>6773664</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11653,7 +11654,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11885,45 +11885,54 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129516271</v>
+        <v>129516247</v>
       </c>
       <c r="B106" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>455378</v>
+        <v>455382</v>
       </c>
       <c r="R106" t="n">
-        <v>6773718</v>
+        <v>6773633</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11964,6 +11973,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11982,54 +11992,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129516247</v>
+        <v>129516271</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>455382</v>
+        <v>455378</v>
       </c>
       <c r="R107" t="n">
-        <v>6773633</v>
+        <v>6773718</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12070,7 +12071,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12507,54 +12507,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129516252</v>
+        <v>129516226</v>
       </c>
       <c r="B112" t="n">
-        <v>8450</v>
+        <v>91504</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>112</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>455472</v>
+        <v>455448</v>
       </c>
       <c r="R112" t="n">
-        <v>6773649</v>
+        <v>6773621</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12595,7 +12586,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12614,10 +12604,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129516226</v>
+        <v>129516227</v>
       </c>
       <c r="B113" t="n">
-        <v>91504</v>
+        <v>57724</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12625,34 +12615,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>455448</v>
+        <v>455382</v>
       </c>
       <c r="R113" t="n">
-        <v>6773621</v>
+        <v>6773594</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12711,40 +12709,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129516227</v>
+        <v>129516252</v>
       </c>
       <c r="B114" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12754,10 +12753,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455382</v>
+        <v>455472</v>
       </c>
       <c r="R114" t="n">
-        <v>6773594</v>
+        <v>6773649</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12798,6 +12797,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12913,10 +12913,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129516275</v>
+        <v>129516228</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12924,34 +12924,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>455381</v>
+        <v>455480</v>
       </c>
       <c r="R116" t="n">
-        <v>6773638</v>
+        <v>6773643</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13010,10 +13018,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129516228</v>
+        <v>129516275</v>
       </c>
       <c r="B117" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13021,42 +13029,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>455480</v>
+        <v>455381</v>
       </c>
       <c r="R117" t="n">
-        <v>6773643</v>
+        <v>6773638</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13436,10 +13436,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129516270</v>
+        <v>129516222</v>
       </c>
       <c r="B121" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13447,21 +13447,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>455383</v>
+        <v>455510</v>
       </c>
       <c r="R121" t="n">
-        <v>6773719</v>
+        <v>6773641</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13533,10 +13533,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129516222</v>
+        <v>129516270</v>
       </c>
       <c r="B122" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13544,21 +13544,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13568,10 +13568,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>455510</v>
+        <v>455383</v>
       </c>
       <c r="R122" t="n">
-        <v>6773641</v>
+        <v>6773719</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14476,45 +14476,49 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129520126</v>
+        <v>129524264</v>
       </c>
       <c r="B131" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>455494</v>
+        <v>455687</v>
       </c>
       <c r="R131" t="n">
-        <v>6773317</v>
+        <v>6773304</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14546,7 +14550,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14556,7 +14560,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14583,49 +14587,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129524264</v>
+        <v>129520126</v>
       </c>
       <c r="B132" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>455687</v>
+        <v>455494</v>
       </c>
       <c r="R132" t="n">
-        <v>6773304</v>
+        <v>6773317</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14694,45 +14694,49 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129524757</v>
+        <v>129522291</v>
       </c>
       <c r="B133" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>455745</v>
+        <v>455660</v>
       </c>
       <c r="R133" t="n">
-        <v>6773387</v>
+        <v>6773320</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14764,7 +14768,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14774,7 +14778,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14801,7 +14805,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129521661</v>
+        <v>129524757</v>
       </c>
       <c r="B134" t="n">
         <v>79044</v>
@@ -14836,10 +14840,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>455547</v>
+        <v>455745</v>
       </c>
       <c r="R134" t="n">
-        <v>6773313</v>
+        <v>6773387</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14871,7 +14875,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14881,12 +14885,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i äldre tallar samt gran</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14913,49 +14912,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129522291</v>
+        <v>129521661</v>
       </c>
       <c r="B135" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>455660</v>
+        <v>455547</v>
       </c>
       <c r="R135" t="n">
-        <v>6773320</v>
+        <v>6773313</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14998,6 +14993,11 @@
       <c r="AB135" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i äldre tallar samt gran</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15243,32 +15243,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129521094</v>
+        <v>129524794</v>
       </c>
       <c r="B138" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15278,10 +15278,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>455547</v>
+        <v>455725</v>
       </c>
       <c r="R138" t="n">
-        <v>6773313</v>
+        <v>6773375</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15350,45 +15350,49 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129524794</v>
+        <v>129522884</v>
       </c>
       <c r="B139" t="n">
-        <v>79663</v>
+        <v>92835</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>455725</v>
+        <v>455654</v>
       </c>
       <c r="R139" t="n">
-        <v>6773375</v>
+        <v>6773335</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15420,7 +15424,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15430,7 +15434,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15457,10 +15461,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129522884</v>
+        <v>129521094</v>
       </c>
       <c r="B140" t="n">
-        <v>92835</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15468,38 +15472,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>455654</v>
+        <v>455547</v>
       </c>
       <c r="R140" t="n">
-        <v>6773335</v>
+        <v>6773313</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15568,10 +15568,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129520408</v>
+        <v>129525475</v>
       </c>
       <c r="B141" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15579,34 +15579,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>455524</v>
+        <v>455623</v>
       </c>
       <c r="R141" t="n">
-        <v>6773304</v>
+        <v>6773393</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15638,7 +15643,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15648,7 +15653,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15675,7 +15680,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129522134</v>
+        <v>129520408</v>
       </c>
       <c r="B142" t="n">
         <v>79044</v>
@@ -15710,10 +15715,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>455646</v>
+        <v>455524</v>
       </c>
       <c r="R142" t="n">
-        <v>6773308</v>
+        <v>6773304</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15782,7 +15787,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129522761</v>
+        <v>129522134</v>
       </c>
       <c r="B143" t="n">
         <v>79044</v>
@@ -15817,10 +15822,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>455639</v>
+        <v>455646</v>
       </c>
       <c r="R143" t="n">
-        <v>6773364</v>
+        <v>6773308</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15863,11 +15868,6 @@
       <c r="AB143" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15894,7 +15894,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129525475</v>
+        <v>129524463</v>
       </c>
       <c r="B144" t="n">
         <v>57724</v>
@@ -15925,7 +15925,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -15934,10 +15934,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>455623</v>
+        <v>455664</v>
       </c>
       <c r="R144" t="n">
-        <v>6773393</v>
+        <v>6773257</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16006,38 +16006,38 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129524463</v>
+        <v>129522915</v>
       </c>
       <c r="B145" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>455664</v>
+        <v>455660</v>
       </c>
       <c r="R145" t="n">
-        <v>6773257</v>
+        <v>6773320</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16118,50 +16118,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129522915</v>
+        <v>129522761</v>
       </c>
       <c r="B146" t="n">
-        <v>56917</v>
+        <v>79044</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>455660</v>
+        <v>455639</v>
       </c>
       <c r="R146" t="n">
-        <v>6773320</v>
+        <v>6773364</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16204,6 +16199,11 @@
       <c r="AB146" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16230,32 +16230,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129520622</v>
+        <v>129525079</v>
       </c>
       <c r="B147" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16265,10 +16265,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>455540</v>
+        <v>455743</v>
       </c>
       <c r="R147" t="n">
-        <v>6773296</v>
+        <v>6773438</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16300,7 +16300,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16310,7 +16310,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16449,32 +16449,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129525079</v>
+        <v>129520622</v>
       </c>
       <c r="B149" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16484,10 +16484,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>455743</v>
+        <v>455540</v>
       </c>
       <c r="R149" t="n">
-        <v>6773438</v>
+        <v>6773296</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17759,10 +17759,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129522130</v>
+        <v>129520605</v>
       </c>
       <c r="B161" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17770,21 +17770,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17794,10 +17794,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>455646</v>
+        <v>455537</v>
       </c>
       <c r="R161" t="n">
-        <v>6773308</v>
+        <v>6773309</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17840,6 +17840,11 @@
       <c r="AB161" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17866,10 +17871,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129520605</v>
+        <v>129522130</v>
       </c>
       <c r="B162" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17877,21 +17882,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17901,10 +17906,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>455537</v>
+        <v>455646</v>
       </c>
       <c r="R162" t="n">
-        <v>6773309</v>
+        <v>6773308</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17947,11 +17952,6 @@
       <c r="AB162" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18416,10 +18416,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129521993</v>
+        <v>129522648</v>
       </c>
       <c r="B167" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18427,37 +18427,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>455615</v>
+        <v>455650</v>
       </c>
       <c r="R167" t="n">
-        <v>6773317</v>
+        <v>6773365</v>
       </c>
       <c r="S167" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18497,11 +18502,6 @@
       <c r="AB167" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18528,10 +18528,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129522648</v>
+        <v>129521993</v>
       </c>
       <c r="B168" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18539,42 +18539,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>455650</v>
+        <v>455615</v>
       </c>
       <c r="R168" t="n">
-        <v>6773365</v>
+        <v>6773317</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18614,6 +18609,11 @@
       <c r="AB168" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19073,45 +19073,49 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129520755</v>
+        <v>129524033</v>
       </c>
       <c r="B173" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>455550</v>
+        <v>455658</v>
       </c>
       <c r="R173" t="n">
-        <v>6773288</v>
+        <v>6773278</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19154,11 +19158,6 @@
       <c r="AB173" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Vedsvamp på låga bredvid</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19185,62 +19184,48 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129520115</v>
+        <v>129524675</v>
       </c>
       <c r="B174" t="n">
-        <v>56917</v>
+        <v>91574</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>455499</v>
+        <v>455677</v>
       </c>
       <c r="R174" t="n">
-        <v>6773331</v>
+        <v>6773324</v>
       </c>
       <c r="S174" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19269,7 +19254,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19279,12 +19264,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19311,10 +19291,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129524675</v>
+        <v>129520755</v>
       </c>
       <c r="B175" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19322,21 +19302,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19346,10 +19326,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>455677</v>
+        <v>455550</v>
       </c>
       <c r="R175" t="n">
-        <v>6773324</v>
+        <v>6773288</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19381,7 +19361,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19391,7 +19371,12 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Vedsvamp på låga bredvid</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19418,48 +19403,62 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129520654</v>
+        <v>129520115</v>
       </c>
       <c r="B176" t="n">
-        <v>79663</v>
+        <v>56917</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>455559</v>
+        <v>455499</v>
       </c>
       <c r="R176" t="n">
-        <v>6773284</v>
+        <v>6773331</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19499,6 +19498,11 @@
       <c r="AB176" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19525,49 +19529,45 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129524033</v>
+        <v>129520654</v>
       </c>
       <c r="B177" t="n">
-        <v>92835</v>
+        <v>79663</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>455658</v>
+        <v>455559</v>
       </c>
       <c r="R177" t="n">
-        <v>6773278</v>
+        <v>6773284</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19636,10 +19636,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129561832</v>
+        <v>129561893</v>
       </c>
       <c r="B178" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19647,37 +19647,42 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>455852</v>
+        <v>455839</v>
       </c>
       <c r="R178" t="n">
-        <v>6773480</v>
+        <v>6773507</v>
       </c>
       <c r="S178" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19743,10 +19748,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129561893</v>
+        <v>129561832</v>
       </c>
       <c r="B179" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19754,42 +19759,37 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>455839</v>
+        <v>455852</v>
       </c>
       <c r="R179" t="n">
-        <v>6773507</v>
+        <v>6773480</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19855,37 +19855,38 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129563002</v>
+        <v>129561895</v>
       </c>
       <c r="B180" t="n">
-        <v>98727</v>
+        <v>8450</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -19894,10 +19895,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>455729</v>
+        <v>455839</v>
       </c>
       <c r="R180" t="n">
-        <v>6773474</v>
+        <v>6773507</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19929,7 +19930,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19939,12 +19940,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Massor minst 100 st</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19971,45 +19967,49 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129561879</v>
+        <v>129563002</v>
       </c>
       <c r="B181" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>455839</v>
+        <v>455729</v>
       </c>
       <c r="R181" t="n">
-        <v>6773507</v>
+        <v>6773474</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20041,7 +20041,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20051,7 +20051,12 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Massor minst 100 st</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20078,10 +20083,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129561829</v>
+        <v>129561879</v>
       </c>
       <c r="B182" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20089,42 +20094,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>455852</v>
+        <v>455839</v>
       </c>
       <c r="R182" t="n">
-        <v>6773480</v>
+        <v>6773507</v>
       </c>
       <c r="S182" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20190,38 +20190,38 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129561895</v>
+        <v>129561829</v>
       </c>
       <c r="B183" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="M183" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -20230,13 +20230,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>455839</v>
+        <v>455852</v>
       </c>
       <c r="R183" t="n">
-        <v>6773507</v>
+        <v>6773480</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112438</v>
+        <v>129112479</v>
       </c>
       <c r="B2" t="n">
         <v>79044</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455258</v>
+        <v>455272</v>
       </c>
       <c r="R2" t="n">
-        <v>6773321</v>
+        <v>6773302</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129112479</v>
+        <v>129108044</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455272</v>
+        <v>455412</v>
       </c>
       <c r="R3" t="n">
-        <v>6773302</v>
+        <v>6773172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129108044</v>
+        <v>129112438</v>
       </c>
       <c r="B5" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455412</v>
+        <v>455258</v>
       </c>
       <c r="R5" t="n">
-        <v>6773172</v>
+        <v>6773321</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129113882</v>
+        <v>129110737</v>
       </c>
       <c r="B8" t="n">
-        <v>97598</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455329</v>
+        <v>455259</v>
       </c>
       <c r="R8" t="n">
-        <v>6773342</v>
+        <v>6773216</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129107453</v>
+        <v>129113882</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455385</v>
+        <v>455329</v>
       </c>
       <c r="R9" t="n">
-        <v>6773193</v>
+        <v>6773342</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129113163</v>
+        <v>129110825</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455283</v>
+        <v>455259</v>
       </c>
       <c r="R10" t="n">
-        <v>6773359</v>
+        <v>6773246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129110737</v>
+        <v>129107453</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455259</v>
+        <v>455385</v>
       </c>
       <c r="R11" t="n">
-        <v>6773216</v>
+        <v>6773193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129110825</v>
+        <v>129109404</v>
       </c>
       <c r="B12" t="n">
         <v>79044</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455259</v>
+        <v>455484</v>
       </c>
       <c r="R12" t="n">
-        <v>6773246</v>
+        <v>6773211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129109404</v>
+        <v>129113163</v>
       </c>
       <c r="B13" t="n">
         <v>79044</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455484</v>
+        <v>455283</v>
       </c>
       <c r="R13" t="n">
-        <v>6773211</v>
+        <v>6773359</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129109613</v>
+        <v>129107601</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455494</v>
+        <v>455352</v>
       </c>
       <c r="R22" t="n">
-        <v>6773197</v>
+        <v>6773200</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129107601</v>
+        <v>129112407</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455352</v>
+        <v>455248</v>
       </c>
       <c r="R23" t="n">
-        <v>6773200</v>
+        <v>6773310</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129111088</v>
+        <v>129107736</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455248</v>
+        <v>455372</v>
       </c>
       <c r="R24" t="n">
-        <v>6773274</v>
+        <v>6773181</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129112407</v>
+        <v>129109613</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455248</v>
+        <v>455494</v>
       </c>
       <c r="R25" t="n">
-        <v>6773310</v>
+        <v>6773197</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129107736</v>
+        <v>129111088</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455372</v>
+        <v>455248</v>
       </c>
       <c r="R26" t="n">
-        <v>6773181</v>
+        <v>6773274</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129110462</v>
+        <v>129113791</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,37 +3585,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455333</v>
+        <v>455304</v>
       </c>
       <c r="R29" t="n">
-        <v>6773289</v>
+        <v>6773316</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3681,7 +3686,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129112885</v>
+        <v>129110462</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3716,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455288</v>
+        <v>455333</v>
       </c>
       <c r="R30" t="n">
-        <v>6773318</v>
+        <v>6773289</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3788,10 +3793,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129113791</v>
+        <v>129112885</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3799,42 +3804,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455304</v>
+        <v>455288</v>
       </c>
       <c r="R31" t="n">
-        <v>6773316</v>
+        <v>6773318</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129109514</v>
+        <v>129110662</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,39 +4018,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455494</v>
+        <v>455273</v>
       </c>
       <c r="R33" t="n">
-        <v>6773187</v>
+        <v>6773208</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4119,7 +4114,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129110662</v>
+        <v>129106783</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -4154,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455273</v>
+        <v>455407</v>
       </c>
       <c r="R34" t="n">
-        <v>6773208</v>
+        <v>6773196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4226,7 +4221,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129106783</v>
+        <v>129110692</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4261,13 +4256,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455407</v>
+        <v>455270</v>
       </c>
       <c r="R35" t="n">
-        <v>6773196</v>
+        <v>6773216</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4333,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129110692</v>
+        <v>129107986</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,21 +4339,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4368,13 +4363,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455270</v>
+        <v>455389</v>
       </c>
       <c r="R36" t="n">
-        <v>6773216</v>
+        <v>6773170</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4440,10 +4435,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129107986</v>
+        <v>129109514</v>
       </c>
       <c r="B37" t="n">
-        <v>78801</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4451,34 +4446,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455389</v>
+        <v>455494</v>
       </c>
       <c r="R37" t="n">
-        <v>6773170</v>
+        <v>6773187</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129110029</v>
+        <v>129107072</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455333</v>
+        <v>455389</v>
       </c>
       <c r="R41" t="n">
-        <v>6773241</v>
+        <v>6773203</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129114507</v>
+        <v>129107679</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455391</v>
+        <v>455353</v>
       </c>
       <c r="R42" t="n">
-        <v>6773367</v>
+        <v>6773191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129107679</v>
+        <v>129110029</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455353</v>
+        <v>455333</v>
       </c>
       <c r="R43" t="n">
-        <v>6773191</v>
+        <v>6773241</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129107072</v>
+        <v>129114507</v>
       </c>
       <c r="B44" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455389</v>
+        <v>455391</v>
       </c>
       <c r="R44" t="n">
-        <v>6773203</v>
+        <v>6773367</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5729,50 +5729,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129109267</v>
+        <v>129110148</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455477</v>
+        <v>455349</v>
       </c>
       <c r="R49" t="n">
-        <v>6773206</v>
+        <v>6773250</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5836,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129110148</v>
+        <v>129114165</v>
       </c>
       <c r="B50" t="n">
         <v>79044</v>
@@ -5876,10 +5871,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455349</v>
+        <v>455390</v>
       </c>
       <c r="R50" t="n">
-        <v>6773250</v>
+        <v>6773344</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5948,7 +5943,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129114165</v>
+        <v>129109151</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5983,10 +5978,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455390</v>
+        <v>455459</v>
       </c>
       <c r="R51" t="n">
-        <v>6773344</v>
+        <v>6773195</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6055,45 +6050,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129109151</v>
+        <v>129109267</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455459</v>
+        <v>455477</v>
       </c>
       <c r="R52" t="n">
-        <v>6773195</v>
+        <v>6773206</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6162,45 +6162,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129112375</v>
+        <v>129112645</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>58157</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>103001</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455269</v>
+        <v>455308</v>
       </c>
       <c r="R53" t="n">
-        <v>6773288</v>
+        <v>6773282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6269,54 +6278,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129112645</v>
+        <v>129112375</v>
       </c>
       <c r="B54" t="n">
-        <v>58157</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103001</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455308</v>
+        <v>455269</v>
       </c>
       <c r="R54" t="n">
-        <v>6773282</v>
+        <v>6773288</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6385,32 +6385,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129110915</v>
+        <v>129114697</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455267</v>
+        <v>455428</v>
       </c>
       <c r="R55" t="n">
-        <v>6773233</v>
+        <v>6773376</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6492,50 +6492,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129108995</v>
+        <v>129110757</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455473</v>
+        <v>455252</v>
       </c>
       <c r="R56" t="n">
-        <v>6773221</v>
+        <v>6773222</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6604,32 +6599,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129112005</v>
+        <v>129113107</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6639,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455235</v>
+        <v>455308</v>
       </c>
       <c r="R57" t="n">
-        <v>6773290</v>
+        <v>6773336</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6711,10 +6706,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129113107</v>
+        <v>129114115</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>83012</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6722,21 +6717,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6746,13 +6741,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455308</v>
+        <v>455394</v>
       </c>
       <c r="R58" t="n">
-        <v>6773336</v>
+        <v>6773349</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6818,32 +6813,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129114697</v>
+        <v>129112005</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6853,10 +6848,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>455428</v>
+        <v>455235</v>
       </c>
       <c r="R59" t="n">
-        <v>6773376</v>
+        <v>6773290</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6925,32 +6920,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129110757</v>
+        <v>129110915</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6960,10 +6955,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>455252</v>
+        <v>455267</v>
       </c>
       <c r="R60" t="n">
-        <v>6773222</v>
+        <v>6773233</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7032,48 +7027,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129114115</v>
+        <v>129108995</v>
       </c>
       <c r="B61" t="n">
-        <v>83012</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>455394</v>
+        <v>455473</v>
       </c>
       <c r="R61" t="n">
-        <v>6773349</v>
+        <v>6773221</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7139,32 +7139,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129114704</v>
+        <v>129112093</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455438</v>
+        <v>455241</v>
       </c>
       <c r="R62" t="n">
-        <v>6773400</v>
+        <v>6773279</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129112093</v>
+        <v>129110960</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455241</v>
+        <v>455260</v>
       </c>
       <c r="R63" t="n">
-        <v>6773279</v>
+        <v>6773245</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7353,10 +7353,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129110960</v>
+        <v>129107474</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7364,34 +7364,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455260</v>
+        <v>455385</v>
       </c>
       <c r="R64" t="n">
-        <v>6773245</v>
+        <v>6773193</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7460,38 +7465,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129107474</v>
+        <v>129110475</v>
       </c>
       <c r="B65" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7500,10 +7505,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455385</v>
+        <v>455333</v>
       </c>
       <c r="R65" t="n">
-        <v>6773193</v>
+        <v>6773289</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7572,7 +7577,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129110475</v>
+        <v>129114704</v>
       </c>
       <c r="B66" t="n">
         <v>8450</v>
@@ -7601,21 +7606,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455333</v>
+        <v>455438</v>
       </c>
       <c r="R66" t="n">
-        <v>6773289</v>
+        <v>6773400</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7684,7 +7684,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129110941</v>
+        <v>129112114</v>
       </c>
       <c r="B67" t="n">
         <v>79044</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455281</v>
+        <v>455233</v>
       </c>
       <c r="R67" t="n">
-        <v>6773251</v>
+        <v>6773294</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,10 +7791,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129113193</v>
+        <v>129110941</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7802,39 +7802,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455283</v>
+        <v>455281</v>
       </c>
       <c r="R68" t="n">
-        <v>6773359</v>
+        <v>6773251</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7903,10 +7898,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129112114</v>
+        <v>129113193</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7914,34 +7909,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455233</v>
+        <v>455283</v>
       </c>
       <c r="R69" t="n">
-        <v>6773294</v>
+        <v>6773359</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8117,10 +8117,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129113854</v>
+        <v>129124330</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>92873</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8128,34 +8128,41 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455337</v>
+        <v>455412</v>
       </c>
       <c r="R71" t="n">
-        <v>6773325</v>
+        <v>6773178</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8185,27 +8192,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8224,10 +8222,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124330</v>
+        <v>129113854</v>
       </c>
       <c r="B72" t="n">
-        <v>92873</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8235,41 +8233,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455412</v>
+        <v>455337</v>
       </c>
       <c r="R72" t="n">
-        <v>6773178</v>
+        <v>6773325</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8299,18 +8290,27 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8436,51 +8436,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129114483</v>
+        <v>129112107</v>
       </c>
       <c r="B74" t="n">
-        <v>90935</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455394</v>
+        <v>455235</v>
       </c>
       <c r="R74" t="n">
-        <v>6773349</v>
+        <v>6773290</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8522,18 +8519,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8552,10 +8543,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129112107</v>
+        <v>129110810</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8563,34 +8554,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455235</v>
+        <v>455237</v>
       </c>
       <c r="R75" t="n">
-        <v>6773290</v>
+        <v>6773232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8659,53 +8655,51 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129110810</v>
+        <v>129114483</v>
       </c>
       <c r="B76" t="n">
-        <v>57724</v>
+        <v>90935</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455237</v>
+        <v>455394</v>
       </c>
       <c r="R76" t="n">
-        <v>6773232</v>
+        <v>6773349</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8747,12 +8741,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129114734</v>
+        <v>129113900</v>
       </c>
       <c r="B88" t="n">
         <v>79044</v>
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>455438</v>
+        <v>455329</v>
       </c>
       <c r="R88" t="n">
-        <v>6773400</v>
+        <v>6773342</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129113900</v>
+        <v>129114734</v>
       </c>
       <c r="B89" t="n">
         <v>79044</v>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>455329</v>
+        <v>455438</v>
       </c>
       <c r="R89" t="n">
-        <v>6773342</v>
+        <v>6773400</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11468,54 +11468,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129516245</v>
+        <v>129516220</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>455365</v>
+        <v>455424</v>
       </c>
       <c r="R102" t="n">
-        <v>6773649</v>
+        <v>6773664</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11556,7 +11547,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11575,45 +11565,54 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129516220</v>
+        <v>129516245</v>
       </c>
       <c r="B103" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>455424</v>
+        <v>455365</v>
       </c>
       <c r="R103" t="n">
-        <v>6773664</v>
+        <v>6773649</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11654,6 +11653,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11885,54 +11885,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129516247</v>
+        <v>129516271</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>455382</v>
+        <v>455378</v>
       </c>
       <c r="R106" t="n">
-        <v>6773633</v>
+        <v>6773718</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11973,7 +11964,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11992,45 +11982,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129516271</v>
+        <v>129516247</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>455378</v>
+        <v>455382</v>
       </c>
       <c r="R107" t="n">
-        <v>6773718</v>
+        <v>6773633</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12071,6 +12070,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -12816,10 +12816,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129516231</v>
+        <v>129516275</v>
       </c>
       <c r="B115" t="n">
-        <v>92873</v>
+        <v>79044</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12827,21 +12827,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12851,10 +12851,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>455353</v>
+        <v>455381</v>
       </c>
       <c r="R115" t="n">
-        <v>6773643</v>
+        <v>6773638</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13018,10 +13018,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129516275</v>
+        <v>129516231</v>
       </c>
       <c r="B117" t="n">
-        <v>79044</v>
+        <v>92873</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13029,21 +13029,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13053,10 +13053,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>455381</v>
+        <v>455353</v>
       </c>
       <c r="R117" t="n">
-        <v>6773638</v>
+        <v>6773643</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13436,10 +13436,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129516222</v>
+        <v>129516270</v>
       </c>
       <c r="B121" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13447,21 +13447,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>455510</v>
+        <v>455383</v>
       </c>
       <c r="R121" t="n">
-        <v>6773641</v>
+        <v>6773719</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13533,10 +13533,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129516270</v>
+        <v>129516222</v>
       </c>
       <c r="B122" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13544,21 +13544,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13568,10 +13568,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>455383</v>
+        <v>455510</v>
       </c>
       <c r="R122" t="n">
-        <v>6773719</v>
+        <v>6773641</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13739,7 +13739,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129516277</v>
+        <v>129516274</v>
       </c>
       <c r="B124" t="n">
         <v>79044</v>
@@ -13774,10 +13774,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>455410</v>
+        <v>455353</v>
       </c>
       <c r="R124" t="n">
-        <v>6773604</v>
+        <v>6773642</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13836,7 +13836,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129516274</v>
+        <v>129516277</v>
       </c>
       <c r="B125" t="n">
         <v>79044</v>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>455353</v>
+        <v>455410</v>
       </c>
       <c r="R125" t="n">
-        <v>6773642</v>
+        <v>6773604</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15024,7 +15024,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129524992</v>
+        <v>129524157</v>
       </c>
       <c r="B136" t="n">
         <v>79044</v>
@@ -15059,10 +15059,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>455715</v>
+        <v>455658</v>
       </c>
       <c r="R136" t="n">
-        <v>6773435</v>
+        <v>6773278</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15105,6 +15105,11 @@
       <c r="AB136" t="inlineStr">
         <is>
           <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15131,7 +15136,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129524157</v>
+        <v>129524992</v>
       </c>
       <c r="B137" t="n">
         <v>79044</v>
@@ -15166,10 +15171,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>455658</v>
+        <v>455715</v>
       </c>
       <c r="R137" t="n">
-        <v>6773278</v>
+        <v>6773435</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15212,11 +15217,6 @@
       <c r="AB137" t="inlineStr">
         <is>
           <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15243,45 +15243,49 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129524794</v>
+        <v>129522884</v>
       </c>
       <c r="B138" t="n">
-        <v>79663</v>
+        <v>92835</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>455725</v>
+        <v>455654</v>
       </c>
       <c r="R138" t="n">
-        <v>6773375</v>
+        <v>6773335</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15313,7 +15317,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15323,7 +15327,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15350,49 +15354,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129522884</v>
+        <v>129524794</v>
       </c>
       <c r="B139" t="n">
-        <v>92835</v>
+        <v>79663</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>455654</v>
+        <v>455725</v>
       </c>
       <c r="R139" t="n">
-        <v>6773335</v>
+        <v>6773375</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15424,7 +15424,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15568,10 +15568,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129525475</v>
+        <v>129522761</v>
       </c>
       <c r="B141" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15579,39 +15579,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>455623</v>
+        <v>455639</v>
       </c>
       <c r="R141" t="n">
-        <v>6773393</v>
+        <v>6773364</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15643,7 +15638,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15653,7 +15648,12 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15894,38 +15894,38 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129524463</v>
+        <v>129522915</v>
       </c>
       <c r="B144" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -15934,10 +15934,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>455664</v>
+        <v>455660</v>
       </c>
       <c r="R144" t="n">
-        <v>6773257</v>
+        <v>6773320</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15979,7 +15979,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16006,38 +16006,38 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129522915</v>
+        <v>129525475</v>
       </c>
       <c r="B145" t="n">
-        <v>56917</v>
+        <v>57724</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>455660</v>
+        <v>455623</v>
       </c>
       <c r="R145" t="n">
-        <v>6773320</v>
+        <v>6773393</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16118,10 +16118,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129522761</v>
+        <v>129524463</v>
       </c>
       <c r="B146" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16129,34 +16129,39 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>455639</v>
+        <v>455664</v>
       </c>
       <c r="R146" t="n">
-        <v>6773364</v>
+        <v>6773257</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16188,7 +16193,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16198,12 +16203,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16230,45 +16230,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129525079</v>
+        <v>129520906</v>
       </c>
       <c r="B147" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>455743</v>
+        <v>455570</v>
       </c>
       <c r="R147" t="n">
-        <v>6773438</v>
+        <v>6773300</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16300,7 +16305,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16310,7 +16315,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16337,10 +16342,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129520906</v>
+        <v>129520622</v>
       </c>
       <c r="B148" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16348,39 +16353,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>455570</v>
+        <v>455540</v>
       </c>
       <c r="R148" t="n">
-        <v>6773300</v>
+        <v>6773296</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16449,32 +16449,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129520622</v>
+        <v>129525079</v>
       </c>
       <c r="B149" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16484,10 +16484,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>455540</v>
+        <v>455743</v>
       </c>
       <c r="R149" t="n">
-        <v>6773296</v>
+        <v>6773438</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16667,7 +16667,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129524645</v>
+        <v>129525476</v>
       </c>
       <c r="B151" t="n">
         <v>79044</v>
@@ -16702,10 +16702,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>455677</v>
+        <v>455623</v>
       </c>
       <c r="R151" t="n">
-        <v>6773324</v>
+        <v>6773393</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16774,7 +16774,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129525476</v>
+        <v>129524645</v>
       </c>
       <c r="B152" t="n">
         <v>79044</v>
@@ -16809,10 +16809,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>455623</v>
+        <v>455677</v>
       </c>
       <c r="R152" t="n">
-        <v>6773393</v>
+        <v>6773324</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17103,49 +17103,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129522797</v>
+        <v>129520463</v>
       </c>
       <c r="B155" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>455650</v>
+        <v>455514</v>
       </c>
       <c r="R155" t="n">
-        <v>6773365</v>
+        <v>6773311</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17214,45 +17210,49 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129525097</v>
+        <v>129522797</v>
       </c>
       <c r="B156" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>455756</v>
+        <v>455650</v>
       </c>
       <c r="R156" t="n">
-        <v>6773423</v>
+        <v>6773365</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17321,7 +17321,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129520463</v>
+        <v>129525097</v>
       </c>
       <c r="B157" t="n">
         <v>79044</v>
@@ -17356,10 +17356,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>455514</v>
+        <v>455756</v>
       </c>
       <c r="R157" t="n">
-        <v>6773311</v>
+        <v>6773423</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17401,7 +17401,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18197,10 +18197,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129520768</v>
+        <v>129524860</v>
       </c>
       <c r="B165" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18208,34 +18208,39 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>455562</v>
+        <v>455743</v>
       </c>
       <c r="R165" t="n">
-        <v>6773304</v>
+        <v>6773384</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18267,7 +18272,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18277,7 +18282,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18304,10 +18309,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129524860</v>
+        <v>129521008</v>
       </c>
       <c r="B166" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18315,39 +18320,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>455743</v>
+        <v>455562</v>
       </c>
       <c r="R166" t="n">
-        <v>6773384</v>
+        <v>6773304</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18379,7 +18379,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18389,7 +18389,12 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18416,10 +18421,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129522648</v>
+        <v>129521993</v>
       </c>
       <c r="B167" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18427,42 +18432,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>455650</v>
+        <v>455615</v>
       </c>
       <c r="R167" t="n">
-        <v>6773365</v>
+        <v>6773317</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18502,6 +18502,11 @@
       <c r="AB167" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18528,10 +18533,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129521993</v>
+        <v>129522648</v>
       </c>
       <c r="B168" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18539,37 +18544,42 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>455615</v>
+        <v>455650</v>
       </c>
       <c r="R168" t="n">
-        <v>6773317</v>
+        <v>6773365</v>
       </c>
       <c r="S168" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18609,11 +18619,6 @@
       <c r="AB168" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18640,7 +18645,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129525452</v>
+        <v>129524742</v>
       </c>
       <c r="B169" t="n">
         <v>79044</v>
@@ -18675,10 +18680,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>455677</v>
+        <v>455747</v>
       </c>
       <c r="R169" t="n">
-        <v>6773354</v>
+        <v>6773363</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18721,11 +18726,6 @@
       <c r="AB169" t="inlineStr">
         <is>
           <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18752,7 +18752,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129524742</v>
+        <v>129520910</v>
       </c>
       <c r="B170" t="n">
         <v>79044</v>
@@ -18787,10 +18787,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>455747</v>
+        <v>455570</v>
       </c>
       <c r="R170" t="n">
-        <v>6773363</v>
+        <v>6773300</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18966,7 +18966,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129520910</v>
+        <v>129525452</v>
       </c>
       <c r="B172" t="n">
         <v>79044</v>
@@ -19001,10 +19001,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>455570</v>
+        <v>455677</v>
       </c>
       <c r="R172" t="n">
-        <v>6773300</v>
+        <v>6773354</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19036,7 +19036,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19046,7 +19046,12 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19636,10 +19641,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129561893</v>
+        <v>129561832</v>
       </c>
       <c r="B178" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19647,42 +19652,37 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>455839</v>
+        <v>455852</v>
       </c>
       <c r="R178" t="n">
-        <v>6773507</v>
+        <v>6773480</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19748,10 +19748,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129561832</v>
+        <v>129561893</v>
       </c>
       <c r="B179" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19759,37 +19759,42 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>455852</v>
+        <v>455839</v>
       </c>
       <c r="R179" t="n">
-        <v>6773480</v>
+        <v>6773507</v>
       </c>
       <c r="S179" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19855,40 +19860,35 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129561895</v>
+        <v>129561879</v>
       </c>
       <c r="B180" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
@@ -19967,37 +19967,38 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129563002</v>
+        <v>129561829</v>
       </c>
       <c r="B181" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20006,13 +20007,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>455729</v>
+        <v>455852</v>
       </c>
       <c r="R181" t="n">
-        <v>6773474</v>
+        <v>6773480</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20041,7 +20042,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20051,12 +20052,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Massor minst 100 st</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20083,45 +20079,49 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129561879</v>
+        <v>129563002</v>
       </c>
       <c r="B182" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>455839</v>
+        <v>455729</v>
       </c>
       <c r="R182" t="n">
-        <v>6773507</v>
+        <v>6773474</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20163,7 +20163,12 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Massor minst 100 st</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20190,38 +20195,38 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129561829</v>
+        <v>129561895</v>
       </c>
       <c r="B183" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="M183" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -20230,13 +20235,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>455852</v>
+        <v>455839</v>
       </c>
       <c r="R183" t="n">
-        <v>6773480</v>
+        <v>6773507</v>
       </c>
       <c r="S183" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112479</v>
+        <v>129112804</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455272</v>
+        <v>455289</v>
       </c>
       <c r="R2" t="n">
-        <v>6773302</v>
+        <v>6773299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129108044</v>
+        <v>129112610</v>
       </c>
       <c r="B3" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455412</v>
+        <v>455308</v>
       </c>
       <c r="R3" t="n">
-        <v>6773172</v>
+        <v>6773282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129112610</v>
+        <v>129112438</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455308</v>
+        <v>455258</v>
       </c>
       <c r="R4" t="n">
-        <v>6773282</v>
+        <v>6773321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112438</v>
+        <v>129112479</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455258</v>
+        <v>455272</v>
       </c>
       <c r="R5" t="n">
-        <v>6773321</v>
+        <v>6773302</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129112804</v>
+        <v>129108044</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455289</v>
+        <v>455412</v>
       </c>
       <c r="R6" t="n">
-        <v>6773299</v>
+        <v>6773172</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1429,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129113882</v>
+        <v>129107453</v>
       </c>
       <c r="B9" t="n">
-        <v>97598</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455329</v>
+        <v>455385</v>
       </c>
       <c r="R9" t="n">
-        <v>6773342</v>
+        <v>6773193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129107453</v>
+        <v>129109404</v>
       </c>
       <c r="B11" t="n">
         <v>79044</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455385</v>
+        <v>455484</v>
       </c>
       <c r="R11" t="n">
-        <v>6773193</v>
+        <v>6773211</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129109404</v>
+        <v>129113163</v>
       </c>
       <c r="B12" t="n">
         <v>79044</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455484</v>
+        <v>455283</v>
       </c>
       <c r="R12" t="n">
-        <v>6773211</v>
+        <v>6773359</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129113163</v>
+        <v>129113882</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455283</v>
+        <v>455329</v>
       </c>
       <c r="R13" t="n">
-        <v>6773359</v>
+        <v>6773342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129113791</v>
+        <v>129112885</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,42 +3585,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455304</v>
+        <v>455288</v>
       </c>
       <c r="R29" t="n">
-        <v>6773316</v>
+        <v>6773318</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3793,10 +3788,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129112885</v>
+        <v>129113791</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3804,37 +3799,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455288</v>
+        <v>455304</v>
       </c>
       <c r="R31" t="n">
-        <v>6773318</v>
+        <v>6773316</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129110861</v>
+        <v>129108956</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455267</v>
+        <v>455473</v>
       </c>
       <c r="R38" t="n">
-        <v>6773233</v>
+        <v>6773221</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129108956</v>
+        <v>129110861</v>
       </c>
       <c r="B39" t="n">
         <v>79044</v>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455473</v>
+        <v>455267</v>
       </c>
       <c r="R39" t="n">
-        <v>6773221</v>
+        <v>6773233</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129107679</v>
+        <v>129114507</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455353</v>
+        <v>455391</v>
       </c>
       <c r="R42" t="n">
-        <v>6773191</v>
+        <v>6773367</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129110029</v>
+        <v>129107679</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455333</v>
+        <v>455353</v>
       </c>
       <c r="R43" t="n">
-        <v>6773241</v>
+        <v>6773191</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,7 +5194,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129114507</v>
+        <v>129110029</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455391</v>
+        <v>455333</v>
       </c>
       <c r="R44" t="n">
-        <v>6773367</v>
+        <v>6773241</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129112093</v>
+        <v>129107474</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,34 +7150,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455241</v>
+        <v>455385</v>
       </c>
       <c r="R62" t="n">
-        <v>6773279</v>
+        <v>6773193</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7246,7 +7251,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129110960</v>
+        <v>129112093</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7281,10 +7286,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455260</v>
+        <v>455241</v>
       </c>
       <c r="R63" t="n">
-        <v>6773245</v>
+        <v>6773279</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7353,10 +7358,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129107474</v>
+        <v>129110960</v>
       </c>
       <c r="B64" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7364,39 +7369,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455385</v>
+        <v>455260</v>
       </c>
       <c r="R64" t="n">
-        <v>6773193</v>
+        <v>6773245</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7684,7 +7684,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129112114</v>
+        <v>129110941</v>
       </c>
       <c r="B67" t="n">
         <v>79044</v>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455233</v>
+        <v>455281</v>
       </c>
       <c r="R67" t="n">
-        <v>6773294</v>
+        <v>6773251</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129110941</v>
+        <v>129112114</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7826,10 +7826,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455281</v>
+        <v>455233</v>
       </c>
       <c r="R68" t="n">
-        <v>6773251</v>
+        <v>6773294</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7898,50 +7898,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129113193</v>
+        <v>129110844</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455283</v>
+        <v>455259</v>
       </c>
       <c r="R69" t="n">
-        <v>6773359</v>
+        <v>6773246</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8010,45 +8005,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129110844</v>
+        <v>129113193</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455259</v>
+        <v>455283</v>
       </c>
       <c r="R70" t="n">
-        <v>6773246</v>
+        <v>6773359</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8117,10 +8117,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129124330</v>
+        <v>129113854</v>
       </c>
       <c r="B71" t="n">
-        <v>92873</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8128,41 +8128,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455412</v>
+        <v>455337</v>
       </c>
       <c r="R71" t="n">
-        <v>6773178</v>
+        <v>6773325</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8192,18 +8185,27 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8222,10 +8224,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129113854</v>
+        <v>129124330</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>92873</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8233,34 +8235,41 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455337</v>
+        <v>455412</v>
       </c>
       <c r="R72" t="n">
-        <v>6773325</v>
+        <v>6773178</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8290,27 +8299,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8543,53 +8543,51 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129110810</v>
+        <v>129114483</v>
       </c>
       <c r="B75" t="n">
-        <v>57724</v>
+        <v>90935</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455237</v>
+        <v>455394</v>
       </c>
       <c r="R75" t="n">
-        <v>6773232</v>
+        <v>6773349</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8631,12 +8629,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8655,51 +8659,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129114483</v>
+        <v>129110810</v>
       </c>
       <c r="B76" t="n">
-        <v>90935</v>
+        <v>57724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455394</v>
+        <v>455237</v>
       </c>
       <c r="R76" t="n">
-        <v>6773349</v>
+        <v>6773232</v>
       </c>
       <c r="S76" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8741,18 +8747,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129113900</v>
+        <v>129112739</v>
       </c>
       <c r="B88" t="n">
         <v>79044</v>
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>455329</v>
+        <v>455290</v>
       </c>
       <c r="R88" t="n">
-        <v>6773342</v>
+        <v>6773279</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129114734</v>
+        <v>129113900</v>
       </c>
       <c r="B89" t="n">
         <v>79044</v>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>455438</v>
+        <v>455329</v>
       </c>
       <c r="R89" t="n">
-        <v>6773400</v>
+        <v>6773342</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10182,7 +10182,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129112739</v>
+        <v>129114734</v>
       </c>
       <c r="B90" t="n">
         <v>79044</v>
@@ -10217,10 +10217,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>455290</v>
+        <v>455438</v>
       </c>
       <c r="R90" t="n">
-        <v>6773279</v>
+        <v>6773400</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10517,35 +10517,44 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129516232</v>
+        <v>129516242</v>
       </c>
       <c r="B93" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
@@ -10555,7 +10564,7 @@
         <v>455380</v>
       </c>
       <c r="R93" t="n">
-        <v>6773633</v>
+        <v>6773669</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10596,6 +10605,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10614,41 +10624,40 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129516242</v>
+        <v>129516224</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>57887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -10658,10 +10667,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>455380</v>
+        <v>455383</v>
       </c>
       <c r="R94" t="n">
-        <v>6773669</v>
+        <v>6773634</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10702,7 +10711,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10721,40 +10729,41 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129516224</v>
+        <v>129516251</v>
       </c>
       <c r="B95" t="n">
-        <v>57887</v>
+        <v>8450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10764,10 +10773,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>455383</v>
+        <v>455481</v>
       </c>
       <c r="R95" t="n">
-        <v>6773634</v>
+        <v>6773645</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10808,6 +10817,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10826,7 +10836,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129516251</v>
+        <v>129516243</v>
       </c>
       <c r="B96" t="n">
         <v>8450</v>
@@ -10870,10 +10880,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>455481</v>
+        <v>455377</v>
       </c>
       <c r="R96" t="n">
-        <v>6773645</v>
+        <v>6773671</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10933,7 +10943,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129516243</v>
+        <v>129516248</v>
       </c>
       <c r="B97" t="n">
         <v>8450</v>
@@ -10977,10 +10987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>455377</v>
+        <v>455414</v>
       </c>
       <c r="R97" t="n">
-        <v>6773671</v>
+        <v>6773624</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11040,7 +11050,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129516248</v>
+        <v>129516249</v>
       </c>
       <c r="B98" t="n">
         <v>8450</v>
@@ -11084,10 +11094,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>455414</v>
+        <v>455432</v>
       </c>
       <c r="R98" t="n">
-        <v>6773624</v>
+        <v>6773615</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11147,7 +11157,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129516249</v>
+        <v>129516237</v>
       </c>
       <c r="B99" t="n">
         <v>8450</v>
@@ -11191,10 +11201,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>455432</v>
+        <v>455395</v>
       </c>
       <c r="R99" t="n">
-        <v>6773615</v>
+        <v>6773693</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11254,7 +11264,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129516237</v>
+        <v>129516236</v>
       </c>
       <c r="B100" t="n">
         <v>8450</v>
@@ -11288,7 +11298,7 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -11298,10 +11308,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>455395</v>
+        <v>455443</v>
       </c>
       <c r="R100" t="n">
-        <v>6773693</v>
+        <v>6773653</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11361,54 +11371,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129516236</v>
+        <v>129516220</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>455443</v>
+        <v>455424</v>
       </c>
       <c r="R101" t="n">
-        <v>6773653</v>
+        <v>6773664</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11449,7 +11450,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11468,45 +11468,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129516220</v>
+        <v>129516245</v>
       </c>
       <c r="B102" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>455424</v>
+        <v>455365</v>
       </c>
       <c r="R102" t="n">
-        <v>6773664</v>
+        <v>6773649</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11547,6 +11556,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11565,10 +11575,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129516245</v>
+        <v>129516229</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>56917</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11576,43 +11586,38 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>455365</v>
+        <v>455351</v>
       </c>
       <c r="R103" t="n">
-        <v>6773649</v>
+        <v>6773588</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11647,13 +11652,17 @@
           <t>2025-11-03</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Död höna nyligen slagen</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11672,10 +11681,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129516229</v>
+        <v>129516253</v>
       </c>
       <c r="B104" t="n">
-        <v>56917</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11683,38 +11692,43 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>455351</v>
+        <v>455476</v>
       </c>
       <c r="R104" t="n">
-        <v>6773588</v>
+        <v>6773655</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11749,17 +11763,13 @@
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Död höna nyligen slagen</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11778,7 +11788,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129516253</v>
+        <v>129516247</v>
       </c>
       <c r="B105" t="n">
         <v>8450</v>
@@ -11822,10 +11832,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>455476</v>
+        <v>455382</v>
       </c>
       <c r="R105" t="n">
-        <v>6773655</v>
+        <v>6773633</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11982,7 +11992,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129516247</v>
+        <v>129516241</v>
       </c>
       <c r="B107" t="n">
         <v>8450</v>
@@ -12026,10 +12036,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>455382</v>
+        <v>455391</v>
       </c>
       <c r="R107" t="n">
-        <v>6773633</v>
+        <v>6773687</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12089,7 +12099,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129516241</v>
+        <v>129516240</v>
       </c>
       <c r="B108" t="n">
         <v>8450</v>
@@ -12133,10 +12143,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>455391</v>
+        <v>455369</v>
       </c>
       <c r="R108" t="n">
-        <v>6773687</v>
+        <v>6773717</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12196,7 +12206,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129516240</v>
+        <v>129516235</v>
       </c>
       <c r="B109" t="n">
         <v>8450</v>
@@ -12240,10 +12250,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>455369</v>
+        <v>455444</v>
       </c>
       <c r="R109" t="n">
-        <v>6773717</v>
+        <v>6773639</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12303,54 +12313,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129516235</v>
+        <v>129516272</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>455444</v>
+        <v>455357</v>
       </c>
       <c r="R110" t="n">
-        <v>6773639</v>
+        <v>6773686</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12391,7 +12392,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12410,10 +12410,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129516272</v>
+        <v>129516226</v>
       </c>
       <c r="B111" t="n">
-        <v>79044</v>
+        <v>91504</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12421,21 +12421,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12445,10 +12445,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>455357</v>
+        <v>455448</v>
       </c>
       <c r="R111" t="n">
-        <v>6773686</v>
+        <v>6773621</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12507,10 +12507,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129516226</v>
+        <v>129516227</v>
       </c>
       <c r="B112" t="n">
-        <v>91504</v>
+        <v>57724</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12518,34 +12518,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>455448</v>
+        <v>455382</v>
       </c>
       <c r="R112" t="n">
-        <v>6773621</v>
+        <v>6773594</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12604,40 +12612,41 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129516227</v>
+        <v>129516252</v>
       </c>
       <c r="B113" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12647,10 +12656,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>455382</v>
+        <v>455472</v>
       </c>
       <c r="R113" t="n">
-        <v>6773594</v>
+        <v>6773649</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12691,6 +12700,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12709,41 +12719,40 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129516252</v>
+        <v>129516228</v>
       </c>
       <c r="B114" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12753,10 +12762,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455472</v>
+        <v>455480</v>
       </c>
       <c r="R114" t="n">
-        <v>6773649</v>
+        <v>6773643</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12797,7 +12806,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12816,10 +12824,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129516275</v>
+        <v>129516231</v>
       </c>
       <c r="B115" t="n">
-        <v>79044</v>
+        <v>92873</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12827,21 +12835,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12851,10 +12859,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>455381</v>
+        <v>455353</v>
       </c>
       <c r="R115" t="n">
-        <v>6773638</v>
+        <v>6773643</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12913,10 +12921,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129516228</v>
+        <v>129516275</v>
       </c>
       <c r="B116" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12924,42 +12932,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>455480</v>
+        <v>455381</v>
       </c>
       <c r="R116" t="n">
-        <v>6773643</v>
+        <v>6773638</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13018,45 +13018,54 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129516231</v>
+        <v>129516238</v>
       </c>
       <c r="B117" t="n">
-        <v>92873</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>455353</v>
+        <v>455392</v>
       </c>
       <c r="R117" t="n">
-        <v>6773643</v>
+        <v>6773703</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13097,6 +13106,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13115,7 +13125,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129516238</v>
+        <v>129516239</v>
       </c>
       <c r="B118" t="n">
         <v>8450</v>
@@ -13159,10 +13169,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>455392</v>
+        <v>455382</v>
       </c>
       <c r="R118" t="n">
-        <v>6773703</v>
+        <v>6773720</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13222,7 +13232,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129516239</v>
+        <v>129516234</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -13256,7 +13266,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -13266,10 +13276,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>455382</v>
+        <v>455459</v>
       </c>
       <c r="R119" t="n">
-        <v>6773720</v>
+        <v>6773658</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13329,54 +13339,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129516234</v>
+        <v>129516270</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>455459</v>
+        <v>455383</v>
       </c>
       <c r="R120" t="n">
-        <v>6773658</v>
+        <v>6773719</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13417,7 +13418,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13436,10 +13436,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129516270</v>
+        <v>129516222</v>
       </c>
       <c r="B121" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13447,21 +13447,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>455383</v>
+        <v>455510</v>
       </c>
       <c r="R121" t="n">
-        <v>6773719</v>
+        <v>6773641</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13533,10 +13533,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129516222</v>
+        <v>129516223</v>
       </c>
       <c r="B122" t="n">
-        <v>79634</v>
+        <v>57887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13544,34 +13544,46 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>455510</v>
+        <v>455394</v>
       </c>
       <c r="R122" t="n">
-        <v>6773641</v>
+        <v>6773684</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13630,10 +13642,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129516223</v>
+        <v>129516277</v>
       </c>
       <c r="B123" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13641,46 +13653,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>455394</v>
+        <v>455410</v>
       </c>
       <c r="R123" t="n">
-        <v>6773684</v>
+        <v>6773604</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13836,45 +13836,49 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129516277</v>
+        <v>129524323</v>
       </c>
       <c r="B125" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Kurutjärnsberget, Dlr</t>
+          <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>455410</v>
+        <v>455677</v>
       </c>
       <c r="R125" t="n">
-        <v>6773604</v>
+        <v>6773324</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13901,12 +13905,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13921,57 +13935,61 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129525056</v>
+        <v>129520976</v>
       </c>
       <c r="B126" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>455743</v>
+        <v>455562</v>
       </c>
       <c r="R126" t="n">
-        <v>6773438</v>
+        <v>6773304</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14003,7 +14021,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14013,7 +14031,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14040,49 +14058,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129524323</v>
+        <v>129525056</v>
       </c>
       <c r="B127" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>455677</v>
+        <v>455743</v>
       </c>
       <c r="R127" t="n">
-        <v>6773324</v>
+        <v>6773438</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14151,49 +14165,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129520976</v>
+        <v>129520384</v>
       </c>
       <c r="B128" t="n">
-        <v>92835</v>
+        <v>79663</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>455562</v>
+        <v>455530</v>
       </c>
       <c r="R128" t="n">
-        <v>6773304</v>
+        <v>6773282</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14262,10 +14272,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129520384</v>
+        <v>129520392</v>
       </c>
       <c r="B129" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14273,21 +14283,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14369,45 +14379,49 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129520392</v>
+        <v>129524264</v>
       </c>
       <c r="B130" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>455530</v>
+        <v>455687</v>
       </c>
       <c r="R130" t="n">
-        <v>6773282</v>
+        <v>6773304</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14439,7 +14453,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14449,7 +14463,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14476,49 +14490,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129524264</v>
+        <v>129520126</v>
       </c>
       <c r="B131" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>455687</v>
+        <v>455494</v>
       </c>
       <c r="R131" t="n">
-        <v>6773304</v>
+        <v>6773317</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14550,7 +14560,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14560,7 +14570,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14587,45 +14597,49 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129520126</v>
+        <v>129522291</v>
       </c>
       <c r="B132" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>455494</v>
+        <v>455660</v>
       </c>
       <c r="R132" t="n">
-        <v>6773317</v>
+        <v>6773320</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14694,49 +14708,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129522291</v>
+        <v>129524757</v>
       </c>
       <c r="B133" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>455660</v>
+        <v>455745</v>
       </c>
       <c r="R133" t="n">
-        <v>6773320</v>
+        <v>6773387</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14768,7 +14778,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14778,7 +14788,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14805,7 +14815,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129524757</v>
+        <v>129521661</v>
       </c>
       <c r="B134" t="n">
         <v>79044</v>
@@ -14840,10 +14850,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>455745</v>
+        <v>455547</v>
       </c>
       <c r="R134" t="n">
-        <v>6773387</v>
+        <v>6773313</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14875,7 +14885,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14885,7 +14895,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i äldre tallar samt gran</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14912,7 +14927,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129521661</v>
+        <v>129524992</v>
       </c>
       <c r="B135" t="n">
         <v>79044</v>
@@ -14947,10 +14962,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>455547</v>
+        <v>455715</v>
       </c>
       <c r="R135" t="n">
-        <v>6773313</v>
+        <v>6773435</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14982,7 +14997,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14992,12 +15007,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i äldre tallar samt gran</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15136,45 +15146,49 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129524992</v>
+        <v>129522884</v>
       </c>
       <c r="B137" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>455715</v>
+        <v>455654</v>
       </c>
       <c r="R137" t="n">
-        <v>6773435</v>
+        <v>6773335</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15206,7 +15220,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15216,7 +15230,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15243,49 +15257,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129522884</v>
+        <v>129524794</v>
       </c>
       <c r="B138" t="n">
-        <v>92835</v>
+        <v>79663</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>455654</v>
+        <v>455725</v>
       </c>
       <c r="R138" t="n">
-        <v>6773335</v>
+        <v>6773375</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15317,7 +15327,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15327,7 +15337,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15354,32 +15364,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129524794</v>
+        <v>129521094</v>
       </c>
       <c r="B139" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15389,10 +15399,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>455725</v>
+        <v>455547</v>
       </c>
       <c r="R139" t="n">
-        <v>6773375</v>
+        <v>6773313</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15424,7 +15434,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15434,7 +15444,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15461,45 +15471,50 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129521094</v>
+        <v>129525475</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>455547</v>
+        <v>455623</v>
       </c>
       <c r="R140" t="n">
-        <v>6773313</v>
+        <v>6773393</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15531,7 +15546,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15541,7 +15556,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15568,10 +15583,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129522761</v>
+        <v>129524463</v>
       </c>
       <c r="B141" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15579,34 +15594,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>455639</v>
+        <v>455664</v>
       </c>
       <c r="R141" t="n">
-        <v>6773364</v>
+        <v>6773257</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15638,7 +15658,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15648,12 +15668,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15680,7 +15695,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129520408</v>
+        <v>129522134</v>
       </c>
       <c r="B142" t="n">
         <v>79044</v>
@@ -15715,10 +15730,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>455524</v>
+        <v>455646</v>
       </c>
       <c r="R142" t="n">
-        <v>6773304</v>
+        <v>6773308</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15787,7 +15802,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129522134</v>
+        <v>129522761</v>
       </c>
       <c r="B143" t="n">
         <v>79044</v>
@@ -15822,10 +15837,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>455646</v>
+        <v>455639</v>
       </c>
       <c r="R143" t="n">
-        <v>6773308</v>
+        <v>6773364</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15868,6 +15883,11 @@
       <c r="AB143" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15894,50 +15914,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129522915</v>
+        <v>129520550</v>
       </c>
       <c r="B144" t="n">
-        <v>56917</v>
+        <v>79044</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>455660</v>
+        <v>455524</v>
       </c>
       <c r="R144" t="n">
-        <v>6773320</v>
+        <v>6773304</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16006,38 +16021,38 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129525475</v>
+        <v>129522915</v>
       </c>
       <c r="B145" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16046,10 +16061,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>455623</v>
+        <v>455660</v>
       </c>
       <c r="R145" t="n">
-        <v>6773393</v>
+        <v>6773320</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16081,7 +16096,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16091,7 +16106,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16118,10 +16133,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129524463</v>
+        <v>129520622</v>
       </c>
       <c r="B146" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16129,39 +16144,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>455664</v>
+        <v>455540</v>
       </c>
       <c r="R146" t="n">
-        <v>6773257</v>
+        <v>6773296</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16193,7 +16203,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16203,7 +16213,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16342,32 +16352,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129520622</v>
+        <v>129525079</v>
       </c>
       <c r="B148" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16377,10 +16387,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>455540</v>
+        <v>455743</v>
       </c>
       <c r="R148" t="n">
-        <v>6773296</v>
+        <v>6773438</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16412,7 +16422,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16422,7 +16432,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16449,45 +16459,49 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129525079</v>
+        <v>129524776</v>
       </c>
       <c r="B149" t="n">
-        <v>98727</v>
+        <v>92835</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>455743</v>
+        <v>455745</v>
       </c>
       <c r="R149" t="n">
-        <v>6773438</v>
+        <v>6773387</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16556,49 +16570,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129524776</v>
+        <v>129524645</v>
       </c>
       <c r="B150" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>455745</v>
+        <v>455677</v>
       </c>
       <c r="R150" t="n">
-        <v>6773387</v>
+        <v>6773324</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16774,45 +16784,49 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129524645</v>
+        <v>129521282</v>
       </c>
       <c r="B152" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>455677</v>
+        <v>455537</v>
       </c>
       <c r="R152" t="n">
-        <v>6773324</v>
+        <v>6773309</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16844,7 +16858,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16854,7 +16868,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16881,7 +16895,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129521282</v>
+        <v>129524704</v>
       </c>
       <c r="B153" t="n">
         <v>92835</v>
@@ -16911,7 +16925,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -16920,10 +16934,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>455537</v>
+        <v>455681</v>
       </c>
       <c r="R153" t="n">
-        <v>6773309</v>
+        <v>6773324</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16955,7 +16969,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16965,7 +16979,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16992,7 +17006,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129524704</v>
+        <v>129522797</v>
       </c>
       <c r="B154" t="n">
         <v>92835</v>
@@ -17022,7 +17036,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -17031,10 +17045,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>455681</v>
+        <v>455650</v>
       </c>
       <c r="R154" t="n">
-        <v>6773324</v>
+        <v>6773365</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17066,7 +17080,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17076,7 +17090,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17103,7 +17117,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129520463</v>
+        <v>129525097</v>
       </c>
       <c r="B155" t="n">
         <v>79044</v>
@@ -17138,10 +17152,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>455514</v>
+        <v>455756</v>
       </c>
       <c r="R155" t="n">
-        <v>6773311</v>
+        <v>6773423</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17173,7 +17187,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17183,7 +17197,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17210,49 +17224,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129522797</v>
+        <v>129520463</v>
       </c>
       <c r="B156" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>455650</v>
+        <v>455514</v>
       </c>
       <c r="R156" t="n">
-        <v>6773365</v>
+        <v>6773311</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17321,7 +17331,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129525097</v>
+        <v>129520135</v>
       </c>
       <c r="B157" t="n">
         <v>79044</v>
@@ -17356,10 +17366,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>455756</v>
+        <v>455497</v>
       </c>
       <c r="R157" t="n">
-        <v>6773423</v>
+        <v>6773300</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17391,7 +17401,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17401,7 +17411,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17428,10 +17438,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129520135</v>
+        <v>129521090</v>
       </c>
       <c r="B158" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17439,34 +17449,39 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>455497</v>
+        <v>455547</v>
       </c>
       <c r="R158" t="n">
-        <v>6773300</v>
+        <v>6773313</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17535,10 +17550,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129521090</v>
+        <v>129522366</v>
       </c>
       <c r="B159" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17546,39 +17561,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>455547</v>
+        <v>455660</v>
       </c>
       <c r="R159" t="n">
-        <v>6773313</v>
+        <v>6773320</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17621,6 +17631,11 @@
       <c r="AB159" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Rikligt i synfältet, radie på ca 50 meter</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17647,7 +17662,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129522366</v>
+        <v>129520605</v>
       </c>
       <c r="B160" t="n">
         <v>79044</v>
@@ -17682,10 +17697,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>455660</v>
+        <v>455537</v>
       </c>
       <c r="R160" t="n">
-        <v>6773320</v>
+        <v>6773309</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17732,7 +17747,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Rikligt i synfältet, radie på ca 50 meter</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17759,10 +17774,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129520605</v>
+        <v>129522130</v>
       </c>
       <c r="B161" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17770,21 +17785,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17794,10 +17809,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>455537</v>
+        <v>455646</v>
       </c>
       <c r="R161" t="n">
-        <v>6773309</v>
+        <v>6773308</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17840,11 +17855,6 @@
       <c r="AB161" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17871,10 +17881,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129522130</v>
+        <v>129520400</v>
       </c>
       <c r="B162" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17882,21 +17892,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17906,10 +17916,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>455646</v>
+        <v>455528</v>
       </c>
       <c r="R162" t="n">
-        <v>6773308</v>
+        <v>6773294</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18090,7 +18100,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129520400</v>
+        <v>129520768</v>
       </c>
       <c r="B164" t="n">
         <v>79044</v>
@@ -18125,10 +18135,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>455528</v>
+        <v>455562</v>
       </c>
       <c r="R164" t="n">
-        <v>6773294</v>
+        <v>6773304</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18309,10 +18319,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129521008</v>
+        <v>129522648</v>
       </c>
       <c r="B166" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18320,34 +18330,39 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>455562</v>
+        <v>455650</v>
       </c>
       <c r="R166" t="n">
-        <v>6773304</v>
+        <v>6773365</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18390,11 +18405,6 @@
       <c r="AB166" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18533,10 +18543,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129522648</v>
+        <v>129525452</v>
       </c>
       <c r="B168" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18544,39 +18554,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>455650</v>
+        <v>455677</v>
       </c>
       <c r="R168" t="n">
-        <v>6773365</v>
+        <v>6773354</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18608,7 +18613,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18618,7 +18623,12 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18752,7 +18762,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129520910</v>
+        <v>129524269</v>
       </c>
       <c r="B170" t="n">
         <v>79044</v>
@@ -18787,10 +18797,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>455570</v>
+        <v>455687</v>
       </c>
       <c r="R170" t="n">
-        <v>6773300</v>
+        <v>6773304</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18822,7 +18832,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18832,7 +18842,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18859,7 +18869,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129524269</v>
+        <v>129520910</v>
       </c>
       <c r="B171" t="n">
         <v>79044</v>
@@ -18894,10 +18904,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>455687</v>
+        <v>455570</v>
       </c>
       <c r="R171" t="n">
-        <v>6773304</v>
+        <v>6773300</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18929,7 +18939,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18939,7 +18949,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18966,7 +18976,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129525452</v>
+        <v>129520755</v>
       </c>
       <c r="B172" t="n">
         <v>79044</v>
@@ -19001,10 +19011,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>455677</v>
+        <v>455550</v>
       </c>
       <c r="R172" t="n">
-        <v>6773354</v>
+        <v>6773288</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19036,7 +19046,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19046,12 +19056,12 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter</t>
+          <t>Vedsvamp på låga bredvid</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19078,10 +19088,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129524033</v>
+        <v>129520115</v>
       </c>
       <c r="B173" t="n">
-        <v>92835</v>
+        <v>56917</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19089,26 +19099,36 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19117,13 +19137,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>455658</v>
+        <v>455499</v>
       </c>
       <c r="R173" t="n">
-        <v>6773278</v>
+        <v>6773331</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19163,6 +19183,11 @@
       <c r="AB173" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19296,10 +19321,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129520755</v>
+        <v>129520654</v>
       </c>
       <c r="B175" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19307,21 +19332,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19331,10 +19356,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>455550</v>
+        <v>455559</v>
       </c>
       <c r="R175" t="n">
-        <v>6773288</v>
+        <v>6773284</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19377,11 +19402,6 @@
       <c r="AB175" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Vedsvamp på låga bredvid</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19408,10 +19428,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129520115</v>
+        <v>129524033</v>
       </c>
       <c r="B176" t="n">
-        <v>56917</v>
+        <v>92835</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19419,36 +19439,26 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -19457,13 +19467,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>455499</v>
+        <v>455658</v>
       </c>
       <c r="R176" t="n">
-        <v>6773331</v>
+        <v>6773278</v>
       </c>
       <c r="S176" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19503,11 +19513,6 @@
       <c r="AB176" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19534,10 +19539,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129520654</v>
+        <v>129561832</v>
       </c>
       <c r="B177" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19545,37 +19550,37 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Skärberget, Dlr</t>
+          <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>455559</v>
+        <v>455852</v>
       </c>
       <c r="R177" t="n">
-        <v>6773284</v>
+        <v>6773480</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19599,22 +19604,22 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19641,10 +19646,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129561832</v>
+        <v>129561893</v>
       </c>
       <c r="B178" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19652,37 +19657,42 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>455852</v>
+        <v>455839</v>
       </c>
       <c r="R178" t="n">
-        <v>6773480</v>
+        <v>6773507</v>
       </c>
       <c r="S178" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19748,7 +19758,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129561893</v>
+        <v>129561829</v>
       </c>
       <c r="B179" t="n">
         <v>57724</v>
@@ -19788,13 +19798,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>455839</v>
+        <v>455852</v>
       </c>
       <c r="R179" t="n">
-        <v>6773507</v>
+        <v>6773480</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19967,38 +19977,38 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129561829</v>
+        <v>129561895</v>
       </c>
       <c r="B181" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20007,13 +20017,13 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>455852</v>
+        <v>455839</v>
       </c>
       <c r="R181" t="n">
-        <v>6773480</v>
+        <v>6773507</v>
       </c>
       <c r="S181" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20195,50 +20205,45 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129561895</v>
+        <v>129555147</v>
       </c>
       <c r="B183" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Kurutjärnen, Dlr</t>
+          <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>455839</v>
+        <v>455622</v>
       </c>
       <c r="R183" t="n">
-        <v>6773507</v>
+        <v>6773376</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20307,7 +20312,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129555147</v>
+        <v>129555566</v>
       </c>
       <c r="B184" t="n">
         <v>79044</v>
@@ -20342,10 +20347,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>455622</v>
+        <v>455671</v>
       </c>
       <c r="R184" t="n">
-        <v>6773376</v>
+        <v>6773369</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20388,6 +20393,11 @@
       <c r="AB184" t="inlineStr">
         <is>
           <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20414,7 +20424,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129555566</v>
+        <v>129555318</v>
       </c>
       <c r="B185" t="n">
         <v>79044</v>
@@ -20449,10 +20459,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>455671</v>
+        <v>455588</v>
       </c>
       <c r="R185" t="n">
-        <v>6773369</v>
+        <v>6773371</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20495,11 +20505,6 @@
       <c r="AB185" t="inlineStr">
         <is>
           <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20526,7 +20531,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129555318</v>
+        <v>129562560</v>
       </c>
       <c r="B186" t="n">
         <v>79044</v>
@@ -20557,14 +20562,14 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Skärberget, Dlr</t>
+          <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>455588</v>
+        <v>455727</v>
       </c>
       <c r="R186" t="n">
-        <v>6773371</v>
+        <v>6773501</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20596,7 +20601,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20606,7 +20611,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20633,7 +20638,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129562560</v>
+        <v>129555967</v>
       </c>
       <c r="B187" t="n">
         <v>79044</v>
@@ -20664,14 +20669,14 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Kurutjärnen, Dlr</t>
+          <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>455727</v>
+        <v>455737</v>
       </c>
       <c r="R187" t="n">
-        <v>6773501</v>
+        <v>6773382</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20703,7 +20708,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20713,7 +20718,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20740,48 +20745,53 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129555967</v>
+        <v>129562306</v>
       </c>
       <c r="B188" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Skärberget, Dlr</t>
+          <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>455737</v>
+        <v>455754</v>
       </c>
       <c r="R188" t="n">
-        <v>6773382</v>
+        <v>6773518</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20810,7 +20820,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20820,7 +20830,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20847,53 +20857,48 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129562306</v>
+        <v>129559838</v>
       </c>
       <c r="B189" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Kurutjärnen, Dlr</t>
+          <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>455754</v>
+        <v>455782</v>
       </c>
       <c r="R189" t="n">
-        <v>6773518</v>
+        <v>6773516</v>
       </c>
       <c r="S189" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20922,7 +20927,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20932,7 +20937,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20959,45 +20964,50 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129559838</v>
+        <v>129560778</v>
       </c>
       <c r="B190" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Skärberget, Dlr</t>
+          <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>455782</v>
+        <v>455843</v>
       </c>
       <c r="R190" t="n">
-        <v>6773516</v>
+        <v>6773492</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21066,50 +21076,45 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129560778</v>
+        <v>129562442</v>
       </c>
       <c r="B191" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>455843</v>
+        <v>455705</v>
       </c>
       <c r="R191" t="n">
-        <v>6773492</v>
+        <v>6773527</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21141,7 +21146,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21151,7 +21156,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21178,7 +21183,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129562442</v>
+        <v>129555275</v>
       </c>
       <c r="B192" t="n">
         <v>79044</v>
@@ -21209,14 +21214,14 @@
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Kurutjärnen, Dlr</t>
+          <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>455705</v>
+        <v>455583</v>
       </c>
       <c r="R192" t="n">
-        <v>6773527</v>
+        <v>6773359</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21248,7 +21253,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21258,7 +21263,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21285,7 +21290,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129555275</v>
+        <v>129559217</v>
       </c>
       <c r="B193" t="n">
         <v>79044</v>
@@ -21320,10 +21325,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>455583</v>
+        <v>455762</v>
       </c>
       <c r="R193" t="n">
-        <v>6773359</v>
+        <v>6773481</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21366,6 +21371,11 @@
       <c r="AB193" t="inlineStr">
         <is>
           <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Garnlav samt miljöbilder för området. Gammal skog, tall och gran</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21392,10 +21402,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129559217</v>
+        <v>129560763</v>
       </c>
       <c r="B194" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21403,34 +21413,39 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Skärberget, Dlr</t>
+          <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>455762</v>
+        <v>455843</v>
       </c>
       <c r="R194" t="n">
-        <v>6773481</v>
+        <v>6773492</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21473,11 +21488,6 @@
       <c r="AB194" t="inlineStr">
         <is>
           <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Garnlav samt miljöbilder för området. Gammal skog, tall och gran</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21504,10 +21514,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129560763</v>
+        <v>129562358</v>
       </c>
       <c r="B195" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21515,42 +21525,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>455843</v>
+        <v>455754</v>
       </c>
       <c r="R195" t="n">
-        <v>6773492</v>
+        <v>6773518</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21579,7 +21584,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21589,7 +21594,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21616,45 +21621,50 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129562358</v>
+        <v>129561831</v>
       </c>
       <c r="B196" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>455754</v>
+        <v>455852</v>
       </c>
       <c r="R196" t="n">
-        <v>6773518</v>
+        <v>6773480</v>
       </c>
       <c r="S196" t="n">
         <v>50</v>
@@ -21686,7 +21696,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21696,7 +21706,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21723,53 +21733,48 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129561831</v>
+        <v>129555030</v>
       </c>
       <c r="B197" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Kurutjärnen, Dlr</t>
+          <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>455852</v>
+        <v>455599</v>
       </c>
       <c r="R197" t="n">
-        <v>6773480</v>
+        <v>6773404</v>
       </c>
       <c r="S197" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21835,7 +21840,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129555030</v>
+        <v>129555824</v>
       </c>
       <c r="B198" t="n">
         <v>79044</v>
@@ -21870,10 +21875,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>455599</v>
+        <v>455731</v>
       </c>
       <c r="R198" t="n">
-        <v>6773404</v>
+        <v>6773361</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21942,10 +21947,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129555824</v>
+        <v>129555631</v>
       </c>
       <c r="B199" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21953,34 +21958,39 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>455731</v>
+        <v>455677</v>
       </c>
       <c r="R199" t="n">
-        <v>6773361</v>
+        <v>6773354</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22049,10 +22059,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129555631</v>
+        <v>129555339</v>
       </c>
       <c r="B200" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22060,42 +22070,37 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>455677</v>
+        <v>455612</v>
       </c>
       <c r="R200" t="n">
-        <v>6773354</v>
+        <v>6773368</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22135,6 +22140,11 @@
       <c r="AB200" t="inlineStr">
         <is>
           <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22161,7 +22171,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129555339</v>
+        <v>129555039</v>
       </c>
       <c r="B201" t="n">
         <v>79044</v>
@@ -22196,13 +22206,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>455612</v>
+        <v>455617</v>
       </c>
       <c r="R201" t="n">
-        <v>6773368</v>
+        <v>6773406</v>
       </c>
       <c r="S201" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22242,11 +22252,6 @@
       <c r="AB201" t="inlineStr">
         <is>
           <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22273,7 +22278,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129555039</v>
+        <v>129559639</v>
       </c>
       <c r="B202" t="n">
         <v>79044</v>
@@ -22308,10 +22313,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>455617</v>
+        <v>455773</v>
       </c>
       <c r="R202" t="n">
-        <v>6773406</v>
+        <v>6773504</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22380,7 +22385,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129559639</v>
+        <v>129555463</v>
       </c>
       <c r="B203" t="n">
         <v>79044</v>
@@ -22415,13 +22420,13 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>455773</v>
+        <v>455663</v>
       </c>
       <c r="R203" t="n">
-        <v>6773504</v>
+        <v>6773398</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22461,6 +22466,11 @@
       <c r="AB203" t="inlineStr">
         <is>
           <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22487,48 +22497,52 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129555463</v>
+        <v>129562904</v>
       </c>
       <c r="B204" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Skärberget, Dlr</t>
+          <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>455663</v>
+        <v>455727</v>
       </c>
       <c r="R204" t="n">
-        <v>6773398</v>
+        <v>6773501</v>
       </c>
       <c r="S204" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -22557,7 +22571,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22567,12 +22581,12 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>Minst hundra!</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22599,7 +22613,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129562904</v>
+        <v>129580035</v>
       </c>
       <c r="B205" t="n">
         <v>98727</v>
@@ -22629,7 +22643,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -22638,10 +22652,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>455727</v>
+        <v>455742</v>
       </c>
       <c r="R205" t="n">
-        <v>6773501</v>
+        <v>6773450</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22668,27 +22682,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>Minst hundra!</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22715,37 +22724,38 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129580035</v>
+        <v>129578682</v>
       </c>
       <c r="B206" t="n">
-        <v>98727</v>
+        <v>56917</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -22754,10 +22764,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>455742</v>
+        <v>455767</v>
       </c>
       <c r="R206" t="n">
-        <v>6773450</v>
+        <v>6773448</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22826,50 +22836,45 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129578682</v>
+        <v>129516232</v>
       </c>
       <c r="B207" t="n">
-        <v>56917</v>
+        <v>92873</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Kurutjärnen, Dlr</t>
+          <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>455767</v>
+        <v>455380</v>
       </c>
       <c r="R207" t="n">
-        <v>6773448</v>
+        <v>6773633</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22896,22 +22901,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22926,12 +22921,12 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112804</v>
+        <v>129112610</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455289</v>
+        <v>455308</v>
       </c>
       <c r="R2" t="n">
-        <v>6773299</v>
+        <v>6773282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129112610</v>
+        <v>129112438</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455308</v>
+        <v>455258</v>
       </c>
       <c r="R3" t="n">
-        <v>6773282</v>
+        <v>6773321</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129112438</v>
+        <v>129108044</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455258</v>
+        <v>455412</v>
       </c>
       <c r="R4" t="n">
-        <v>6773321</v>
+        <v>6773172</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129108044</v>
+        <v>129112804</v>
       </c>
       <c r="B6" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455412</v>
+        <v>455289</v>
       </c>
       <c r="R6" t="n">
-        <v>6773172</v>
+        <v>6773299</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129107453</v>
+        <v>129110825</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455385</v>
+        <v>455259</v>
       </c>
       <c r="R9" t="n">
-        <v>6773193</v>
+        <v>6773246</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129110825</v>
+        <v>129107453</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455259</v>
+        <v>455385</v>
       </c>
       <c r="R10" t="n">
-        <v>6773246</v>
+        <v>6773193</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129110662</v>
+        <v>129107986</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455273</v>
+        <v>455389</v>
       </c>
       <c r="R33" t="n">
-        <v>6773208</v>
+        <v>6773170</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129106783</v>
+        <v>129110662</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455407</v>
+        <v>455273</v>
       </c>
       <c r="R34" t="n">
-        <v>6773196</v>
+        <v>6773208</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129110692</v>
+        <v>129106783</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4256,13 +4256,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455270</v>
+        <v>455407</v>
       </c>
       <c r="R35" t="n">
-        <v>6773216</v>
+        <v>6773196</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129107986</v>
+        <v>129110692</v>
       </c>
       <c r="B36" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4339,21 +4339,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4363,13 +4363,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455389</v>
+        <v>455270</v>
       </c>
       <c r="R36" t="n">
-        <v>6773170</v>
+        <v>6773216</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129108956</v>
+        <v>129110861</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455473</v>
+        <v>455267</v>
       </c>
       <c r="R38" t="n">
-        <v>6773221</v>
+        <v>6773233</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129110861</v>
+        <v>129108956</v>
       </c>
       <c r="B39" t="n">
         <v>79044</v>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455267</v>
+        <v>455473</v>
       </c>
       <c r="R39" t="n">
-        <v>6773233</v>
+        <v>6773221</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129107072</v>
+        <v>129114507</v>
       </c>
       <c r="B41" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455389</v>
+        <v>455391</v>
       </c>
       <c r="R41" t="n">
-        <v>6773203</v>
+        <v>6773367</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129114507</v>
+        <v>129107679</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455391</v>
+        <v>455353</v>
       </c>
       <c r="R42" t="n">
-        <v>6773367</v>
+        <v>6773191</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129107679</v>
+        <v>129110029</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455353</v>
+        <v>455333</v>
       </c>
       <c r="R43" t="n">
-        <v>6773191</v>
+        <v>6773241</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129110029</v>
+        <v>129107072</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455333</v>
+        <v>455389</v>
       </c>
       <c r="R44" t="n">
-        <v>6773241</v>
+        <v>6773203</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5729,45 +5729,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129110148</v>
+        <v>129109267</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455349</v>
+        <v>455477</v>
       </c>
       <c r="R49" t="n">
-        <v>6773250</v>
+        <v>6773206</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,7 +5841,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129114165</v>
+        <v>129110148</v>
       </c>
       <c r="B50" t="n">
         <v>79044</v>
@@ -5871,10 +5876,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455390</v>
+        <v>455349</v>
       </c>
       <c r="R50" t="n">
-        <v>6773344</v>
+        <v>6773250</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5943,7 +5948,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129109151</v>
+        <v>129114165</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5978,10 +5983,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455459</v>
+        <v>455390</v>
       </c>
       <c r="R51" t="n">
-        <v>6773195</v>
+        <v>6773344</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6050,50 +6055,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129109267</v>
+        <v>129109151</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455477</v>
+        <v>455459</v>
       </c>
       <c r="R52" t="n">
-        <v>6773206</v>
+        <v>6773195</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6385,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129114697</v>
+        <v>129113107</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,21 +6396,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>455428</v>
+        <v>455308</v>
       </c>
       <c r="R55" t="n">
-        <v>6773376</v>
+        <v>6773336</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6492,10 +6492,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129110757</v>
+        <v>129114115</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6503,21 +6503,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>455252</v>
+        <v>455394</v>
       </c>
       <c r="R56" t="n">
-        <v>6773222</v>
+        <v>6773349</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6599,10 +6599,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129113107</v>
+        <v>129114697</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6610,21 +6610,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>455308</v>
+        <v>455428</v>
       </c>
       <c r="R57" t="n">
-        <v>6773336</v>
+        <v>6773376</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129114115</v>
+        <v>129110757</v>
       </c>
       <c r="B58" t="n">
-        <v>83012</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6741,13 +6741,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>455394</v>
+        <v>455252</v>
       </c>
       <c r="R58" t="n">
-        <v>6773349</v>
+        <v>6773222</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129107474</v>
+        <v>129112093</v>
       </c>
       <c r="B62" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7150,39 +7150,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>455385</v>
+        <v>455241</v>
       </c>
       <c r="R62" t="n">
-        <v>6773193</v>
+        <v>6773279</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7251,7 +7246,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129112093</v>
+        <v>129110960</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7286,10 +7281,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>455241</v>
+        <v>455260</v>
       </c>
       <c r="R63" t="n">
-        <v>6773279</v>
+        <v>6773245</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7358,10 +7353,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129110960</v>
+        <v>129107474</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7369,34 +7364,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455260</v>
+        <v>455385</v>
       </c>
       <c r="R64" t="n">
-        <v>6773245</v>
+        <v>6773193</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7898,45 +7898,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129110844</v>
+        <v>129113193</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455259</v>
+        <v>455283</v>
       </c>
       <c r="R69" t="n">
-        <v>6773246</v>
+        <v>6773359</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8005,50 +8010,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129113193</v>
+        <v>129110844</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455283</v>
+        <v>455259</v>
       </c>
       <c r="R70" t="n">
-        <v>6773359</v>
+        <v>6773246</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -10836,7 +10836,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129516243</v>
+        <v>129516248</v>
       </c>
       <c r="B96" t="n">
         <v>8450</v>
@@ -10880,10 +10880,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>455377</v>
+        <v>455414</v>
       </c>
       <c r="R96" t="n">
-        <v>6773671</v>
+        <v>6773624</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10943,7 +10943,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129516248</v>
+        <v>129516243</v>
       </c>
       <c r="B97" t="n">
         <v>8450</v>
@@ -10987,10 +10987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>455414</v>
+        <v>455377</v>
       </c>
       <c r="R97" t="n">
-        <v>6773624</v>
+        <v>6773671</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11050,7 +11050,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129516249</v>
+        <v>129516237</v>
       </c>
       <c r="B98" t="n">
         <v>8450</v>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>455432</v>
+        <v>455395</v>
       </c>
       <c r="R98" t="n">
-        <v>6773615</v>
+        <v>6773693</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129516237</v>
+        <v>129516249</v>
       </c>
       <c r="B99" t="n">
         <v>8450</v>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>455395</v>
+        <v>455432</v>
       </c>
       <c r="R99" t="n">
-        <v>6773693</v>
+        <v>6773615</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11788,54 +11788,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129516247</v>
+        <v>129516271</v>
       </c>
       <c r="B105" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>455382</v>
+        <v>455378</v>
       </c>
       <c r="R105" t="n">
-        <v>6773633</v>
+        <v>6773718</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11876,7 +11867,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11895,45 +11885,54 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129516271</v>
+        <v>129516247</v>
       </c>
       <c r="B106" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>455378</v>
+        <v>455382</v>
       </c>
       <c r="R106" t="n">
-        <v>6773718</v>
+        <v>6773633</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11974,6 +11973,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -12719,10 +12719,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129516228</v>
+        <v>129516275</v>
       </c>
       <c r="B114" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12730,42 +12730,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455480</v>
+        <v>455381</v>
       </c>
       <c r="R114" t="n">
-        <v>6773643</v>
+        <v>6773638</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12824,10 +12816,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129516231</v>
+        <v>129516228</v>
       </c>
       <c r="B115" t="n">
-        <v>92873</v>
+        <v>57724</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12835,31 +12827,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>455353</v>
+        <v>455480</v>
       </c>
       <c r="R115" t="n">
         <v>6773643</v>
@@ -12921,10 +12921,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129516275</v>
+        <v>129516231</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>92873</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12932,21 +12932,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12956,10 +12956,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>455381</v>
+        <v>455353</v>
       </c>
       <c r="R116" t="n">
-        <v>6773638</v>
+        <v>6773643</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14165,10 +14165,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129520384</v>
+        <v>129520392</v>
       </c>
       <c r="B128" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14176,21 +14176,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14272,10 +14272,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129520392</v>
+        <v>129520384</v>
       </c>
       <c r="B129" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14283,21 +14283,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15471,10 +15471,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129525475</v>
+        <v>129522761</v>
       </c>
       <c r="B140" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15482,39 +15482,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>455623</v>
+        <v>455639</v>
       </c>
       <c r="R140" t="n">
-        <v>6773393</v>
+        <v>6773364</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15546,7 +15541,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15556,7 +15551,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15583,7 +15583,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129524463</v>
+        <v>129525475</v>
       </c>
       <c r="B141" t="n">
         <v>57724</v>
@@ -15614,7 +15614,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15623,10 +15623,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>455664</v>
+        <v>455623</v>
       </c>
       <c r="R141" t="n">
-        <v>6773257</v>
+        <v>6773393</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15695,10 +15695,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129522134</v>
+        <v>129524463</v>
       </c>
       <c r="B142" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15706,34 +15706,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>455646</v>
+        <v>455664</v>
       </c>
       <c r="R142" t="n">
-        <v>6773308</v>
+        <v>6773257</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15765,7 +15770,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15775,7 +15780,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15802,7 +15807,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129522761</v>
+        <v>129520408</v>
       </c>
       <c r="B143" t="n">
         <v>79044</v>
@@ -15837,10 +15842,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>455639</v>
+        <v>455524</v>
       </c>
       <c r="R143" t="n">
-        <v>6773364</v>
+        <v>6773304</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15883,11 +15888,6 @@
       <c r="AB143" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15914,7 +15914,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129520550</v>
+        <v>129522134</v>
       </c>
       <c r="B144" t="n">
         <v>79044</v>
@@ -15949,10 +15949,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>455524</v>
+        <v>455646</v>
       </c>
       <c r="R144" t="n">
-        <v>6773304</v>
+        <v>6773308</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17117,7 +17117,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129525097</v>
+        <v>129520463</v>
       </c>
       <c r="B155" t="n">
         <v>79044</v>
@@ -17152,10 +17152,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>455756</v>
+        <v>455514</v>
       </c>
       <c r="R155" t="n">
-        <v>6773423</v>
+        <v>6773311</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17224,7 +17224,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129520463</v>
+        <v>129525097</v>
       </c>
       <c r="B156" t="n">
         <v>79044</v>
@@ -17259,10 +17259,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>455514</v>
+        <v>455756</v>
       </c>
       <c r="R156" t="n">
-        <v>6773311</v>
+        <v>6773423</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17881,10 +17881,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129520400</v>
+        <v>129524253</v>
       </c>
       <c r="B162" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17892,34 +17892,39 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>455528</v>
+        <v>455687</v>
       </c>
       <c r="R162" t="n">
-        <v>6773294</v>
+        <v>6773304</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17951,7 +17956,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17961,7 +17966,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17988,10 +17993,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129524253</v>
+        <v>129520400</v>
       </c>
       <c r="B163" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17999,39 +18004,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>455687</v>
+        <v>455528</v>
       </c>
       <c r="R163" t="n">
-        <v>6773304</v>
+        <v>6773294</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18319,10 +18319,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129522648</v>
+        <v>129521993</v>
       </c>
       <c r="B166" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18330,42 +18330,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>455650</v>
+        <v>455615</v>
       </c>
       <c r="R166" t="n">
-        <v>6773365</v>
+        <v>6773317</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18405,6 +18400,11 @@
       <c r="AB166" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18431,10 +18431,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129521993</v>
+        <v>129522648</v>
       </c>
       <c r="B167" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18442,37 +18442,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>455615</v>
+        <v>455650</v>
       </c>
       <c r="R167" t="n">
-        <v>6773317</v>
+        <v>6773365</v>
       </c>
       <c r="S167" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18512,11 +18517,6 @@
       <c r="AB167" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18762,7 +18762,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129524269</v>
+        <v>129520910</v>
       </c>
       <c r="B170" t="n">
         <v>79044</v>
@@ -18797,10 +18797,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>455687</v>
+        <v>455570</v>
       </c>
       <c r="R170" t="n">
-        <v>6773304</v>
+        <v>6773300</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18869,7 +18869,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129520910</v>
+        <v>129524269</v>
       </c>
       <c r="B171" t="n">
         <v>79044</v>
@@ -18904,10 +18904,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>455570</v>
+        <v>455687</v>
       </c>
       <c r="R171" t="n">
-        <v>6773300</v>
+        <v>6773304</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18939,7 +18939,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18976,45 +18976,49 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129520755</v>
+        <v>129524033</v>
       </c>
       <c r="B172" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>455550</v>
+        <v>455658</v>
       </c>
       <c r="R172" t="n">
-        <v>6773288</v>
+        <v>6773278</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19057,11 +19061,6 @@
       <c r="AB172" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>Vedsvamp på låga bredvid</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19088,62 +19087,48 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129520115</v>
+        <v>129524675</v>
       </c>
       <c r="B173" t="n">
-        <v>56917</v>
+        <v>91574</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>455499</v>
+        <v>455677</v>
       </c>
       <c r="R173" t="n">
-        <v>6773331</v>
+        <v>6773324</v>
       </c>
       <c r="S173" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19172,7 +19157,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19182,12 +19167,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19214,10 +19194,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129524675</v>
+        <v>129520654</v>
       </c>
       <c r="B174" t="n">
-        <v>91574</v>
+        <v>79663</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19225,21 +19205,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19249,10 +19229,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>455677</v>
+        <v>455559</v>
       </c>
       <c r="R174" t="n">
-        <v>6773324</v>
+        <v>6773284</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19284,7 +19264,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19294,7 +19274,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19321,48 +19301,62 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129520654</v>
+        <v>129520115</v>
       </c>
       <c r="B175" t="n">
-        <v>79663</v>
+        <v>56917</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>455559</v>
+        <v>455499</v>
       </c>
       <c r="R175" t="n">
-        <v>6773284</v>
+        <v>6773331</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19402,6 +19396,11 @@
       <c r="AB175" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19428,49 +19427,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129524033</v>
+        <v>129520755</v>
       </c>
       <c r="B176" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>455658</v>
+        <v>455550</v>
       </c>
       <c r="R176" t="n">
-        <v>6773278</v>
+        <v>6773288</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19513,6 +19508,11 @@
       <c r="AB176" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Vedsvamp på låga bredvid</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -21183,10 +21183,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129555275</v>
+        <v>129560763</v>
       </c>
       <c r="B192" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21194,34 +21194,39 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Skärberget, Dlr</t>
+          <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>455583</v>
+        <v>455843</v>
       </c>
       <c r="R192" t="n">
-        <v>6773359</v>
+        <v>6773492</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21290,7 +21295,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129559217</v>
+        <v>129555275</v>
       </c>
       <c r="B193" t="n">
         <v>79044</v>
@@ -21325,10 +21330,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>455762</v>
+        <v>455583</v>
       </c>
       <c r="R193" t="n">
-        <v>6773481</v>
+        <v>6773359</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21371,11 +21376,6 @@
       <c r="AB193" t="inlineStr">
         <is>
           <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Garnlav samt miljöbilder för området. Gammal skog, tall och gran</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21402,10 +21402,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129560763</v>
+        <v>129559217</v>
       </c>
       <c r="B194" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21413,39 +21413,34 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Kurutjärnen, Dlr</t>
+          <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>455843</v>
+        <v>455762</v>
       </c>
       <c r="R194" t="n">
-        <v>6773492</v>
+        <v>6773481</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21488,6 +21483,11 @@
       <c r="AB194" t="inlineStr">
         <is>
           <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Garnlav samt miljöbilder för området. Gammal skog, tall och gran</t>
         </is>
       </c>
       <c r="AD194" t="b">

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129112610</v>
+        <v>129112438</v>
       </c>
       <c r="B2" t="n">
         <v>79044</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455308</v>
+        <v>455258</v>
       </c>
       <c r="R2" t="n">
-        <v>6773282</v>
+        <v>6773321</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129112438</v>
+        <v>129108044</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455258</v>
+        <v>455412</v>
       </c>
       <c r="R3" t="n">
-        <v>6773321</v>
+        <v>6773172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129108044</v>
+        <v>129108187</v>
       </c>
       <c r="B4" t="n">
-        <v>79663</v>
+        <v>79634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129112479</v>
+        <v>129112610</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455272</v>
+        <v>455308</v>
       </c>
       <c r="R5" t="n">
-        <v>6773302</v>
+        <v>6773282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129112804</v>
+        <v>129112479</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455289</v>
+        <v>455272</v>
       </c>
       <c r="R6" t="n">
-        <v>6773299</v>
+        <v>6773302</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129108187</v>
+        <v>129112804</v>
       </c>
       <c r="B7" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455412</v>
+        <v>455289</v>
       </c>
       <c r="R7" t="n">
-        <v>6773172</v>
+        <v>6773299</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129110737</v>
+        <v>129110825</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
         <v>455259</v>
       </c>
       <c r="R8" t="n">
-        <v>6773216</v>
+        <v>6773246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129110825</v>
+        <v>129109404</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455259</v>
+        <v>455484</v>
       </c>
       <c r="R9" t="n">
-        <v>6773246</v>
+        <v>6773211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129107453</v>
+        <v>129113163</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455385</v>
+        <v>455283</v>
       </c>
       <c r="R10" t="n">
-        <v>6773193</v>
+        <v>6773359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129109404</v>
+        <v>129107453</v>
       </c>
       <c r="B11" t="n">
         <v>79044</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455484</v>
+        <v>455385</v>
       </c>
       <c r="R11" t="n">
-        <v>6773211</v>
+        <v>6773193</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129113163</v>
+        <v>129113882</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455283</v>
+        <v>455329</v>
       </c>
       <c r="R12" t="n">
-        <v>6773359</v>
+        <v>6773342</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129113882</v>
+        <v>129110737</v>
       </c>
       <c r="B13" t="n">
-        <v>97598</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455329</v>
+        <v>455259</v>
       </c>
       <c r="R13" t="n">
-        <v>6773342</v>
+        <v>6773216</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129107736</v>
+        <v>129114098</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455372</v>
+        <v>455394</v>
       </c>
       <c r="R24" t="n">
-        <v>6773181</v>
+        <v>6773349</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129114098</v>
+        <v>129113094</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455394</v>
+        <v>455301</v>
       </c>
       <c r="R27" t="n">
-        <v>6773349</v>
+        <v>6773331</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129113094</v>
+        <v>129107736</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3502,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455301</v>
+        <v>455372</v>
       </c>
       <c r="R28" t="n">
-        <v>6773331</v>
+        <v>6773181</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129112885</v>
+        <v>129113791</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,37 +3585,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455288</v>
+        <v>455304</v>
       </c>
       <c r="R29" t="n">
-        <v>6773318</v>
+        <v>6773316</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3681,7 +3686,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129110462</v>
+        <v>129112885</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3716,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455333</v>
+        <v>455288</v>
       </c>
       <c r="R30" t="n">
-        <v>6773289</v>
+        <v>6773318</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3788,10 +3793,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129113791</v>
+        <v>129110462</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3799,42 +3804,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455304</v>
+        <v>455333</v>
       </c>
       <c r="R31" t="n">
-        <v>6773316</v>
+        <v>6773289</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129114507</v>
+        <v>129107072</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4884,21 +4884,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455391</v>
+        <v>455389</v>
       </c>
       <c r="R41" t="n">
-        <v>6773367</v>
+        <v>6773203</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129107679</v>
+        <v>129114507</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455353</v>
+        <v>455391</v>
       </c>
       <c r="R42" t="n">
-        <v>6773191</v>
+        <v>6773367</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129110029</v>
+        <v>129107679</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455333</v>
+        <v>455353</v>
       </c>
       <c r="R43" t="n">
-        <v>6773241</v>
+        <v>6773191</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129107072</v>
+        <v>129110029</v>
       </c>
       <c r="B44" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5205,21 +5205,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455389</v>
+        <v>455333</v>
       </c>
       <c r="R44" t="n">
-        <v>6773203</v>
+        <v>6773241</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129109369</v>
+        <v>129112595</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455473</v>
+        <v>455279</v>
       </c>
       <c r="R46" t="n">
-        <v>6773219</v>
+        <v>6773275</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129112595</v>
+        <v>129109369</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455279</v>
+        <v>455473</v>
       </c>
       <c r="R47" t="n">
-        <v>6773275</v>
+        <v>6773219</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129114165</v>
+        <v>129109151</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455390</v>
+        <v>455459</v>
       </c>
       <c r="R51" t="n">
-        <v>6773344</v>
+        <v>6773195</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129109151</v>
+        <v>129114165</v>
       </c>
       <c r="B52" t="n">
         <v>79044</v>
@@ -6090,10 +6090,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455459</v>
+        <v>455390</v>
       </c>
       <c r="R52" t="n">
-        <v>6773195</v>
+        <v>6773344</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7353,38 +7353,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129107474</v>
+        <v>129110475</v>
       </c>
       <c r="B64" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>455385</v>
+        <v>455333</v>
       </c>
       <c r="R64" t="n">
-        <v>6773193</v>
+        <v>6773289</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7465,7 +7465,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129110475</v>
+        <v>129114704</v>
       </c>
       <c r="B65" t="n">
         <v>8450</v>
@@ -7494,21 +7494,16 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>455333</v>
+        <v>455438</v>
       </c>
       <c r="R65" t="n">
-        <v>6773289</v>
+        <v>6773400</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7577,45 +7572,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129114704</v>
+        <v>129107474</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>455438</v>
+        <v>455385</v>
       </c>
       <c r="R66" t="n">
-        <v>6773400</v>
+        <v>6773193</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7684,32 +7684,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129110941</v>
+        <v>129110844</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>455281</v>
+        <v>455259</v>
       </c>
       <c r="R67" t="n">
-        <v>6773251</v>
+        <v>6773246</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129112114</v>
+        <v>129110941</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7826,10 +7826,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>455233</v>
+        <v>455281</v>
       </c>
       <c r="R68" t="n">
-        <v>6773294</v>
+        <v>6773251</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7898,10 +7898,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129113193</v>
+        <v>129112114</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7909,39 +7909,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>455283</v>
+        <v>455233</v>
       </c>
       <c r="R69" t="n">
-        <v>6773359</v>
+        <v>6773294</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8010,45 +8005,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129110844</v>
+        <v>129113193</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>455259</v>
+        <v>455283</v>
       </c>
       <c r="R70" t="n">
-        <v>6773246</v>
+        <v>6773359</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8436,48 +8436,51 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129112107</v>
+        <v>129114483</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>90935</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455235</v>
+        <v>455394</v>
       </c>
       <c r="R74" t="n">
-        <v>6773290</v>
+        <v>6773349</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8519,12 +8522,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8543,51 +8552,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129114483</v>
+        <v>129112107</v>
       </c>
       <c r="B75" t="n">
-        <v>90935</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455394</v>
+        <v>455235</v>
       </c>
       <c r="R75" t="n">
-        <v>6773349</v>
+        <v>6773290</v>
       </c>
       <c r="S75" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8629,18 +8635,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,34 +9108,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R80" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9204,10 +9209,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9215,39 +9220,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R81" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129112739</v>
+        <v>129114734</v>
       </c>
       <c r="B88" t="n">
         <v>79044</v>
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>455290</v>
+        <v>455438</v>
       </c>
       <c r="R88" t="n">
-        <v>6773279</v>
+        <v>6773400</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10182,7 +10182,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129114734</v>
+        <v>129112739</v>
       </c>
       <c r="B90" t="n">
         <v>79044</v>
@@ -10217,10 +10217,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>455438</v>
+        <v>455290</v>
       </c>
       <c r="R90" t="n">
-        <v>6773400</v>
+        <v>6773279</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10836,7 +10836,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129516248</v>
+        <v>129516243</v>
       </c>
       <c r="B96" t="n">
         <v>8450</v>
@@ -10880,10 +10880,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>455414</v>
+        <v>455377</v>
       </c>
       <c r="R96" t="n">
-        <v>6773624</v>
+        <v>6773671</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10943,7 +10943,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129516243</v>
+        <v>129516248</v>
       </c>
       <c r="B97" t="n">
         <v>8450</v>
@@ -10987,10 +10987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>455377</v>
+        <v>455414</v>
       </c>
       <c r="R97" t="n">
-        <v>6773671</v>
+        <v>6773624</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11050,7 +11050,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129516237</v>
+        <v>129516249</v>
       </c>
       <c r="B98" t="n">
         <v>8450</v>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>455395</v>
+        <v>455432</v>
       </c>
       <c r="R98" t="n">
-        <v>6773693</v>
+        <v>6773615</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11157,7 +11157,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129516249</v>
+        <v>129516237</v>
       </c>
       <c r="B99" t="n">
         <v>8450</v>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>455432</v>
+        <v>455395</v>
       </c>
       <c r="R99" t="n">
-        <v>6773615</v>
+        <v>6773693</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11371,45 +11371,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129516220</v>
+        <v>129516245</v>
       </c>
       <c r="B101" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>455424</v>
+        <v>455365</v>
       </c>
       <c r="R101" t="n">
-        <v>6773664</v>
+        <v>6773649</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11450,6 +11459,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11468,54 +11478,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129516245</v>
+        <v>129516220</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>455365</v>
+        <v>455424</v>
       </c>
       <c r="R102" t="n">
-        <v>6773649</v>
+        <v>6773664</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11556,7 +11557,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11788,45 +11788,54 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129516271</v>
+        <v>129516247</v>
       </c>
       <c r="B105" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>455378</v>
+        <v>455382</v>
       </c>
       <c r="R105" t="n">
-        <v>6773718</v>
+        <v>6773633</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11867,6 +11876,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11885,54 +11895,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129516247</v>
+        <v>129516271</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>455382</v>
+        <v>455378</v>
       </c>
       <c r="R106" t="n">
-        <v>6773633</v>
+        <v>6773718</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11973,7 +11974,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -12410,45 +12410,54 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129516226</v>
+        <v>129516252</v>
       </c>
       <c r="B111" t="n">
-        <v>91504</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>112</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>455448</v>
+        <v>455472</v>
       </c>
       <c r="R111" t="n">
-        <v>6773621</v>
+        <v>6773649</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12489,6 +12498,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12507,10 +12517,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129516227</v>
+        <v>129516226</v>
       </c>
       <c r="B112" t="n">
-        <v>57724</v>
+        <v>91504</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12518,42 +12528,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>455382</v>
+        <v>455448</v>
       </c>
       <c r="R112" t="n">
-        <v>6773594</v>
+        <v>6773621</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12612,41 +12614,40 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129516252</v>
+        <v>129516227</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12656,10 +12657,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>455472</v>
+        <v>455382</v>
       </c>
       <c r="R113" t="n">
-        <v>6773649</v>
+        <v>6773594</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12700,7 +12701,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12719,10 +12719,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129516275</v>
+        <v>129516228</v>
       </c>
       <c r="B114" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12730,34 +12730,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455381</v>
+        <v>455480</v>
       </c>
       <c r="R114" t="n">
-        <v>6773638</v>
+        <v>6773643</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12816,10 +12824,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129516228</v>
+        <v>129516231</v>
       </c>
       <c r="B115" t="n">
-        <v>57724</v>
+        <v>92873</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12827,39 +12835,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>455480</v>
+        <v>455353</v>
       </c>
       <c r="R115" t="n">
         <v>6773643</v>
@@ -12921,10 +12921,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129516231</v>
+        <v>129516275</v>
       </c>
       <c r="B116" t="n">
-        <v>92873</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12932,21 +12932,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12956,10 +12956,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>455353</v>
+        <v>455381</v>
       </c>
       <c r="R116" t="n">
-        <v>6773643</v>
+        <v>6773638</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14379,49 +14379,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129524264</v>
+        <v>129520126</v>
       </c>
       <c r="B130" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>455687</v>
+        <v>455494</v>
       </c>
       <c r="R130" t="n">
-        <v>6773304</v>
+        <v>6773317</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14453,7 +14449,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14463,7 +14459,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14490,45 +14486,49 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129520126</v>
+        <v>129524264</v>
       </c>
       <c r="B131" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>455494</v>
+        <v>455687</v>
       </c>
       <c r="R131" t="n">
-        <v>6773317</v>
+        <v>6773304</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14560,7 +14560,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14597,49 +14597,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129522291</v>
+        <v>129524757</v>
       </c>
       <c r="B132" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>455660</v>
+        <v>455745</v>
       </c>
       <c r="R132" t="n">
-        <v>6773320</v>
+        <v>6773387</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14671,7 +14667,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14681,7 +14677,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14708,7 +14704,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129524757</v>
+        <v>129521661</v>
       </c>
       <c r="B133" t="n">
         <v>79044</v>
@@ -14743,10 +14739,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>455745</v>
+        <v>455547</v>
       </c>
       <c r="R133" t="n">
-        <v>6773387</v>
+        <v>6773313</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14778,7 +14774,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14788,7 +14784,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i äldre tallar samt gran</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14815,45 +14816,49 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129521661</v>
+        <v>129522291</v>
       </c>
       <c r="B134" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>455547</v>
+        <v>455660</v>
       </c>
       <c r="R134" t="n">
-        <v>6773313</v>
+        <v>6773320</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14896,11 +14901,6 @@
       <c r="AB134" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i äldre tallar samt gran</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15471,10 +15471,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129522761</v>
+        <v>129525475</v>
       </c>
       <c r="B140" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15482,34 +15482,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>455639</v>
+        <v>455623</v>
       </c>
       <c r="R140" t="n">
-        <v>6773364</v>
+        <v>6773393</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15541,7 +15546,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15551,12 +15556,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15583,7 +15583,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129525475</v>
+        <v>129524463</v>
       </c>
       <c r="B141" t="n">
         <v>57724</v>
@@ -15614,7 +15614,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15623,10 +15623,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>455623</v>
+        <v>455664</v>
       </c>
       <c r="R141" t="n">
-        <v>6773393</v>
+        <v>6773257</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15695,10 +15695,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129524463</v>
+        <v>129520408</v>
       </c>
       <c r="B142" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15706,39 +15706,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>455664</v>
+        <v>455524</v>
       </c>
       <c r="R142" t="n">
-        <v>6773257</v>
+        <v>6773304</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15770,7 +15765,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15780,7 +15775,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15807,7 +15802,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129520408</v>
+        <v>129522134</v>
       </c>
       <c r="B143" t="n">
         <v>79044</v>
@@ -15842,10 +15837,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>455524</v>
+        <v>455646</v>
       </c>
       <c r="R143" t="n">
-        <v>6773304</v>
+        <v>6773308</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15914,7 +15909,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129522134</v>
+        <v>129522761</v>
       </c>
       <c r="B144" t="n">
         <v>79044</v>
@@ -15949,10 +15944,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>455646</v>
+        <v>455639</v>
       </c>
       <c r="R144" t="n">
-        <v>6773308</v>
+        <v>6773364</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15995,6 +15990,11 @@
       <c r="AB144" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17117,7 +17117,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129520463</v>
+        <v>129525097</v>
       </c>
       <c r="B155" t="n">
         <v>79044</v>
@@ -17152,10 +17152,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>455514</v>
+        <v>455756</v>
       </c>
       <c r="R155" t="n">
-        <v>6773311</v>
+        <v>6773423</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17224,7 +17224,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129525097</v>
+        <v>129520463</v>
       </c>
       <c r="B156" t="n">
         <v>79044</v>
@@ -17259,10 +17259,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>455756</v>
+        <v>455514</v>
       </c>
       <c r="R156" t="n">
-        <v>6773423</v>
+        <v>6773311</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17662,10 +17662,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129520605</v>
+        <v>129522130</v>
       </c>
       <c r="B160" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17673,21 +17673,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17697,10 +17697,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>455537</v>
+        <v>455646</v>
       </c>
       <c r="R160" t="n">
-        <v>6773309</v>
+        <v>6773308</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17743,11 +17743,6 @@
       <c r="AB160" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17774,10 +17769,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129522130</v>
+        <v>129520605</v>
       </c>
       <c r="B161" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17785,21 +17780,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17809,10 +17804,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>455646</v>
+        <v>455537</v>
       </c>
       <c r="R161" t="n">
-        <v>6773308</v>
+        <v>6773309</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17855,6 +17850,11 @@
       <c r="AB161" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18762,7 +18762,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129520910</v>
+        <v>129524269</v>
       </c>
       <c r="B170" t="n">
         <v>79044</v>
@@ -18797,10 +18797,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>455570</v>
+        <v>455687</v>
       </c>
       <c r="R170" t="n">
-        <v>6773300</v>
+        <v>6773304</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18869,7 +18869,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129524269</v>
+        <v>129520910</v>
       </c>
       <c r="B171" t="n">
         <v>79044</v>
@@ -18904,10 +18904,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>455687</v>
+        <v>455570</v>
       </c>
       <c r="R171" t="n">
-        <v>6773304</v>
+        <v>6773300</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18939,7 +18939,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19087,10 +19087,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129524675</v>
+        <v>129520755</v>
       </c>
       <c r="B173" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19098,21 +19098,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19122,10 +19122,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>455677</v>
+        <v>455550</v>
       </c>
       <c r="R173" t="n">
-        <v>6773324</v>
+        <v>6773288</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19157,7 +19157,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19167,7 +19167,12 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Vedsvamp på låga bredvid</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19194,48 +19199,62 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129520654</v>
+        <v>129520115</v>
       </c>
       <c r="B174" t="n">
-        <v>79663</v>
+        <v>56917</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>455559</v>
+        <v>455499</v>
       </c>
       <c r="R174" t="n">
-        <v>6773284</v>
+        <v>6773331</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19275,6 +19294,11 @@
       <c r="AB174" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19301,62 +19325,48 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129520115</v>
+        <v>129524675</v>
       </c>
       <c r="B175" t="n">
-        <v>56917</v>
+        <v>91574</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>455499</v>
+        <v>455677</v>
       </c>
       <c r="R175" t="n">
-        <v>6773331</v>
+        <v>6773324</v>
       </c>
       <c r="S175" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19385,7 +19395,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19395,12 +19405,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19427,10 +19432,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129520755</v>
+        <v>129520654</v>
       </c>
       <c r="B176" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19438,21 +19443,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19462,10 +19467,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>455550</v>
+        <v>455559</v>
       </c>
       <c r="R176" t="n">
-        <v>6773288</v>
+        <v>6773284</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19508,11 +19513,6 @@
       <c r="AB176" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Vedsvamp på låga bredvid</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19539,10 +19539,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129561832</v>
+        <v>129561893</v>
       </c>
       <c r="B177" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19550,37 +19550,42 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>455852</v>
+        <v>455839</v>
       </c>
       <c r="R177" t="n">
-        <v>6773480</v>
+        <v>6773507</v>
       </c>
       <c r="S177" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19646,10 +19651,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129561893</v>
+        <v>129561832</v>
       </c>
       <c r="B178" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19657,42 +19662,37 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>455839</v>
+        <v>455852</v>
       </c>
       <c r="R178" t="n">
-        <v>6773507</v>
+        <v>6773480</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19758,10 +19758,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129561829</v>
+        <v>129561879</v>
       </c>
       <c r="B179" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19769,42 +19769,37 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>455852</v>
+        <v>455839</v>
       </c>
       <c r="R179" t="n">
-        <v>6773480</v>
+        <v>6773507</v>
       </c>
       <c r="S179" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19870,10 +19865,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129561879</v>
+        <v>129561829</v>
       </c>
       <c r="B180" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19881,37 +19876,42 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>455839</v>
+        <v>455852</v>
       </c>
       <c r="R180" t="n">
-        <v>6773507</v>
+        <v>6773480</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -21514,45 +21514,50 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129562358</v>
+        <v>129561831</v>
       </c>
       <c r="B195" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>455754</v>
+        <v>455852</v>
       </c>
       <c r="R195" t="n">
-        <v>6773518</v>
+        <v>6773480</v>
       </c>
       <c r="S195" t="n">
         <v>50</v>
@@ -21584,7 +21589,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21594,7 +21599,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21621,50 +21626,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129561831</v>
+        <v>129562358</v>
       </c>
       <c r="B196" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>455852</v>
+        <v>455754</v>
       </c>
       <c r="R196" t="n">
-        <v>6773480</v>
+        <v>6773518</v>
       </c>
       <c r="S196" t="n">
         <v>50</v>
@@ -21696,7 +21696,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21706,7 +21706,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21733,10 +21733,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129555030</v>
+        <v>129555631</v>
       </c>
       <c r="B197" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21744,34 +21744,39 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>455599</v>
+        <v>455677</v>
       </c>
       <c r="R197" t="n">
-        <v>6773404</v>
+        <v>6773354</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21840,7 +21845,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129555824</v>
+        <v>129555030</v>
       </c>
       <c r="B198" t="n">
         <v>79044</v>
@@ -21875,10 +21880,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>455731</v>
+        <v>455599</v>
       </c>
       <c r="R198" t="n">
-        <v>6773361</v>
+        <v>6773404</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21947,10 +21952,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129555631</v>
+        <v>129555824</v>
       </c>
       <c r="B199" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21958,39 +21963,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>455677</v>
+        <v>455731</v>
       </c>
       <c r="R199" t="n">
-        <v>6773354</v>
+        <v>6773361</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -8117,10 +8117,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129113854</v>
+        <v>129124330</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>92901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8128,34 +8128,41 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>455337</v>
+        <v>455412</v>
       </c>
       <c r="R71" t="n">
-        <v>6773325</v>
+        <v>6773178</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8185,27 +8192,18 @@
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8224,10 +8222,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129124330</v>
+        <v>129113854</v>
       </c>
       <c r="B72" t="n">
-        <v>92873</v>
+        <v>79070</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8235,41 +8233,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>455412</v>
+        <v>455337</v>
       </c>
       <c r="R72" t="n">
-        <v>6773178</v>
+        <v>6773325</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8299,18 +8290,27 @@
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8332,7 +8332,7 @@
         <v>129107854</v>
       </c>
       <c r="B73" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8436,51 +8436,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129114483</v>
+        <v>129112107</v>
       </c>
       <c r="B74" t="n">
-        <v>90935</v>
+        <v>79070</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>455394</v>
+        <v>455235</v>
       </c>
       <c r="R74" t="n">
-        <v>6773349</v>
+        <v>6773290</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8522,18 +8519,12 @@
           <t>10:04</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Vedsvamp tallåga</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8552,10 +8543,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129112107</v>
+        <v>129110810</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8563,34 +8554,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>455235</v>
+        <v>455237</v>
       </c>
       <c r="R75" t="n">
-        <v>6773290</v>
+        <v>6773232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8659,53 +8655,51 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129110810</v>
+        <v>129114483</v>
       </c>
       <c r="B76" t="n">
-        <v>57724</v>
+        <v>90963</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>455237</v>
+        <v>455394</v>
       </c>
       <c r="R76" t="n">
-        <v>6773232</v>
+        <v>6773349</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8747,12 +8741,18 @@
           <t>10:04</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Vedsvamp tallåga</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>129109071</v>
       </c>
       <c r="B77" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8883,10 +8883,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129107895</v>
+        <v>129109466</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>455397</v>
+        <v>455479</v>
       </c>
       <c r="R78" t="n">
-        <v>6773180</v>
+        <v>6773185</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8990,10 +8990,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129109466</v>
+        <v>129107895</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>455479</v>
+        <v>455397</v>
       </c>
       <c r="R79" t="n">
-        <v>6773185</v>
+        <v>6773180</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129114154</v>
+        <v>129109225</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9108,39 +9108,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>455390</v>
+        <v>455468</v>
       </c>
       <c r="R80" t="n">
-        <v>6773344</v>
+        <v>6773198</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9209,10 +9204,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129109225</v>
+        <v>129114154</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9220,34 +9215,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>455468</v>
+        <v>455390</v>
       </c>
       <c r="R81" t="n">
-        <v>6773198</v>
+        <v>6773344</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9319,7 +9319,7 @@
         <v>129107617</v>
       </c>
       <c r="B82" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>129113130</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>129111012</v>
       </c>
       <c r="B84" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>129112346</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>129110007</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9968,10 +9968,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129114734</v>
+        <v>129113900</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>455438</v>
+        <v>455329</v>
       </c>
       <c r="R88" t="n">
-        <v>6773400</v>
+        <v>6773342</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10075,10 +10075,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129113900</v>
+        <v>129114734</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>455329</v>
+        <v>455438</v>
       </c>
       <c r="R89" t="n">
-        <v>6773342</v>
+        <v>6773400</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10185,7 +10185,7 @@
         <v>129112739</v>
       </c>
       <c r="B90" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>129114442</v>
       </c>
       <c r="B91" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>129112774</v>
       </c>
       <c r="B92" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10624,40 +10624,41 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129516224</v>
+        <v>129516251</v>
       </c>
       <c r="B94" t="n">
-        <v>57887</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -10667,10 +10668,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>455383</v>
+        <v>455481</v>
       </c>
       <c r="R94" t="n">
-        <v>6773634</v>
+        <v>6773645</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10711,6 +10712,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10729,41 +10731,40 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129516251</v>
+        <v>129516224</v>
       </c>
       <c r="B95" t="n">
-        <v>8450</v>
+        <v>57890</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10773,10 +10774,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>455481</v>
+        <v>455383</v>
       </c>
       <c r="R95" t="n">
-        <v>6773645</v>
+        <v>6773634</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10817,7 +10818,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10836,7 +10836,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129516243</v>
+        <v>129516248</v>
       </c>
       <c r="B96" t="n">
         <v>8450</v>
@@ -10880,10 +10880,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>455377</v>
+        <v>455414</v>
       </c>
       <c r="R96" t="n">
-        <v>6773671</v>
+        <v>6773624</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10943,7 +10943,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129516248</v>
+        <v>129516243</v>
       </c>
       <c r="B97" t="n">
         <v>8450</v>
@@ -10987,10 +10987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>455414</v>
+        <v>455377</v>
       </c>
       <c r="R97" t="n">
-        <v>6773624</v>
+        <v>6773671</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11371,54 +11371,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129516245</v>
+        <v>129516220</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>79689</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>455365</v>
+        <v>455424</v>
       </c>
       <c r="R101" t="n">
-        <v>6773649</v>
+        <v>6773664</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11459,7 +11450,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11478,45 +11468,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129516220</v>
+        <v>129516245</v>
       </c>
       <c r="B102" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>455424</v>
+        <v>455365</v>
       </c>
       <c r="R102" t="n">
-        <v>6773664</v>
+        <v>6773649</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11557,6 +11556,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11578,7 +11578,7 @@
         <v>129516229</v>
       </c>
       <c r="B103" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11788,54 +11788,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129516247</v>
+        <v>129516271</v>
       </c>
       <c r="B105" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>455382</v>
+        <v>455378</v>
       </c>
       <c r="R105" t="n">
-        <v>6773633</v>
+        <v>6773718</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11876,7 +11867,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11895,45 +11885,54 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129516271</v>
+        <v>129516247</v>
       </c>
       <c r="B106" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>455378</v>
+        <v>455382</v>
       </c>
       <c r="R106" t="n">
-        <v>6773718</v>
+        <v>6773633</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11974,6 +11973,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -12316,7 +12316,7 @@
         <v>129516272</v>
       </c>
       <c r="B110" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12410,54 +12410,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129516252</v>
+        <v>129516226</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>91532</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>112</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>455472</v>
+        <v>455448</v>
       </c>
       <c r="R111" t="n">
-        <v>6773649</v>
+        <v>6773621</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12498,7 +12489,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12517,10 +12507,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129516226</v>
+        <v>129516227</v>
       </c>
       <c r="B112" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12528,34 +12518,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>455448</v>
+        <v>455382</v>
       </c>
       <c r="R112" t="n">
-        <v>6773621</v>
+        <v>6773594</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12614,40 +12612,41 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129516227</v>
+        <v>129516252</v>
       </c>
       <c r="B113" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -12657,10 +12656,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>455382</v>
+        <v>455472</v>
       </c>
       <c r="R113" t="n">
-        <v>6773594</v>
+        <v>6773649</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12701,6 +12700,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12719,10 +12719,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129516228</v>
+        <v>129516231</v>
       </c>
       <c r="B114" t="n">
-        <v>57724</v>
+        <v>92901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12730,39 +12730,31 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455480</v>
+        <v>455353</v>
       </c>
       <c r="R114" t="n">
         <v>6773643</v>
@@ -12824,10 +12816,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129516231</v>
+        <v>129516228</v>
       </c>
       <c r="B115" t="n">
-        <v>92873</v>
+        <v>57727</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12835,31 +12827,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>455353</v>
+        <v>455480</v>
       </c>
       <c r="R115" t="n">
         <v>6773643</v>
@@ -12924,7 +12924,7 @@
         <v>129516275</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>129516270</v>
       </c>
       <c r="B120" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>129516222</v>
       </c>
       <c r="B121" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>129516223</v>
       </c>
       <c r="B122" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>129516277</v>
       </c>
       <c r="B123" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>129516274</v>
       </c>
       <c r="B124" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>129524323</v>
       </c>
       <c r="B125" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>129520976</v>
       </c>
       <c r="B126" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>129525056</v>
       </c>
       <c r="B127" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>129520392</v>
       </c>
       <c r="B128" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>129520384</v>
       </c>
       <c r="B129" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14379,45 +14379,49 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129520126</v>
+        <v>129524264</v>
       </c>
       <c r="B130" t="n">
-        <v>79044</v>
+        <v>92863</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>455494</v>
+        <v>455687</v>
       </c>
       <c r="R130" t="n">
-        <v>6773317</v>
+        <v>6773304</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14449,7 +14453,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14459,7 +14463,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14486,49 +14490,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129524264</v>
+        <v>129520126</v>
       </c>
       <c r="B131" t="n">
-        <v>92835</v>
+        <v>79070</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>455687</v>
+        <v>455494</v>
       </c>
       <c r="R131" t="n">
-        <v>6773304</v>
+        <v>6773317</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14560,7 +14560,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14597,45 +14597,49 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129524757</v>
+        <v>129522291</v>
       </c>
       <c r="B132" t="n">
-        <v>79044</v>
+        <v>92863</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>455745</v>
+        <v>455660</v>
       </c>
       <c r="R132" t="n">
-        <v>6773387</v>
+        <v>6773320</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14667,7 +14671,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14677,7 +14681,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14704,10 +14708,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129521661</v>
+        <v>129524757</v>
       </c>
       <c r="B133" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14739,10 +14743,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>455547</v>
+        <v>455745</v>
       </c>
       <c r="R133" t="n">
-        <v>6773313</v>
+        <v>6773387</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14774,7 +14778,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14784,12 +14788,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i äldre tallar samt gran</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14816,49 +14815,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129522291</v>
+        <v>129521661</v>
       </c>
       <c r="B134" t="n">
-        <v>92835</v>
+        <v>79070</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>455660</v>
+        <v>455547</v>
       </c>
       <c r="R134" t="n">
-        <v>6773320</v>
+        <v>6773313</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14901,6 +14896,11 @@
       <c r="AB134" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i äldre tallar samt gran</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14930,7 +14930,7 @@
         <v>129524992</v>
       </c>
       <c r="B135" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>129524157</v>
       </c>
       <c r="B136" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>129522884</v>
       </c>
       <c r="B137" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>129524794</v>
       </c>
       <c r="B138" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15471,38 +15471,38 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129525475</v>
+        <v>129522915</v>
       </c>
       <c r="B140" t="n">
-        <v>57724</v>
+        <v>56920</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -15511,10 +15511,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>455623</v>
+        <v>455660</v>
       </c>
       <c r="R140" t="n">
-        <v>6773393</v>
+        <v>6773320</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15583,10 +15583,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129524463</v>
+        <v>129520408</v>
       </c>
       <c r="B141" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15594,39 +15594,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>455664</v>
+        <v>455524</v>
       </c>
       <c r="R141" t="n">
-        <v>6773257</v>
+        <v>6773304</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15658,7 +15653,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15668,7 +15663,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15695,10 +15690,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129520408</v>
+        <v>129522134</v>
       </c>
       <c r="B142" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15730,10 +15725,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>455524</v>
+        <v>455646</v>
       </c>
       <c r="R142" t="n">
-        <v>6773304</v>
+        <v>6773308</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15802,10 +15797,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129522134</v>
+        <v>129522761</v>
       </c>
       <c r="B143" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15837,10 +15832,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>455646</v>
+        <v>455639</v>
       </c>
       <c r="R143" t="n">
-        <v>6773308</v>
+        <v>6773364</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15883,6 +15878,11 @@
       <c r="AB143" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15909,10 +15909,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129522761</v>
+        <v>129525475</v>
       </c>
       <c r="B144" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15920,34 +15920,39 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>455639</v>
+        <v>455623</v>
       </c>
       <c r="R144" t="n">
-        <v>6773364</v>
+        <v>6773393</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15979,7 +15984,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15989,12 +15994,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16021,38 +16021,38 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129522915</v>
+        <v>129524463</v>
       </c>
       <c r="B145" t="n">
-        <v>56917</v>
+        <v>57727</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16061,10 +16061,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>455660</v>
+        <v>455664</v>
       </c>
       <c r="R145" t="n">
-        <v>6773320</v>
+        <v>6773257</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16133,32 +16133,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129520622</v>
+        <v>129525079</v>
       </c>
       <c r="B146" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16168,10 +16168,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>455540</v>
+        <v>455743</v>
       </c>
       <c r="R146" t="n">
-        <v>6773296</v>
+        <v>6773438</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16243,7 +16243,7 @@
         <v>129520906</v>
       </c>
       <c r="B147" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16352,32 +16352,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129525079</v>
+        <v>129520622</v>
       </c>
       <c r="B148" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16387,10 +16387,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>455743</v>
+        <v>455540</v>
       </c>
       <c r="R148" t="n">
-        <v>6773438</v>
+        <v>6773296</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16422,7 +16422,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16432,7 +16432,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16462,7 +16462,7 @@
         <v>129524776</v>
       </c>
       <c r="B149" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>129524645</v>
       </c>
       <c r="B150" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>129525476</v>
       </c>
       <c r="B151" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>129521282</v>
       </c>
       <c r="B152" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>129524704</v>
       </c>
       <c r="B153" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>129522797</v>
       </c>
       <c r="B154" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>129525097</v>
       </c>
       <c r="B155" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>129520463</v>
       </c>
       <c r="B156" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>129520135</v>
       </c>
       <c r="B157" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>129521090</v>
       </c>
       <c r="B158" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>129522366</v>
       </c>
       <c r="B159" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17662,10 +17662,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129522130</v>
+        <v>129520605</v>
       </c>
       <c r="B160" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17673,21 +17673,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17697,10 +17697,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>455646</v>
+        <v>455537</v>
       </c>
       <c r="R160" t="n">
-        <v>6773308</v>
+        <v>6773309</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17743,6 +17743,11 @@
       <c r="AB160" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17769,10 +17774,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129520605</v>
+        <v>129522130</v>
       </c>
       <c r="B161" t="n">
-        <v>79044</v>
+        <v>79689</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17780,21 +17785,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17804,10 +17809,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>455537</v>
+        <v>455646</v>
       </c>
       <c r="R161" t="n">
-        <v>6773309</v>
+        <v>6773308</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17850,11 +17855,6 @@
       <c r="AB161" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17884,7 +17884,7 @@
         <v>129524253</v>
       </c>
       <c r="B162" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>129520400</v>
       </c>
       <c r="B163" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>129520768</v>
       </c>
       <c r="B164" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>129524860</v>
       </c>
       <c r="B165" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>129521993</v>
       </c>
       <c r="B166" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>129522648</v>
       </c>
       <c r="B167" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>129525452</v>
       </c>
       <c r="B168" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>129524742</v>
       </c>
       <c r="B169" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>129524269</v>
       </c>
       <c r="B170" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>129520910</v>
       </c>
       <c r="B171" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18976,10 +18976,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129524033</v>
+        <v>129520115</v>
       </c>
       <c r="B172" t="n">
-        <v>92835</v>
+        <v>56920</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18987,26 +18987,36 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -19015,13 +19025,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>455658</v>
+        <v>455499</v>
       </c>
       <c r="R172" t="n">
-        <v>6773278</v>
+        <v>6773331</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19061,6 +19071,11 @@
       <c r="AB172" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19087,10 +19102,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129520755</v>
+        <v>129524675</v>
       </c>
       <c r="B173" t="n">
-        <v>79044</v>
+        <v>91602</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19098,21 +19113,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19122,10 +19137,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>455550</v>
+        <v>455677</v>
       </c>
       <c r="R173" t="n">
-        <v>6773288</v>
+        <v>6773324</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19157,7 +19172,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19167,12 +19182,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Vedsvamp på låga bredvid</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19199,10 +19209,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129520115</v>
+        <v>129524033</v>
       </c>
       <c r="B174" t="n">
-        <v>56917</v>
+        <v>92863</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19210,36 +19220,26 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -19248,13 +19248,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>455499</v>
+        <v>455658</v>
       </c>
       <c r="R174" t="n">
-        <v>6773331</v>
+        <v>6773278</v>
       </c>
       <c r="S174" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19294,11 +19294,6 @@
       <c r="AB174" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19325,10 +19320,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129524675</v>
+        <v>129520654</v>
       </c>
       <c r="B175" t="n">
-        <v>91574</v>
+        <v>79689</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19336,21 +19331,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19360,10 +19355,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>455677</v>
+        <v>455559</v>
       </c>
       <c r="R175" t="n">
-        <v>6773324</v>
+        <v>6773284</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19395,7 +19390,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19405,7 +19400,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19432,10 +19427,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129520654</v>
+        <v>129520755</v>
       </c>
       <c r="B176" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19443,21 +19438,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19467,10 +19462,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>455559</v>
+        <v>455550</v>
       </c>
       <c r="R176" t="n">
-        <v>6773284</v>
+        <v>6773288</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19513,6 +19508,11 @@
       <c r="AB176" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Vedsvamp på låga bredvid</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19539,10 +19539,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129561893</v>
+        <v>129561832</v>
       </c>
       <c r="B177" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19550,42 +19550,37 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>455839</v>
+        <v>455852</v>
       </c>
       <c r="R177" t="n">
-        <v>6773507</v>
+        <v>6773480</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19651,10 +19646,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129561832</v>
+        <v>129561893</v>
       </c>
       <c r="B178" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19662,37 +19657,42 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>455852</v>
+        <v>455839</v>
       </c>
       <c r="R178" t="n">
-        <v>6773480</v>
+        <v>6773507</v>
       </c>
       <c r="S178" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>129561879</v>
       </c>
       <c r="B179" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>129561829</v>
       </c>
       <c r="B180" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19977,38 +19977,37 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129561895</v>
+        <v>129563002</v>
       </c>
       <c r="B181" t="n">
-        <v>8450</v>
+        <v>98756</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20017,10 +20016,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>455839</v>
+        <v>455729</v>
       </c>
       <c r="R181" t="n">
-        <v>6773507</v>
+        <v>6773474</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20052,7 +20051,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20062,7 +20061,12 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Massor minst 100 st</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20089,37 +20093,38 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129563002</v>
+        <v>129561895</v>
       </c>
       <c r="B182" t="n">
-        <v>98727</v>
+        <v>8450</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -20128,10 +20133,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>455729</v>
+        <v>455839</v>
       </c>
       <c r="R182" t="n">
-        <v>6773474</v>
+        <v>6773507</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20163,7 +20168,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20173,12 +20178,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Massor minst 100 st</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20208,7 +20208,7 @@
         <v>129555147</v>
       </c>
       <c r="B183" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>129555566</v>
       </c>
       <c r="B184" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>129555318</v>
       </c>
       <c r="B185" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>129562560</v>
       </c>
       <c r="B186" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>129555967</v>
       </c>
       <c r="B187" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>129562306</v>
       </c>
       <c r="B188" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>129559838</v>
       </c>
       <c r="B189" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>129562442</v>
       </c>
       <c r="B191" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>129560763</v>
       </c>
       <c r="B192" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>129555275</v>
       </c>
       <c r="B193" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>129559217</v>
       </c>
       <c r="B194" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21514,50 +21514,45 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129561831</v>
+        <v>129562358</v>
       </c>
       <c r="B195" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>455852</v>
+        <v>455754</v>
       </c>
       <c r="R195" t="n">
-        <v>6773480</v>
+        <v>6773518</v>
       </c>
       <c r="S195" t="n">
         <v>50</v>
@@ -21589,7 +21584,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21599,7 +21594,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21626,45 +21621,50 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129562358</v>
+        <v>129561831</v>
       </c>
       <c r="B196" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>455754</v>
+        <v>455852</v>
       </c>
       <c r="R196" t="n">
-        <v>6773518</v>
+        <v>6773480</v>
       </c>
       <c r="S196" t="n">
         <v>50</v>
@@ -21696,7 +21696,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21706,7 +21706,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21736,7 +21736,7 @@
         <v>129555631</v>
       </c>
       <c r="B197" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>129555030</v>
       </c>
       <c r="B198" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>129555824</v>
       </c>
       <c r="B199" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>129555339</v>
       </c>
       <c r="B200" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>129555039</v>
       </c>
       <c r="B201" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>129559639</v>
       </c>
       <c r="B202" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>129555463</v>
       </c>
       <c r="B203" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>129562904</v>
       </c>
       <c r="B204" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>129580035</v>
       </c>
       <c r="B205" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>129578682</v>
       </c>
       <c r="B206" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>129516232</v>
       </c>
       <c r="B207" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -10836,7 +10836,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129516248</v>
+        <v>129516243</v>
       </c>
       <c r="B96" t="n">
         <v>8450</v>
@@ -10880,10 +10880,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>455414</v>
+        <v>455377</v>
       </c>
       <c r="R96" t="n">
-        <v>6773624</v>
+        <v>6773671</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10943,7 +10943,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129516243</v>
+        <v>129516248</v>
       </c>
       <c r="B97" t="n">
         <v>8450</v>
@@ -10987,10 +10987,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>455377</v>
+        <v>455414</v>
       </c>
       <c r="R97" t="n">
-        <v>6773671</v>
+        <v>6773624</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12410,45 +12410,54 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129516226</v>
+        <v>129516252</v>
       </c>
       <c r="B111" t="n">
-        <v>91532</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>112</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>455448</v>
+        <v>455472</v>
       </c>
       <c r="R111" t="n">
-        <v>6773621</v>
+        <v>6773649</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12489,6 +12498,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12612,54 +12622,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129516252</v>
+        <v>129516226</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>91532</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>112</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>455472</v>
+        <v>455448</v>
       </c>
       <c r="R113" t="n">
-        <v>6773649</v>
+        <v>6773621</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12700,7 +12701,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12719,10 +12719,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129516231</v>
+        <v>129516275</v>
       </c>
       <c r="B114" t="n">
-        <v>92901</v>
+        <v>79070</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12730,21 +12730,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12754,10 +12754,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455353</v>
+        <v>455381</v>
       </c>
       <c r="R114" t="n">
-        <v>6773643</v>
+        <v>6773638</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12816,10 +12816,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129516228</v>
+        <v>129516231</v>
       </c>
       <c r="B115" t="n">
-        <v>57727</v>
+        <v>92901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12827,39 +12827,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>455480</v>
+        <v>455353</v>
       </c>
       <c r="R115" t="n">
         <v>6773643</v>
@@ -12921,10 +12913,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129516275</v>
+        <v>129516228</v>
       </c>
       <c r="B116" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12932,34 +12924,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>455381</v>
+        <v>455480</v>
       </c>
       <c r="R116" t="n">
-        <v>6773638</v>
+        <v>6773643</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15471,50 +15471,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129522915</v>
+        <v>129520408</v>
       </c>
       <c r="B140" t="n">
-        <v>56920</v>
+        <v>79070</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>455660</v>
+        <v>455524</v>
       </c>
       <c r="R140" t="n">
-        <v>6773320</v>
+        <v>6773304</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15583,7 +15578,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129520408</v>
+        <v>129522134</v>
       </c>
       <c r="B141" t="n">
         <v>79070</v>
@@ -15618,10 +15613,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>455524</v>
+        <v>455646</v>
       </c>
       <c r="R141" t="n">
-        <v>6773304</v>
+        <v>6773308</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15690,7 +15685,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129522134</v>
+        <v>129522761</v>
       </c>
       <c r="B142" t="n">
         <v>79070</v>
@@ -15725,10 +15720,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>455646</v>
+        <v>455639</v>
       </c>
       <c r="R142" t="n">
-        <v>6773308</v>
+        <v>6773364</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15771,6 +15766,11 @@
       <c r="AB142" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15797,10 +15797,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129522761</v>
+        <v>129525475</v>
       </c>
       <c r="B143" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15808,34 +15808,39 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>455639</v>
+        <v>455623</v>
       </c>
       <c r="R143" t="n">
-        <v>6773364</v>
+        <v>6773393</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15867,7 +15872,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15877,12 +15882,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15909,7 +15909,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129525475</v>
+        <v>129524463</v>
       </c>
       <c r="B144" t="n">
         <v>57727</v>
@@ -15940,7 +15940,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -15949,10 +15949,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>455623</v>
+        <v>455664</v>
       </c>
       <c r="R144" t="n">
-        <v>6773393</v>
+        <v>6773257</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16021,38 +16021,38 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129524463</v>
+        <v>129522915</v>
       </c>
       <c r="B145" t="n">
-        <v>57727</v>
+        <v>56920</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16061,10 +16061,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>455664</v>
+        <v>455660</v>
       </c>
       <c r="R145" t="n">
-        <v>6773257</v>
+        <v>6773320</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17331,10 +17331,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129520135</v>
+        <v>129521090</v>
       </c>
       <c r="B157" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17342,34 +17342,39 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>455497</v>
+        <v>455547</v>
       </c>
       <c r="R157" t="n">
-        <v>6773300</v>
+        <v>6773313</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17438,10 +17443,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129521090</v>
+        <v>129520135</v>
       </c>
       <c r="B158" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17449,39 +17454,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>455547</v>
+        <v>455497</v>
       </c>
       <c r="R158" t="n">
-        <v>6773313</v>
+        <v>6773300</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -19209,49 +19209,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129524033</v>
+        <v>129520654</v>
       </c>
       <c r="B174" t="n">
-        <v>92863</v>
+        <v>79689</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>455658</v>
+        <v>455559</v>
       </c>
       <c r="R174" t="n">
-        <v>6773278</v>
+        <v>6773284</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19320,10 +19316,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129520654</v>
+        <v>129520755</v>
       </c>
       <c r="B175" t="n">
-        <v>79689</v>
+        <v>79070</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19331,21 +19327,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19355,10 +19351,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>455559</v>
+        <v>455550</v>
       </c>
       <c r="R175" t="n">
-        <v>6773284</v>
+        <v>6773288</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19401,6 +19397,11 @@
       <c r="AB175" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Vedsvamp på låga bredvid</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19427,45 +19428,49 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129520755</v>
+        <v>129524033</v>
       </c>
       <c r="B176" t="n">
-        <v>79070</v>
+        <v>92863</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>455550</v>
+        <v>455658</v>
       </c>
       <c r="R176" t="n">
-        <v>6773288</v>
+        <v>6773278</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19508,11 +19513,6 @@
       <c r="AB176" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Vedsvamp på låga bredvid</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19758,10 +19758,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129561879</v>
+        <v>129561829</v>
       </c>
       <c r="B179" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19769,37 +19769,42 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>455839</v>
+        <v>455852</v>
       </c>
       <c r="R179" t="n">
-        <v>6773507</v>
+        <v>6773480</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19865,10 +19870,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129561829</v>
+        <v>129561879</v>
       </c>
       <c r="B180" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19876,42 +19881,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>455852</v>
+        <v>455839</v>
       </c>
       <c r="R180" t="n">
-        <v>6773480</v>
+        <v>6773507</v>
       </c>
       <c r="S180" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20638,48 +20638,53 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129555967</v>
+        <v>129562306</v>
       </c>
       <c r="B187" t="n">
-        <v>79070</v>
+        <v>58100</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Skärberget, Dlr</t>
+          <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>455737</v>
+        <v>455754</v>
       </c>
       <c r="R187" t="n">
-        <v>6773382</v>
+        <v>6773518</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20708,7 +20713,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20718,7 +20723,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20745,53 +20750,48 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129562306</v>
+        <v>129555967</v>
       </c>
       <c r="B188" t="n">
-        <v>58100</v>
+        <v>79070</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Kurutjärnen, Dlr</t>
+          <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>455754</v>
+        <v>455737</v>
       </c>
       <c r="R188" t="n">
-        <v>6773518</v>
+        <v>6773382</v>
       </c>
       <c r="S188" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20830,7 +20830,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21183,10 +21183,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129560763</v>
+        <v>129555275</v>
       </c>
       <c r="B192" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21194,39 +21194,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Kurutjärnen, Dlr</t>
+          <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>455843</v>
+        <v>455583</v>
       </c>
       <c r="R192" t="n">
-        <v>6773492</v>
+        <v>6773359</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21295,7 +21290,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129555275</v>
+        <v>129559217</v>
       </c>
       <c r="B193" t="n">
         <v>79070</v>
@@ -21330,10 +21325,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>455583</v>
+        <v>455762</v>
       </c>
       <c r="R193" t="n">
-        <v>6773359</v>
+        <v>6773481</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21376,6 +21371,11 @@
       <c r="AB193" t="inlineStr">
         <is>
           <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Garnlav samt miljöbilder för området. Gammal skog, tall och gran</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21402,10 +21402,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129559217</v>
+        <v>129560763</v>
       </c>
       <c r="B194" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21413,34 +21413,39 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Skärberget, Dlr</t>
+          <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>455762</v>
+        <v>455843</v>
       </c>
       <c r="R194" t="n">
-        <v>6773481</v>
+        <v>6773492</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21483,11 +21488,6 @@
       <c r="AB194" t="inlineStr">
         <is>
           <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Garnlav samt miljöbilder för området. Gammal skog, tall och gran</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21733,10 +21733,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129555631</v>
+        <v>129555030</v>
       </c>
       <c r="B197" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21744,39 +21744,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>455677</v>
+        <v>455599</v>
       </c>
       <c r="R197" t="n">
-        <v>6773354</v>
+        <v>6773404</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21845,7 +21840,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129555030</v>
+        <v>129555824</v>
       </c>
       <c r="B198" t="n">
         <v>79070</v>
@@ -21880,10 +21875,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>455599</v>
+        <v>455731</v>
       </c>
       <c r="R198" t="n">
-        <v>6773404</v>
+        <v>6773361</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21952,10 +21947,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129555824</v>
+        <v>129555631</v>
       </c>
       <c r="B199" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21963,34 +21958,39 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>455731</v>
+        <v>455677</v>
       </c>
       <c r="R199" t="n">
-        <v>6773361</v>
+        <v>6773354</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -10734,7 +10734,7 @@
         <v>129516224</v>
       </c>
       <c r="B95" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>129516220</v>
       </c>
       <c r="B101" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>129516229</v>
       </c>
       <c r="B103" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>129516271</v>
       </c>
       <c r="B105" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>129516272</v>
       </c>
       <c r="B110" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12410,54 +12410,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129516252</v>
+        <v>129516226</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>91538</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>112</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>455472</v>
+        <v>455448</v>
       </c>
       <c r="R111" t="n">
-        <v>6773649</v>
+        <v>6773621</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12498,7 +12489,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12520,7 +12510,7 @@
         <v>129516227</v>
       </c>
       <c r="B112" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12622,45 +12612,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129516226</v>
+        <v>129516252</v>
       </c>
       <c r="B113" t="n">
-        <v>91532</v>
+        <v>8450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>112</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>455448</v>
+        <v>455472</v>
       </c>
       <c r="R113" t="n">
-        <v>6773621</v>
+        <v>6773649</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12701,6 +12700,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12719,10 +12719,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129516275</v>
+        <v>129516231</v>
       </c>
       <c r="B114" t="n">
-        <v>79070</v>
+        <v>92907</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12730,21 +12730,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12754,10 +12754,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455381</v>
+        <v>455353</v>
       </c>
       <c r="R114" t="n">
-        <v>6773638</v>
+        <v>6773643</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12816,10 +12816,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129516231</v>
+        <v>129516275</v>
       </c>
       <c r="B115" t="n">
-        <v>92901</v>
+        <v>79075</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12827,21 +12827,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12851,10 +12851,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>455353</v>
+        <v>455381</v>
       </c>
       <c r="R115" t="n">
-        <v>6773643</v>
+        <v>6773638</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12916,7 +12916,7 @@
         <v>129516228</v>
       </c>
       <c r="B116" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13339,10 +13339,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129516270</v>
+        <v>129516222</v>
       </c>
       <c r="B120" t="n">
-        <v>79070</v>
+        <v>79665</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13350,21 +13350,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13374,10 +13374,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>455383</v>
+        <v>455510</v>
       </c>
       <c r="R120" t="n">
-        <v>6773719</v>
+        <v>6773641</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13436,10 +13436,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129516222</v>
+        <v>129516270</v>
       </c>
       <c r="B121" t="n">
-        <v>79660</v>
+        <v>79075</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13447,21 +13447,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>455510</v>
+        <v>455383</v>
       </c>
       <c r="R121" t="n">
-        <v>6773641</v>
+        <v>6773719</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13536,7 +13536,7 @@
         <v>129516223</v>
       </c>
       <c r="B122" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>129516277</v>
       </c>
       <c r="B123" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>129516274</v>
       </c>
       <c r="B124" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>129524323</v>
       </c>
       <c r="B125" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>129520976</v>
       </c>
       <c r="B126" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>129525056</v>
       </c>
       <c r="B127" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>129520392</v>
       </c>
       <c r="B128" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>129520384</v>
       </c>
       <c r="B129" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>129524264</v>
       </c>
       <c r="B130" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>129520126</v>
       </c>
       <c r="B131" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>129522291</v>
       </c>
       <c r="B132" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>129524757</v>
       </c>
       <c r="B133" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>129521661</v>
       </c>
       <c r="B134" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>129524992</v>
       </c>
       <c r="B135" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>129524157</v>
       </c>
       <c r="B136" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>129522884</v>
       </c>
       <c r="B137" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>129524794</v>
       </c>
       <c r="B138" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>129520408</v>
       </c>
       <c r="B140" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>129522134</v>
       </c>
       <c r="B141" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>129522761</v>
       </c>
       <c r="B142" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>129525475</v>
       </c>
       <c r="B143" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>129524463</v>
       </c>
       <c r="B144" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>129522915</v>
       </c>
       <c r="B145" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16133,32 +16133,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129525079</v>
+        <v>129520622</v>
       </c>
       <c r="B146" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16168,10 +16168,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>455743</v>
+        <v>455540</v>
       </c>
       <c r="R146" t="n">
-        <v>6773438</v>
+        <v>6773296</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16243,7 +16243,7 @@
         <v>129520906</v>
       </c>
       <c r="B147" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16352,32 +16352,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129520622</v>
+        <v>129525079</v>
       </c>
       <c r="B148" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16387,10 +16387,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>455540</v>
+        <v>455743</v>
       </c>
       <c r="R148" t="n">
-        <v>6773296</v>
+        <v>6773438</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16422,7 +16422,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16432,7 +16432,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16462,7 +16462,7 @@
         <v>129524776</v>
       </c>
       <c r="B149" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>129524645</v>
       </c>
       <c r="B150" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>129525476</v>
       </c>
       <c r="B151" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>129521282</v>
       </c>
       <c r="B152" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>129524704</v>
       </c>
       <c r="B153" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>129522797</v>
       </c>
       <c r="B154" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>129525097</v>
       </c>
       <c r="B155" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>129520463</v>
       </c>
       <c r="B156" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129521090</v>
+        <v>129520135</v>
       </c>
       <c r="B157" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17342,39 +17342,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>455547</v>
+        <v>455497</v>
       </c>
       <c r="R157" t="n">
-        <v>6773313</v>
+        <v>6773300</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17443,10 +17438,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129520135</v>
+        <v>129521090</v>
       </c>
       <c r="B158" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17454,34 +17449,39 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>455497</v>
+        <v>455547</v>
       </c>
       <c r="R158" t="n">
-        <v>6773300</v>
+        <v>6773313</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17553,7 +17553,7 @@
         <v>129522366</v>
       </c>
       <c r="B159" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>129520605</v>
       </c>
       <c r="B160" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>129522130</v>
       </c>
       <c r="B161" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17881,10 +17881,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129524253</v>
+        <v>129520400</v>
       </c>
       <c r="B162" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17892,39 +17892,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>455687</v>
+        <v>455528</v>
       </c>
       <c r="R162" t="n">
-        <v>6773304</v>
+        <v>6773294</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17956,7 +17951,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17966,7 +17961,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17993,10 +17988,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129520400</v>
+        <v>129524253</v>
       </c>
       <c r="B163" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18004,34 +17999,39 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>455528</v>
+        <v>455687</v>
       </c>
       <c r="R163" t="n">
-        <v>6773294</v>
+        <v>6773304</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18100,10 +18100,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129520768</v>
+        <v>129524860</v>
       </c>
       <c r="B164" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18111,34 +18111,39 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>455562</v>
+        <v>455743</v>
       </c>
       <c r="R164" t="n">
-        <v>6773304</v>
+        <v>6773384</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18170,7 +18175,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18180,7 +18185,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18207,10 +18212,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129524860</v>
+        <v>129520768</v>
       </c>
       <c r="B165" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18218,39 +18223,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>455743</v>
+        <v>455562</v>
       </c>
       <c r="R165" t="n">
-        <v>6773384</v>
+        <v>6773304</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18282,7 +18282,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18292,7 +18292,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18322,7 +18322,7 @@
         <v>129521993</v>
       </c>
       <c r="B166" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>129522648</v>
       </c>
       <c r="B167" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18543,10 +18543,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129525452</v>
+        <v>129524269</v>
       </c>
       <c r="B168" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18578,10 +18578,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>455677</v>
+        <v>455687</v>
       </c>
       <c r="R168" t="n">
-        <v>6773354</v>
+        <v>6773304</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18624,11 +18624,6 @@
       <c r="AB168" t="inlineStr">
         <is>
           <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18655,10 +18650,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129524742</v>
+        <v>129525452</v>
       </c>
       <c r="B169" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18690,10 +18685,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>455747</v>
+        <v>455677</v>
       </c>
       <c r="R169" t="n">
-        <v>6773363</v>
+        <v>6773354</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18736,6 +18731,11 @@
       <c r="AB169" t="inlineStr">
         <is>
           <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18762,10 +18762,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129524269</v>
+        <v>129524742</v>
       </c>
       <c r="B170" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18797,10 +18797,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>455687</v>
+        <v>455747</v>
       </c>
       <c r="R170" t="n">
-        <v>6773304</v>
+        <v>6773363</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18872,7 +18872,7 @@
         <v>129520910</v>
       </c>
       <c r="B171" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18976,10 +18976,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129520115</v>
+        <v>129524033</v>
       </c>
       <c r="B172" t="n">
-        <v>56920</v>
+        <v>92869</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18987,36 +18987,26 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -19025,13 +19015,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>455499</v>
+        <v>455658</v>
       </c>
       <c r="R172" t="n">
-        <v>6773331</v>
+        <v>6773278</v>
       </c>
       <c r="S172" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19071,11 +19061,6 @@
       <c r="AB172" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19105,7 +19090,7 @@
         <v>129524675</v>
       </c>
       <c r="B173" t="n">
-        <v>91602</v>
+        <v>91608</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19209,10 +19194,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129520654</v>
+        <v>129520755</v>
       </c>
       <c r="B174" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19220,21 +19205,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19244,10 +19229,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>455559</v>
+        <v>455550</v>
       </c>
       <c r="R174" t="n">
-        <v>6773284</v>
+        <v>6773288</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19290,6 +19275,11 @@
       <c r="AB174" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Vedsvamp på låga bredvid</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19316,10 +19306,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129520755</v>
+        <v>129520654</v>
       </c>
       <c r="B175" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19327,21 +19317,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19351,10 +19341,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>455550</v>
+        <v>455559</v>
       </c>
       <c r="R175" t="n">
-        <v>6773288</v>
+        <v>6773284</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19397,11 +19387,6 @@
       <c r="AB175" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Vedsvamp på låga bredvid</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19428,10 +19413,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129524033</v>
+        <v>129520115</v>
       </c>
       <c r="B176" t="n">
-        <v>92863</v>
+        <v>56925</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19439,26 +19424,36 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -19467,13 +19462,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>455658</v>
+        <v>455499</v>
       </c>
       <c r="R176" t="n">
-        <v>6773278</v>
+        <v>6773331</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19513,6 +19508,11 @@
       <c r="AB176" t="inlineStr">
         <is>
           <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19542,7 +19542,7 @@
         <v>129561832</v>
       </c>
       <c r="B177" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>129561893</v>
       </c>
       <c r="B178" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19758,38 +19758,38 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129561829</v>
+        <v>129561895</v>
       </c>
       <c r="B179" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -19798,13 +19798,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>455852</v>
+        <v>455839</v>
       </c>
       <c r="R179" t="n">
-        <v>6773480</v>
+        <v>6773507</v>
       </c>
       <c r="S179" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19870,45 +19870,49 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129561879</v>
+        <v>129563002</v>
       </c>
       <c r="B180" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>455839</v>
+        <v>455729</v>
       </c>
       <c r="R180" t="n">
-        <v>6773507</v>
+        <v>6773474</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19940,7 +19944,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19950,7 +19954,12 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Massor minst 100 st</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19977,49 +19986,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129563002</v>
+        <v>129561879</v>
       </c>
       <c r="B181" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>455729</v>
+        <v>455839</v>
       </c>
       <c r="R181" t="n">
-        <v>6773474</v>
+        <v>6773507</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20051,7 +20056,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20061,12 +20066,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Massor minst 100 st</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20093,38 +20093,38 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129561895</v>
+        <v>129561829</v>
       </c>
       <c r="B182" t="n">
-        <v>8450</v>
+        <v>57732</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -20133,13 +20133,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>455839</v>
+        <v>455852</v>
       </c>
       <c r="R182" t="n">
-        <v>6773507</v>
+        <v>6773480</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>129555147</v>
       </c>
       <c r="B183" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>129555566</v>
       </c>
       <c r="B184" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>129555318</v>
       </c>
       <c r="B185" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>129562560</v>
       </c>
       <c r="B186" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>129562306</v>
       </c>
       <c r="B187" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>129555967</v>
       </c>
       <c r="B188" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>129559838</v>
       </c>
       <c r="B189" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>129562442</v>
       </c>
       <c r="B191" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>129555275</v>
       </c>
       <c r="B192" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>129559217</v>
       </c>
       <c r="B193" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>129560763</v>
       </c>
       <c r="B194" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21514,45 +21514,50 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129562358</v>
+        <v>129561831</v>
       </c>
       <c r="B195" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>455754</v>
+        <v>455852</v>
       </c>
       <c r="R195" t="n">
-        <v>6773518</v>
+        <v>6773480</v>
       </c>
       <c r="S195" t="n">
         <v>50</v>
@@ -21584,7 +21589,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21594,7 +21599,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21621,50 +21626,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129561831</v>
+        <v>129562358</v>
       </c>
       <c r="B196" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>455852</v>
+        <v>455754</v>
       </c>
       <c r="R196" t="n">
-        <v>6773480</v>
+        <v>6773518</v>
       </c>
       <c r="S196" t="n">
         <v>50</v>
@@ -21696,7 +21696,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21706,7 +21706,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21736,7 +21736,7 @@
         <v>129555030</v>
       </c>
       <c r="B197" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>129555824</v>
       </c>
       <c r="B198" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>129555631</v>
       </c>
       <c r="B199" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>129555339</v>
       </c>
       <c r="B200" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>129555039</v>
       </c>
       <c r="B201" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22278,45 +22278,49 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129559639</v>
+        <v>129562904</v>
       </c>
       <c r="B202" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Skärberget, Dlr</t>
+          <t>Kurutjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>455773</v>
+        <v>455727</v>
       </c>
       <c r="R202" t="n">
-        <v>6773504</v>
+        <v>6773501</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22348,7 +22352,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22358,7 +22362,12 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Minst hundra!</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22385,10 +22394,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129555463</v>
+        <v>129559639</v>
       </c>
       <c r="B203" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22420,13 +22429,13 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>455663</v>
+        <v>455773</v>
       </c>
       <c r="R203" t="n">
-        <v>6773398</v>
+        <v>6773504</v>
       </c>
       <c r="S203" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22466,11 +22475,6 @@
       <c r="AB203" t="inlineStr">
         <is>
           <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22497,52 +22501,48 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129562904</v>
+        <v>129555463</v>
       </c>
       <c r="B204" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Kurutjärnen, Dlr</t>
+          <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>455727</v>
+        <v>455663</v>
       </c>
       <c r="R204" t="n">
-        <v>6773501</v>
+        <v>6773398</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22581,12 +22581,12 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>Minst hundra!</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22616,7 +22616,7 @@
         <v>129580035</v>
       </c>
       <c r="B205" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>129578682</v>
       </c>
       <c r="B206" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>129516232</v>
       </c>
       <c r="B207" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 47081-2025 artfynd.xlsx
+++ b/artfynd/A 47081-2025 artfynd.xlsx
@@ -10734,7 +10734,7 @@
         <v>129516224</v>
       </c>
       <c r="B95" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11371,45 +11371,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129516220</v>
+        <v>129516245</v>
       </c>
       <c r="B101" t="n">
-        <v>79694</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>455424</v>
+        <v>455365</v>
       </c>
       <c r="R101" t="n">
-        <v>6773664</v>
+        <v>6773649</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11450,6 +11459,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11468,54 +11478,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129516245</v>
+        <v>129516220</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>79695</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>455365</v>
+        <v>455424</v>
       </c>
       <c r="R102" t="n">
-        <v>6773649</v>
+        <v>6773664</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11556,7 +11557,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11578,7 +11578,7 @@
         <v>129516229</v>
       </c>
       <c r="B103" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>129516271</v>
       </c>
       <c r="B105" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>129516272</v>
       </c>
       <c r="B110" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>129516226</v>
       </c>
       <c r="B111" t="n">
-        <v>91538</v>
+        <v>91539</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>129516227</v>
       </c>
       <c r="B112" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12719,10 +12719,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129516231</v>
+        <v>129516228</v>
       </c>
       <c r="B114" t="n">
-        <v>92907</v>
+        <v>57733</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12730,31 +12730,39 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>455353</v>
+        <v>455480</v>
       </c>
       <c r="R114" t="n">
         <v>6773643</v>
@@ -12816,10 +12824,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129516275</v>
+        <v>129516231</v>
       </c>
       <c r="B115" t="n">
-        <v>79075</v>
+        <v>92908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12827,21 +12835,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12851,10 +12859,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>455381</v>
+        <v>455353</v>
       </c>
       <c r="R115" t="n">
-        <v>6773638</v>
+        <v>6773643</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12913,10 +12921,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129516228</v>
+        <v>129516275</v>
       </c>
       <c r="B116" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12924,42 +12932,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kurutjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>455480</v>
+        <v>455381</v>
       </c>
       <c r="R116" t="n">
-        <v>6773643</v>
+        <v>6773638</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13339,10 +13339,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129516222</v>
+        <v>129516270</v>
       </c>
       <c r="B120" t="n">
-        <v>79665</v>
+        <v>79076</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13350,21 +13350,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13374,10 +13374,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>455510</v>
+        <v>455383</v>
       </c>
       <c r="R120" t="n">
-        <v>6773641</v>
+        <v>6773719</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13436,10 +13436,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129516270</v>
+        <v>129516222</v>
       </c>
       <c r="B121" t="n">
-        <v>79075</v>
+        <v>79666</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13447,21 +13447,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>455383</v>
+        <v>455510</v>
       </c>
       <c r="R121" t="n">
-        <v>6773719</v>
+        <v>6773641</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13536,7 +13536,7 @@
         <v>129516223</v>
       </c>
       <c r="B122" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>129516277</v>
       </c>
       <c r="B123" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>129516274</v>
       </c>
       <c r="B124" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13836,10 +13836,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129524323</v>
+        <v>129520976</v>
       </c>
       <c r="B125" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -13875,10 +13875,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>455677</v>
+        <v>455562</v>
       </c>
       <c r="R125" t="n">
-        <v>6773324</v>
+        <v>6773304</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13947,49 +13947,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129520976</v>
+        <v>129525056</v>
       </c>
       <c r="B126" t="n">
-        <v>92869</v>
+        <v>79076</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>455562</v>
+        <v>455743</v>
       </c>
       <c r="R126" t="n">
-        <v>6773304</v>
+        <v>6773438</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14021,7 +14017,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14031,7 +14027,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14058,45 +14054,49 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129525056</v>
+        <v>129524323</v>
       </c>
       <c r="B127" t="n">
-        <v>79075</v>
+        <v>92870</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>455743</v>
+        <v>455677</v>
       </c>
       <c r="R127" t="n">
-        <v>6773438</v>
+        <v>6773324</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14168,7 +14168,7 @@
         <v>129520392</v>
       </c>
       <c r="B128" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>129520384</v>
       </c>
       <c r="B129" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14379,49 +14379,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129524264</v>
+        <v>129520126</v>
       </c>
       <c r="B130" t="n">
-        <v>92869</v>
+        <v>79076</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>455687</v>
+        <v>455494</v>
       </c>
       <c r="R130" t="n">
-        <v>6773304</v>
+        <v>6773317</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14453,7 +14449,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14463,7 +14459,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14490,45 +14486,49 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129520126</v>
+        <v>129524264</v>
       </c>
       <c r="B131" t="n">
-        <v>79075</v>
+        <v>92870</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>455494</v>
+        <v>455687</v>
       </c>
       <c r="R131" t="n">
-        <v>6773317</v>
+        <v>6773304</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14560,7 +14560,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14597,49 +14597,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129522291</v>
+        <v>129524757</v>
       </c>
       <c r="B132" t="n">
-        <v>92869</v>
+        <v>79076</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>455660</v>
+        <v>455745</v>
       </c>
       <c r="R132" t="n">
-        <v>6773320</v>
+        <v>6773387</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14671,7 +14667,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14681,7 +14677,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14708,10 +14704,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129524757</v>
+        <v>129521661</v>
       </c>
       <c r="B133" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14743,10 +14739,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>455745</v>
+        <v>455547</v>
       </c>
       <c r="R133" t="n">
-        <v>6773387</v>
+        <v>6773313</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14778,7 +14774,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14788,7 +14784,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i äldre tallar samt gran</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14815,45 +14816,49 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129521661</v>
+        <v>129522291</v>
       </c>
       <c r="B134" t="n">
-        <v>79075</v>
+        <v>92870</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Skärberget, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>455547</v>
+        <v>455660</v>
       </c>
       <c r="R134" t="n">
-        <v>6773313</v>
+        <v>6773320</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14896,11 +14901,6 @@
       <c r="AB134" t="inlineStr">
         <is>
           <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i äldre tallar samt gran</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14930,7 +14930,7 @@
         <v>129524992</v>
       </c>
       <c r="B135" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>129524157</v>
       </c>
       <c r="B136" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>129522884</v>
       </c>
       <c r="B137" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15257,32 +15257,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129524794</v>
+        <v>129521094</v>
       </c>
       <c r="B138" t="n">
-        <v>79694</v>
+        <v>8450</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15292,10 +15292,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>455725</v>
+        <v>455547</v>
       </c>
       <c r="R138" t="n">
-        <v>6773375</v>
+        <v>6773313</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15364,32 +15364,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129521094</v>
+        <v>129524794</v>
       </c>
       <c r="B139" t="n">
-        <v>8450</v>
+        <v>79695</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+       